--- a/Game Stuff/Spreadsheet.xlsx
+++ b/Game Stuff/Spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Nicos Blueprints_Abyssal chains of shandalar\Game Stuff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Nicos Blueprints_Riveteers District - Final\Game Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF56F2DF-5903-4F0B-A121-7806DE3D8551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2E70E9-A7EE-4AF7-9F91-96A7B04A868D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6280" yWindow="3300" windowWidth="28820" windowHeight="15380" firstSheet="6" activeTab="10" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
+    <workbookView xWindow="45972" yWindow="-4944" windowWidth="17496" windowHeight="30216" firstSheet="11" activeTab="11" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Summary" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Ghirapur Gridworks" sheetId="10" r:id="rId9"/>
     <sheet name="Kaladesh Refinery" sheetId="11" r:id="rId10"/>
     <sheet name="The Abyssal Chains of Shandalar" sheetId="12" r:id="rId11"/>
+    <sheet name="Riveteers District" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="155">
   <si>
     <t>Item</t>
   </si>
@@ -466,6 +467,51 @@
   </si>
   <si>
     <t>63.39 Hours</t>
+  </si>
+  <si>
+    <t>Bottom Right going to Riveteers District has an extra 233.33 Copper Ingots</t>
+  </si>
+  <si>
+    <t>Riverteers District</t>
+  </si>
+  <si>
+    <t>Bottom Right</t>
+  </si>
+  <si>
+    <t>Riveteers District</t>
+  </si>
+  <si>
+    <t>Bauxite</t>
+  </si>
+  <si>
+    <t>Water Exctractors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xantcha's Crucible </t>
+  </si>
+  <si>
+    <t>Alclcad Aluminum Sheet</t>
+  </si>
+  <si>
+    <t>Aluminum Scrap</t>
+  </si>
+  <si>
+    <t>Aluminum Ingots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aluminum Casing </t>
+  </si>
+  <si>
+    <t>1458.4 MW</t>
+  </si>
+  <si>
+    <t>-1458.4 MW</t>
+  </si>
+  <si>
+    <t>7300 Wh</t>
+  </si>
+  <si>
+    <t>4.80 Hours</t>
   </si>
 </sst>
 </file>
@@ -497,7 +543,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -688,17 +734,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -768,6 +803,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -785,7 +855,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -795,22 +864,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -824,7 +884,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -849,6 +909,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -861,15 +930,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1204,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3DEAD1A-BE12-4BD3-A45F-18807DFF108B}">
-  <dimension ref="C3:J38"/>
+  <dimension ref="C3:J59"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
@@ -1217,38 +1285,38 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="40" t="s">
+      <c r="D4" s="40"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="42"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="41"/>
     </row>
     <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="17" t="s">
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="44" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1256,19 +1324,19 @@
       <c r="C6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>10</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="39">
+      <c r="I6" s="35">
         <v>15</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="46" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1276,7 +1344,7 @@
       <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>58.332999999999998</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -1285,7 +1353,7 @@
       <c r="H7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="13">
         <v>5</v>
       </c>
       <c r="J7" s="8" t="s">
@@ -1296,16 +1364,16 @@
       <c r="C8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>1999.848</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>1.4065000000000001</v>
       </c>
       <c r="J8" s="8" t="s">
@@ -1316,16 +1384,16 @@
       <c r="C9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="12">
-        <v>1889.01666</v>
+      <c r="D9" s="11">
+        <v>1655.6866600000001</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="13">
         <v>2.25</v>
       </c>
       <c r="J9" s="8" t="s">
@@ -1336,16 +1404,16 @@
       <c r="C10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>204</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="13">
         <v>2.5</v>
       </c>
       <c r="J10" s="8" t="s">
@@ -1356,16 +1424,16 @@
       <c r="C11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>1140</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="13">
         <v>45</v>
       </c>
       <c r="J11" s="8" t="s">
@@ -1376,16 +1444,16 @@
       <c r="C12" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>669.33299999999997</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="13">
         <v>5</v>
       </c>
       <c r="J12" s="8" t="s">
@@ -1396,16 +1464,16 @@
       <c r="C13" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>635.40554999999995</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="13">
         <v>7.3125</v>
       </c>
       <c r="J13" s="8" t="s">
@@ -1416,16 +1484,16 @@
       <c r="C14" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <v>467.5</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="13">
         <v>3</v>
       </c>
       <c r="J14" s="8" t="s">
@@ -1436,7 +1504,7 @@
       <c r="C15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <v>348</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -1445,7 +1513,7 @@
       <c r="H15" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="13">
         <v>30</v>
       </c>
       <c r="J15" s="8" t="s">
@@ -1453,13 +1521,19 @@
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C16" s="4"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="4"/>
+      <c r="C16" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="13">
+        <v>246.666</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="H16" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="13">
         <v>0.5</v>
       </c>
       <c r="J16" s="8" t="s">
@@ -1468,12 +1542,12 @@
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C17" s="4"/>
-      <c r="D17" s="12"/>
+      <c r="D17" s="11"/>
       <c r="E17" s="4"/>
       <c r="H17" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="13">
         <v>33.125</v>
       </c>
       <c r="J17" s="8" t="s">
@@ -1482,12 +1556,12 @@
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C18" s="2"/>
-      <c r="D18" s="12"/>
+      <c r="D18" s="11"/>
       <c r="E18" s="2"/>
       <c r="H18" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="13">
         <v>61.6875</v>
       </c>
       <c r="J18" s="8" t="s">
@@ -1496,12 +1570,12 @@
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C19" s="2"/>
-      <c r="D19" s="12"/>
+      <c r="D19" s="11"/>
       <c r="E19" s="2"/>
       <c r="H19" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="13">
         <v>7.25</v>
       </c>
       <c r="J19" s="8" t="s">
@@ -1510,12 +1584,12 @@
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C20" s="2"/>
-      <c r="D20" s="12"/>
+      <c r="D20" s="11"/>
       <c r="E20" s="2"/>
       <c r="H20" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="13">
         <v>30</v>
       </c>
       <c r="J20" s="8" t="s">
@@ -1524,12 +1598,12 @@
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C21" s="2"/>
-      <c r="D21" s="12"/>
+      <c r="D21" s="11"/>
       <c r="E21" s="2"/>
       <c r="H21" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="13">
         <v>45</v>
       </c>
       <c r="J21" s="8" t="s">
@@ -1538,12 +1612,12 @@
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C22" s="2"/>
-      <c r="D22" s="12"/>
+      <c r="D22" s="11"/>
       <c r="E22" s="2"/>
       <c r="H22" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="13">
         <v>22.5</v>
       </c>
       <c r="J22" s="8" t="s">
@@ -1552,12 +1626,12 @@
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C23" s="2"/>
-      <c r="D23" s="12"/>
+      <c r="D23" s="11"/>
       <c r="E23" s="2"/>
       <c r="H23" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="13">
         <v>20.5</v>
       </c>
       <c r="J23" s="8" t="s">
@@ -1566,12 +1640,12 @@
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C24" s="2"/>
-      <c r="D24" s="12"/>
+      <c r="D24" s="11"/>
       <c r="E24" s="2"/>
       <c r="H24" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="13">
         <v>15</v>
       </c>
       <c r="J24" s="8" t="s">
@@ -1580,12 +1654,12 @@
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C25" s="2"/>
-      <c r="D25" s="12"/>
+      <c r="D25" s="11"/>
       <c r="E25" s="2"/>
       <c r="H25" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="13">
         <v>25</v>
       </c>
       <c r="J25" s="8" t="s">
@@ -1594,12 +1668,12 @@
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C26" s="2"/>
-      <c r="D26" s="12"/>
+      <c r="D26" s="11"/>
       <c r="E26" s="2"/>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="13">
         <v>23.332999999999998</v>
       </c>
       <c r="J26" s="8" t="s">
@@ -1608,12 +1682,12 @@
     </row>
     <row r="27" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C27" s="2"/>
-      <c r="D27" s="12"/>
+      <c r="D27" s="11"/>
       <c r="E27" s="2"/>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="13">
         <v>19.443999999999999</v>
       </c>
       <c r="J27" s="8" t="s">
@@ -1622,145 +1696,274 @@
     </row>
     <row r="28" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C28" s="2"/>
-      <c r="D28" s="12"/>
+      <c r="D28" s="11"/>
       <c r="E28" s="2"/>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="13">
         <v>1.5</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="8" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C29" s="2"/>
-      <c r="D29" s="12"/>
+      <c r="D29" s="11"/>
       <c r="E29" s="2"/>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="13">
         <v>1.5</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="8" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="30" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C30" s="2"/>
-      <c r="D30" s="12"/>
+      <c r="D30" s="11"/>
       <c r="E30" s="2"/>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="13">
         <v>2.25</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="8" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C31" s="2"/>
-      <c r="D31" s="12"/>
+      <c r="D31" s="11"/>
       <c r="E31" s="2"/>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="13">
         <v>3</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="8" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C32" s="2"/>
-      <c r="D32" s="12"/>
+      <c r="D32" s="11"/>
       <c r="E32" s="2"/>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="13">
         <v>6</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="8" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C33" s="2"/>
-      <c r="D33" s="12"/>
+      <c r="D33" s="11"/>
       <c r="E33" s="2"/>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="13">
         <v>25</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="J33" s="8" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C34" s="2"/>
-      <c r="D34" s="12"/>
+      <c r="D34" s="11"/>
       <c r="E34" s="2"/>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="13">
         <v>20</v>
       </c>
-      <c r="J34" s="4" t="s">
+      <c r="J34" s="8" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C35" s="2"/>
-      <c r="D35" s="12"/>
+      <c r="D35" s="11"/>
       <c r="E35" s="2"/>
       <c r="H35" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="13">
         <v>0.5</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="J35" s="8" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C36" s="2"/>
-      <c r="D36" s="12"/>
+      <c r="D36" s="11"/>
       <c r="E36" s="2"/>
       <c r="H36" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I36" s="13">
         <v>0.5</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="8" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="37" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C37" s="2"/>
-      <c r="D37" s="12"/>
+      <c r="D37" s="11"/>
       <c r="E37" s="2"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="9"/>
+      <c r="H37" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I37" s="13">
+        <v>49.332999999999998</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="38" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3"/>
-      <c r="D38" s="13"/>
+      <c r="D38" s="12"/>
       <c r="E38" s="3"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="10"/>
+      <c r="H38" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I38" s="13">
+        <v>12</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H39" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="I39" s="13">
+        <v>200</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I40" s="13">
+        <v>222</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H41" s="6"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="8"/>
+    </row>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H42" s="6"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="8"/>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H43" s="6"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="8"/>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H44" s="6"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="8"/>
+    </row>
+    <row r="45" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H45" s="6"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="8"/>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H46" s="6"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H47" s="6"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="8"/>
+    </row>
+    <row r="48" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="H48" s="6"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="8"/>
+    </row>
+    <row r="49" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H49" s="6"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="8"/>
+    </row>
+    <row r="50" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H50" s="6"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="8"/>
+    </row>
+    <row r="51" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H51" s="6"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="8"/>
+    </row>
+    <row r="52" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H52" s="6"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H53" s="6"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="8"/>
+    </row>
+    <row r="54" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H54" s="6"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="8"/>
+    </row>
+    <row r="55" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H55" s="6"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="8"/>
+    </row>
+    <row r="56" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H56" s="6"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="8"/>
+    </row>
+    <row r="57" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H57" s="6"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="8"/>
+    </row>
+    <row r="58" spans="8:10" x14ac:dyDescent="0.35">
+      <c r="H58" s="6"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" spans="8:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H59" s="7"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1789,113 +1992,113 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="27" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="31" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="30"/>
-      <c r="E10" s="40" t="s">
+      <c r="C10" s="26"/>
+      <c r="E10" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="J10" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="42"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="41"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="30"/>
-      <c r="E11" s="21" t="s">
+      <c r="C11" s="26"/>
+      <c r="E11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="46" t="s">
+      <c r="M11" s="38" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C12" s="30"/>
+      <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>300</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -1904,28 +2107,28 @@
       <c r="J12" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <v>25</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="26"/>
-      <c r="O12" s="43" t="s">
+      <c r="M12" s="22"/>
+      <c r="O12" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="42"/>
+      <c r="T12" s="42"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="11">
         <v>1000</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -1934,381 +2137,381 @@
       <c r="J13" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <v>467.5</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="12"/>
+      <c r="F14" s="11"/>
       <c r="G14" s="4"/>
       <c r="J14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <v>348</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>25</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="42"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="12"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="2"/>
       <c r="J15" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <v>20</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="42"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="2"/>
       <c r="J16" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <v>7.5</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>122</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="O16" s="43" t="s">
+      <c r="O16" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="42"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="12"/>
+      <c r="F17" s="11"/>
       <c r="G17" s="2"/>
       <c r="J17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="11">
         <v>42</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>122</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="42"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="12"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="4"/>
       <c r="M18" s="2"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="42"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C19" s="30"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="12"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="4"/>
       <c r="M19" s="2"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="42"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="42"/>
+      <c r="T19" s="42"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C20" s="30"/>
+      <c r="C20" s="26"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="12"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="4"/>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C21" s="30"/>
+      <c r="C21" s="26"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="12"/>
+      <c r="K21" s="11"/>
       <c r="L21" s="4"/>
       <c r="M21" s="2"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C22" s="30"/>
+      <c r="C22" s="26"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="12"/>
+      <c r="K22" s="11"/>
       <c r="L22" s="4"/>
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C23" s="30"/>
+      <c r="C23" s="26"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="11"/>
       <c r="L23" s="4"/>
       <c r="M23" s="2"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C24" s="30"/>
+      <c r="C24" s="26"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="11"/>
       <c r="L24" s="4"/>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C25" s="30"/>
+      <c r="C25" s="26"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="12"/>
+      <c r="K25" s="11"/>
       <c r="L25" s="4"/>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C26" s="30"/>
+      <c r="C26" s="26"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="12"/>
+      <c r="K26" s="11"/>
       <c r="L26" s="4"/>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C27" s="30"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="12"/>
+      <c r="K27" s="11"/>
       <c r="L27" s="4"/>
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C28" s="30"/>
+      <c r="C28" s="26"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="11"/>
       <c r="L28" s="4"/>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C29" s="30"/>
+      <c r="C29" s="26"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="12"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="12"/>
+      <c r="K29" s="11"/>
       <c r="L29" s="4"/>
       <c r="M29" s="2"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C30" s="30"/>
+      <c r="C30" s="26"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="12"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C31" s="30"/>
+      <c r="C31" s="26"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="12"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="12"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C32" s="30"/>
+      <c r="C32" s="26"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="11"/>
       <c r="G32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="12"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C33" s="30"/>
+      <c r="C33" s="26"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="12"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C34" s="30"/>
+      <c r="C34" s="26"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11"/>
       <c r="G34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="12"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
     <row r="35" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C35" s="30"/>
+      <c r="C35" s="26"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="12"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
     <row r="36" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C36" s="30"/>
+      <c r="C36" s="26"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="12"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="12"/>
+      <c r="K36" s="11"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E37" s="2"/>
-      <c r="F37" s="12"/>
+      <c r="F37" s="11"/>
       <c r="G37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="12"/>
+      <c r="K37" s="11"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
     <row r="38" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E38" s="2"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="11"/>
       <c r="G38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="12"/>
+      <c r="K38" s="11"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E39" s="2"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="12"/>
+      <c r="K39" s="11"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
     <row r="40" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E40" s="2"/>
-      <c r="F40" s="12"/>
+      <c r="F40" s="11"/>
       <c r="G40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="12"/>
+      <c r="K40" s="11"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
     <row r="41" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E41" s="2"/>
-      <c r="F41" s="12"/>
+      <c r="F41" s="11"/>
       <c r="G41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="12"/>
+      <c r="K41" s="11"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
     <row r="42" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E42" s="2"/>
-      <c r="F42" s="12"/>
+      <c r="F42" s="11"/>
       <c r="G42" s="2"/>
       <c r="J42" s="2"/>
-      <c r="K42" s="12"/>
+      <c r="K42" s="11"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E43" s="2"/>
-      <c r="F43" s="12"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="12"/>
+      <c r="K43" s="11"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E44" s="3"/>
-      <c r="F44" s="13"/>
+      <c r="F44" s="12"/>
       <c r="G44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="13"/>
+      <c r="K44" s="12"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
@@ -2340,109 +2543,109 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="27" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="31" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="30"/>
-      <c r="E10" s="40" t="s">
+      <c r="C10" s="26"/>
+      <c r="E10" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="J10" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="30"/>
-      <c r="E11" s="21" t="s">
+      <c r="C11" s="26"/>
+      <c r="E11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C12" s="30"/>
+      <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>18.75</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -2451,7 +2654,7 @@
       <c r="J12" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <v>0.5</v>
       </c>
       <c r="L12" s="4" t="s">
@@ -2459,11 +2662,11 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="11">
         <v>28.625</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -2472,7 +2675,7 @@
       <c r="J13" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <v>0.5</v>
       </c>
       <c r="L13" s="4" t="s">
@@ -2480,298 +2683,777 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
       <c r="E14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="11">
         <v>113.833</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J14" s="4"/>
-      <c r="K14" s="12"/>
+      <c r="K14" s="11"/>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
       <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="11">
         <v>234.25</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="J15" s="4"/>
-      <c r="K15" s="12"/>
+      <c r="K15" s="11"/>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
       <c r="E16" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <v>42</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>117</v>
       </c>
       <c r="J16" s="4"/>
-      <c r="K16" s="12"/>
+      <c r="K16" s="11"/>
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
       <c r="E17" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="11">
         <v>7.5</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>117</v>
       </c>
       <c r="J17" s="4"/>
-      <c r="K17" s="12"/>
+      <c r="K17" s="11"/>
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="12"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="30"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="12"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="30"/>
+      <c r="C20" s="26"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="12"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="30"/>
+      <c r="C21" s="26"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="12"/>
+      <c r="K21" s="11"/>
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="30"/>
+      <c r="C22" s="26"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="12"/>
+      <c r="K22" s="11"/>
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="30"/>
+      <c r="C23" s="26"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="11"/>
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="30"/>
+      <c r="C24" s="26"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="11"/>
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="30"/>
+      <c r="C25" s="26"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="12"/>
+      <c r="K25" s="11"/>
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="30"/>
+      <c r="C26" s="26"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="12"/>
+      <c r="K26" s="11"/>
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="30"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="12"/>
+      <c r="K27" s="11"/>
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="30"/>
+      <c r="C28" s="26"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="11"/>
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="30"/>
+      <c r="C29" s="26"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="12"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="12"/>
+      <c r="K29" s="11"/>
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="30"/>
+      <c r="C30" s="26"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="12"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="30"/>
+      <c r="C31" s="26"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="12"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="12"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="30"/>
+      <c r="C32" s="26"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="11"/>
       <c r="G32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="12"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="30"/>
+      <c r="C33" s="26"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="12"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="30"/>
+      <c r="C34" s="26"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11"/>
       <c r="G34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="12"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="30"/>
+      <c r="C35" s="26"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="12"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="30"/>
+      <c r="C36" s="26"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="12"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="12"/>
+      <c r="K36" s="11"/>
       <c r="L36" s="2"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E37" s="2"/>
-      <c r="F37" s="12"/>
+      <c r="F37" s="11"/>
       <c r="G37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="12"/>
+      <c r="K37" s="11"/>
       <c r="L37" s="2"/>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E38" s="2"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="11"/>
       <c r="G38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="12"/>
+      <c r="K38" s="11"/>
       <c r="L38" s="2"/>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E39" s="2"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="12"/>
+      <c r="K39" s="11"/>
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E40" s="2"/>
-      <c r="F40" s="12"/>
+      <c r="F40" s="11"/>
       <c r="G40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="12"/>
+      <c r="K40" s="11"/>
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E41" s="2"/>
-      <c r="F41" s="12"/>
+      <c r="F41" s="11"/>
       <c r="G41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="12"/>
+      <c r="K41" s="11"/>
       <c r="L41" s="2"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E42" s="2"/>
-      <c r="F42" s="12"/>
+      <c r="F42" s="11"/>
       <c r="G42" s="2"/>
       <c r="J42" s="2"/>
-      <c r="K42" s="12"/>
+      <c r="K42" s="11"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E43" s="2"/>
-      <c r="F43" s="12"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="12"/>
+      <c r="K43" s="11"/>
       <c r="L43" s="2"/>
     </row>
     <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E44" s="3"/>
-      <c r="F44" s="13"/>
+      <c r="F44" s="12"/>
       <c r="G44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="13"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="J10:L10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED21A768-E1F1-4F70-B6C9-A662B38F9ACD}">
+  <dimension ref="B1:L44"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B4" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B6" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B7" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B8" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="26"/>
+      <c r="E10" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="J10" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
+    </row>
+    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="26"/>
+      <c r="E11" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C12" s="26"/>
+      <c r="E12" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="10">
+        <v>600</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="K12" s="10">
+        <v>49.332999999999998</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C13" s="26"/>
+      <c r="E13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="K13" s="11">
+        <v>246.666</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C14" s="26"/>
+      <c r="E14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="11">
+        <v>400</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="K14" s="11">
+        <v>12</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C15" s="26"/>
+      <c r="E15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="11">
+        <v>200</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="K15" s="11">
+        <v>200</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C16" s="26"/>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="11">
+        <v>240</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="K16" s="11">
+        <v>222</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C17" s="26"/>
+      <c r="E17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="11">
+        <v>246.67</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J17" s="4"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C18" s="26"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="2"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C19" s="26"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="4"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C20" s="26"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C21" s="26"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="4"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C22" s="26"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C23" s="26"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="4"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C24" s="26"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="4"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C25" s="26"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="4"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C26" s="26"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C27" s="26"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="4"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C28" s="26"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="4"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C29" s="26"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C30" s="26"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C31" s="26"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C32" s="26"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C33" s="26"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C34" s="26"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C35" s="26"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C36" s="26"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E37" s="2"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E38" s="2"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E39" s="2"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E40" s="2"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E41" s="2"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E42" s="2"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E43" s="2"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E44" s="3"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="12"/>
       <c r="L44" s="3"/>
     </row>
   </sheetData>
@@ -2800,51 +3482,51 @@
   <sheetData>
     <row r="3" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="42"/>
-      <c r="K4" s="40" t="s">
+      <c r="G4" s="40"/>
+      <c r="H4" s="41"/>
+      <c r="K4" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="41"/>
-      <c r="M4" s="42"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="41"/>
     </row>
     <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="21" t="s">
+      <c r="K5" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="21" t="s">
+      <c r="M5" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="20" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -2853,7 +3535,7 @@
       <c r="F6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <v>480</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -2862,7 +3544,7 @@
       <c r="K6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <v>15</v>
       </c>
       <c r="M6" s="4" t="s">
@@ -2870,7 +3552,7 @@
       </c>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="20" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -2879,7 +3561,7 @@
       <c r="F7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <v>480</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -2888,7 +3570,7 @@
       <c r="K7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <v>5</v>
       </c>
       <c r="M7" s="4" t="s">
@@ -2896,7 +3578,7 @@
       </c>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -2905,7 +3587,7 @@
       <c r="F8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="11">
         <v>780</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -2914,7 +3596,7 @@
       <c r="K8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="11">
         <v>58.332999999999998</v>
       </c>
       <c r="M8" s="2" t="s">
@@ -2922,7 +3604,7 @@
       </c>
     </row>
     <row r="9" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="21" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -2931,7 +3613,7 @@
       <c r="F9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="11">
         <v>300</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -2940,7 +3622,7 @@
       <c r="K9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="11">
         <v>10</v>
       </c>
       <c r="M9" s="2" t="s">
@@ -2949,234 +3631,234 @@
     </row>
     <row r="10" spans="3:13" x14ac:dyDescent="0.35">
       <c r="F10" s="2"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="12"/>
+      <c r="L10" s="11"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="3:13" x14ac:dyDescent="0.35">
       <c r="F11" s="2"/>
-      <c r="G11" s="12"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="12"/>
+      <c r="L11" s="11"/>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.35">
       <c r="F12" s="2"/>
-      <c r="G12" s="12"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="12"/>
+      <c r="L12" s="11"/>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.35">
       <c r="F13" s="2"/>
-      <c r="G13" s="12"/>
+      <c r="G13" s="11"/>
       <c r="H13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="12"/>
+      <c r="L13" s="11"/>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.35">
       <c r="F14" s="2"/>
-      <c r="G14" s="12"/>
+      <c r="G14" s="11"/>
       <c r="H14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="12"/>
+      <c r="L14" s="11"/>
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.35">
       <c r="F15" s="2"/>
-      <c r="G15" s="12"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="12"/>
+      <c r="L15" s="11"/>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.35">
       <c r="F16" s="2"/>
-      <c r="G16" s="12"/>
+      <c r="G16" s="11"/>
       <c r="H16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="12"/>
+      <c r="L16" s="11"/>
       <c r="M16" s="2"/>
     </row>
     <row r="17" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="11"/>
       <c r="H17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="12"/>
+      <c r="L17" s="11"/>
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="11"/>
       <c r="H18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="12"/>
+      <c r="L18" s="11"/>
       <c r="M18" s="2"/>
     </row>
     <row r="19" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F19" s="2"/>
-      <c r="G19" s="12"/>
+      <c r="G19" s="11"/>
       <c r="H19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="12"/>
+      <c r="L19" s="11"/>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F20" s="2"/>
-      <c r="G20" s="12"/>
+      <c r="G20" s="11"/>
       <c r="H20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="12"/>
+      <c r="L20" s="11"/>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F21" s="2"/>
-      <c r="G21" s="12"/>
+      <c r="G21" s="11"/>
       <c r="H21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="12"/>
+      <c r="L21" s="11"/>
       <c r="M21" s="2"/>
     </row>
     <row r="22" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F22" s="2"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="11"/>
       <c r="H22" s="2"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="12"/>
+      <c r="L22" s="11"/>
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F23" s="2"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="11"/>
       <c r="H23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="12"/>
+      <c r="L23" s="11"/>
       <c r="M23" s="2"/>
     </row>
     <row r="24" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F24" s="2"/>
-      <c r="G24" s="12"/>
+      <c r="G24" s="11"/>
       <c r="H24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="12"/>
+      <c r="L24" s="11"/>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F25" s="2"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="11"/>
       <c r="H25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="12"/>
+      <c r="L25" s="11"/>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F26" s="2"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="11"/>
       <c r="H26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="12"/>
+      <c r="L26" s="11"/>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F27" s="2"/>
-      <c r="G27" s="12"/>
+      <c r="G27" s="11"/>
       <c r="H27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="12"/>
+      <c r="L27" s="11"/>
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F28" s="2"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="11"/>
       <c r="H28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="12"/>
+      <c r="L28" s="11"/>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F29" s="2"/>
-      <c r="G29" s="12"/>
+      <c r="G29" s="11"/>
       <c r="H29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="12"/>
+      <c r="L29" s="11"/>
       <c r="M29" s="2"/>
     </row>
     <row r="30" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F30" s="2"/>
-      <c r="G30" s="12"/>
+      <c r="G30" s="11"/>
       <c r="H30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="12"/>
+      <c r="L30" s="11"/>
       <c r="M30" s="2"/>
     </row>
     <row r="31" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
-      <c r="G31" s="12"/>
+      <c r="G31" s="11"/>
       <c r="H31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="12"/>
+      <c r="L31" s="11"/>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
-      <c r="G32" s="12"/>
+      <c r="G32" s="11"/>
       <c r="H32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="12"/>
+      <c r="L32" s="11"/>
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F33" s="2"/>
-      <c r="G33" s="12"/>
+      <c r="G33" s="11"/>
       <c r="H33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="12"/>
+      <c r="L33" s="11"/>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
-      <c r="G34" s="12"/>
+      <c r="G34" s="11"/>
       <c r="H34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="12"/>
+      <c r="L34" s="11"/>
       <c r="M34" s="2"/>
     </row>
     <row r="35" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F35" s="2"/>
-      <c r="G35" s="12"/>
+      <c r="G35" s="11"/>
       <c r="H35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="12"/>
+      <c r="L35" s="11"/>
       <c r="M35" s="2"/>
     </row>
     <row r="36" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F36" s="2"/>
-      <c r="G36" s="12"/>
+      <c r="G36" s="11"/>
       <c r="H36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="12"/>
+      <c r="L36" s="11"/>
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="6:13" x14ac:dyDescent="0.35">
       <c r="F37" s="2"/>
-      <c r="G37" s="12"/>
+      <c r="G37" s="11"/>
       <c r="H37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="12"/>
+      <c r="L37" s="11"/>
       <c r="M37" s="2"/>
     </row>
     <row r="38" spans="6:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F38" s="3"/>
-      <c r="G38" s="13"/>
+      <c r="G38" s="12"/>
       <c r="H38" s="3"/>
       <c r="K38" s="3"/>
-      <c r="L38" s="13"/>
+      <c r="L38" s="12"/>
       <c r="M38" s="3"/>
     </row>
   </sheetData>
@@ -3194,7 +3876,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" style="30" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" style="26" customWidth="1"/>
     <col min="6" max="6" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -3207,118 +3889,118 @@
   <sheetData>
     <row r="3" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="27" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="3:20" ht="54" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="33" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="7" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="28" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="28" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="29" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="13" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="42"/>
-      <c r="K13" s="40" t="s">
+      <c r="G13" s="40"/>
+      <c r="H13" s="41"/>
+      <c r="K13" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="42"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="41"/>
     </row>
     <row r="14" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="21" t="s">
+      <c r="K14" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="M14" s="21" t="s">
+      <c r="M14" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="46" t="s">
+      <c r="N14" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="P14" s="43" t="s">
+      <c r="P14" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="42"/>
     </row>
     <row r="15" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <v>1800</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -3327,24 +4009,24 @@
       <c r="K15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="10">
         <v>1999.848</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="26"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
+      <c r="N15" s="22"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="42"/>
     </row>
     <row r="16" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="11">
         <v>514.27200000000005</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -3353,7 +4035,7 @@
       <c r="K16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="11">
         <v>960</v>
       </c>
       <c r="M16" s="2" t="s">
@@ -3362,20 +4044,20 @@
       <c r="N16" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="42"/>
     </row>
     <row r="17" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="11"/>
       <c r="H17" s="2"/>
       <c r="K17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="11">
         <v>111.25</v>
       </c>
       <c r="M17" s="2" t="s">
@@ -3384,20 +4066,20 @@
       <c r="N17" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="42"/>
     </row>
     <row r="18" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="11"/>
       <c r="H18" s="2"/>
       <c r="K18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="11">
         <v>37.5</v>
       </c>
       <c r="M18" s="2" t="s">
@@ -3409,12 +4091,12 @@
     </row>
     <row r="19" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F19" s="2"/>
-      <c r="G19" s="12"/>
+      <c r="G19" s="11"/>
       <c r="H19" s="2"/>
       <c r="K19" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="11">
         <v>234.25</v>
       </c>
       <c r="M19" s="2" t="s">
@@ -3426,10 +4108,10 @@
     </row>
     <row r="20" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F20" s="2"/>
-      <c r="G20" s="12"/>
+      <c r="G20" s="11"/>
       <c r="H20" s="2"/>
       <c r="K20" s="4"/>
-      <c r="L20" s="12"/>
+      <c r="L20" s="11"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="P20">
@@ -3439,244 +4121,244 @@
     </row>
     <row r="21" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F21" s="2"/>
-      <c r="G21" s="12"/>
+      <c r="G21" s="11"/>
       <c r="H21" s="2"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="12"/>
+      <c r="L21" s="11"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F22" s="2"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="11"/>
       <c r="H22" s="2"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="12"/>
+      <c r="L22" s="11"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
     </row>
     <row r="23" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F23" s="2"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="11"/>
       <c r="H23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="12"/>
+      <c r="L23" s="11"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
     </row>
     <row r="24" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F24" s="2"/>
-      <c r="G24" s="12"/>
+      <c r="G24" s="11"/>
       <c r="H24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="12"/>
+      <c r="L24" s="11"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
     </row>
     <row r="25" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F25" s="2"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="11"/>
       <c r="H25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="12"/>
+      <c r="L25" s="11"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
     <row r="26" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F26" s="2"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="11"/>
       <c r="H26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="12"/>
+      <c r="L26" s="11"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
     <row r="27" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F27" s="2"/>
-      <c r="G27" s="12"/>
+      <c r="G27" s="11"/>
       <c r="H27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="12"/>
+      <c r="L27" s="11"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
     <row r="28" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F28" s="2"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="11"/>
       <c r="H28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="12"/>
+      <c r="L28" s="11"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
     </row>
     <row r="29" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F29" s="2"/>
-      <c r="G29" s="12"/>
+      <c r="G29" s="11"/>
       <c r="H29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="12"/>
+      <c r="L29" s="11"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
     <row r="30" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F30" s="2"/>
-      <c r="G30" s="12"/>
+      <c r="G30" s="11"/>
       <c r="H30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="12"/>
+      <c r="L30" s="11"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
     <row r="31" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
-      <c r="G31" s="12"/>
+      <c r="G31" s="11"/>
       <c r="H31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="12"/>
+      <c r="L31" s="11"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
-      <c r="G32" s="12"/>
+      <c r="G32" s="11"/>
       <c r="H32" s="2"/>
       <c r="K32" s="2"/>
-      <c r="L32" s="12"/>
+      <c r="L32" s="11"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F33" s="2"/>
-      <c r="G33" s="12"/>
+      <c r="G33" s="11"/>
       <c r="H33" s="2"/>
       <c r="K33" s="2"/>
-      <c r="L33" s="12"/>
+      <c r="L33" s="11"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
     <row r="34" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
-      <c r="G34" s="12"/>
+      <c r="G34" s="11"/>
       <c r="H34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="L34" s="12"/>
+      <c r="L34" s="11"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
     <row r="35" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F35" s="2"/>
-      <c r="G35" s="12"/>
+      <c r="G35" s="11"/>
       <c r="H35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="12"/>
+      <c r="L35" s="11"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
     <row r="36" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F36" s="2"/>
-      <c r="G36" s="12"/>
+      <c r="G36" s="11"/>
       <c r="H36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="12"/>
+      <c r="L36" s="11"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
     <row r="37" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F37" s="2"/>
-      <c r="G37" s="12"/>
+      <c r="G37" s="11"/>
       <c r="H37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="12"/>
+      <c r="L37" s="11"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
     </row>
     <row r="38" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F38" s="2"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="11"/>
       <c r="H38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="12"/>
+      <c r="L38" s="11"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
     </row>
     <row r="39" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F39" s="2"/>
-      <c r="G39" s="12"/>
+      <c r="G39" s="11"/>
       <c r="H39" s="2"/>
       <c r="K39" s="2"/>
-      <c r="L39" s="12"/>
+      <c r="L39" s="11"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
     </row>
     <row r="40" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F40" s="2"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="11"/>
       <c r="H40" s="2"/>
       <c r="K40" s="2"/>
-      <c r="L40" s="12"/>
+      <c r="L40" s="11"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
     </row>
     <row r="41" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F41" s="2"/>
-      <c r="G41" s="12"/>
+      <c r="G41" s="11"/>
       <c r="H41" s="2"/>
       <c r="K41" s="2"/>
-      <c r="L41" s="12"/>
+      <c r="L41" s="11"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
     </row>
     <row r="42" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F42" s="2"/>
-      <c r="G42" s="12"/>
+      <c r="G42" s="11"/>
       <c r="H42" s="2"/>
       <c r="K42" s="2"/>
-      <c r="L42" s="12"/>
+      <c r="L42" s="11"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
     <row r="43" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F43" s="2"/>
-      <c r="G43" s="12"/>
+      <c r="G43" s="11"/>
       <c r="H43" s="2"/>
       <c r="K43" s="2"/>
-      <c r="L43" s="12"/>
+      <c r="L43" s="11"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
     <row r="44" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F44" s="2"/>
-      <c r="G44" s="12"/>
+      <c r="G44" s="11"/>
       <c r="H44" s="2"/>
       <c r="K44" s="2"/>
-      <c r="L44" s="12"/>
+      <c r="L44" s="11"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
     <row r="45" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F45" s="2"/>
-      <c r="G45" s="12"/>
+      <c r="G45" s="11"/>
       <c r="H45" s="2"/>
       <c r="K45" s="2"/>
-      <c r="L45" s="12"/>
+      <c r="L45" s="11"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
     <row r="46" spans="6:14" x14ac:dyDescent="0.35">
       <c r="F46" s="2"/>
-      <c r="G46" s="12"/>
+      <c r="G46" s="11"/>
       <c r="H46" s="2"/>
       <c r="K46" s="2"/>
-      <c r="L46" s="12"/>
+      <c r="L46" s="11"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
     <row r="47" spans="6:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F47" s="3"/>
-      <c r="G47" s="13"/>
+      <c r="G47" s="12"/>
       <c r="H47" s="3"/>
       <c r="K47" s="3"/>
-      <c r="L47" s="13"/>
+      <c r="L47" s="12"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
     </row>
@@ -3704,7 +4386,7 @@
     <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.453125" customWidth="1"/>
     <col min="12" max="12" width="27.6328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.6328125" customWidth="1"/>
     <col min="15" max="15" width="18.08984375" customWidth="1"/>
@@ -3712,124 +4394,124 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="27" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="30"/>
+      <c r="C10" s="26"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="30"/>
-      <c r="E11" s="40" t="s">
+      <c r="C11" s="26"/>
+      <c r="E11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="42"/>
-      <c r="J11" s="40" t="s">
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
+      <c r="J11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="42"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="41"/>
     </row>
     <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C12" s="30"/>
-      <c r="E12" s="21" t="s">
+      <c r="C12" s="26"/>
+      <c r="E12" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J12" s="44" t="s">
+      <c r="J12" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="K12" s="45" t="s">
+      <c r="K12" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="L12" s="44" t="s">
+      <c r="L12" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="46" t="s">
+      <c r="M12" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="O12" s="43" t="s">
+      <c r="O12" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="42"/>
+      <c r="T12" s="42"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
       <c r="E13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <v>900</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -3838,26 +4520,26 @@
       <c r="J13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K13" s="11">
-        <v>1889.01666</v>
+      <c r="K13" s="10">
+        <v>1655.6866600000001</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="26"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
+      <c r="M13" s="22"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="11">
         <v>600</v>
       </c>
       <c r="G14" s="4" t="s">
@@ -3866,7 +4548,7 @@
       <c r="J14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <v>142.5</v>
       </c>
       <c r="L14" s="6" t="s">
@@ -3875,22 +4557,22 @@
       <c r="M14" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="42"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="12"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="2"/>
       <c r="J15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <v>104.65</v>
       </c>
       <c r="L15" s="6" t="s">
@@ -3899,22 +4581,22 @@
       <c r="M15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="42"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="2"/>
       <c r="J16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <v>113.833</v>
       </c>
       <c r="L16" s="6" t="s">
@@ -3923,320 +4605,355 @@
       <c r="M16" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="O16" s="43" t="s">
+      <c r="O16" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="42"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="12"/>
+      <c r="F17" s="11"/>
       <c r="G17" s="2"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="2"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
+      <c r="J17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" s="11">
+        <v>246.67</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="42"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="12"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="6"/>
       <c r="M18" s="2"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="42"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C19" s="30"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="2"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="12"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="6"/>
       <c r="M19" s="2"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="42"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="42"/>
+      <c r="T19" s="42"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C20" s="30"/>
+      <c r="C20" s="26"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="12"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="6"/>
       <c r="M20" s="2"/>
+      <c r="O20" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="42"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C21" s="30"/>
+      <c r="C21" s="26"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="12"/>
+      <c r="K21" s="11"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="42"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="42"/>
+      <c r="T21" s="42"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C22" s="30"/>
+      <c r="C22" s="26"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="12"/>
+      <c r="K22" s="11"/>
       <c r="L22" s="6"/>
       <c r="M22" s="2"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42"/>
+      <c r="T22" s="42"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C23" s="30"/>
+      <c r="C23" s="26"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="11"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="42"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="42"/>
+      <c r="T23" s="42"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C24" s="30"/>
+      <c r="C24" s="26"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="11"/>
       <c r="L24" s="6"/>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C25" s="30"/>
+      <c r="C25" s="26"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="12"/>
+      <c r="K25" s="11"/>
       <c r="L25" s="6"/>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C26" s="30"/>
+      <c r="C26" s="26"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="12"/>
+      <c r="K26" s="11"/>
       <c r="L26" s="6"/>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C27" s="30"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="12"/>
+      <c r="K27" s="11"/>
       <c r="L27" s="6"/>
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C28" s="30"/>
+      <c r="C28" s="26"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="11"/>
       <c r="L28" s="6"/>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C29" s="30"/>
+      <c r="C29" s="26"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="12"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="12"/>
+      <c r="K29" s="11"/>
       <c r="L29" s="6"/>
       <c r="M29" s="2"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C30" s="30"/>
+      <c r="C30" s="26"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="12"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="6"/>
       <c r="M30" s="2"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C31" s="30"/>
+      <c r="C31" s="26"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="12"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="12"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="6"/>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C32" s="30"/>
+      <c r="C32" s="26"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="11"/>
       <c r="G32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="12"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="6"/>
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C33" s="30"/>
+      <c r="C33" s="26"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="12"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="6"/>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C34" s="30"/>
+      <c r="C34" s="26"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11"/>
       <c r="G34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="12"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="6"/>
       <c r="M34" s="2"/>
     </row>
     <row r="35" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C35" s="30"/>
+      <c r="C35" s="26"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="12"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="6"/>
       <c r="M35" s="2"/>
     </row>
     <row r="36" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C36" s="30"/>
+      <c r="C36" s="26"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="12"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="12"/>
+      <c r="K36" s="11"/>
       <c r="L36" s="6"/>
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E37" s="2"/>
-      <c r="F37" s="12"/>
+      <c r="F37" s="11"/>
       <c r="G37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="12"/>
+      <c r="K37" s="11"/>
       <c r="L37" s="6"/>
       <c r="M37" s="2"/>
     </row>
     <row r="38" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E38" s="2"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="11"/>
       <c r="G38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="12"/>
+      <c r="K38" s="11"/>
       <c r="L38" s="6"/>
       <c r="M38" s="2"/>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E39" s="2"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="12"/>
+      <c r="K39" s="11"/>
       <c r="L39" s="6"/>
       <c r="M39" s="2"/>
     </row>
     <row r="40" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E40" s="2"/>
-      <c r="F40" s="12"/>
+      <c r="F40" s="11"/>
       <c r="G40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="12"/>
+      <c r="K40" s="11"/>
       <c r="L40" s="6"/>
       <c r="M40" s="2"/>
     </row>
     <row r="41" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E41" s="2"/>
-      <c r="F41" s="12"/>
+      <c r="F41" s="11"/>
       <c r="G41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="12"/>
+      <c r="K41" s="11"/>
       <c r="L41" s="6"/>
       <c r="M41" s="2"/>
     </row>
     <row r="42" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E42" s="2"/>
-      <c r="F42" s="12"/>
+      <c r="F42" s="11"/>
       <c r="G42" s="2"/>
       <c r="J42" s="2"/>
-      <c r="K42" s="12"/>
+      <c r="K42" s="11"/>
       <c r="L42" s="6"/>
       <c r="M42" s="2"/>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E43" s="2"/>
-      <c r="F43" s="12"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="12"/>
+      <c r="K43" s="11"/>
       <c r="L43" s="6"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E44" s="2"/>
-      <c r="F44" s="12"/>
+      <c r="F44" s="11"/>
       <c r="G44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="12"/>
+      <c r="K44" s="11"/>
       <c r="L44" s="6"/>
       <c r="M44" s="2"/>
     </row>
     <row r="45" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E45" s="3"/>
-      <c r="F45" s="13"/>
+      <c r="F45" s="12"/>
       <c r="G45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="13"/>
+      <c r="K45" s="12"/>
       <c r="L45" s="7"/>
       <c r="M45" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="O12:T15"/>
     <mergeCell ref="O16:T19"/>
     <mergeCell ref="J11:M11"/>
+    <mergeCell ref="O20:T23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4259,112 +4976,112 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="27" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="30"/>
+      <c r="C10" s="26"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="30"/>
-      <c r="E11" s="40" t="s">
+      <c r="C11" s="26"/>
+      <c r="E11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="42"/>
-      <c r="J11" s="40" t="s">
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
+      <c r="J11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="42"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="41"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C12" s="30"/>
-      <c r="E12" s="21" t="s">
+      <c r="C12" s="26"/>
+      <c r="E12" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="L12" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
       <c r="E13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <v>480</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -4373,7 +5090,7 @@
       <c r="J13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="10">
         <v>204</v>
       </c>
       <c r="L13" s="4" t="s">
@@ -4381,11 +5098,11 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="11">
         <v>480</v>
       </c>
       <c r="G14" s="4" t="s">
@@ -4394,7 +5111,7 @@
       <c r="J14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <v>18</v>
       </c>
       <c r="L14" s="2" t="s">
@@ -4402,14 +5119,14 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="12"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="2"/>
       <c r="J15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <v>18</v>
       </c>
       <c r="L15" s="2" t="s">
@@ -4417,264 +5134,264 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="2"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="12"/>
+      <c r="K16" s="11"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="12"/>
+      <c r="F17" s="11"/>
       <c r="G17" s="2"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="12"/>
+      <c r="K17" s="11"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="12"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="30"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="2"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="12"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="30"/>
+      <c r="C20" s="26"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="12"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="30"/>
+      <c r="C21" s="26"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="12"/>
+      <c r="K21" s="11"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="30"/>
+      <c r="C22" s="26"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="12"/>
+      <c r="K22" s="11"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="30"/>
+      <c r="C23" s="26"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="11"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="30"/>
+      <c r="C24" s="26"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="11"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="30"/>
+      <c r="C25" s="26"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="12"/>
+      <c r="K25" s="11"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="30"/>
+      <c r="C26" s="26"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="12"/>
+      <c r="K26" s="11"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="30"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="12"/>
+      <c r="K27" s="11"/>
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="30"/>
+      <c r="C28" s="26"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="11"/>
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="30"/>
+      <c r="C29" s="26"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="12"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="12"/>
+      <c r="K29" s="11"/>
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="30"/>
+      <c r="C30" s="26"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="12"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="30"/>
+      <c r="C31" s="26"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="12"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="12"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="30"/>
+      <c r="C32" s="26"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="11"/>
       <c r="G32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="12"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="30"/>
+      <c r="C33" s="26"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="12"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="30"/>
+      <c r="C34" s="26"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11"/>
       <c r="G34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="12"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="30"/>
+      <c r="C35" s="26"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="12"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="30"/>
+      <c r="C36" s="26"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="12"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="12"/>
+      <c r="K36" s="11"/>
       <c r="L36" s="2"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E37" s="2"/>
-      <c r="F37" s="12"/>
+      <c r="F37" s="11"/>
       <c r="G37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="12"/>
+      <c r="K37" s="11"/>
       <c r="L37" s="2"/>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E38" s="2"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="11"/>
       <c r="G38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="12"/>
+      <c r="K38" s="11"/>
       <c r="L38" s="2"/>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E39" s="2"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="12"/>
+      <c r="K39" s="11"/>
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E40" s="2"/>
-      <c r="F40" s="12"/>
+      <c r="F40" s="11"/>
       <c r="G40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="12"/>
+      <c r="K40" s="11"/>
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E41" s="2"/>
-      <c r="F41" s="12"/>
+      <c r="F41" s="11"/>
       <c r="G41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="12"/>
+      <c r="K41" s="11"/>
       <c r="L41" s="2"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E42" s="2"/>
-      <c r="F42" s="12"/>
+      <c r="F42" s="11"/>
       <c r="G42" s="2"/>
       <c r="J42" s="2"/>
-      <c r="K42" s="12"/>
+      <c r="K42" s="11"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E43" s="2"/>
-      <c r="F43" s="12"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="12"/>
+      <c r="K43" s="11"/>
       <c r="L43" s="2"/>
     </row>
     <row r="44" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E44" s="2"/>
-      <c r="F44" s="12"/>
+      <c r="F44" s="11"/>
       <c r="G44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="12"/>
+      <c r="K44" s="11"/>
       <c r="L44" s="2"/>
     </row>
     <row r="45" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E45" s="3"/>
-      <c r="F45" s="13"/>
+      <c r="F45" s="12"/>
       <c r="G45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="13"/>
+      <c r="K45" s="12"/>
       <c r="L45" s="3"/>
     </row>
   </sheetData>
@@ -4703,68 +5420,68 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="42"/>
-      <c r="J2" s="40" t="s">
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+      <c r="J2" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="41"/>
-      <c r="L2" s="42"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="41"/>
     </row>
     <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="L3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="43" t="s">
+      <c r="N3" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>84</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>960</v>
       </c>
       <c r="G4" s="4" t="s">
@@ -4773,30 +5490,30 @@
       <c r="J4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="10">
         <v>1140</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <v>960</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -4805,322 +5522,322 @@
       <c r="J5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="11">
         <v>300</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>59</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="12"/>
+      <c r="F6" s="11"/>
       <c r="G6" s="2"/>
       <c r="J6" s="4"/>
-      <c r="K6" s="12"/>
+      <c r="K6" s="11"/>
       <c r="L6" s="2"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>60</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="12"/>
+      <c r="F7" s="11"/>
       <c r="G7" s="2"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="12"/>
+      <c r="K7" s="11"/>
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>61</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="12"/>
+      <c r="F8" s="11"/>
       <c r="G8" s="2"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="12"/>
+      <c r="K8" s="11"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>62</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="12"/>
+      <c r="F9" s="11"/>
       <c r="G9" s="2"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="12"/>
+      <c r="K9" s="11"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C10" s="30"/>
+      <c r="C10" s="26"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="12"/>
+      <c r="F10" s="11"/>
       <c r="G10" s="2"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="12"/>
+      <c r="K10" s="11"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C11" s="30"/>
+      <c r="C11" s="26"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="12"/>
+      <c r="F11" s="11"/>
       <c r="G11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="12"/>
+      <c r="K11" s="11"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C12" s="30"/>
+      <c r="C12" s="26"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="12"/>
+      <c r="F12" s="11"/>
       <c r="G12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="12"/>
+      <c r="K12" s="11"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="12"/>
+      <c r="F13" s="11"/>
       <c r="G13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="12"/>
+      <c r="K13" s="11"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="12"/>
+      <c r="F14" s="11"/>
       <c r="G14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="12"/>
+      <c r="K14" s="11"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="12"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="12"/>
+      <c r="K15" s="11"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="12"/>
+      <c r="K16" s="11"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="12"/>
+      <c r="F17" s="11"/>
       <c r="G17" s="2"/>
       <c r="J17" s="2"/>
-      <c r="K17" s="12"/>
+      <c r="K17" s="11"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="2"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="12"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="30"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="12"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="30"/>
+      <c r="C20" s="26"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="12"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="30"/>
+      <c r="C21" s="26"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="12"/>
+      <c r="K21" s="11"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="30"/>
+      <c r="C22" s="26"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="12"/>
+      <c r="K22" s="11"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="30"/>
+      <c r="C23" s="26"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="11"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="30"/>
+      <c r="C24" s="26"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="11"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="30"/>
+      <c r="C25" s="26"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="12"/>
+      <c r="K25" s="11"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="30"/>
+      <c r="C26" s="26"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="12"/>
+      <c r="K26" s="11"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="30"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="12"/>
+      <c r="K27" s="11"/>
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="30"/>
+      <c r="C28" s="26"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="11"/>
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="30"/>
+      <c r="C29" s="26"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="12"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="12"/>
+      <c r="K29" s="11"/>
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="30"/>
+      <c r="C30" s="26"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="12"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="30"/>
+      <c r="C31" s="26"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="12"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="12"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="30"/>
+      <c r="C32" s="26"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="11"/>
       <c r="G32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="12"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="30"/>
+      <c r="C33" s="26"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="12"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="30"/>
+      <c r="C34" s="26"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11"/>
       <c r="G34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="12"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="30"/>
+      <c r="C35" s="26"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="12"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C36" s="30"/>
+      <c r="C36" s="26"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="13"/>
+      <c r="F36" s="12"/>
       <c r="G36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="13"/>
+      <c r="K36" s="12"/>
       <c r="L36" s="3"/>
     </row>
   </sheetData>
@@ -5150,109 +5867,109 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="27" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="31" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="30"/>
-      <c r="E10" s="40" t="s">
+      <c r="C10" s="26"/>
+      <c r="E10" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="J10" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="30"/>
-      <c r="E11" s="21" t="s">
+      <c r="C11" s="26"/>
+      <c r="E11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C12" s="30"/>
+      <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>480</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -5261,7 +5978,7 @@
       <c r="J12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <v>61.6875</v>
       </c>
       <c r="L12" s="4" t="s">
@@ -5269,11 +5986,11 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="11">
         <v>422.5</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -5282,7 +5999,7 @@
       <c r="J13" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <v>45</v>
       </c>
       <c r="L13" s="4" t="s">
@@ -5290,11 +6007,11 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
       <c r="E14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="11">
         <v>300</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -5303,7 +6020,7 @@
       <c r="J14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <v>45</v>
       </c>
       <c r="L14" s="4" t="s">
@@ -5311,11 +6028,11 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
       <c r="E15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="11">
         <v>142.5</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -5324,7 +6041,7 @@
       <c r="J15" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <v>33.125</v>
       </c>
       <c r="L15" s="4" t="s">
@@ -5332,11 +6049,11 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
       <c r="E16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <v>111.25</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -5345,7 +6062,7 @@
       <c r="J16" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <v>30</v>
       </c>
       <c r="L16" s="4" t="s">
@@ -5353,11 +6070,11 @@
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
       <c r="E17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="11">
         <v>18</v>
       </c>
       <c r="G17" s="2" t="s">
@@ -5366,7 +6083,7 @@
       <c r="J17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="11">
         <v>30</v>
       </c>
       <c r="L17" s="4" t="s">
@@ -5374,14 +6091,14 @@
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="11">
         <v>25</v>
       </c>
       <c r="L18" s="4" t="s">
@@ -5389,14 +6106,14 @@
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="30"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="2"/>
       <c r="J19" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="11">
         <v>22.5</v>
       </c>
       <c r="L19" s="4" t="s">
@@ -5404,14 +6121,14 @@
       </c>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="30"/>
+      <c r="C20" s="26"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="11">
         <v>20.5</v>
       </c>
       <c r="L20" s="4" t="s">
@@ -5419,14 +6136,14 @@
       </c>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="30"/>
+      <c r="C21" s="26"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="11">
         <v>15</v>
       </c>
       <c r="L21" s="4" t="s">
@@ -5434,14 +6151,14 @@
       </c>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="30"/>
+      <c r="C22" s="26"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="11">
         <v>7.3125</v>
       </c>
       <c r="L22" s="4" t="s">
@@ -5449,14 +6166,14 @@
       </c>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="30"/>
+      <c r="C23" s="26"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="2"/>
       <c r="J23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="11">
         <v>7.25</v>
       </c>
       <c r="L23" s="4" t="s">
@@ -5464,14 +6181,14 @@
       </c>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="30"/>
+      <c r="C24" s="26"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="11">
         <v>5</v>
       </c>
       <c r="L24" s="4" t="s">
@@ -5479,14 +6196,14 @@
       </c>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="30"/>
+      <c r="C25" s="26"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K25" s="12">
+      <c r="K25" s="11">
         <v>3</v>
       </c>
       <c r="L25" s="4" t="s">
@@ -5494,14 +6211,14 @@
       </c>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="30"/>
+      <c r="C26" s="26"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="11">
         <v>2.5</v>
       </c>
       <c r="L26" s="4" t="s">
@@ -5509,14 +6226,14 @@
       </c>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="30"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="11">
         <v>2.25</v>
       </c>
       <c r="L27" s="4" t="s">
@@ -5524,14 +6241,14 @@
       </c>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="30"/>
+      <c r="C28" s="26"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K28" s="12">
+      <c r="K28" s="11">
         <v>1.4065000000000001</v>
       </c>
       <c r="L28" s="4" t="s">
@@ -5539,14 +6256,14 @@
       </c>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="30"/>
+      <c r="C29" s="26"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="12"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="11">
         <v>0.5</v>
       </c>
       <c r="L29" s="4" t="s">
@@ -5554,130 +6271,130 @@
       </c>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="30"/>
+      <c r="C30" s="26"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="12"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="30"/>
+      <c r="C31" s="26"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="12"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="12"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="30"/>
+      <c r="C32" s="26"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="11"/>
       <c r="G32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="12"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="30"/>
+      <c r="C33" s="26"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="12"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="30"/>
+      <c r="C34" s="26"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11"/>
       <c r="G34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="12"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="30"/>
+      <c r="C35" s="26"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="12"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="30"/>
+      <c r="C36" s="26"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="12"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="12"/>
+      <c r="K36" s="11"/>
       <c r="L36" s="2"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E37" s="2"/>
-      <c r="F37" s="12"/>
+      <c r="F37" s="11"/>
       <c r="G37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="12"/>
+      <c r="K37" s="11"/>
       <c r="L37" s="2"/>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E38" s="2"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="11"/>
       <c r="G38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="12"/>
+      <c r="K38" s="11"/>
       <c r="L38" s="2"/>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E39" s="2"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="12"/>
+      <c r="K39" s="11"/>
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E40" s="2"/>
-      <c r="F40" s="12"/>
+      <c r="F40" s="11"/>
       <c r="G40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="12"/>
+      <c r="K40" s="11"/>
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E41" s="2"/>
-      <c r="F41" s="12"/>
+      <c r="F41" s="11"/>
       <c r="G41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="12"/>
+      <c r="K41" s="11"/>
       <c r="L41" s="2"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E42" s="2"/>
-      <c r="F42" s="12"/>
+      <c r="F42" s="11"/>
       <c r="G42" s="2"/>
       <c r="J42" s="2"/>
-      <c r="K42" s="12"/>
+      <c r="K42" s="11"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E43" s="2"/>
-      <c r="F43" s="12"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="12"/>
+      <c r="K43" s="11"/>
       <c r="L43" s="2"/>
     </row>
     <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E44" s="3"/>
-      <c r="F44" s="13"/>
+      <c r="F44" s="12"/>
       <c r="G44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="13"/>
+      <c r="K44" s="12"/>
       <c r="L44" s="3"/>
     </row>
   </sheetData>
@@ -5711,100 +6428,100 @@
   <sheetData>
     <row r="1" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="27" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="31" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="30"/>
-      <c r="E10" s="40" t="s">
+      <c r="C10" s="26"/>
+      <c r="E10" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="J10" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
     </row>
     <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="30"/>
-      <c r="E11" s="21" t="s">
+      <c r="C11" s="26"/>
+      <c r="E11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="17" t="s">
         <v>24</v>
       </c>
       <c r="P11" t="s">
@@ -5812,11 +6529,11 @@
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C12" s="30"/>
+      <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>1260</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -5825,7 +6542,7 @@
       <c r="J12" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <v>23.332999999999998</v>
       </c>
       <c r="L12" s="4" t="s">
@@ -5836,11 +6553,11 @@
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
       <c r="E13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="11">
         <v>500</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -5849,7 +6566,7 @@
       <c r="J13" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <v>19.443999999999999</v>
       </c>
       <c r="L13" s="4" t="s">
@@ -5857,11 +6574,11 @@
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="11">
         <v>533.33299999999997</v>
       </c>
       <c r="G14" s="4" t="s">
@@ -5870,7 +6587,7 @@
       <c r="J14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <v>669.33299999999997</v>
       </c>
       <c r="L14" s="4" t="s">
@@ -5878,14 +6595,14 @@
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="12"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="2"/>
       <c r="J15" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <v>635.40554999999995</v>
       </c>
       <c r="L15" s="4" t="s">
@@ -5893,14 +6610,14 @@
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="2"/>
       <c r="J16" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <v>54</v>
       </c>
       <c r="L16" s="4" t="s">
@@ -5908,14 +6625,14 @@
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="12"/>
+      <c r="F17" s="11"/>
       <c r="G17" s="2"/>
       <c r="J17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="11">
         <v>45.15</v>
       </c>
       <c r="L17" s="4" t="s">
@@ -5923,238 +6640,238 @@
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="12"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="30"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="12"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="30"/>
+      <c r="C20" s="26"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="12"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="30"/>
+      <c r="C21" s="26"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="12"/>
+      <c r="K21" s="11"/>
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="30"/>
+      <c r="C22" s="26"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="12"/>
+      <c r="K22" s="11"/>
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="30"/>
+      <c r="C23" s="26"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="11"/>
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="30"/>
+      <c r="C24" s="26"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="11"/>
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="30"/>
+      <c r="C25" s="26"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="12"/>
+      <c r="K25" s="11"/>
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="30"/>
+      <c r="C26" s="26"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="12"/>
+      <c r="K26" s="11"/>
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="30"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="12"/>
+      <c r="K27" s="11"/>
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="30"/>
+      <c r="C28" s="26"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="11"/>
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="30"/>
+      <c r="C29" s="26"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="12"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="12"/>
+      <c r="K29" s="11"/>
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="30"/>
+      <c r="C30" s="26"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="12"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="30"/>
+      <c r="C31" s="26"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="12"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="12"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="30"/>
+      <c r="C32" s="26"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="11"/>
       <c r="G32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="12"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="30"/>
+      <c r="C33" s="26"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="12"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="30"/>
+      <c r="C34" s="26"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11"/>
       <c r="G34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="12"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="30"/>
+      <c r="C35" s="26"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="12"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="30"/>
+      <c r="C36" s="26"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="12"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="12"/>
+      <c r="K36" s="11"/>
       <c r="L36" s="2"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E37" s="2"/>
-      <c r="F37" s="12"/>
+      <c r="F37" s="11"/>
       <c r="G37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="12"/>
+      <c r="K37" s="11"/>
       <c r="L37" s="2"/>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E38" s="2"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="11"/>
       <c r="G38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="12"/>
+      <c r="K38" s="11"/>
       <c r="L38" s="2"/>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E39" s="2"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="12"/>
+      <c r="K39" s="11"/>
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E40" s="2"/>
-      <c r="F40" s="12"/>
+      <c r="F40" s="11"/>
       <c r="G40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="12"/>
+      <c r="K40" s="11"/>
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E41" s="2"/>
-      <c r="F41" s="12"/>
+      <c r="F41" s="11"/>
       <c r="G41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="12"/>
+      <c r="K41" s="11"/>
       <c r="L41" s="2"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E42" s="2"/>
-      <c r="F42" s="12"/>
+      <c r="F42" s="11"/>
       <c r="G42" s="2"/>
       <c r="J42" s="2"/>
-      <c r="K42" s="12"/>
+      <c r="K42" s="11"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E43" s="2"/>
-      <c r="F43" s="12"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="12"/>
+      <c r="K43" s="11"/>
       <c r="L43" s="2"/>
     </row>
     <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E44" s="3"/>
-      <c r="F44" s="13"/>
+      <c r="F44" s="12"/>
       <c r="G44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="13"/>
+      <c r="K44" s="12"/>
       <c r="L44" s="3"/>
     </row>
   </sheetData>
@@ -6183,109 +6900,109 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="27" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="31" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="29" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="30"/>
-      <c r="E10" s="40" t="s">
+      <c r="C10" s="26"/>
+      <c r="E10" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="J10" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="30"/>
-      <c r="E11" s="21" t="s">
+      <c r="C11" s="26"/>
+      <c r="E11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C12" s="30"/>
+      <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>18</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -6294,7 +7011,7 @@
       <c r="J12" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <v>1.5</v>
       </c>
       <c r="L12" s="4" t="s">
@@ -6302,11 +7019,11 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="30"/>
+      <c r="C13" s="26"/>
       <c r="E13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="11">
         <v>37.5</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -6315,7 +7032,7 @@
       <c r="J13" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <v>1.5</v>
       </c>
       <c r="L13" s="4" t="s">
@@ -6323,11 +7040,11 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="30"/>
+      <c r="C14" s="26"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="11">
         <v>37.65</v>
       </c>
       <c r="G14" s="4" t="s">
@@ -6336,7 +7053,7 @@
       <c r="J14" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <v>2.25</v>
       </c>
       <c r="L14" s="4" t="s">
@@ -6344,11 +7061,11 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="30"/>
+      <c r="C15" s="26"/>
       <c r="E15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="11">
         <v>45.15</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -6357,7 +7074,7 @@
       <c r="J15" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <v>3</v>
       </c>
       <c r="L15" s="4" t="s">
@@ -6365,11 +7082,11 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="30"/>
+      <c r="C16" s="26"/>
       <c r="E16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <v>54</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -6378,7 +7095,7 @@
       <c r="J16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <v>6</v>
       </c>
       <c r="L16" s="4" t="s">
@@ -6386,253 +7103,253 @@
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="30"/>
+      <c r="C17" s="26"/>
       <c r="E17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="11">
         <v>104.65</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>91</v>
       </c>
       <c r="J17" s="4"/>
-      <c r="K17" s="12"/>
+      <c r="K17" s="11"/>
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="30"/>
+      <c r="C18" s="26"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="12"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="30"/>
+      <c r="C19" s="26"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="12"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="30"/>
+      <c r="C20" s="26"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="12"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="30"/>
+      <c r="C21" s="26"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="12"/>
+      <c r="K21" s="11"/>
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="30"/>
+      <c r="C22" s="26"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="12"/>
+      <c r="K22" s="11"/>
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="30"/>
+      <c r="C23" s="26"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="11"/>
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="30"/>
+      <c r="C24" s="26"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="11"/>
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="30"/>
+      <c r="C25" s="26"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="12"/>
+      <c r="K25" s="11"/>
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="30"/>
+      <c r="C26" s="26"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="12"/>
+      <c r="K26" s="11"/>
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="30"/>
+      <c r="C27" s="26"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="12"/>
+      <c r="K27" s="11"/>
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="30"/>
+      <c r="C28" s="26"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="12"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="11"/>
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="30"/>
+      <c r="C29" s="26"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="12"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="12"/>
+      <c r="K29" s="11"/>
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="30"/>
+      <c r="C30" s="26"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="12"/>
+      <c r="K30" s="11"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="30"/>
+      <c r="C31" s="26"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="12"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="12"/>
+      <c r="K31" s="11"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="30"/>
+      <c r="C32" s="26"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="11"/>
       <c r="G32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="12"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="30"/>
+      <c r="C33" s="26"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="12"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="12"/>
+      <c r="K33" s="11"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="30"/>
+      <c r="C34" s="26"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11"/>
       <c r="G34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="12"/>
+      <c r="K34" s="11"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="30"/>
+      <c r="C35" s="26"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="12"/>
+      <c r="K35" s="11"/>
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="30"/>
+      <c r="C36" s="26"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="12"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="2"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="12"/>
+      <c r="K36" s="11"/>
       <c r="L36" s="2"/>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E37" s="2"/>
-      <c r="F37" s="12"/>
+      <c r="F37" s="11"/>
       <c r="G37" s="2"/>
       <c r="J37" s="2"/>
-      <c r="K37" s="12"/>
+      <c r="K37" s="11"/>
       <c r="L37" s="2"/>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E38" s="2"/>
-      <c r="F38" s="12"/>
+      <c r="F38" s="11"/>
       <c r="G38" s="2"/>
       <c r="J38" s="2"/>
-      <c r="K38" s="12"/>
+      <c r="K38" s="11"/>
       <c r="L38" s="2"/>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E39" s="2"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="12"/>
+      <c r="K39" s="11"/>
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E40" s="2"/>
-      <c r="F40" s="12"/>
+      <c r="F40" s="11"/>
       <c r="G40" s="2"/>
       <c r="J40" s="2"/>
-      <c r="K40" s="12"/>
+      <c r="K40" s="11"/>
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E41" s="2"/>
-      <c r="F41" s="12"/>
+      <c r="F41" s="11"/>
       <c r="G41" s="2"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="12"/>
+      <c r="K41" s="11"/>
       <c r="L41" s="2"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E42" s="2"/>
-      <c r="F42" s="12"/>
+      <c r="F42" s="11"/>
       <c r="G42" s="2"/>
       <c r="J42" s="2"/>
-      <c r="K42" s="12"/>
+      <c r="K42" s="11"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E43" s="2"/>
-      <c r="F43" s="12"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="2"/>
       <c r="J43" s="2"/>
-      <c r="K43" s="12"/>
+      <c r="K43" s="11"/>
       <c r="L43" s="2"/>
     </row>
     <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E44" s="3"/>
-      <c r="F44" s="13"/>
+      <c r="F44" s="12"/>
       <c r="G44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="13"/>
+      <c r="K44" s="12"/>
       <c r="L44" s="3"/>
     </row>
   </sheetData>

--- a/Game Stuff/Spreadsheet.xlsx
+++ b/Game Stuff/Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Nicos Blueprints_Riveteers District - Final\Game Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2E70E9-A7EE-4AF7-9F91-96A7B04A868D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2832CC62-93BC-4A84-A8F6-48ADB6E7CD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="-4944" windowWidth="17496" windowHeight="30216" firstSheet="11" activeTab="11" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Summary" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="156">
   <si>
     <t>Item</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>4.80 Hours</t>
+  </si>
+  <si>
+    <t>Alclcd Aluminum Sheet</t>
   </si>
 </sst>
 </file>
@@ -918,6 +921,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -930,14 +941,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1285,18 +1288,18 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="17" t="s">
@@ -1310,13 +1313,13 @@
       </c>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
-      <c r="H5" s="43" t="s">
+      <c r="H5" s="39" t="s">
         <v>0</v>
       </c>
       <c r="I5" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="40" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1330,13 +1333,13 @@
       <c r="E6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="41" t="s">
         <v>5</v>
       </c>
       <c r="I6" s="35">
         <v>15</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="42" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1522,7 +1525,7 @@
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C16" s="6" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D16" s="13">
         <v>246.666</v>
@@ -1541,9 +1544,15 @@
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C17" s="4"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="11">
+        <v>410</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="H17" s="6" t="s">
         <v>75</v>
       </c>
@@ -2057,17 +2066,17 @@
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="45"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -2114,14 +2123,14 @@
         <v>8</v>
       </c>
       <c r="M12" s="22"/>
-      <c r="O12" s="42" t="s">
+      <c r="O12" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="26"/>
@@ -2144,12 +2153,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="26"/>
@@ -2166,12 +2175,12 @@
         <v>25</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="26"/>
@@ -2188,12 +2197,12 @@
         <v>8</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="26"/>
@@ -2210,14 +2219,14 @@
         <v>122</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="O16" s="42" t="s">
+      <c r="O16" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="26"/>
@@ -2234,12 +2243,12 @@
         <v>122</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="26"/>
@@ -2250,12 +2259,12 @@
       <c r="K18" s="11"/>
       <c r="L18" s="4"/>
       <c r="M18" s="2"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="26"/>
@@ -2266,12 +2275,12 @@
       <c r="K19" s="11"/>
       <c r="L19" s="4"/>
       <c r="M19" s="2"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C20" s="26"/>
@@ -2608,16 +2617,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -3069,16 +3078,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -3217,9 +3226,15 @@
       <c r="G17" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="4"/>
+      <c r="J17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" s="11">
+        <v>410</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C18" s="26"/>
@@ -3488,16 +3503,16 @@
       <c r="D4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
-      <c r="K4" s="39" t="s">
+      <c r="G4" s="44"/>
+      <c r="H4" s="45"/>
+      <c r="K4" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="41"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="45"/>
     </row>
     <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="20" t="s">
@@ -3954,17 +3969,17 @@
     </row>
     <row r="12" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="13" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
-      <c r="K13" s="39" t="s">
+      <c r="G13" s="44"/>
+      <c r="H13" s="45"/>
+      <c r="K13" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="41"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="45"/>
     </row>
     <row r="14" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F14" s="17" t="s">
@@ -3988,13 +4003,13 @@
       <c r="N14" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="P14" s="42" t="s">
+      <c r="P14" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
     </row>
     <row r="15" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F15" s="4" t="s">
@@ -4016,11 +4031,11 @@
         <v>25</v>
       </c>
       <c r="N15" s="22"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
     </row>
     <row r="16" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F16" s="2" t="s">
@@ -4044,11 +4059,11 @@
       <c r="N16" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
     </row>
     <row r="17" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
@@ -4066,11 +4081,11 @@
       <c r="N17" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
     </row>
     <row r="18" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
@@ -4462,17 +4477,17 @@
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-      <c r="J11" s="39" t="s">
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
+      <c r="J11" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="41"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="45"/>
     </row>
     <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="26"/>
@@ -4497,14 +4512,14 @@
       <c r="M12" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="O12" s="42" t="s">
+      <c r="O12" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="26"/>
@@ -4527,12 +4542,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="22"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="26"/>
@@ -4557,12 +4572,12 @@
       <c r="M14" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="26"/>
@@ -4581,12 +4596,12 @@
       <c r="M15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="26"/>
@@ -4605,14 +4620,14 @@
       <c r="M16" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="O16" s="42" t="s">
+      <c r="O16" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="26"/>
@@ -4631,12 +4646,12 @@
       <c r="M17" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="26"/>
@@ -4647,12 +4662,12 @@
       <c r="K18" s="11"/>
       <c r="L18" s="6"/>
       <c r="M18" s="2"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="26"/>
@@ -4663,12 +4678,12 @@
       <c r="K19" s="11"/>
       <c r="L19" s="6"/>
       <c r="M19" s="2"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C20" s="26"/>
@@ -4679,14 +4694,14 @@
       <c r="K20" s="11"/>
       <c r="L20" s="6"/>
       <c r="M20" s="2"/>
-      <c r="O20" s="42" t="s">
+      <c r="O20" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="42"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="46"/>
+      <c r="T20" s="46"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C21" s="26"/>
@@ -4697,12 +4712,12 @@
       <c r="K21" s="11"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="42"/>
-      <c r="R21" s="42"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="42"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="46"/>
+      <c r="T21" s="46"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="26"/>
@@ -4713,12 +4728,12 @@
       <c r="K22" s="11"/>
       <c r="L22" s="6"/>
       <c r="M22" s="2"/>
-      <c r="O22" s="42"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="42"/>
+      <c r="O22" s="46"/>
+      <c r="P22" s="46"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="46"/>
+      <c r="T22" s="46"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C23" s="26"/>
@@ -4729,12 +4744,12 @@
       <c r="K23" s="11"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="42"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="42"/>
+      <c r="O23" s="46"/>
+      <c r="P23" s="46"/>
+      <c r="Q23" s="46"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="46"/>
+      <c r="T23" s="46"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="26"/>
@@ -5044,16 +5059,16 @@
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-      <c r="J11" s="39" t="s">
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
+      <c r="J11" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="40"/>
-      <c r="L11" s="41"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="45"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="26"/>
@@ -5426,16 +5441,16 @@
       <c r="C2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="J2" s="39" t="s">
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
+      <c r="J2" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="45"/>
     </row>
     <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="24" t="s">
@@ -5462,14 +5477,14 @@
       <c r="L3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B4" s="24" t="s">
@@ -5496,12 +5511,12 @@
       <c r="L4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B5" s="24" t="s">
@@ -5528,12 +5543,12 @@
       <c r="L5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B6" s="24" t="s">
@@ -5548,12 +5563,12 @@
       <c r="J6" s="4"/>
       <c r="K6" s="11"/>
       <c r="L6" s="2"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="46"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B7" s="24" t="s">
@@ -5932,16 +5947,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -6493,16 +6508,16 @@
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -6965,16 +6980,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>

--- a/Game Stuff/Spreadsheet.xlsx
+++ b/Game Stuff/Spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Nicos Blueprints_Riveteers District - Final\Game Stuff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Nicos Blueprints_Trains\Game Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2E70E9-A7EE-4AF7-9F91-96A7B04A868D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7822684-F23A-4D8D-A970-8ADD0544EEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="-4944" windowWidth="17496" windowHeight="30216" firstSheet="11" activeTab="11" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
+    <workbookView xWindow="45972" yWindow="-4944" windowWidth="17496" windowHeight="30216" firstSheet="2" activeTab="3" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Summary" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="157">
   <si>
     <t>Item</t>
   </si>
@@ -202,15 +202,6 @@
     <t>Oran-Rief Mines</t>
   </si>
   <si>
-    <t>803.3 MW</t>
-  </si>
-  <si>
-    <t>-803.3 MW</t>
-  </si>
-  <si>
-    <t>2.74 Hours</t>
-  </si>
-  <si>
     <t>2200 MWh</t>
   </si>
   <si>
@@ -334,18 +325,9 @@
     <t>Raw Quartz</t>
   </si>
   <si>
-    <t>1016.2 MW</t>
-  </si>
-  <si>
-    <t>-1016.2 MW</t>
-  </si>
-  <si>
     <t>4300 Wh</t>
   </si>
   <si>
-    <t>4.23 Hours</t>
-  </si>
-  <si>
     <t>Ghirapur Gridworks</t>
   </si>
   <si>
@@ -469,9 +451,6 @@
     <t>63.39 Hours</t>
   </si>
   <si>
-    <t>Bottom Right going to Riveteers District has an extra 233.33 Copper Ingots</t>
-  </si>
-  <si>
     <t>Riverteers District</t>
   </si>
   <si>
@@ -512,6 +491,33 @@
   </si>
   <si>
     <t>4.80 Hours</t>
+  </si>
+  <si>
+    <t>1011.1 MW</t>
+  </si>
+  <si>
+    <t>-1011.1 MW</t>
+  </si>
+  <si>
+    <t>2.17 Hours</t>
+  </si>
+  <si>
+    <t>Alclad Aluminum Sheet</t>
+  </si>
+  <si>
+    <t>1108 MW</t>
+  </si>
+  <si>
+    <t>-1108 MW</t>
+  </si>
+  <si>
+    <t>3.88 Hours</t>
+  </si>
+  <si>
+    <t>On the desert</t>
+  </si>
+  <si>
+    <t>Top belt going to Riveteers district has an extra 533.33 Copper</t>
   </si>
 </sst>
 </file>
@@ -842,7 +848,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -918,6 +924,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -930,14 +944,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1285,18 +1294,18 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="17" t="s">
@@ -1310,13 +1319,13 @@
       </c>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
-      <c r="H5" s="43" t="s">
+      <c r="H5" s="39" t="s">
         <v>0</v>
       </c>
       <c r="I5" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="40" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1330,13 +1339,13 @@
       <c r="E6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="41" t="s">
         <v>5</v>
       </c>
       <c r="I6" s="35">
         <v>15</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="42" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1371,13 +1380,13 @@
         <v>42</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I8" s="13">
         <v>1.4065000000000001</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.35">
@@ -1391,113 +1400,113 @@
         <v>44</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I9" s="13">
         <v>2.25</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C10" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D10" s="11">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>50</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I10" s="13">
         <v>2.5</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" s="11">
         <v>1140</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I11" s="13">
         <v>45</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C12" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D12" s="11">
-        <v>669.33299999999997</v>
+        <v>759.75</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I12" s="13">
         <v>5</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C13" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D13" s="11">
         <v>635.40554999999995</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I13" s="13">
         <v>7.3125</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C14" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D14" s="11">
         <v>467.5</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I14" s="13">
         <v>3</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.35">
@@ -1508,50 +1517,56 @@
         <v>348</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I15" s="13">
         <v>30</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C16" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D16" s="13">
         <v>246.666</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I16" s="13">
         <v>0.5</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C17" s="4"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="11">
+        <v>410</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="H17" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I17" s="13">
         <v>33.125</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.35">
@@ -1559,13 +1574,13 @@
       <c r="D18" s="11"/>
       <c r="E18" s="2"/>
       <c r="H18" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I18" s="13">
         <v>61.6875</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.35">
@@ -1573,13 +1588,13 @@
       <c r="D19" s="11"/>
       <c r="E19" s="2"/>
       <c r="H19" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I19" s="13">
         <v>7.25</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.35">
@@ -1587,13 +1602,13 @@
       <c r="D20" s="11"/>
       <c r="E20" s="2"/>
       <c r="H20" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I20" s="13">
         <v>30</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.35">
@@ -1601,13 +1616,13 @@
       <c r="D21" s="11"/>
       <c r="E21" s="2"/>
       <c r="H21" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I21" s="13">
         <v>45</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.35">
@@ -1615,13 +1630,13 @@
       <c r="D22" s="11"/>
       <c r="E22" s="2"/>
       <c r="H22" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I22" s="13">
         <v>22.5</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.35">
@@ -1629,13 +1644,13 @@
       <c r="D23" s="11"/>
       <c r="E23" s="2"/>
       <c r="H23" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I23" s="13">
         <v>20.5</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.35">
@@ -1643,13 +1658,13 @@
       <c r="D24" s="11"/>
       <c r="E24" s="2"/>
       <c r="H24" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I24" s="13">
         <v>15</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.35">
@@ -1657,13 +1672,13 @@
       <c r="D25" s="11"/>
       <c r="E25" s="2"/>
       <c r="H25" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I25" s="13">
         <v>25</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.35">
@@ -1671,13 +1686,13 @@
       <c r="D26" s="11"/>
       <c r="E26" s="2"/>
       <c r="H26" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I26" s="13">
-        <v>23.332999999999998</v>
+        <v>26.25</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="3:10" x14ac:dyDescent="0.35">
@@ -1685,13 +1700,13 @@
       <c r="D27" s="11"/>
       <c r="E27" s="2"/>
       <c r="H27" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I27" s="13">
         <v>19.443999999999999</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="3:10" x14ac:dyDescent="0.35">
@@ -1699,13 +1714,13 @@
       <c r="D28" s="11"/>
       <c r="E28" s="2"/>
       <c r="H28" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I28" s="13">
         <v>1.5</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.35">
@@ -1713,13 +1728,13 @@
       <c r="D29" s="11"/>
       <c r="E29" s="2"/>
       <c r="H29" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I29" s="13">
         <v>1.5</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="3:10" x14ac:dyDescent="0.35">
@@ -1727,13 +1742,13 @@
       <c r="D30" s="11"/>
       <c r="E30" s="2"/>
       <c r="H30" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I30" s="13">
         <v>2.25</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.35">
@@ -1741,13 +1756,13 @@
       <c r="D31" s="11"/>
       <c r="E31" s="2"/>
       <c r="H31" s="6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="I31" s="13">
         <v>3</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.35">
@@ -1755,13 +1770,13 @@
       <c r="D32" s="11"/>
       <c r="E32" s="2"/>
       <c r="H32" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I32" s="13">
         <v>6</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.35">
@@ -1769,13 +1784,13 @@
       <c r="D33" s="11"/>
       <c r="E33" s="2"/>
       <c r="H33" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I33" s="13">
         <v>25</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.35">
@@ -1783,13 +1798,13 @@
       <c r="D34" s="11"/>
       <c r="E34" s="2"/>
       <c r="H34" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I34" s="13">
         <v>20</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.35">
@@ -1797,13 +1812,13 @@
       <c r="D35" s="11"/>
       <c r="E35" s="2"/>
       <c r="H35" s="6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I35" s="13">
         <v>0.5</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.35">
@@ -1811,13 +1826,13 @@
       <c r="D36" s="11"/>
       <c r="E36" s="2"/>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I36" s="13">
         <v>0.5</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="3:10" x14ac:dyDescent="0.35">
@@ -1825,13 +1840,13 @@
       <c r="D37" s="11"/>
       <c r="E37" s="2"/>
       <c r="H37" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="I37" s="13">
         <v>49.332999999999998</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1839,35 +1854,35 @@
       <c r="D38" s="12"/>
       <c r="E38" s="3"/>
       <c r="H38" s="6" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="I38" s="13">
         <v>12</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H39" s="6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I39" s="13">
         <v>200</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H40" s="6" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I40" s="13">
         <v>222</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="3:10" x14ac:dyDescent="0.35">
@@ -1996,7 +2011,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.35">
@@ -2028,7 +2043,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
@@ -2036,7 +2051,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
@@ -2052,22 +2067,22 @@
         <v>32</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="45"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -2090,13 +2105,13 @@
         <v>24</v>
       </c>
       <c r="M11" s="38" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F12" s="10">
         <v>300</v>
@@ -2105,7 +2120,7 @@
         <v>23</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K12" s="10">
         <v>25</v>
@@ -2114,14 +2129,14 @@
         <v>8</v>
       </c>
       <c r="M12" s="22"/>
-      <c r="O12" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
+      <c r="O12" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="26"/>
@@ -2135,7 +2150,7 @@
         <v>19</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K13" s="11">
         <v>467.5</v>
@@ -2144,12 +2159,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="26"/>
@@ -2166,12 +2181,12 @@
         <v>25</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="26"/>
@@ -2179,7 +2194,7 @@
       <c r="F15" s="11"/>
       <c r="G15" s="2"/>
       <c r="J15" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="K15" s="11">
         <v>20</v>
@@ -2188,12 +2203,12 @@
         <v>8</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="26"/>
@@ -2201,23 +2216,23 @@
       <c r="F16" s="11"/>
       <c r="G16" s="2"/>
       <c r="J16" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K16" s="11">
         <v>7.5</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="O16" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
+      <c r="O16" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="26"/>
@@ -2231,15 +2246,15 @@
         <v>42</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="26"/>
@@ -2250,12 +2265,12 @@
       <c r="K18" s="11"/>
       <c r="L18" s="4"/>
       <c r="M18" s="2"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="26"/>
@@ -2266,12 +2281,12 @@
       <c r="K19" s="11"/>
       <c r="L19" s="4"/>
       <c r="M19" s="2"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C20" s="26"/>
@@ -2547,7 +2562,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="87" x14ac:dyDescent="0.35">
@@ -2555,7 +2570,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
@@ -2579,7 +2594,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -2587,7 +2602,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -2595,7 +2610,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2603,21 +2618,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -2643,16 +2658,16 @@
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F12" s="10">
         <v>18.75</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K12" s="10">
         <v>0.5</v>
@@ -2670,10 +2685,10 @@
         <v>28.625</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K13" s="11">
         <v>0.5</v>
@@ -2721,7 +2736,7 @@
         <v>42</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="11"/>
@@ -2730,13 +2745,13 @@
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C17" s="26"/>
       <c r="E17" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F17" s="11">
         <v>7.5</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="11"/>
@@ -3008,7 +3023,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
@@ -3040,7 +3055,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -3048,7 +3063,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -3056,7 +3071,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3064,21 +3079,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -3104,16 +3119,16 @@
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F12" s="10">
         <v>600</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K12" s="10">
         <v>49.332999999999998</v>
@@ -3125,16 +3140,16 @@
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C13" s="26"/>
       <c r="E13" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F13" s="11">
         <v>1000</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K13" s="11">
         <v>246.666</v>
@@ -3152,10 +3167,10 @@
         <v>400</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="K14" s="11">
         <v>12</v>
@@ -3173,10 +3188,10 @@
         <v>200</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K15" s="11">
         <v>200</v>
@@ -3194,10 +3209,10 @@
         <v>240</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="K16" s="11">
         <v>222</v>
@@ -3215,11 +3230,17 @@
         <v>246.67</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="4"/>
+        <v>139</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K17" s="11">
+        <v>410</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C18" s="26"/>
@@ -3488,16 +3509,16 @@
       <c r="D4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
-      <c r="K4" s="39" t="s">
+      <c r="G4" s="44"/>
+      <c r="H4" s="45"/>
+      <c r="K4" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="41"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="45"/>
     </row>
     <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="20" t="s">
@@ -3909,7 +3930,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="3:20" x14ac:dyDescent="0.35">
@@ -3954,17 +3975,17 @@
     </row>
     <row r="12" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="13" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
-      <c r="K13" s="39" t="s">
+      <c r="G13" s="44"/>
+      <c r="H13" s="45"/>
+      <c r="K13" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="41"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="45"/>
     </row>
     <row r="14" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F14" s="17" t="s">
@@ -3986,15 +4007,15 @@
         <v>24</v>
       </c>
       <c r="N14" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="P14" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
+        <v>117</v>
+      </c>
+      <c r="P14" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
     </row>
     <row r="15" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F15" s="4" t="s">
@@ -4016,11 +4037,11 @@
         <v>25</v>
       </c>
       <c r="N15" s="22"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
     </row>
     <row r="16" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F16" s="2" t="s">
@@ -4039,16 +4060,16 @@
         <v>960</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
+        <v>122</v>
+      </c>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
     </row>
     <row r="17" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
@@ -4061,16 +4082,16 @@
         <v>111.25</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+        <v>121</v>
+      </c>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
     </row>
     <row r="18" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
@@ -4083,10 +4104,10 @@
         <v>37.5</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="6:20" x14ac:dyDescent="0.35">
@@ -4094,16 +4115,16 @@
       <c r="G19" s="11"/>
       <c r="H19" s="2"/>
       <c r="K19" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="L19" s="11">
         <v>234.25</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="6:20" x14ac:dyDescent="0.35">
@@ -4414,7 +4435,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
@@ -4462,17 +4483,17 @@
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-      <c r="J11" s="39" t="s">
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
+      <c r="J11" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="41"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="45"/>
     </row>
     <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="26"/>
@@ -4495,16 +4516,16 @@
         <v>24</v>
       </c>
       <c r="M12" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="O12" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
+        <v>117</v>
+      </c>
+      <c r="O12" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="26"/>
@@ -4527,12 +4548,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="22"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="26"/>
@@ -4552,17 +4573,17 @@
         <v>142.5</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
+        <v>119</v>
+      </c>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="26"/>
@@ -4576,17 +4597,17 @@
         <v>104.65</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
+        <v>119</v>
+      </c>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="26"/>
@@ -4600,19 +4621,19 @@
         <v>113.833</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="O16" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
+        <v>118</v>
+      </c>
+      <c r="O16" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="26"/>
@@ -4626,17 +4647,17 @@
         <v>246.67</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+        <v>135</v>
+      </c>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="26"/>
@@ -4647,12 +4668,12 @@
       <c r="K18" s="11"/>
       <c r="L18" s="6"/>
       <c r="M18" s="2"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="26"/>
@@ -4663,14 +4684,14 @@
       <c r="K19" s="11"/>
       <c r="L19" s="6"/>
       <c r="M19" s="2"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
+    </row>
+    <row r="20" spans="3:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="26"/>
       <c r="E20" s="2"/>
       <c r="F20" s="11"/>
@@ -4679,14 +4700,6 @@
       <c r="K20" s="11"/>
       <c r="L20" s="6"/>
       <c r="M20" s="2"/>
-      <c r="O20" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="42"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C21" s="26"/>
@@ -4697,12 +4710,14 @@
       <c r="K21" s="11"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="42"/>
-      <c r="R21" s="42"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="42"/>
+      <c r="O21" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="P21" s="47"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="26"/>
@@ -4713,12 +4728,6 @@
       <c r="K22" s="11"/>
       <c r="L22" s="6"/>
       <c r="M22" s="2"/>
-      <c r="O22" s="42"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="42"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C23" s="26"/>
@@ -4729,12 +4738,14 @@
       <c r="K23" s="11"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="42"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="42"/>
+      <c r="O23" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="P23" s="46"/>
+      <c r="Q23" s="46"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="46"/>
+      <c r="T23" s="46"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="26"/>
@@ -4745,6 +4756,12 @@
       <c r="K24" s="11"/>
       <c r="L24" s="6"/>
       <c r="M24" s="2"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="46"/>
+      <c r="Q24" s="46"/>
+      <c r="R24" s="46"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C25" s="26"/>
@@ -4755,6 +4772,12 @@
       <c r="K25" s="11"/>
       <c r="L25" s="6"/>
       <c r="M25" s="2"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="46"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="46"/>
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="26"/>
@@ -4765,6 +4788,12 @@
       <c r="K26" s="11"/>
       <c r="L26" s="6"/>
       <c r="M26" s="2"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C27" s="26"/>
@@ -4948,12 +4977,13 @@
       <c r="M45" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="O12:T15"/>
     <mergeCell ref="O16:T19"/>
     <mergeCell ref="J11:M11"/>
-    <mergeCell ref="O20:T23"/>
+    <mergeCell ref="O23:T26"/>
+    <mergeCell ref="O21:T21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4996,7 +5026,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -5012,7 +5042,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -5020,7 +5050,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -5028,7 +5058,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5036,7 +5066,7 @@
         <v>32</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5044,16 +5074,16 @@
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-      <c r="J11" s="39" t="s">
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
+      <c r="J11" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="40"/>
-      <c r="L11" s="41"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="45"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="26"/>
@@ -5079,19 +5109,19 @@
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C13" s="26"/>
       <c r="E13" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F13" s="10">
-        <v>480</v>
+        <v>576</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K13" s="10">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>25</v>
@@ -5103,19 +5133,19 @@
         <v>19</v>
       </c>
       <c r="F14" s="11">
-        <v>480</v>
+        <v>576</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>22</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K14" s="11">
         <v>18</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
@@ -5124,13 +5154,13 @@
       <c r="F15" s="11"/>
       <c r="G15" s="2"/>
       <c r="J15" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K15" s="11">
         <v>18</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
@@ -5424,18 +5454,18 @@
         <v>9</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="J2" s="39" t="s">
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
+      <c r="J2" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="45"/>
     </row>
     <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="24" t="s">
@@ -5462,21 +5492,21 @@
       <c r="L3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
+      <c r="N3" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>41</v>
@@ -5488,7 +5518,7 @@
         <v>33</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K4" s="10">
         <v>1140</v>
@@ -5496,12 +5526,12 @@
       <c r="L4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B5" s="24" t="s">
@@ -5517,30 +5547,30 @@
         <v>960</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K5" s="11">
         <v>300</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
+        <v>81</v>
+      </c>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B6" s="24" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="11"/>
@@ -5548,19 +5578,19 @@
       <c r="J6" s="4"/>
       <c r="K6" s="11"/>
       <c r="L6" s="2"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="46"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B7" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="11"/>
@@ -5574,7 +5604,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="11"/>
@@ -5588,7 +5618,7 @@
         <v>32</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="11"/>
@@ -5871,7 +5901,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="46" customHeight="1" x14ac:dyDescent="0.35">
@@ -5879,7 +5909,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
@@ -5903,7 +5933,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -5911,7 +5941,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -5919,7 +5949,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5927,21 +5957,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -5967,16 +5997,16 @@
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F12" s="10">
         <v>480</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K12" s="10">
         <v>61.6875</v>
@@ -5994,10 +6024,10 @@
         <v>422.5</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K13" s="11">
         <v>45</v>
@@ -6009,16 +6039,16 @@
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C14" s="26"/>
       <c r="E14" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F14" s="11">
         <v>300</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K14" s="11">
         <v>45</v>
@@ -6039,7 +6069,7 @@
         <v>44</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K15" s="11">
         <v>33.125</v>
@@ -6060,7 +6090,7 @@
         <v>42</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K16" s="11">
         <v>30</v>
@@ -6072,7 +6102,7 @@
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C17" s="26"/>
       <c r="E17" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F17" s="11">
         <v>18</v>
@@ -6081,7 +6111,7 @@
         <v>50</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K17" s="11">
         <v>30</v>
@@ -6096,7 +6126,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K18" s="11">
         <v>25</v>
@@ -6111,7 +6141,7 @@
       <c r="F19" s="11"/>
       <c r="G19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K19" s="11">
         <v>22.5</v>
@@ -6126,7 +6156,7 @@
       <c r="F20" s="11"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K20" s="11">
         <v>20.5</v>
@@ -6141,7 +6171,7 @@
       <c r="F21" s="11"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K21" s="11">
         <v>15</v>
@@ -6156,7 +6186,7 @@
       <c r="F22" s="11"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K22" s="11">
         <v>7.3125</v>
@@ -6171,7 +6201,7 @@
       <c r="F23" s="11"/>
       <c r="G23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K23" s="11">
         <v>7.25</v>
@@ -6186,7 +6216,7 @@
       <c r="F24" s="11"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K24" s="11">
         <v>5</v>
@@ -6201,7 +6231,7 @@
       <c r="F25" s="11"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K25" s="11">
         <v>3</v>
@@ -6216,7 +6246,7 @@
       <c r="F26" s="11"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K26" s="11">
         <v>2.5</v>
@@ -6231,7 +6261,7 @@
       <c r="F27" s="11"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K27" s="11">
         <v>2.25</v>
@@ -6246,7 +6276,7 @@
       <c r="F28" s="11"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K28" s="11">
         <v>1.4065000000000001</v>
@@ -6261,7 +6291,7 @@
       <c r="F29" s="11"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K29" s="11">
         <v>0.5</v>
@@ -6432,7 +6462,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.35">
@@ -6448,7 +6478,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.35">
@@ -6464,7 +6494,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
@@ -6472,7 +6502,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
@@ -6480,7 +6510,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6488,21 +6518,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -6525,46 +6555,46 @@
         <v>24</v>
       </c>
       <c r="P11" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F12" s="10">
-        <v>1260</v>
+        <v>1380</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K12" s="10">
-        <v>23.332999999999998</v>
+        <v>26.25</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="P12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C13" s="26"/>
       <c r="E13" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F13" s="11">
         <v>500</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K13" s="11">
         <v>19.443999999999999</v>
@@ -6579,16 +6609,16 @@
         <v>19</v>
       </c>
       <c r="F14" s="11">
-        <v>533.33299999999997</v>
+        <v>600</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K14" s="11">
-        <v>669.33299999999997</v>
+        <v>759.75</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>25</v>
@@ -6600,7 +6630,7 @@
       <c r="F15" s="11"/>
       <c r="G15" s="2"/>
       <c r="J15" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K15" s="11">
         <v>635.40554999999995</v>
@@ -6615,13 +6645,13 @@
       <c r="F16" s="11"/>
       <c r="G16" s="2"/>
       <c r="J16" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K16" s="11">
         <v>54</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
@@ -6630,13 +6660,13 @@
       <c r="F17" s="11"/>
       <c r="G17" s="2"/>
       <c r="J17" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K17" s="11">
         <v>45.15</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
@@ -6904,7 +6934,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
@@ -6936,7 +6966,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -6944,7 +6974,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -6952,7 +6982,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6960,21 +6990,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="26"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="J10" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="26"/>
@@ -7000,7 +7030,7 @@
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C12" s="26"/>
       <c r="E12" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F12" s="10">
         <v>18</v>
@@ -7009,7 +7039,7 @@
         <v>50</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K12" s="10">
         <v>1.5</v>
@@ -7030,7 +7060,7 @@
         <v>33</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="K13" s="11">
         <v>1.5</v>
@@ -7048,10 +7078,10 @@
         <v>37.65</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K14" s="11">
         <v>2.25</v>
@@ -7063,16 +7093,16 @@
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C15" s="26"/>
       <c r="E15" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F15" s="11">
         <v>45.15</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="K15" s="11">
         <v>3</v>
@@ -7084,16 +7114,16 @@
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C16" s="26"/>
       <c r="E16" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F16" s="11">
         <v>54</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="K16" s="11">
         <v>6</v>
@@ -7111,7 +7141,7 @@
         <v>104.65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="11"/>

--- a/Game Stuff/Spreadsheet.xlsx
+++ b/Game Stuff/Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Nicos Blueprints_Phyrexian Datavault\Game Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE4B23D-EA0A-4594-9859-6DBA38760E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15F8E50-39B7-4FEC-916E-ACB1662AFF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="11" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Summary" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="176">
   <si>
     <t>Item</t>
   </si>
@@ -573,6 +573,9 @@
   </si>
   <si>
     <t>1.76 Hours</t>
+  </si>
+  <si>
+    <t>Empty Fluid Tank</t>
   </si>
 </sst>
 </file>
@@ -864,7 +867,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -944,6 +947,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -959,11 +968,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1312,18 +1318,18 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="15" t="s">
@@ -1886,7 +1892,7 @@
         <v>140</v>
       </c>
       <c r="I39" s="11">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>134</v>
@@ -1904,7 +1910,7 @@
       </c>
     </row>
     <row r="41" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="46" t="s">
         <v>169</v>
       </c>
       <c r="I41" s="11">
@@ -1915,7 +1921,7 @@
       </c>
     </row>
     <row r="42" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H42" s="11" t="s">
+      <c r="H42" s="46" t="s">
         <v>170</v>
       </c>
       <c r="I42" s="11">
@@ -1926,9 +1932,15 @@
       </c>
     </row>
     <row r="43" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H43" s="2"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="2"/>
+      <c r="H43" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I43" s="11">
+        <v>5</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="44" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H44" s="2"/>
@@ -2056,7 +2068,7 @@
       <c r="B4" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="39" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2102,17 +2114,17 @@
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="24"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="J10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="43"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="24"/>
@@ -2159,14 +2171,14 @@
         <v>8</v>
       </c>
       <c r="M12" s="20"/>
-      <c r="O12" s="42" t="s">
+      <c r="O12" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="24"/>
@@ -2189,12 +2201,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="24"/>
@@ -2211,12 +2223,12 @@
         <v>25</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="24"/>
@@ -2233,12 +2245,12 @@
         <v>8</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="24"/>
@@ -2255,14 +2267,14 @@
         <v>114</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="O16" s="42" t="s">
+      <c r="O16" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="24"/>
@@ -2279,12 +2291,12 @@
         <v>114</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="44"/>
+      <c r="T17" s="44"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="24"/>
@@ -2301,12 +2313,12 @@
         <v>154</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="44"/>
+      <c r="T18" s="44"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="24"/>
@@ -2323,12 +2335,12 @@
         <v>154</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="44"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C20" s="24"/>
@@ -2349,14 +2361,14 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="43" t="s">
+      <c r="O21" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="43"/>
-      <c r="S21" s="43"/>
-      <c r="T21" s="43"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="45"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="24"/>
@@ -2377,14 +2389,14 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="42" t="s">
+      <c r="O23" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="42"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="24"/>
@@ -2395,12 +2407,12 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
-      <c r="S24" s="42"/>
-      <c r="T24" s="42"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="44"/>
+      <c r="S24" s="44"/>
+      <c r="T24" s="44"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C25" s="24"/>
@@ -2411,12 +2423,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="42"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="42"/>
-      <c r="S25" s="42"/>
-      <c r="T25" s="42"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
+      <c r="S25" s="44"/>
+      <c r="T25" s="44"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="24"/>
@@ -2427,12 +2439,12 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="42"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C27" s="24"/>
@@ -2443,14 +2455,14 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="42" t="s">
+      <c r="O27" s="44" t="s">
         <v>157</v>
       </c>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="42"/>
-      <c r="S27" s="42"/>
-      <c r="T27" s="42"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="44"/>
+      <c r="T27" s="44"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C28" s="24"/>
@@ -2461,12 +2473,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="42"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="44"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="44"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C29" s="24"/>
@@ -2477,12 +2489,12 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="42"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="44"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C30" s="24"/>
@@ -2493,12 +2505,12 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="42"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C31" s="24"/>
@@ -2728,16 +2740,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="24"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="J10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="24"/>
@@ -3189,16 +3201,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="24"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="J10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="24"/>
@@ -3299,7 +3311,7 @@
         <v>140</v>
       </c>
       <c r="K15" s="9">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>8</v>
@@ -3367,9 +3379,15 @@
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="4"/>
+      <c r="J19" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="K19" s="9">
+        <v>5</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C20" s="24"/>
@@ -3679,16 +3697,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="24"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="J10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="24"/>
@@ -3722,7 +3740,7 @@
       <c r="G12" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="J12" s="45">
+      <c r="J12" s="40">
         <v>10</v>
       </c>
       <c r="K12" s="8" t="s">
@@ -3743,7 +3761,7 @@
       <c r="G13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J13" s="45">
+      <c r="J13" s="40">
         <v>10</v>
       </c>
       <c r="K13" s="9" t="s">
@@ -3764,7 +3782,7 @@
       <c r="G14" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J14" s="45"/>
+      <c r="J14" s="40"/>
       <c r="K14" s="9"/>
       <c r="L14" s="4"/>
     </row>
@@ -3779,7 +3797,7 @@
       <c r="G15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J15" s="45"/>
+      <c r="J15" s="40"/>
       <c r="K15" s="9"/>
       <c r="L15" s="4"/>
     </row>
@@ -3794,7 +3812,7 @@
       <c r="G16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="45"/>
+      <c r="J16" s="40"/>
       <c r="K16" s="9"/>
       <c r="L16" s="4"/>
     </row>
@@ -3809,7 +3827,7 @@
       <c r="G17" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J17" s="45"/>
+      <c r="J17" s="40"/>
       <c r="K17" s="9"/>
       <c r="L17" s="4"/>
     </row>
@@ -3824,7 +3842,7 @@
       <c r="G18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="45"/>
+      <c r="J18" s="40"/>
       <c r="K18" s="9"/>
       <c r="L18" s="4"/>
     </row>
@@ -4092,16 +4110,16 @@
       <c r="D4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
-      <c r="K4" s="39" t="s">
+      <c r="G4" s="42"/>
+      <c r="H4" s="43"/>
+      <c r="K4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="41"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="43"/>
     </row>
     <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="18" t="s">
@@ -4558,17 +4576,17 @@
     </row>
     <row r="12" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="13" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
-      <c r="K13" s="39" t="s">
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
+      <c r="K13" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="41"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="43"/>
     </row>
     <row r="14" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F14" s="15" t="s">
@@ -4592,13 +4610,13 @@
       <c r="N14" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="P14" s="42" t="s">
+      <c r="P14" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44"/>
     </row>
     <row r="15" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F15" s="4" t="s">
@@ -4620,11 +4638,11 @@
         <v>25</v>
       </c>
       <c r="N15" s="20"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
     </row>
     <row r="16" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F16" s="2" t="s">
@@ -4648,11 +4666,11 @@
       <c r="N16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
     </row>
     <row r="17" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
@@ -4670,11 +4688,11 @@
       <c r="N17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="44"/>
+      <c r="T17" s="44"/>
     </row>
     <row r="18" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
@@ -5064,16 +5082,16 @@
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="24"/>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-      <c r="J11" s="39" t="s">
+      <c r="F11" s="42"/>
+      <c r="G11" s="43"/>
+      <c r="J11" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="40"/>
-      <c r="L11" s="41"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="43"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="24"/>
@@ -5517,17 +5535,17 @@
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="24"/>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-      <c r="J11" s="39" t="s">
+      <c r="F11" s="42"/>
+      <c r="G11" s="43"/>
+      <c r="J11" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="41"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="43"/>
     </row>
     <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="24"/>
@@ -5552,14 +5570,14 @@
       <c r="M12" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="O12" s="42" t="s">
+      <c r="O12" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="24"/>
@@ -5583,12 +5601,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="20"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="24"/>
@@ -5613,12 +5631,12 @@
       <c r="M14" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="44"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="24"/>
@@ -5637,12 +5655,12 @@
       <c r="M15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="24"/>
@@ -5661,14 +5679,14 @@
       <c r="M16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="O16" s="42" t="s">
+      <c r="O16" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="24"/>
@@ -5687,12 +5705,12 @@
       <c r="M17" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="44"/>
+      <c r="T17" s="44"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="24"/>
@@ -5709,12 +5727,12 @@
         <v>154</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="44"/>
+      <c r="T18" s="44"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="24"/>
@@ -5725,12 +5743,12 @@
       <c r="K19" s="9"/>
       <c r="L19" s="6"/>
       <c r="M19" s="2"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="44"/>
     </row>
     <row r="20" spans="3:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="24"/>
@@ -5751,14 +5769,14 @@
       <c r="K21" s="9"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="43" t="s">
+      <c r="O21" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="43"/>
-      <c r="S21" s="43"/>
-      <c r="T21" s="43"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="45"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="24"/>
@@ -5779,14 +5797,14 @@
       <c r="K23" s="9"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="42" t="s">
+      <c r="O23" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="42"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="24"/>
@@ -5797,12 +5815,12 @@
       <c r="K24" s="9"/>
       <c r="L24" s="6"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
-      <c r="S24" s="42"/>
-      <c r="T24" s="42"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="44"/>
+      <c r="S24" s="44"/>
+      <c r="T24" s="44"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C25" s="24"/>
@@ -5813,12 +5831,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="6"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="42"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="42"/>
-      <c r="S25" s="42"/>
-      <c r="T25" s="42"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
+      <c r="S25" s="44"/>
+      <c r="T25" s="44"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="24"/>
@@ -5829,12 +5847,12 @@
       <c r="K26" s="9"/>
       <c r="L26" s="6"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="42"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
+      <c r="T26" s="44"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C27" s="24"/>
@@ -5845,14 +5863,14 @@
       <c r="K27" s="9"/>
       <c r="L27" s="6"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="42" t="s">
+      <c r="O27" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="42"/>
-      <c r="S27" s="42"/>
-      <c r="T27" s="42"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="44"/>
+      <c r="T27" s="44"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C28" s="24"/>
@@ -5863,12 +5881,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="6"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="42"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="44"/>
+      <c r="S28" s="44"/>
+      <c r="T28" s="44"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C29" s="24"/>
@@ -5879,12 +5897,12 @@
       <c r="K29" s="9"/>
       <c r="L29" s="6"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="42"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="44"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C30" s="24"/>
@@ -5895,12 +5913,12 @@
       <c r="K30" s="9"/>
       <c r="L30" s="6"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="42"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C31" s="24"/>
@@ -5911,14 +5929,14 @@
       <c r="K31" s="9"/>
       <c r="L31" s="6"/>
       <c r="M31" s="2"/>
-      <c r="O31" s="42" t="s">
+      <c r="O31" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="42"/>
-      <c r="S31" s="42"/>
-      <c r="T31" s="42"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
+      <c r="T31" s="44"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C32" s="24"/>
@@ -5929,12 +5947,12 @@
       <c r="K32" s="9"/>
       <c r="L32" s="6"/>
       <c r="M32" s="2"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="42"/>
-      <c r="S32" s="42"/>
-      <c r="T32" s="42"/>
+      <c r="O32" s="44"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="44"/>
+      <c r="S32" s="44"/>
+      <c r="T32" s="44"/>
     </row>
     <row r="33" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C33" s="24"/>
@@ -5945,12 +5963,12 @@
       <c r="K33" s="9"/>
       <c r="L33" s="6"/>
       <c r="M33" s="2"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="42"/>
-      <c r="S33" s="42"/>
-      <c r="T33" s="42"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="44"/>
+      <c r="S33" s="44"/>
+      <c r="T33" s="44"/>
     </row>
     <row r="34" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C34" s="24"/>
@@ -5961,12 +5979,12 @@
       <c r="K34" s="9"/>
       <c r="L34" s="6"/>
       <c r="M34" s="2"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="42"/>
-      <c r="S34" s="42"/>
-      <c r="T34" s="42"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="44"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="44"/>
     </row>
     <row r="35" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C35" s="24"/>
@@ -6107,16 +6125,16 @@
       <c r="C2" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="J2" s="39" t="s">
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="J2" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="41"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="43"/>
     </row>
     <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="22" t="s">
@@ -6143,14 +6161,14 @@
       <c r="L3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="44"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B4" s="22" t="s">
@@ -6177,12 +6195,12 @@
       <c r="L4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B5" s="22" t="s">
@@ -6209,12 +6227,12 @@
       <c r="L5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B6" s="22" t="s">
@@ -6229,12 +6247,12 @@
       <c r="J6" s="4"/>
       <c r="K6" s="9"/>
       <c r="L6" s="2"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B7" s="22" t="s">
@@ -6613,16 +6631,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="24"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="J10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="24"/>
@@ -7128,7 +7146,7 @@
       <c r="B4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="39" t="s">
         <v>163</v>
       </c>
     </row>
@@ -7174,16 +7192,16 @@
     </row>
     <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="24"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="J10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
     </row>
     <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="24"/>
@@ -7247,14 +7265,14 @@
       <c r="L13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="42" t="s">
+      <c r="N13" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C14" s="24"/>
@@ -7276,12 +7294,12 @@
       <c r="L14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C15" s="24"/>
@@ -7297,12 +7315,12 @@
       <c r="L15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="42"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
     </row>
     <row r="16" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C16" s="24"/>
@@ -7318,12 +7336,12 @@
       <c r="L16" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="N16" s="42"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="44"/>
     </row>
     <row r="17" spans="3:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C17" s="24"/>
@@ -7339,14 +7357,14 @@
       <c r="L17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="N17" s="42" t="s">
+      <c r="N17" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="44"/>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C18" s="24"/>
@@ -7362,12 +7380,12 @@
       <c r="L18" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="44"/>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C19" s="24"/>
@@ -7383,12 +7401,12 @@
       <c r="L19" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="44"/>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C20" s="24"/>
@@ -7398,12 +7416,12 @@
       <c r="J20" s="2"/>
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="44"/>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C21" s="24"/>
@@ -7422,14 +7440,14 @@
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
-      <c r="N22" s="43" t="s">
+      <c r="N22" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="O22" s="43"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43"/>
-      <c r="S22" s="43"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="45"/>
+      <c r="R22" s="45"/>
+      <c r="S22" s="45"/>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C23" s="24"/>
@@ -7448,14 +7466,14 @@
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
-      <c r="N24" s="42" t="s">
+      <c r="N24" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
-      <c r="S24" s="42"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="44"/>
+      <c r="S24" s="44"/>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C25" s="24"/>
@@ -7465,12 +7483,12 @@
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="42"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="42"/>
-      <c r="S25" s="42"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
+      <c r="S25" s="44"/>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C26" s="24"/>
@@ -7480,12 +7498,12 @@
       <c r="J26" s="2"/>
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="44"/>
+      <c r="S26" s="44"/>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C27" s="24"/>
@@ -7495,12 +7513,12 @@
       <c r="J27" s="2"/>
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="42"/>
-      <c r="S27" s="42"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="44"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="44"/>
+      <c r="S27" s="44"/>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C28" s="24"/>
@@ -7510,14 +7528,14 @@
       <c r="J28" s="2"/>
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
-      <c r="N28" s="42" t="s">
+      <c r="N28" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
-      <c r="S28" s="42"/>
+      <c r="O28" s="44"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="44"/>
+      <c r="S28" s="44"/>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C29" s="24"/>
@@ -7527,12 +7545,12 @@
       <c r="J29" s="2"/>
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C30" s="24"/>
@@ -7542,12 +7560,12 @@
       <c r="J30" s="2"/>
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C31" s="24"/>
@@ -7557,12 +7575,12 @@
       <c r="J31" s="2"/>
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="42"/>
-      <c r="S31" s="42"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="44"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="44"/>
+      <c r="S31" s="44"/>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C32" s="24"/>
@@ -7769,16 +7787,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="24"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="J10" s="39" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="J10" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="43"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="24"/>

--- a/Game Stuff/Spreadsheet.xlsx
+++ b/Game Stuff/Spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\jUND ICONOCLAST\Game Stuff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Jund Pyroclast\Game Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F8CFFF-043A-41C0-A981-8B04EF560A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F82A9D1-D18A-4DB9-9A31-29A05C66C190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="4" activeTab="11" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
+    <workbookView xWindow="45972" yWindow="-4944" windowWidth="17496" windowHeight="30216" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Summary" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="The Abyssal Chains of Shandalar" sheetId="12" r:id="rId11"/>
     <sheet name="Riveteers District" sheetId="13" r:id="rId12"/>
     <sheet name="Phyrexian Datavault" sheetId="14" r:id="rId13"/>
+    <sheet name="Jund Pyroclast" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="187">
   <si>
     <t>Item</t>
   </si>
@@ -579,6 +580,36 @@
   </si>
   <si>
     <t>Jund Pyroclast</t>
+  </si>
+  <si>
+    <t>2800 MWh</t>
+  </si>
+  <si>
+    <t>Infinite</t>
+  </si>
+  <si>
+    <t>17042.1 MW</t>
+  </si>
+  <si>
+    <t>18917.3 Mw</t>
+  </si>
+  <si>
+    <t>1875.2 MW</t>
+  </si>
+  <si>
+    <t>Nitrogen Gas</t>
+  </si>
+  <si>
+    <t>Extractor</t>
+  </si>
+  <si>
+    <t>Polymer Resin</t>
+  </si>
+  <si>
+    <t>Compacted Coal</t>
+  </si>
+  <si>
+    <t>Packaged Rocket Fuel</t>
   </si>
 </sst>
 </file>
@@ -610,7 +641,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -866,11 +897,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -891,9 +972,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -932,9 +1010,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -972,6 +1047,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1321,38 +1408,38 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="42" t="s">
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="43"/>
-      <c r="J4" s="44"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="42"/>
     </row>
     <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="37" t="s">
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="J5" s="36" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1366,13 +1453,13 @@
       <c r="E6" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="33">
+      <c r="I6" s="47">
         <v>15</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="19" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1389,7 +1476,7 @@
       <c r="H7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="46">
         <v>5</v>
       </c>
       <c r="J7" s="2" t="s">
@@ -1409,7 +1496,7 @@
       <c r="H8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="46">
         <v>1.4065000000000001</v>
       </c>
       <c r="J8" s="2" t="s">
@@ -1429,7 +1516,7 @@
       <c r="H9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="46">
         <v>2.25</v>
       </c>
       <c r="J9" s="2" t="s">
@@ -1449,7 +1536,7 @@
       <c r="H10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="46">
         <v>2.5</v>
       </c>
       <c r="J10" s="2" t="s">
@@ -1469,7 +1556,7 @@
       <c r="H11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="46">
         <v>45</v>
       </c>
       <c r="J11" s="2" t="s">
@@ -1489,7 +1576,7 @@
       <c r="H12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="46">
         <v>5</v>
       </c>
       <c r="J12" s="2" t="s">
@@ -1509,7 +1596,7 @@
       <c r="H13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="46">
         <v>7.3125</v>
       </c>
       <c r="J13" s="2" t="s">
@@ -1529,7 +1616,7 @@
       <c r="H14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="46">
         <v>3</v>
       </c>
       <c r="J14" s="2" t="s">
@@ -1549,7 +1636,7 @@
       <c r="H15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="46">
         <v>30</v>
       </c>
       <c r="J15" s="2" t="s">
@@ -1569,7 +1656,7 @@
       <c r="H16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="46">
         <v>0.5</v>
       </c>
       <c r="J16" s="2" t="s">
@@ -1577,13 +1664,19 @@
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C17" s="4"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="9">
+        <v>29.17</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>176</v>
+      </c>
       <c r="H17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="46">
         <v>33.125</v>
       </c>
       <c r="J17" s="2" t="s">
@@ -1597,7 +1690,7 @@
       <c r="H18" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="46">
         <v>61.6875</v>
       </c>
       <c r="J18" s="2" t="s">
@@ -1611,7 +1704,7 @@
       <c r="H19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="46">
         <v>7.25</v>
       </c>
       <c r="J19" s="2" t="s">
@@ -1625,7 +1718,7 @@
       <c r="H20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="46">
         <v>30</v>
       </c>
       <c r="J20" s="2" t="s">
@@ -1639,7 +1732,7 @@
       <c r="H21" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="46">
         <v>45</v>
       </c>
       <c r="J21" s="2" t="s">
@@ -1653,7 +1746,7 @@
       <c r="H22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="46">
         <v>22.5</v>
       </c>
       <c r="J22" s="2" t="s">
@@ -1667,7 +1760,7 @@
       <c r="H23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="46">
         <v>20.5</v>
       </c>
       <c r="J23" s="2" t="s">
@@ -1681,7 +1774,7 @@
       <c r="H24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="46">
         <v>15</v>
       </c>
       <c r="J24" s="2" t="s">
@@ -1695,7 +1788,7 @@
       <c r="H25" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="46">
         <v>25</v>
       </c>
       <c r="J25" s="2" t="s">
@@ -1709,7 +1802,7 @@
       <c r="H26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="46">
         <v>26.25</v>
       </c>
       <c r="J26" s="2" t="s">
@@ -1723,7 +1816,7 @@
       <c r="H27" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="46">
         <v>19.443999999999999</v>
       </c>
       <c r="J27" s="2" t="s">
@@ -1737,7 +1830,7 @@
       <c r="H28" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="46">
         <v>1.5</v>
       </c>
       <c r="J28" s="2" t="s">
@@ -1751,7 +1844,7 @@
       <c r="H29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="46">
         <v>1.5</v>
       </c>
       <c r="J29" s="2" t="s">
@@ -1765,7 +1858,7 @@
       <c r="H30" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="46">
         <v>2.25</v>
       </c>
       <c r="J30" s="2" t="s">
@@ -1779,7 +1872,7 @@
       <c r="H31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="46">
         <v>3</v>
       </c>
       <c r="J31" s="2" t="s">
@@ -1793,7 +1886,7 @@
       <c r="H32" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="46">
         <v>6</v>
       </c>
       <c r="J32" s="2" t="s">
@@ -1807,7 +1900,7 @@
       <c r="H33" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="46">
         <v>25</v>
       </c>
       <c r="J33" s="2" t="s">
@@ -1821,7 +1914,7 @@
       <c r="H34" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="46">
         <v>20</v>
       </c>
       <c r="J34" s="2" t="s">
@@ -1835,7 +1928,7 @@
       <c r="H35" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="46">
         <v>0.5</v>
       </c>
       <c r="J35" s="2" t="s">
@@ -1849,7 +1942,7 @@
       <c r="H36" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="46">
         <v>0.5</v>
       </c>
       <c r="J36" s="2" t="s">
@@ -1863,7 +1956,7 @@
       <c r="H37" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="46">
         <v>49.332999999999998</v>
       </c>
       <c r="J37" s="2" t="s">
@@ -1877,7 +1970,7 @@
       <c r="H38" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="46">
         <v>12</v>
       </c>
       <c r="J38" s="2" t="s">
@@ -1888,7 +1981,7 @@
       <c r="H39" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="46">
         <v>195</v>
       </c>
       <c r="J39" s="2" t="s">
@@ -1899,7 +1992,7 @@
       <c r="H40" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40" s="46">
         <v>62</v>
       </c>
       <c r="J40" s="2" t="s">
@@ -1907,10 +2000,10 @@
       </c>
     </row>
     <row r="41" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H41" s="41" t="s">
+      <c r="H41" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="I41" s="11">
+      <c r="I41" s="46">
         <v>10</v>
       </c>
       <c r="J41" s="2" t="s">
@@ -1918,10 +2011,10 @@
       </c>
     </row>
     <row r="42" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H42" s="41" t="s">
+      <c r="H42" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="I42" s="11">
+      <c r="I42" s="46">
         <v>10</v>
       </c>
       <c r="J42" s="2" t="s">
@@ -1932,7 +2025,7 @@
       <c r="H43" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="46">
         <v>5</v>
       </c>
       <c r="J43" s="2" t="s">
@@ -1943,7 +2036,7 @@
       <c r="H44" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="46">
         <v>10</v>
       </c>
       <c r="J44" s="2" t="s">
@@ -1951,78 +2044,96 @@
       </c>
     </row>
     <row r="45" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H45" s="2"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="2"/>
+      <c r="H45" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I45" s="45">
+        <v>12.5</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="46" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H46" s="2"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="2"/>
+      <c r="H46" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="I46" s="45">
+        <v>12.5</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="47" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H47" s="2"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="2"/>
+      <c r="H47" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="I47" s="45">
+        <v>150</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="48" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H48" s="2"/>
-      <c r="I48" s="11"/>
+      <c r="I48" s="46"/>
       <c r="J48" s="2"/>
     </row>
     <row r="49" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H49" s="2"/>
-      <c r="I49" s="11"/>
+      <c r="I49" s="46"/>
       <c r="J49" s="2"/>
     </row>
     <row r="50" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H50" s="2"/>
-      <c r="I50" s="11"/>
+      <c r="I50" s="46"/>
       <c r="J50" s="2"/>
     </row>
     <row r="51" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H51" s="2"/>
-      <c r="I51" s="11"/>
+      <c r="I51" s="46"/>
       <c r="J51" s="2"/>
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H52" s="2"/>
-      <c r="I52" s="11"/>
+      <c r="I52" s="46"/>
       <c r="J52" s="2"/>
     </row>
     <row r="53" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H53" s="2"/>
-      <c r="I53" s="11"/>
+      <c r="I53" s="46"/>
       <c r="J53" s="2"/>
     </row>
     <row r="54" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H54" s="2"/>
-      <c r="I54" s="11"/>
+      <c r="I54" s="46"/>
       <c r="J54" s="2"/>
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H55" s="2"/>
-      <c r="I55" s="11"/>
+      <c r="I55" s="46"/>
       <c r="J55" s="2"/>
     </row>
     <row r="56" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H56" s="2"/>
-      <c r="I56" s="11"/>
+      <c r="I56" s="46"/>
       <c r="J56" s="2"/>
     </row>
     <row r="57" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H57" s="2"/>
-      <c r="I57" s="11"/>
+      <c r="I57" s="46"/>
       <c r="J57" s="2"/>
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H58" s="2"/>
-      <c r="I58" s="11"/>
+      <c r="I58" s="46"/>
       <c r="J58" s="2"/>
     </row>
     <row r="59" spans="8:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H59" s="3"/>
-      <c r="I59" s="12"/>
+      <c r="I59" s="48"/>
       <c r="J59" s="3"/>
     </row>
   </sheetData>
@@ -2052,109 +2163,109 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="37" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="24"/>
-      <c r="E10" s="42" t="s">
+      <c r="C10" s="23"/>
+      <c r="E10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
-      <c r="J10" s="42" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="J10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="44"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="42"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="24"/>
-      <c r="E11" s="15" t="s">
+      <c r="C11" s="23"/>
+      <c r="E11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="36" t="s">
+      <c r="M11" s="34" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C12" s="24"/>
+      <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>108</v>
       </c>
@@ -2173,18 +2284,18 @@
       <c r="L12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="20"/>
-      <c r="O12" s="45" t="s">
+      <c r="M12" s="19"/>
+      <c r="O12" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="45"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
@@ -2204,15 +2315,15 @@
         <v>25</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="45"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2"/>
       <c r="F14" s="9"/>
       <c r="G14" s="4"/>
@@ -2226,15 +2337,15 @@
         <v>25</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="45"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
       <c r="G15" s="2"/>
@@ -2248,15 +2359,15 @@
         <v>8</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
       <c r="G16" s="2"/>
@@ -2270,17 +2381,17 @@
         <v>114</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="O16" s="45" t="s">
+      <c r="O16" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
       <c r="G17" s="2"/>
@@ -2294,15 +2405,15 @@
         <v>114</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="45"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -2316,15 +2427,15 @@
         <v>154</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="43"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -2338,15 +2449,15 @@
         <v>154</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="45"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
-      <c r="T19" s="45"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
@@ -2356,7 +2467,7 @@
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -2364,17 +2475,17 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="46" t="s">
+      <c r="O21" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
@@ -2384,7 +2495,7 @@
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -2392,17 +2503,17 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="45" t="s">
+      <c r="O23" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="45"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
@@ -2410,15 +2521,15 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="45"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="43"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
@@ -2426,15 +2537,15 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="45"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
@@ -2442,15 +2553,15 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
@@ -2458,17 +2569,17 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="45" t="s">
+      <c r="O27" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="45"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="43"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
@@ -2476,15 +2587,15 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
@@ -2492,15 +2603,15 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="45"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="43"/>
+      <c r="R29" s="43"/>
+      <c r="S29" s="43"/>
+      <c r="T29" s="43"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
@@ -2508,15 +2619,15 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
@@ -2526,7 +2637,7 @@
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -2536,7 +2647,7 @@
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -2546,7 +2657,7 @@
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -2556,7 +2667,7 @@
       <c r="M34" s="2"/>
     </row>
     <row r="35" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -2566,7 +2677,7 @@
       <c r="M35" s="2"/>
     </row>
     <row r="36" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>
@@ -2678,105 +2789,105 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="87" x14ac:dyDescent="0.35">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="24"/>
-      <c r="E10" s="42" t="s">
+      <c r="C10" s="23"/>
+      <c r="E10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
-      <c r="J10" s="42" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="J10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="44"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="42"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="24"/>
-      <c r="E11" s="15" t="s">
+      <c r="C11" s="23"/>
+      <c r="E11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C12" s="24"/>
+      <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>61</v>
       </c>
@@ -2797,7 +2908,7 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
@@ -2818,7 +2929,7 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>43</v>
       </c>
@@ -2833,7 +2944,7 @@
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>41</v>
       </c>
@@ -2848,7 +2959,7 @@
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>5</v>
       </c>
@@ -2863,7 +2974,7 @@
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>106</v>
       </c>
@@ -2878,7 +2989,7 @@
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -2887,7 +2998,7 @@
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -2896,7 +3007,7 @@
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
@@ -2905,7 +3016,7 @@
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -2914,7 +3025,7 @@
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
@@ -2923,7 +3034,7 @@
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -2932,7 +3043,7 @@
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
@@ -2941,7 +3052,7 @@
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
@@ -2950,7 +3061,7 @@
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
@@ -2959,7 +3070,7 @@
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
@@ -2968,7 +3079,7 @@
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
@@ -2977,7 +3088,7 @@
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
@@ -2986,7 +3097,7 @@
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
@@ -2995,7 +3106,7 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
@@ -3004,7 +3115,7 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -3013,7 +3124,7 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -3022,7 +3133,7 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -3031,7 +3142,7 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -3040,7 +3151,7 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>
@@ -3139,105 +3250,105 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="24"/>
-      <c r="E10" s="42" t="s">
+      <c r="C10" s="23"/>
+      <c r="E10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
-      <c r="J10" s="42" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="J10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="44"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="42"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="24"/>
-      <c r="E11" s="15" t="s">
+      <c r="C11" s="23"/>
+      <c r="E11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C12" s="24"/>
+      <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>135</v>
       </c>
@@ -3258,7 +3369,7 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>61</v>
       </c>
@@ -3279,7 +3390,7 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>17</v>
       </c>
@@ -3300,7 +3411,7 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>18</v>
       </c>
@@ -3321,7 +3432,7 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>19</v>
       </c>
@@ -3342,7 +3453,7 @@
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>43</v>
       </c>
@@ -3363,7 +3474,7 @@
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -3378,7 +3489,7 @@
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -3393,7 +3504,7 @@
       </c>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
@@ -3408,7 +3519,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -3417,7 +3528,7 @@
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
@@ -3426,7 +3537,7 @@
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -3435,7 +3546,7 @@
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
@@ -3444,7 +3555,7 @@
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
@@ -3453,7 +3564,7 @@
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
@@ -3462,7 +3573,7 @@
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
@@ -3471,7 +3582,7 @@
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
@@ -3480,7 +3591,7 @@
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
@@ -3489,7 +3600,7 @@
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
@@ -3498,7 +3609,7 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
@@ -3507,7 +3618,7 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -3516,7 +3627,7 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -3525,7 +3636,7 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -3534,7 +3645,7 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -3543,7 +3654,7 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>
@@ -3641,105 +3752,105 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="74.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="24"/>
-      <c r="E10" s="42" t="s">
+      <c r="C10" s="23"/>
+      <c r="E10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
-      <c r="J10" s="42" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="J10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="44"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="42"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="24"/>
-      <c r="E11" s="15" t="s">
+      <c r="C11" s="23"/>
+      <c r="E11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C12" s="24"/>
+      <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>43</v>
       </c>
@@ -3749,7 +3860,7 @@
       <c r="G12" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="38">
         <v>10</v>
       </c>
       <c r="K12" s="8" t="s">
@@ -3760,7 +3871,7 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>90</v>
       </c>
@@ -3770,7 +3881,7 @@
       <c r="G13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="38">
         <v>10</v>
       </c>
       <c r="K13" s="9" t="s">
@@ -3781,7 +3892,7 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>89</v>
       </c>
@@ -3791,12 +3902,12 @@
       <c r="G14" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J14" s="40"/>
+      <c r="J14" s="38"/>
       <c r="K14" s="9"/>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>19</v>
       </c>
@@ -3806,12 +3917,12 @@
       <c r="G15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J15" s="40"/>
+      <c r="J15" s="38"/>
       <c r="K15" s="9"/>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>106</v>
       </c>
@@ -3821,12 +3932,12 @@
       <c r="G16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="40"/>
+      <c r="J16" s="38"/>
       <c r="K16" s="9"/>
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>5</v>
       </c>
@@ -3836,12 +3947,12 @@
       <c r="G17" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J17" s="40"/>
+      <c r="J17" s="38"/>
       <c r="K17" s="9"/>
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2" t="s">
         <v>53</v>
       </c>
@@ -3851,12 +3962,12 @@
       <c r="G18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="40"/>
+      <c r="J18" s="38"/>
       <c r="K18" s="9"/>
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2" t="s">
         <v>168</v>
       </c>
@@ -3871,7 +3982,7 @@
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
@@ -3880,7 +3991,7 @@
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -3889,7 +4000,7 @@
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
@@ -3898,7 +4009,7 @@
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -3907,7 +4018,7 @@
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
@@ -3916,7 +4027,7 @@
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
@@ -3925,7 +4036,7 @@
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
@@ -3934,7 +4045,7 @@
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
@@ -3943,7 +4054,7 @@
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
@@ -3952,7 +4063,7 @@
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
@@ -3961,7 +4072,7 @@
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
@@ -3970,7 +4081,7 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
@@ -3979,7 +4090,7 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -3988,7 +4099,7 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -3997,7 +4108,7 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -4006,7 +4117,7 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -4015,7 +4126,479 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="2"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E37" s="2"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="2"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E38" s="2"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="2"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E39" s="2"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="2"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E40" s="2"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="2"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E41" s="2"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E42" s="2"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="E43" s="2"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E44" s="3"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="J10:L10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1051D7C-48A2-4264-A591-A5BE1589053B}">
+  <dimension ref="B1:L44"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.54296875" customWidth="1"/>
+    <col min="11" max="11" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B4" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B7" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B8" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="23"/>
+      <c r="E10" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="J10" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="42"/>
+    </row>
+    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="23"/>
+      <c r="E11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C12" s="23"/>
+      <c r="E12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="8">
+        <v>980.42</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="38">
+        <v>29.17</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C13" s="23"/>
+      <c r="E13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="9">
+        <v>300</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J13" s="38">
+        <v>12.5</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C14" s="23"/>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="9">
+        <v>150</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="38">
+        <v>12.5</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C15" s="23"/>
+      <c r="E15" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15" s="9">
+        <v>150</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J15" s="38">
+        <v>150</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C16" s="23"/>
+      <c r="E16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="9">
+        <v>400</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="38"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="4"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C17" s="23"/>
+      <c r="E17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="9">
+        <v>200</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="38"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C18" s="23"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="2"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C19" s="23"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="2"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="4"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C20" s="23"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="2"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C21" s="23"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="2"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="4"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C22" s="23"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="2"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C23" s="23"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="2"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="4"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C24" s="23"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="2"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="4"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C25" s="23"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="2"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="4"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C26" s="23"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="2"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C27" s="23"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="2"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="4"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C28" s="23"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="2"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="4"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C29" s="23"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="2"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C30" s="23"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="2"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C31" s="23"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="2"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C32" s="23"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="2"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C33" s="23"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="2"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C34" s="23"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="2"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C35" s="23"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="2"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>
@@ -4113,51 +4696,51 @@
   <sheetData>
     <row r="3" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="44"/>
-      <c r="K4" s="42" t="s">
+      <c r="G4" s="41"/>
+      <c r="H4" s="42"/>
+      <c r="K4" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="43"/>
-      <c r="M4" s="44"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="42"/>
     </row>
     <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="L5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -4183,7 +4766,7 @@
       </c>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -4209,7 +4792,7 @@
       </c>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -4235,7 +4818,7 @@
       </c>
     </row>
     <row r="9" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -4507,7 +5090,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" style="24" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" style="23" customWidth="1"/>
     <col min="6" max="6" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
@@ -4520,112 +5103,112 @@
   <sheetData>
     <row r="3" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="24" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="25" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="3:20" ht="54" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="30" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="7" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="25" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="25" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="26" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="13" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
-      <c r="K13" s="42" t="s">
+      <c r="G13" s="41"/>
+      <c r="H13" s="42"/>
+      <c r="K13" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="44"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="42"/>
     </row>
     <row r="14" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="K14" s="15" t="s">
+      <c r="K14" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="M14" s="15" t="s">
+      <c r="M14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="36" t="s">
+      <c r="N14" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="P14" s="45" t="s">
+      <c r="P14" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="45"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
     </row>
     <row r="15" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F15" s="4" t="s">
@@ -4646,12 +5229,12 @@
       <c r="M15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="20"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
+      <c r="N15" s="19"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
     </row>
     <row r="16" spans="3:20" x14ac:dyDescent="0.35">
       <c r="F16" s="2" t="s">
@@ -4675,11 +5258,11 @@
       <c r="N16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
     </row>
     <row r="17" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
@@ -4697,11 +5280,11 @@
       <c r="N17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="45"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
     </row>
     <row r="18" spans="6:20" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
@@ -5023,108 +5606,108 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="25" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="31" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="24"/>
+      <c r="C10" s="23"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="24"/>
-      <c r="E11" s="42" t="s">
+      <c r="C11" s="23"/>
+      <c r="E11" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
-      <c r="J11" s="42" t="s">
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
+      <c r="J11" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="43"/>
-      <c r="L11" s="44"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="42"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C12" s="24"/>
-      <c r="E12" s="15" t="s">
+      <c r="C12" s="23"/>
+      <c r="E12" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="4" t="s">
         <v>52</v>
       </c>
@@ -5145,7 +5728,7 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
@@ -5166,7 +5749,7 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
       <c r="G15" s="2"/>
@@ -5181,7 +5764,7 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
       <c r="G16" s="2"/>
@@ -5196,7 +5779,7 @@
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
       <c r="G17" s="2"/>
@@ -5205,7 +5788,7 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -5214,7 +5797,7 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -5223,7 +5806,7 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
@@ -5232,7 +5815,7 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -5241,7 +5824,7 @@
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
@@ -5250,7 +5833,7 @@
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -5259,7 +5842,7 @@
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
@@ -5268,7 +5851,7 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
@@ -5277,7 +5860,7 @@
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
@@ -5286,7 +5869,7 @@
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
@@ -5295,7 +5878,7 @@
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
@@ -5304,7 +5887,7 @@
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
@@ -5313,7 +5896,7 @@
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
@@ -5322,7 +5905,7 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
@@ -5331,7 +5914,7 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -5340,7 +5923,7 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -5349,7 +5932,7 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -5358,7 +5941,7 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -5367,7 +5950,7 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>
@@ -5476,120 +6059,120 @@
   <sheetData>
     <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="25" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="31" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="24"/>
+      <c r="C10" s="23"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="24"/>
-      <c r="E11" s="42" t="s">
+      <c r="C11" s="23"/>
+      <c r="E11" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
-      <c r="J11" s="42" t="s">
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
+      <c r="J11" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="44"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="42"/>
     </row>
     <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C12" s="24"/>
-      <c r="E12" s="15" t="s">
+      <c r="C12" s="23"/>
+      <c r="E12" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J12" s="34" t="s">
+      <c r="J12" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="K12" s="35" t="s">
+      <c r="K12" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="L12" s="34" t="s">
+      <c r="L12" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="O12" s="45" t="s">
+      <c r="O12" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="45"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="4" t="s">
         <v>49</v>
       </c>
@@ -5609,16 +6192,16 @@
       <c r="L13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="20"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="45"/>
+      <c r="M13" s="19"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
@@ -5640,15 +6223,15 @@
       <c r="M14" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="45"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
       <c r="G15" s="2"/>
@@ -5664,15 +6247,15 @@
       <c r="M15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
       <c r="G16" s="2"/>
@@ -5688,17 +6271,17 @@
       <c r="M16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="O16" s="45" t="s">
+      <c r="O16" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
       <c r="G17" s="2"/>
@@ -5714,15 +6297,15 @@
       <c r="M17" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="45"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -5736,15 +6319,15 @@
         <v>154</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="43"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -5752,15 +6335,15 @@
       <c r="K19" s="9"/>
       <c r="L19" s="6"/>
       <c r="M19" s="2"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="45"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
-      <c r="T19" s="45"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
     </row>
     <row r="20" spans="3:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
@@ -5770,7 +6353,7 @@
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -5778,17 +6361,17 @@
       <c r="K21" s="9"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="46" t="s">
+      <c r="O21" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="44"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
@@ -5798,7 +6381,7 @@
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -5806,17 +6389,17 @@
       <c r="K23" s="9"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="45" t="s">
+      <c r="O23" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="45"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
@@ -5824,15 +6407,15 @@
       <c r="K24" s="9"/>
       <c r="L24" s="6"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="45"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="45"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="43"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
@@ -5840,15 +6423,15 @@
       <c r="K25" s="9"/>
       <c r="L25" s="6"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="45"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="43"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
@@ -5856,15 +6439,15 @@
       <c r="K26" s="9"/>
       <c r="L26" s="6"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
@@ -5872,17 +6455,17 @@
       <c r="K27" s="9"/>
       <c r="L27" s="6"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="45" t="s">
+      <c r="O27" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="45"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="43"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
@@ -5890,15 +6473,15 @@
       <c r="K28" s="9"/>
       <c r="L28" s="6"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
@@ -5906,15 +6489,15 @@
       <c r="K29" s="9"/>
       <c r="L29" s="6"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="45"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="43"/>
+      <c r="R29" s="43"/>
+      <c r="S29" s="43"/>
+      <c r="T29" s="43"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
@@ -5922,15 +6505,15 @@
       <c r="K30" s="9"/>
       <c r="L30" s="6"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
@@ -5938,17 +6521,17 @@
       <c r="K31" s="9"/>
       <c r="L31" s="6"/>
       <c r="M31" s="2"/>
-      <c r="O31" s="45" t="s">
+      <c r="O31" s="43" t="s">
         <v>161</v>
       </c>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="45"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="45"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="43"/>
+      <c r="T31" s="43"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -5956,15 +6539,15 @@
       <c r="K32" s="9"/>
       <c r="L32" s="6"/>
       <c r="M32" s="2"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
+      <c r="O32" s="43"/>
+      <c r="P32" s="43"/>
+      <c r="Q32" s="43"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="43"/>
     </row>
     <row r="33" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -5972,15 +6555,15 @@
       <c r="K33" s="9"/>
       <c r="L33" s="6"/>
       <c r="M33" s="2"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
+      <c r="O33" s="43"/>
+      <c r="P33" s="43"/>
+      <c r="Q33" s="43"/>
+      <c r="R33" s="43"/>
+      <c r="S33" s="43"/>
+      <c r="T33" s="43"/>
     </row>
     <row r="34" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -5988,15 +6571,15 @@
       <c r="K34" s="9"/>
       <c r="L34" s="6"/>
       <c r="M34" s="2"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="45"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="43"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="43"/>
     </row>
     <row r="35" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -6006,7 +6589,7 @@
       <c r="M35" s="2"/>
     </row>
     <row r="36" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>
@@ -6128,62 +6711,62 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
-      <c r="J2" s="42" t="s">
+      <c r="F2" s="41"/>
+      <c r="G2" s="42"/>
+      <c r="J2" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="43"/>
-      <c r="L2" s="44"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="42"/>
     </row>
     <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="45" t="s">
+      <c r="N3" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>81</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -6204,18 +6787,18 @@
       <c r="L4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="45"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -6236,18 +6819,18 @@
       <c r="L5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>56</v>
       </c>
       <c r="E6" s="2"/>
@@ -6256,18 +6839,18 @@
       <c r="J6" s="4"/>
       <c r="K6" s="9"/>
       <c r="L6" s="2"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>57</v>
       </c>
       <c r="E7" s="2"/>
@@ -6278,10 +6861,10 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>58</v>
       </c>
       <c r="E8" s="2"/>
@@ -6292,10 +6875,10 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>59</v>
       </c>
       <c r="E9" s="2"/>
@@ -6306,7 +6889,7 @@
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C10" s="24"/>
+      <c r="C10" s="23"/>
       <c r="E10" s="2"/>
       <c r="F10" s="9"/>
       <c r="G10" s="2"/>
@@ -6315,7 +6898,7 @@
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C11" s="24"/>
+      <c r="C11" s="23"/>
       <c r="E11" s="2"/>
       <c r="F11" s="9"/>
       <c r="G11" s="2"/>
@@ -6324,7 +6907,7 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C12" s="24"/>
+      <c r="C12" s="23"/>
       <c r="E12" s="2"/>
       <c r="F12" s="9"/>
       <c r="G12" s="2"/>
@@ -6333,7 +6916,7 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="2"/>
       <c r="F13" s="9"/>
       <c r="G13" s="2"/>
@@ -6342,7 +6925,7 @@
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2"/>
       <c r="F14" s="9"/>
       <c r="G14" s="2"/>
@@ -6351,7 +6934,7 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
       <c r="G15" s="2"/>
@@ -6360,7 +6943,7 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
       <c r="G16" s="2"/>
@@ -6369,7 +6952,7 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
       <c r="G17" s="2"/>
@@ -6378,7 +6961,7 @@
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -6387,7 +6970,7 @@
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -6396,7 +6979,7 @@
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
@@ -6405,7 +6988,7 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -6414,7 +6997,7 @@
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
@@ -6423,7 +7006,7 @@
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -6432,7 +7015,7 @@
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
@@ -6441,7 +7024,7 @@
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
@@ -6450,7 +7033,7 @@
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
@@ -6459,7 +7042,7 @@
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
@@ -6468,7 +7051,7 @@
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
@@ -6477,7 +7060,7 @@
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
@@ -6486,7 +7069,7 @@
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
@@ -6495,7 +7078,7 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
@@ -6504,7 +7087,7 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -6513,7 +7096,7 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -6522,7 +7105,7 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -6531,7 +7114,7 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -6540,7 +7123,7 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
       <c r="E36" s="3"/>
       <c r="F36" s="10"/>
       <c r="G36" s="3"/>
@@ -6575,105 +7158,105 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="24"/>
-      <c r="E10" s="42" t="s">
+      <c r="C10" s="23"/>
+      <c r="E10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
-      <c r="J10" s="42" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="J10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="44"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="42"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="24"/>
-      <c r="E11" s="15" t="s">
+      <c r="C11" s="23"/>
+      <c r="E11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C12" s="24"/>
+      <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>61</v>
       </c>
@@ -6694,7 +7277,7 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>19</v>
       </c>
@@ -6715,7 +7298,7 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>54</v>
       </c>
@@ -6736,7 +7319,7 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>43</v>
       </c>
@@ -6757,7 +7340,7 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>41</v>
       </c>
@@ -6778,7 +7361,7 @@
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>53</v>
       </c>
@@ -6799,7 +7382,7 @@
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -6814,7 +7397,7 @@
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -6829,7 +7412,7 @@
       </c>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
@@ -6844,7 +7427,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -6859,7 +7442,7 @@
       </c>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
@@ -6874,7 +7457,7 @@
       </c>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -6889,7 +7472,7 @@
       </c>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
@@ -6904,7 +7487,7 @@
       </c>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
@@ -6919,7 +7502,7 @@
       </c>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
@@ -6934,7 +7517,7 @@
       </c>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
@@ -6949,7 +7532,7 @@
       </c>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
@@ -6964,7 +7547,7 @@
       </c>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
@@ -6979,7 +7562,7 @@
       </c>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
@@ -6988,7 +7571,7 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
@@ -6997,7 +7580,7 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -7006,7 +7589,7 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -7015,7 +7598,7 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -7024,7 +7607,7 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -7033,7 +7616,7 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>
@@ -7136,105 +7719,105 @@
   <sheetData>
     <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="37" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="24"/>
-      <c r="E10" s="42" t="s">
+      <c r="C10" s="23"/>
+      <c r="E10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
-      <c r="J10" s="42" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="J10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="44"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="42"/>
     </row>
     <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="24"/>
-      <c r="E11" s="15" t="s">
+      <c r="C11" s="23"/>
+      <c r="E11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C12" s="24"/>
+      <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>91</v>
       </c>
@@ -7255,7 +7838,7 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>61</v>
       </c>
@@ -7274,17 +7857,17 @@
       <c r="L13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="45" t="s">
+      <c r="N13" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
@@ -7303,15 +7886,15 @@
       <c r="L14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
       <c r="G15" s="2"/>
@@ -7324,15 +7907,15 @@
       <c r="L15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
     </row>
     <row r="16" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
       <c r="G16" s="2"/>
@@ -7345,15 +7928,15 @@
       <c r="L16" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="N16" s="45"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
     </row>
     <row r="17" spans="3:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
       <c r="G17" s="2"/>
@@ -7366,17 +7949,17 @@
       <c r="L17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="N17" s="45" t="s">
+      <c r="N17" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="O17" s="45"/>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -7389,15 +7972,15 @@
       <c r="L18" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -7410,30 +7993,30 @@
       <c r="L19" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="45"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="45"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="45"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -7442,24 +8025,24 @@
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
-      <c r="N22" s="46" t="s">
+      <c r="N22" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="O22" s="46"/>
-      <c r="P22" s="46"/>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="46"/>
-      <c r="S22" s="46"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="44"/>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -7468,131 +8051,131 @@
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
-      <c r="N24" s="45" t="s">
+      <c r="N24" s="43" t="s">
         <v>155</v>
       </c>
-      <c r="O24" s="45"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
+      <c r="O24" s="43"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="43"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="45"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="43"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
-      <c r="N28" s="45" t="s">
+      <c r="N28" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="43"/>
+      <c r="R29" s="43"/>
+      <c r="S29" s="43"/>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="43"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="45"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="45"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="43"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="43"/>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -7601,7 +8184,7 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -7610,7 +8193,7 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -7619,7 +8202,7 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -7628,7 +8211,7 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>
@@ -7731,105 +8314,105 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="26" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" s="24"/>
-      <c r="E10" s="42" t="s">
+      <c r="C10" s="23"/>
+      <c r="E10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
-      <c r="J10" s="42" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="J10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="44"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="42"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" s="24"/>
-      <c r="E11" s="15" t="s">
+      <c r="C11" s="23"/>
+      <c r="E11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C12" s="24"/>
+      <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>53</v>
       </c>
@@ -7850,7 +8433,7 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C13" s="24"/>
+      <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>41</v>
       </c>
@@ -7871,7 +8454,7 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C14" s="24"/>
+      <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
@@ -7892,7 +8475,7 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C15" s="24"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>90</v>
       </c>
@@ -7913,7 +8496,7 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C16" s="24"/>
+      <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>89</v>
       </c>
@@ -7934,7 +8517,7 @@
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C17" s="24"/>
+      <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>43</v>
       </c>
@@ -7949,7 +8532,7 @@
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
@@ -7958,7 +8541,7 @@
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C19" s="24"/>
+      <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
@@ -7967,7 +8550,7 @@
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C20" s="24"/>
+      <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
@@ -7976,7 +8559,7 @@
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C21" s="24"/>
+      <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
@@ -7985,7 +8568,7 @@
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C22" s="24"/>
+      <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
@@ -7994,7 +8577,7 @@
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C23" s="24"/>
+      <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
@@ -8003,7 +8586,7 @@
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C24" s="24"/>
+      <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
@@ -8012,7 +8595,7 @@
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C25" s="24"/>
+      <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
@@ -8021,7 +8604,7 @@
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C26" s="24"/>
+      <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
@@ -8030,7 +8613,7 @@
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C27" s="24"/>
+      <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
       <c r="G27" s="2"/>
@@ -8039,7 +8622,7 @@
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C28" s="24"/>
+      <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
       <c r="G28" s="2"/>
@@ -8048,7 +8631,7 @@
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C29" s="24"/>
+      <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
       <c r="G29" s="2"/>
@@ -8057,7 +8640,7 @@
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C30" s="24"/>
+      <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
@@ -8066,7 +8649,7 @@
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C31" s="24"/>
+      <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
       <c r="G31" s="2"/>
@@ -8075,7 +8658,7 @@
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C32" s="24"/>
+      <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
       <c r="G32" s="2"/>
@@ -8084,7 +8667,7 @@
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C33" s="24"/>
+      <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
       <c r="G33" s="2"/>
@@ -8093,7 +8676,7 @@
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C34" s="24"/>
+      <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
@@ -8102,7 +8685,7 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C35" s="24"/>
+      <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
@@ -8111,7 +8694,7 @@
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.35">
-      <c r="C36" s="24"/>
+      <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>

--- a/Game Stuff/Spreadsheet.xlsx
+++ b/Game Stuff/Spreadsheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Keldon Armory\Game Stuff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Urabrask's Refinery\Game Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CCBF14-8178-4A79-85EC-A95819CF0016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C35317-45F6-4768-9ECE-AFE267B0D50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="-4944" windowWidth="17496" windowHeight="30216" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="7" activeTab="15" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Summary" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,8 @@
     <sheet name="Riveteers District" sheetId="13" r:id="rId12"/>
     <sheet name="Phyrexian Datavault" sheetId="14" r:id="rId13"/>
     <sheet name="Jund Pyroclast" sheetId="15" r:id="rId14"/>
-    <sheet name="Sheet1" sheetId="16" r:id="rId15"/>
+    <sheet name="Keldon Armory" sheetId="17" r:id="rId15"/>
+    <sheet name="Urabrask's Refinery" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="219">
   <si>
     <t>Item</t>
   </si>
@@ -301,18 +302,9 @@
     <t>Darksteel Forge, Xantcha's Crucible, Oran-Rief Mines, Thran Foundry</t>
   </si>
   <si>
-    <t>822.8 MW</t>
-  </si>
-  <si>
-    <t>-822.8 MW</t>
-  </si>
-  <si>
     <t>13.1 GWh</t>
   </si>
   <si>
-    <t>15.92 Hours</t>
-  </si>
-  <si>
     <t>Top right belt going to Neko's Nexus has an extra 180 steel on it</t>
   </si>
   <si>
@@ -604,9 +596,6 @@
     <t>Phyrexian Datavault, The Abyssal Chains of Shandalar, Keldon Armory</t>
   </si>
   <si>
-    <t>Phyrexian Datavault, Keldon Armory, Jund Pyroclast</t>
-  </si>
-  <si>
     <t>Neko's Nexus, Ghirapur Gridworks, Phyrexian Datavault, Riveteers District, The Abyssal Chains of Shandalar, Keldon Armory</t>
   </si>
   <si>
@@ -631,6 +620,84 @@
     <t xml:space="preserve">Neko's Nexus, Ghirapur Gridworks, Phyrexian Datavault, Keldon Armory </t>
   </si>
   <si>
+    <t>Nobelisk</t>
+  </si>
+  <si>
+    <t>Pulse Nobelisk</t>
+  </si>
+  <si>
+    <t>Cluster Nobelisk</t>
+  </si>
+  <si>
+    <t>Black Powder</t>
+  </si>
+  <si>
+    <t>Smokeless Powder</t>
+  </si>
+  <si>
+    <t>Rifle Ammo</t>
+  </si>
+  <si>
+    <t>Homing Rifle Ammo</t>
+  </si>
+  <si>
+    <t>Turbo Rifle Ammo</t>
+  </si>
+  <si>
+    <t>Iron Rebar</t>
+  </si>
+  <si>
+    <t>Shatter Rebar</t>
+  </si>
+  <si>
+    <t>Stun Rebar</t>
+  </si>
+  <si>
+    <t>Explosive Rebar</t>
+  </si>
+  <si>
+    <t>Packaged Turbo Fuel</t>
+  </si>
+  <si>
+    <t>Packaged Fuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keldon Armory </t>
+  </si>
+  <si>
+    <t>Urabrask's Refinery</t>
+  </si>
+  <si>
+    <t>0 MW</t>
+  </si>
+  <si>
+    <t>4330.4 MW</t>
+  </si>
+  <si>
+    <t>-4330.4 MW</t>
+  </si>
+  <si>
+    <t>5800 MWh</t>
+  </si>
+  <si>
+    <t>1.33 Hours</t>
+  </si>
+  <si>
+    <t>Riveteers District Miner</t>
+  </si>
+  <si>
+    <t>805.9 MW</t>
+  </si>
+  <si>
+    <t>-805.9 MW</t>
+  </si>
+  <si>
+    <t>16.25 Hours</t>
+  </si>
+  <si>
+    <t>Phyrexian Datavault, Keldon Armory, Jund Pyroclast, Urabrask's Refinery</t>
+  </si>
+  <si>
     <t>Kaladesh Refinery, Riveteers District, Oran-Rief Mines, Xantcha's Crucible, Ketria Crystals, Darksteel Forge</t>
   </si>
   <si>
@@ -641,51 +708,6 @@
   </si>
   <si>
     <t>Miner (Jund Pyroclast)</t>
-  </si>
-  <si>
-    <t>Nobelisk</t>
-  </si>
-  <si>
-    <t>Pulse Nobelisk</t>
-  </si>
-  <si>
-    <t>Cluster Nobelisk</t>
-  </si>
-  <si>
-    <t>Black Powder</t>
-  </si>
-  <si>
-    <t>Smokeless Powder</t>
-  </si>
-  <si>
-    <t>Rifle Ammo</t>
-  </si>
-  <si>
-    <t>Homing Rifle Ammo</t>
-  </si>
-  <si>
-    <t>Turbo Rifle Ammo</t>
-  </si>
-  <si>
-    <t>Iron Rebar</t>
-  </si>
-  <si>
-    <t>Shatter Rebar</t>
-  </si>
-  <si>
-    <t>Stun Rebar</t>
-  </si>
-  <si>
-    <t>Explosive Rebar</t>
-  </si>
-  <si>
-    <t>Packaged Turbo Fuel</t>
-  </si>
-  <si>
-    <t>Packaged Fuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keldon Armory </t>
   </si>
 </sst>
 </file>
@@ -717,7 +739,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1023,11 +1045,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1110,6 +1177,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1125,24 +1212,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1492,27 +1580,27 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="42"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="36" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="15"/>
@@ -1528,33 +1616,33 @@
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C6" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="C6" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="44">
         <v>246.666</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>134</v>
+      <c r="E6" s="40" t="s">
+        <v>131</v>
       </c>
       <c r="H6" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="44">
         <v>15</v>
       </c>
-      <c r="J6" s="48" t="s">
+      <c r="J6" s="40" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="11">
         <v>77.665999999999997</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="41" t="s">
         <v>50</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -1563,18 +1651,18 @@
       <c r="I7" s="11">
         <v>5</v>
       </c>
-      <c r="J7" s="49" t="s">
+      <c r="J7" s="41" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="11">
         <v>356.47699999999998</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="41" t="s">
         <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -1583,18 +1671,18 @@
       <c r="I8" s="11">
         <v>1.4065000000000001</v>
       </c>
-      <c r="J8" s="49" t="s">
+      <c r="J8" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <v>1849.848</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="41" t="s">
         <v>42</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -1603,18 +1691,18 @@
       <c r="I9" s="11">
         <v>2.25</v>
       </c>
-      <c r="J9" s="49" t="s">
+      <c r="J9" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
         <v>58.332999999999998</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="41" t="s">
         <v>4</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -1623,19 +1711,19 @@
       <c r="I10" s="11">
         <v>2.5</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="J10" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="11">
         <v>68</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>109</v>
+      <c r="E11" s="41" t="s">
+        <v>106</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>66</v>
@@ -1643,19 +1731,19 @@
       <c r="I11" s="11">
         <v>45</v>
       </c>
-      <c r="J11" s="49" t="s">
+      <c r="J11" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="11">
         <v>29.17</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>168</v>
+      <c r="E12" s="41" t="s">
+        <v>165</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>67</v>
@@ -1663,19 +1751,19 @@
       <c r="I12" s="11">
         <v>5</v>
       </c>
-      <c r="J12" s="49" t="s">
+      <c r="J12" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="11">
         <v>391.64166599999999</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>211</v>
+      <c r="E13" s="41" t="s">
+        <v>203</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>68</v>
@@ -1683,19 +1771,19 @@
       <c r="I13" s="11">
         <v>7.3125</v>
       </c>
-      <c r="J13" s="49" t="s">
+      <c r="J13" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="9">
+      <c r="C14" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="11">
         <v>440.75</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>88</v>
+      <c r="E14" s="41" t="s">
+        <v>85</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>69</v>
@@ -1703,19 +1791,19 @@
       <c r="I14" s="11">
         <v>3</v>
       </c>
-      <c r="J14" s="49" t="s">
+      <c r="J14" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="11">
+        <v>254.7</v>
+      </c>
+      <c r="E15" s="41" t="s">
         <v>106</v>
-      </c>
-      <c r="D15" s="9">
-        <v>254.7</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>70</v>
@@ -1723,19 +1811,19 @@
       <c r="I15" s="11">
         <v>30</v>
       </c>
-      <c r="J15" s="49" t="s">
+      <c r="J15" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C16" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D16" s="11">
         <v>402.65</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>134</v>
+      <c r="E16" s="41" t="s">
+        <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>71</v>
@@ -1743,19 +1831,19 @@
       <c r="I16" s="11">
         <v>0.5</v>
       </c>
-      <c r="J16" s="49" t="s">
+      <c r="J16" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="9">
+      <c r="C17" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="11">
         <v>29.405555</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>88</v>
+      <c r="E17" s="41" t="s">
+        <v>85</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>72</v>
@@ -1763,18 +1851,18 @@
       <c r="I17" s="11">
         <v>33.125</v>
       </c>
-      <c r="J17" s="49" t="s">
+      <c r="J17" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="11">
         <v>1140</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="41" t="s">
         <v>55</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -1783,343 +1871,349 @@
       <c r="I18" s="11">
         <v>61.6875</v>
       </c>
-      <c r="J18" s="49" t="s">
+      <c r="J18" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C19" s="2"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="2"/>
+      <c r="C19" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="11">
+        <v>2480</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>204</v>
+      </c>
       <c r="H19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I19" s="11">
         <v>7.25</v>
       </c>
-      <c r="J19" s="49" t="s">
+      <c r="J19" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C20" s="2"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="2"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="41"/>
       <c r="H20" s="2" t="s">
         <v>75</v>
       </c>
       <c r="I20" s="11">
         <v>30</v>
       </c>
-      <c r="J20" s="49" t="s">
+      <c r="J20" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C21" s="2"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="2"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="41"/>
       <c r="H21" s="2" t="s">
         <v>76</v>
       </c>
       <c r="I21" s="11">
         <v>45</v>
       </c>
-      <c r="J21" s="49" t="s">
+      <c r="J21" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C22" s="2"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="2"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="41"/>
       <c r="H22" s="2" t="s">
         <v>77</v>
       </c>
       <c r="I22" s="11">
         <v>22.5</v>
       </c>
-      <c r="J22" s="49" t="s">
+      <c r="J22" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C23" s="2"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="2"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="41"/>
       <c r="H23" s="2" t="s">
         <v>78</v>
       </c>
       <c r="I23" s="11">
         <v>20.5</v>
       </c>
-      <c r="J23" s="49" t="s">
+      <c r="J23" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C24" s="2"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="2"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="41"/>
       <c r="H24" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I24" s="11">
         <v>15</v>
       </c>
-      <c r="J24" s="49" t="s">
+      <c r="J24" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C25" s="2"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="2"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="41"/>
       <c r="H25" s="2" t="s">
         <v>80</v>
       </c>
       <c r="I25" s="11">
         <v>25</v>
       </c>
-      <c r="J25" s="49" t="s">
+      <c r="J25" s="41" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C26" s="2"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="2"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="41"/>
       <c r="H26" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I26" s="11">
         <v>26.25</v>
       </c>
-      <c r="J26" s="49" t="s">
-        <v>88</v>
+      <c r="J26" s="41" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C27" s="2"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="2"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="41"/>
       <c r="H27" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I27" s="11">
         <v>19.443999999999999</v>
       </c>
-      <c r="J27" s="49" t="s">
-        <v>88</v>
+      <c r="J27" s="41" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C28" s="2"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="2"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="41"/>
       <c r="H28" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I28" s="11">
         <v>1.5</v>
       </c>
-      <c r="J28" s="49" t="s">
-        <v>93</v>
+      <c r="J28" s="41" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C29" s="2"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="2"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="41"/>
       <c r="H29" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I29" s="11">
         <v>1.5</v>
       </c>
-      <c r="J29" s="49" t="s">
-        <v>93</v>
+      <c r="J29" s="41" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C30" s="2"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="2"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="41"/>
       <c r="H30" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I30" s="11">
         <v>2.25</v>
       </c>
-      <c r="J30" s="49" t="s">
-        <v>93</v>
+      <c r="J30" s="41" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C31" s="2"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="2"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="41"/>
       <c r="H31" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I31" s="11">
         <v>3</v>
       </c>
-      <c r="J31" s="49" t="s">
-        <v>93</v>
+      <c r="J31" s="41" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C32" s="2"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="2"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="41"/>
       <c r="H32" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I32" s="11">
         <v>6</v>
       </c>
-      <c r="J32" s="49" t="s">
-        <v>93</v>
+      <c r="J32" s="41" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C33" s="2"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="2"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="41"/>
       <c r="H33" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I33" s="11">
         <v>25</v>
       </c>
-      <c r="J33" s="49" t="s">
-        <v>109</v>
+      <c r="J33" s="41" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C34" s="2"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="2"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="41"/>
       <c r="H34" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I34" s="11">
         <v>20</v>
       </c>
-      <c r="J34" s="49" t="s">
-        <v>109</v>
+      <c r="J34" s="41" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C35" s="2"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="2"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="41"/>
       <c r="H35" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I35" s="11">
         <v>0.5</v>
       </c>
-      <c r="J35" s="49" t="s">
-        <v>114</v>
+      <c r="J35" s="41" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C36" s="2"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="2"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="41"/>
       <c r="H36" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I36" s="11">
         <v>0.5</v>
       </c>
-      <c r="J36" s="49" t="s">
-        <v>114</v>
+      <c r="J36" s="41" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C37" s="2"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="2"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="41"/>
       <c r="H37" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I37" s="11">
         <v>49.332999999999998</v>
       </c>
-      <c r="J37" s="49" t="s">
-        <v>134</v>
+      <c r="J37" s="41" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C38" s="3"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="3"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="43"/>
       <c r="H38" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I38" s="11">
         <v>12</v>
       </c>
-      <c r="J38" s="49" t="s">
-        <v>134</v>
+      <c r="J38" s="41" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H39" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I39" s="11">
         <v>45</v>
       </c>
-      <c r="J39" s="49" t="s">
-        <v>134</v>
+      <c r="J39" s="41" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H40" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I40" s="11">
         <v>61.7</v>
       </c>
-      <c r="J40" s="49" t="s">
-        <v>134</v>
+      <c r="J40" s="41" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H41" s="39" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I41" s="11">
         <v>10</v>
       </c>
-      <c r="J41" s="49" t="s">
-        <v>154</v>
+      <c r="J41" s="41" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H42" s="39" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I42" s="11">
         <v>10</v>
       </c>
-      <c r="J42" s="49" t="s">
-        <v>154</v>
+      <c r="J42" s="41" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H43" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I43" s="11">
         <v>5</v>
       </c>
-      <c r="J43" s="49" t="s">
-        <v>134</v>
+      <c r="J43" s="41" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="3:10" x14ac:dyDescent="0.35">
@@ -2129,455 +2223,386 @@
       <c r="I44" s="11">
         <v>10</v>
       </c>
-      <c r="J44" s="49" t="s">
+      <c r="J44" s="41" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="45" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H45" s="39" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I45" s="38">
         <v>12.5</v>
       </c>
-      <c r="J45" s="50" t="s">
-        <v>168</v>
+      <c r="J45" s="42" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H46" s="39" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I46" s="38">
         <v>12.5</v>
       </c>
-      <c r="J46" s="50" t="s">
-        <v>168</v>
+      <c r="J46" s="42" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H47" s="39" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I47" s="38">
         <v>150</v>
       </c>
-      <c r="J47" s="50" t="s">
-        <v>168</v>
+      <c r="J47" s="42" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H48" s="54" t="s">
-        <v>197</v>
+      <c r="H48" s="46" t="s">
+        <v>189</v>
       </c>
       <c r="I48" s="38">
         <v>2</v>
       </c>
-      <c r="J48" s="49" t="s">
-        <v>180</v>
+      <c r="J48" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H49" s="39" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="I49" s="38">
         <v>2</v>
       </c>
-      <c r="J49" s="49" t="s">
-        <v>180</v>
+      <c r="J49" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H50" s="39" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="I50" s="38">
         <v>2</v>
       </c>
-      <c r="J50" s="49" t="s">
-        <v>180</v>
+      <c r="J50" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H51" s="39" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="I51" s="38">
         <v>5</v>
       </c>
-      <c r="J51" s="49" t="s">
-        <v>180</v>
+      <c r="J51" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H52" s="39" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I52" s="38">
         <v>5</v>
       </c>
-      <c r="J52" s="49" t="s">
-        <v>180</v>
+      <c r="J52" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H53" s="39" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I53" s="38">
         <v>5</v>
       </c>
-      <c r="J53" s="49" t="s">
-        <v>180</v>
+      <c r="J53" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H54" s="39" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="I54" s="38">
         <v>5</v>
       </c>
-      <c r="J54" s="49" t="s">
-        <v>180</v>
+      <c r="J54" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H55" s="39" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I55" s="11">
         <v>5</v>
       </c>
-      <c r="J55" s="49" t="s">
-        <v>180</v>
+      <c r="J55" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="56" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H56" s="39" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="I56" s="11">
         <v>5</v>
       </c>
-      <c r="J56" s="49" t="s">
-        <v>180</v>
+      <c r="J56" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H57" s="39" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="I57" s="11">
         <v>5</v>
       </c>
-      <c r="J57" s="49" t="s">
-        <v>180</v>
+      <c r="J57" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H58" s="39" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I58" s="11">
         <v>5</v>
       </c>
-      <c r="J58" s="49" t="s">
-        <v>180</v>
+      <c r="J58" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H59" s="39" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I59" s="11">
         <v>5</v>
       </c>
-      <c r="J59" s="49" t="s">
-        <v>180</v>
+      <c r="J59" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H60" s="39" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="I60" s="11">
         <v>5</v>
       </c>
-      <c r="J60" s="49" t="s">
-        <v>180</v>
+      <c r="J60" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H61" s="39" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="I61" s="11">
         <v>11.41666</v>
       </c>
-      <c r="J61" s="49" t="s">
-        <v>180</v>
+      <c r="J61" s="41" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H62" s="2"/>
       <c r="I62" s="11"/>
-      <c r="J62" s="49"/>
+      <c r="J62" s="41"/>
     </row>
     <row r="63" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H63" s="2"/>
       <c r="I63" s="11"/>
-      <c r="J63" s="49"/>
+      <c r="J63" s="41"/>
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H64" s="2"/>
       <c r="I64" s="11"/>
-      <c r="J64" s="49"/>
+      <c r="J64" s="41"/>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H65" s="2"/>
       <c r="I65" s="11"/>
-      <c r="J65" s="49"/>
+      <c r="J65" s="41"/>
     </row>
     <row r="66" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H66" s="2"/>
       <c r="I66" s="11"/>
-      <c r="J66" s="49"/>
+      <c r="J66" s="41"/>
     </row>
     <row r="67" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C67" s="46"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
       <c r="H67" s="2"/>
       <c r="I67" s="11"/>
-      <c r="J67" s="49"/>
+      <c r="J67" s="41"/>
     </row>
     <row r="68" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C68" s="47"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
+      <c r="C68" s="1"/>
       <c r="H68" s="2"/>
       <c r="I68" s="11"/>
-      <c r="J68" s="49"/>
+      <c r="J68" s="41"/>
     </row>
     <row r="69" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
+      <c r="C69" s="1"/>
       <c r="H69" s="2"/>
       <c r="I69" s="11"/>
-      <c r="J69" s="49"/>
+      <c r="J69" s="41"/>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
+      <c r="C70" s="1"/>
       <c r="H70" s="2"/>
       <c r="I70" s="11"/>
-      <c r="J70" s="49"/>
+      <c r="J70" s="41"/>
     </row>
     <row r="71" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
+      <c r="C71" s="1"/>
       <c r="H71" s="2"/>
       <c r="I71" s="11"/>
-      <c r="J71" s="49"/>
+      <c r="J71" s="41"/>
     </row>
     <row r="72" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C72" s="47"/>
-      <c r="D72" s="47"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
+      <c r="C72" s="1"/>
       <c r="H72" s="2"/>
       <c r="I72" s="11"/>
-      <c r="J72" s="49"/>
+      <c r="J72" s="41"/>
     </row>
     <row r="73" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C73" s="47"/>
-      <c r="D73" s="47"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="46"/>
+      <c r="C73" s="1"/>
       <c r="H73" s="2"/>
       <c r="I73" s="11"/>
-      <c r="J73" s="49"/>
+      <c r="J73" s="41"/>
     </row>
     <row r="74" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C74" s="47"/>
-      <c r="D74" s="47"/>
-      <c r="E74" s="46"/>
-      <c r="F74" s="46"/>
+      <c r="C74" s="1"/>
       <c r="H74" s="2"/>
       <c r="I74" s="11"/>
-      <c r="J74" s="49"/>
+      <c r="J74" s="41"/>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C75" s="47"/>
-      <c r="D75" s="47"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
+      <c r="C75" s="1"/>
       <c r="H75" s="2"/>
       <c r="I75" s="11"/>
-      <c r="J75" s="49"/>
+      <c r="J75" s="41"/>
     </row>
     <row r="76" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
+      <c r="C76" s="1"/>
       <c r="H76" s="2"/>
       <c r="I76" s="11"/>
-      <c r="J76" s="49"/>
+      <c r="J76" s="41"/>
     </row>
     <row r="77" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C77" s="47"/>
-      <c r="D77" s="47"/>
-      <c r="E77" s="46"/>
-      <c r="F77" s="46"/>
+      <c r="C77" s="1"/>
       <c r="H77" s="2"/>
       <c r="I77" s="11"/>
-      <c r="J77" s="49"/>
+      <c r="J77" s="41"/>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C78" s="47"/>
-      <c r="D78" s="47"/>
-      <c r="E78" s="46"/>
-      <c r="F78" s="46"/>
+      <c r="C78" s="1"/>
       <c r="H78" s="2"/>
       <c r="I78" s="11"/>
-      <c r="J78" s="49"/>
+      <c r="J78" s="41"/>
     </row>
     <row r="79" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C79" s="47"/>
-      <c r="D79" s="47"/>
-      <c r="E79" s="46"/>
-      <c r="F79" s="46"/>
+      <c r="C79" s="1"/>
       <c r="H79" s="2"/>
       <c r="I79" s="11"/>
-      <c r="J79" s="49"/>
+      <c r="J79" s="41"/>
     </row>
     <row r="80" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C80" s="47"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="46"/>
-      <c r="F80" s="46"/>
+      <c r="C80" s="1"/>
       <c r="H80" s="2"/>
       <c r="I80" s="11"/>
-      <c r="J80" s="49"/>
+      <c r="J80" s="41"/>
     </row>
     <row r="81" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C81" s="47"/>
-      <c r="D81" s="47"/>
-      <c r="E81" s="46"/>
-      <c r="F81" s="46"/>
+      <c r="C81" s="1"/>
       <c r="H81" s="2"/>
       <c r="I81" s="11"/>
-      <c r="J81" s="49"/>
+      <c r="J81" s="41"/>
     </row>
     <row r="82" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C82" s="47"/>
-      <c r="D82" s="47"/>
-      <c r="E82" s="46"/>
-      <c r="F82" s="46"/>
+      <c r="C82" s="1"/>
       <c r="H82" s="2"/>
       <c r="I82" s="11"/>
-      <c r="J82" s="49"/>
+      <c r="J82" s="41"/>
     </row>
     <row r="83" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C83" s="46"/>
-      <c r="D83" s="47"/>
-      <c r="E83" s="46"/>
-      <c r="F83" s="46"/>
       <c r="H83" s="2"/>
       <c r="I83" s="11"/>
-      <c r="J83" s="49"/>
+      <c r="J83" s="41"/>
     </row>
     <row r="84" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C84" s="46"/>
-      <c r="D84" s="47"/>
-      <c r="E84" s="46"/>
-      <c r="F84" s="46"/>
       <c r="H84" s="2"/>
       <c r="I84" s="11"/>
-      <c r="J84" s="49"/>
+      <c r="J84" s="41"/>
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C85" s="46"/>
-      <c r="D85" s="47"/>
-      <c r="E85" s="46"/>
-      <c r="F85" s="46"/>
       <c r="H85" s="2"/>
       <c r="I85" s="11"/>
-      <c r="J85" s="49"/>
+      <c r="J85" s="41"/>
     </row>
     <row r="86" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C86" s="46"/>
-      <c r="D86" s="47"/>
-      <c r="E86" s="46"/>
-      <c r="F86" s="46"/>
       <c r="H86" s="2"/>
       <c r="I86" s="11"/>
-      <c r="J86" s="49"/>
+      <c r="J86" s="41"/>
     </row>
     <row r="87" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C87" s="46"/>
-      <c r="D87" s="47"/>
-      <c r="E87" s="46"/>
-      <c r="F87" s="46"/>
       <c r="H87" s="2"/>
       <c r="I87" s="11"/>
-      <c r="J87" s="49"/>
+      <c r="J87" s="41"/>
     </row>
     <row r="88" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H88" s="2"/>
       <c r="I88" s="11"/>
-      <c r="J88" s="49"/>
+      <c r="J88" s="41"/>
     </row>
     <row r="89" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H89" s="2"/>
       <c r="I89" s="11"/>
-      <c r="J89" s="49"/>
+      <c r="J89" s="41"/>
     </row>
     <row r="90" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H90" s="2"/>
       <c r="I90" s="11"/>
-      <c r="J90" s="49"/>
+      <c r="J90" s="41"/>
     </row>
     <row r="91" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H91" s="2"/>
       <c r="I91" s="11"/>
-      <c r="J91" s="49"/>
+      <c r="J91" s="41"/>
     </row>
     <row r="92" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H92" s="2"/>
       <c r="I92" s="11"/>
-      <c r="J92" s="49"/>
+      <c r="J92" s="41"/>
     </row>
     <row r="93" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H93" s="2"/>
       <c r="I93" s="11"/>
-      <c r="J93" s="49"/>
+      <c r="J93" s="41"/>
     </row>
     <row r="94" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H94" s="2"/>
       <c r="I94" s="11"/>
-      <c r="J94" s="49"/>
+      <c r="J94" s="41"/>
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H95" s="2"/>
       <c r="I95" s="11"/>
-      <c r="J95" s="49"/>
+      <c r="J95" s="41"/>
     </row>
     <row r="96" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H96" s="3"/>
-      <c r="I96" s="53"/>
-      <c r="J96" s="51"/>
+      <c r="I96" s="45"/>
+      <c r="J96" s="43"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:E18">
@@ -2613,7 +2638,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.35">
@@ -2629,7 +2654,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
@@ -2645,7 +2670,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
@@ -2653,7 +2678,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
@@ -2669,22 +2694,22 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="J10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="42"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="52"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -2707,13 +2732,13 @@
         <v>24</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F12" s="8">
         <v>300</v>
@@ -2722,7 +2747,7 @@
         <v>23</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K12" s="8">
         <v>25</v>
@@ -2731,14 +2756,14 @@
         <v>8</v>
       </c>
       <c r="M12" s="19"/>
-      <c r="O12" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
+      <c r="O12" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="53"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
@@ -2752,7 +2777,7 @@
         <v>19</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K13" s="9">
         <v>254.7</v>
@@ -2761,12 +2786,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="53"/>
+      <c r="T13" s="53"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -2783,12 +2808,12 @@
         <v>25</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="53"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -2796,7 +2821,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="2"/>
       <c r="J15" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K15" s="9">
         <v>20</v>
@@ -2805,12 +2830,12 @@
         <v>8</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="53"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -2818,23 +2843,23 @@
       <c r="F16" s="9"/>
       <c r="G16" s="2"/>
       <c r="J16" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K16" s="9">
         <v>7.5</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="O16" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
+      <c r="O16" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="53"/>
+      <c r="T16" s="53"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
@@ -2848,15 +2873,15 @@
         <v>42</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="53"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
@@ -2864,21 +2889,21 @@
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K18" s="9">
         <v>210</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="53"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -2892,15 +2917,15 @@
         <v>280</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="53"/>
+      <c r="T19" s="53"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -2908,13 +2933,13 @@
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K20" s="9">
         <v>2.8</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M20" s="2"/>
     </row>
@@ -2927,14 +2952,14 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="44"/>
-      <c r="S21" s="44"/>
-      <c r="T21" s="44"/>
+      <c r="O21" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="23"/>
@@ -2955,14 +2980,14 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="43"/>
+      <c r="O23" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="53"/>
+      <c r="T23" s="53"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="23"/>
@@ -2973,12 +2998,12 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
-      <c r="T24" s="43"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
+      <c r="R24" s="53"/>
+      <c r="S24" s="53"/>
+      <c r="T24" s="53"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
@@ -2989,12 +3014,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="53"/>
+      <c r="S25" s="53"/>
+      <c r="T25" s="53"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -3005,12 +3030,12 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -3021,14 +3046,14 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="43"/>
-      <c r="R27" s="43"/>
-      <c r="S27" s="43"/>
-      <c r="T27" s="43"/>
+      <c r="O27" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="53"/>
+      <c r="T27" s="53"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -3039,12 +3064,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="43"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="53"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C29" s="23"/>
@@ -3055,12 +3080,12 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="43"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="43"/>
-      <c r="R29" s="43"/>
-      <c r="S29" s="43"/>
-      <c r="T29" s="43"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="53"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="53"/>
+      <c r="S29" s="53"/>
+      <c r="T29" s="53"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -3071,12 +3096,12 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="43"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="43"/>
-      <c r="R30" s="43"/>
-      <c r="S30" s="43"/>
-      <c r="T30" s="43"/>
+      <c r="O30" s="53"/>
+      <c r="P30" s="53"/>
+      <c r="Q30" s="53"/>
+      <c r="R30" s="53"/>
+      <c r="S30" s="53"/>
+      <c r="T30" s="53"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -3245,7 +3270,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="87" x14ac:dyDescent="0.35">
@@ -3253,7 +3278,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
@@ -3277,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -3285,7 +3310,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -3293,7 +3318,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3301,21 +3326,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="J10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -3350,7 +3375,7 @@
         <v>60</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K12" s="8">
         <v>0.5</v>
@@ -3371,7 +3396,7 @@
         <v>62</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K13" s="9">
         <v>0.5</v>
@@ -3419,7 +3444,7 @@
         <v>42</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="9"/>
@@ -3428,13 +3453,13 @@
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F17" s="9">
         <v>7.5</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="9"/>
@@ -3706,7 +3731,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
@@ -3722,7 +3747,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -3738,7 +3763,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -3746,7 +3771,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -3754,7 +3779,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3762,21 +3787,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="J10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -3802,7 +3827,7 @@
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F12" s="8">
         <v>600</v>
@@ -3811,7 +3836,7 @@
         <v>60</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K12" s="8">
         <v>49.332999999999998</v>
@@ -3832,7 +3857,7 @@
         <v>60</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K13" s="9">
         <v>246.666</v>
@@ -3853,7 +3878,7 @@
         <v>60</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K14" s="9">
         <v>12</v>
@@ -3874,7 +3899,7 @@
         <v>60</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K15" s="9">
         <v>45</v>
@@ -3892,10 +3917,10 @@
         <v>240</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K16" s="9">
         <v>62</v>
@@ -3913,16 +3938,16 @@
         <v>246.67</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K17" s="9">
         <v>7.35</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
@@ -3931,7 +3956,7 @@
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K18" s="9">
         <v>402.65</v>
@@ -3946,13 +3971,13 @@
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
       <c r="J19" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K19" s="9">
         <v>160</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
@@ -3961,7 +3986,7 @@
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K20" s="9">
         <v>5</v>
@@ -3976,13 +4001,13 @@
       <c r="F21" s="9"/>
       <c r="G21" s="2"/>
       <c r="J21" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K21" s="9">
         <v>150</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
@@ -3991,13 +4016,13 @@
       <c r="F22" s="9"/>
       <c r="G22" s="2"/>
       <c r="J22" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K22" s="9">
         <v>0.3</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
@@ -4220,7 +4245,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="74.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4228,7 +4253,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
@@ -4252,7 +4277,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -4260,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -4268,7 +4293,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4276,21 +4301,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="J10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -4322,13 +4347,13 @@
         <v>1272.67</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J12" s="38">
         <v>10</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>8</v>
@@ -4337,19 +4362,19 @@
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F13" s="9">
         <v>606</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J13" s="38">
         <v>10</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>8</v>
@@ -4358,13 +4383,13 @@
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F14" s="9">
         <v>300</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J14" s="38"/>
       <c r="K14" s="9"/>
@@ -4388,13 +4413,13 @@
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F16" s="9">
         <v>210</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J16" s="38"/>
       <c r="K16" s="9"/>
@@ -4409,7 +4434,7 @@
         <v>280</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J17" s="38"/>
       <c r="K17" s="9"/>
@@ -4433,13 +4458,13 @@
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
       <c r="E19" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F19" s="9">
         <v>160</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="9"/>
@@ -4692,7 +4717,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
@@ -4700,7 +4725,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
@@ -4716,7 +4741,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
@@ -4724,7 +4749,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -4732,7 +4757,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -4740,7 +4765,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4748,21 +4773,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="J10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -4809,19 +4834,19 @@
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F13" s="9">
         <v>300</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J13" s="38">
         <v>12.5</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>8</v>
@@ -4842,7 +4867,7 @@
         <v>12.5</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>8</v>
@@ -4851,19 +4876,19 @@
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F15" s="9">
         <v>150</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J15" s="38">
         <v>150</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>8</v>
@@ -5144,6 +5169,389 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E137B09C-4CA4-4E20-A3F8-D228D24259AF}">
+  <dimension ref="C2:M27"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="3:13" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="41"/>
+    </row>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C7" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C8" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C9" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F11" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="58"/>
+      <c r="H11" s="59"/>
+      <c r="K11" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="58"/>
+      <c r="M11" s="59"/>
+    </row>
+    <row r="12" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F12" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="L12" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="F13" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="H13" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="M13" s="42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="F14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="H14" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="K14" s="6">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="M14" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="F15" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="2">
+        <v>7.35</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="K15" s="6">
+        <v>2</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="M15" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="F16" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="6">
+        <v>5</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="M16" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="F17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="2">
+        <v>13.2</v>
+      </c>
+      <c r="H17" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="K17" s="6">
+        <v>5</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="M17" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="F18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="2">
+        <v>19</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="K18" s="6">
+        <v>5</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="M18" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="F19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="2">
+        <v>30.4666</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="K19" s="6">
+        <v>5</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="M19" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="F20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="2">
+        <v>30.4666</v>
+      </c>
+      <c r="H20" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="K20" s="6">
+        <v>5</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="M20" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="F21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="2">
+        <v>150</v>
+      </c>
+      <c r="H21" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" s="6">
+        <v>5</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="M21" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="F22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="2">
+        <v>150</v>
+      </c>
+      <c r="H22" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="6">
+        <v>5</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="M22" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="6:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="3">
+        <v>461.41665999999998</v>
+      </c>
+      <c r="H23" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="6">
+        <v>5</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="M23" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="K24" s="6">
+        <v>5</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="M24" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="K25" s="6">
+        <v>5</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="M25" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="K26" s="6">
+        <v>11.41666</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="M26" s="41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="6:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K27" s="7">
+        <v>391.64166599999999</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="K11:M11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BAE874B-EB1A-40E9-945A-ABFDF311093C}">
   <dimension ref="B1:L44"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5152,10 +5560,11 @@
     <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.90625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -5164,15 +5573,15 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" ht="58" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="45" t="s">
-        <v>193</v>
+      <c r="C3" s="47" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
@@ -5187,14 +5596,16 @@
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="25"/>
+      <c r="C5" s="25" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -5202,7 +5613,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -5210,7 +5621,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>51</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5218,21 +5629,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="J10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -5258,293 +5669,191 @@
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
-        <v>160</v>
+        <v>61</v>
       </c>
       <c r="F12" s="8">
-        <v>0.3</v>
+        <v>2214.2849999999999</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="J12" s="38">
-        <v>2</v>
+        <v>2480</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="F13" s="9">
-        <v>2.8</v>
+        <v>620</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="38">
-        <v>2</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="J13" s="38"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F14" s="9">
-        <v>7.35</v>
+        <v>1148.5714</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="J14" s="38">
-        <v>2</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="J14" s="38"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="F15" s="9">
-        <v>9.6</v>
+        <v>180</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="38">
-        <v>5</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="J15" s="38"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="4"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F16" s="9">
-        <v>13.2</v>
+        <v>1240</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="38">
-        <v>5</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="J16" s="38"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="4"/>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="F17" s="9">
-        <v>19</v>
+        <v>744</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J17" s="38">
-        <v>5</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="J17" s="38"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="4"/>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
       <c r="E18" s="2" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="F18" s="9">
-        <v>30.4666</v>
+        <v>1680</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="J18" s="38">
-        <v>5</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="J18" s="38"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="4"/>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
       <c r="E19" s="2" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="F19" s="9">
-        <v>30.4666</v>
+        <v>180</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="J19" s="11">
-        <v>5</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>8</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="J19" s="11"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="4"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
-      <c r="E20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="9">
-        <v>150</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="11">
-        <v>5</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="2"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="4"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C21" s="23"/>
-      <c r="E21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="9">
-        <v>150</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="11">
-        <v>5</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="2"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="4"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C22" s="23"/>
-      <c r="E22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="9">
-        <v>461.41665999999998</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="11">
-        <v>5</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="2"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
       <c r="G23" s="2"/>
-      <c r="J23" s="11">
-        <v>5</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
       <c r="G24" s="2"/>
-      <c r="J24" s="11">
-        <v>5</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="J24" s="11"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="4"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
-      <c r="J25" s="11">
-        <v>11.41666</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="J25" s="11"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="4"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
       <c r="G26" s="2"/>
-      <c r="J26" s="11">
-        <v>391.64166599999999</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="4"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -5732,16 +6041,16 @@
       <c r="D4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="42"/>
-      <c r="K4" s="40" t="s">
+      <c r="G4" s="51"/>
+      <c r="H4" s="52"/>
+      <c r="K4" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="41"/>
-      <c r="M4" s="42"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="52"/>
     </row>
     <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="17" t="s">
@@ -6153,7 +6462,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="3:21" x14ac:dyDescent="0.35">
@@ -6198,17 +6507,17 @@
     </row>
     <row r="12" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="13" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="42"/>
-      <c r="K13" s="40" t="s">
+      <c r="G13" s="51"/>
+      <c r="H13" s="52"/>
+      <c r="K13" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="42"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="52"/>
     </row>
     <row r="14" spans="3:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F14" s="14" t="s">
@@ -6230,16 +6539,16 @@
         <v>24</v>
       </c>
       <c r="N14" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="P14" s="53" t="s">
         <v>115</v>
       </c>
-      <c r="P14" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="53"/>
+      <c r="U14" s="53"/>
     </row>
     <row r="15" spans="3:21" x14ac:dyDescent="0.35">
       <c r="F15" s="4" t="s">
@@ -6261,12 +6570,12 @@
         <v>25</v>
       </c>
       <c r="N15" s="19"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="53"/>
+      <c r="U15" s="53"/>
     </row>
     <row r="16" spans="3:21" x14ac:dyDescent="0.35">
       <c r="F16" s="2" t="s">
@@ -6288,14 +6597,14 @@
         <v>55</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
+        <v>117</v>
+      </c>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="53"/>
+      <c r="T16" s="53"/>
+      <c r="U16" s="53"/>
     </row>
     <row r="17" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
@@ -6311,14 +6620,14 @@
         <v>81</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
+        <v>116</v>
+      </c>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="53"/>
+      <c r="U17" s="53"/>
     </row>
     <row r="18" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
@@ -6331,10 +6640,10 @@
         <v>37.5</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="6:21" x14ac:dyDescent="0.35">
@@ -6342,16 +6651,16 @@
       <c r="G19" s="9"/>
       <c r="H19" s="2"/>
       <c r="K19" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L19" s="9">
         <v>234.25</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="6:21" x14ac:dyDescent="0.35">
@@ -6365,17 +6674,17 @@
         <v>150</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="P20" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
-      <c r="S20" s="44"/>
-      <c r="T20" s="44"/>
-      <c r="U20" s="44"/>
+      <c r="P20" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
+      <c r="U20" s="54"/>
     </row>
     <row r="21" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F21" s="2"/>
@@ -6394,14 +6703,14 @@
       <c r="L22" s="9"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="P22" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43"/>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="43"/>
+      <c r="P22" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="53"/>
+      <c r="T22" s="53"/>
+      <c r="U22" s="53"/>
     </row>
     <row r="23" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F23" s="2"/>
@@ -6411,12 +6720,12 @@
       <c r="L23" s="9"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="43"/>
-      <c r="U23" s="43"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="53"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
     </row>
     <row r="24" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F24" s="2"/>
@@ -6426,12 +6735,12 @@
       <c r="L24" s="9"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="43"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
+      <c r="R24" s="53"/>
+      <c r="S24" s="53"/>
+      <c r="T24" s="53"/>
+      <c r="U24" s="53"/>
     </row>
     <row r="25" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F25" s="2"/>
@@ -6441,12 +6750,12 @@
       <c r="L25" s="9"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="53"/>
+      <c r="S25" s="53"/>
+      <c r="T25" s="53"/>
+      <c r="U25" s="53"/>
     </row>
     <row r="26" spans="6:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F26" s="2"/>
@@ -6456,14 +6765,14 @@
       <c r="L26" s="9"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
-      <c r="P26" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
+      <c r="P26" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
+      <c r="U26" s="53"/>
     </row>
     <row r="27" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F27" s="2"/>
@@ -6473,12 +6782,12 @@
       <c r="L27" s="9"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="43"/>
-      <c r="R27" s="43"/>
-      <c r="S27" s="43"/>
-      <c r="T27" s="43"/>
-      <c r="U27" s="43"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="53"/>
+      <c r="T27" s="53"/>
+      <c r="U27" s="53"/>
     </row>
     <row r="28" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F28" s="2"/>
@@ -6488,12 +6797,12 @@
       <c r="L28" s="9"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="53"/>
+      <c r="U28" s="53"/>
     </row>
     <row r="29" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F29" s="2"/>
@@ -6503,12 +6812,12 @@
       <c r="L29" s="9"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="43"/>
-      <c r="R29" s="43"/>
-      <c r="S29" s="43"/>
-      <c r="T29" s="43"/>
-      <c r="U29" s="43"/>
+      <c r="P29" s="53"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="53"/>
+      <c r="S29" s="53"/>
+      <c r="T29" s="53"/>
+      <c r="U29" s="53"/>
     </row>
     <row r="30" spans="6:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F30" s="2"/>
@@ -6518,14 +6827,14 @@
       <c r="L30" s="9"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="P30" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q30" s="43"/>
-      <c r="R30" s="43"/>
-      <c r="S30" s="43"/>
-      <c r="T30" s="43"/>
-      <c r="U30" s="43"/>
+      <c r="P30" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q30" s="53"/>
+      <c r="R30" s="53"/>
+      <c r="S30" s="53"/>
+      <c r="T30" s="53"/>
+      <c r="U30" s="53"/>
     </row>
     <row r="31" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
@@ -6535,12 +6844,12 @@
       <c r="L31" s="9"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="43"/>
+      <c r="P31" s="53"/>
+      <c r="Q31" s="53"/>
+      <c r="R31" s="53"/>
+      <c r="S31" s="53"/>
+      <c r="T31" s="53"/>
+      <c r="U31" s="53"/>
     </row>
     <row r="32" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
@@ -6550,12 +6859,12 @@
       <c r="L32" s="9"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-      <c r="P32" s="43"/>
-      <c r="Q32" s="43"/>
-      <c r="R32" s="43"/>
-      <c r="S32" s="43"/>
-      <c r="T32" s="43"/>
-      <c r="U32" s="43"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="53"/>
+      <c r="S32" s="53"/>
+      <c r="T32" s="53"/>
+      <c r="U32" s="53"/>
     </row>
     <row r="33" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F33" s="2"/>
@@ -6565,12 +6874,12 @@
       <c r="L33" s="9"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
-      <c r="P33" s="43"/>
-      <c r="Q33" s="43"/>
-      <c r="R33" s="43"/>
-      <c r="S33" s="43"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="43"/>
+      <c r="P33" s="53"/>
+      <c r="Q33" s="53"/>
+      <c r="R33" s="53"/>
+      <c r="S33" s="53"/>
+      <c r="T33" s="53"/>
+      <c r="U33" s="53"/>
     </row>
     <row r="34" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
@@ -6752,7 +7061,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -6768,7 +7077,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -6776,7 +7085,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -6792,7 +7101,7 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6800,16 +7109,16 @@
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="42"/>
-      <c r="J11" s="40" t="s">
+      <c r="F11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="J11" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="42"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="52"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -6886,7 +7195,7 @@
         <v>18</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
@@ -6901,7 +7210,7 @@
         <v>158.333</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
@@ -6916,7 +7225,7 @@
         <v>9.6</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
@@ -7211,7 +7520,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
@@ -7259,17 +7568,17 @@
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="42"/>
-      <c r="J11" s="40" t="s">
+      <c r="F11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="J11" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="42"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="52"/>
     </row>
     <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -7292,16 +7601,16 @@
         <v>24</v>
       </c>
       <c r="M12" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="O12" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
+        <v>112</v>
+      </c>
+      <c r="O12" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="53"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
@@ -7325,12 +7634,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="19"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
+      <c r="O13" s="53"/>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="53"/>
+      <c r="T13" s="53"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -7353,14 +7662,14 @@
         <v>81</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
+        <v>114</v>
+      </c>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
+      <c r="T14" s="53"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -7374,17 +7683,17 @@
         <v>104.65</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
+        <v>114</v>
+      </c>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
+      <c r="T15" s="53"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -7398,19 +7707,19 @@
         <v>113.833</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="O16" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
+      <c r="O16" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="53"/>
+      <c r="T16" s="53"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
@@ -7424,17 +7733,17 @@
         <v>246.67</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
+        <v>130</v>
+      </c>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="53"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
@@ -7448,15 +7757,15 @@
         <v>1272.67</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="53"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -7464,21 +7773,21 @@
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
       <c r="J19" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K19" s="9">
         <v>13.2</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="53"/>
+      <c r="T19" s="53"/>
     </row>
     <row r="20" spans="3:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -7499,14 +7808,14 @@
       <c r="K21" s="9"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="44"/>
-      <c r="S21" s="44"/>
-      <c r="T21" s="44"/>
+      <c r="O21" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="23"/>
@@ -7527,14 +7836,14 @@
       <c r="K23" s="9"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="43"/>
+      <c r="O23" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="53"/>
+      <c r="T23" s="53"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="23"/>
@@ -7545,12 +7854,12 @@
       <c r="K24" s="9"/>
       <c r="L24" s="6"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
-      <c r="T24" s="43"/>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
+      <c r="R24" s="53"/>
+      <c r="S24" s="53"/>
+      <c r="T24" s="53"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
@@ -7561,12 +7870,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="6"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="53"/>
+      <c r="S25" s="53"/>
+      <c r="T25" s="53"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -7577,12 +7886,12 @@
       <c r="K26" s="9"/>
       <c r="L26" s="6"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -7593,14 +7902,14 @@
       <c r="K27" s="9"/>
       <c r="L27" s="6"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="43" t="s">
-        <v>157</v>
-      </c>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="43"/>
-      <c r="R27" s="43"/>
-      <c r="S27" s="43"/>
-      <c r="T27" s="43"/>
+      <c r="O27" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="53"/>
+      <c r="T27" s="53"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -7611,12 +7920,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="6"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="43"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="53"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C29" s="23"/>
@@ -7627,12 +7936,12 @@
       <c r="K29" s="9"/>
       <c r="L29" s="6"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="43"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="43"/>
-      <c r="R29" s="43"/>
-      <c r="S29" s="43"/>
-      <c r="T29" s="43"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="53"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="53"/>
+      <c r="S29" s="53"/>
+      <c r="T29" s="53"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -7643,12 +7952,12 @@
       <c r="K30" s="9"/>
       <c r="L30" s="6"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="43"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="43"/>
-      <c r="R30" s="43"/>
-      <c r="S30" s="43"/>
-      <c r="T30" s="43"/>
+      <c r="O30" s="53"/>
+      <c r="P30" s="53"/>
+      <c r="Q30" s="53"/>
+      <c r="R30" s="53"/>
+      <c r="S30" s="53"/>
+      <c r="T30" s="53"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -7659,14 +7968,14 @@
       <c r="K31" s="9"/>
       <c r="L31" s="6"/>
       <c r="M31" s="2"/>
-      <c r="O31" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="43"/>
+      <c r="O31" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="P31" s="53"/>
+      <c r="Q31" s="53"/>
+      <c r="R31" s="53"/>
+      <c r="S31" s="53"/>
+      <c r="T31" s="53"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C32" s="23"/>
@@ -7677,12 +7986,12 @@
       <c r="K32" s="9"/>
       <c r="L32" s="6"/>
       <c r="M32" s="2"/>
-      <c r="O32" s="43"/>
-      <c r="P32" s="43"/>
-      <c r="Q32" s="43"/>
-      <c r="R32" s="43"/>
-      <c r="S32" s="43"/>
-      <c r="T32" s="43"/>
+      <c r="O32" s="53"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="53"/>
+      <c r="S32" s="53"/>
+      <c r="T32" s="53"/>
     </row>
     <row r="33" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C33" s="23"/>
@@ -7693,12 +8002,12 @@
       <c r="K33" s="9"/>
       <c r="L33" s="6"/>
       <c r="M33" s="2"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="43"/>
-      <c r="Q33" s="43"/>
-      <c r="R33" s="43"/>
-      <c r="S33" s="43"/>
-      <c r="T33" s="43"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="53"/>
+      <c r="Q33" s="53"/>
+      <c r="R33" s="53"/>
+      <c r="S33" s="53"/>
+      <c r="T33" s="53"/>
     </row>
     <row r="34" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C34" s="23"/>
@@ -7709,12 +8018,12 @@
       <c r="K34" s="9"/>
       <c r="L34" s="6"/>
       <c r="M34" s="2"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="43"/>
-      <c r="Q34" s="43"/>
-      <c r="R34" s="43"/>
-      <c r="S34" s="43"/>
-      <c r="T34" s="43"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="53"/>
+      <c r="Q34" s="53"/>
+      <c r="R34" s="53"/>
+      <c r="S34" s="53"/>
+      <c r="T34" s="53"/>
     </row>
     <row r="35" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C35" s="23"/>
@@ -7855,16 +8164,16 @@
       <c r="C2" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="42"/>
-      <c r="J2" s="40" t="s">
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="J2" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="41"/>
-      <c r="L2" s="42"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="52"/>
     </row>
     <row r="3" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="21" t="s">
@@ -7891,14 +8200,14 @@
       <c r="L3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
+      <c r="N3" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B4" s="21" t="s">
@@ -7925,12 +8234,12 @@
       <c r="L4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="53"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="53"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B5" s="21" t="s">
@@ -7957,12 +8266,12 @@
       <c r="L5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="53"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B6" s="21" t="s">
@@ -7977,12 +8286,12 @@
       <c r="J6" s="4"/>
       <c r="K6" s="9"/>
       <c r="L6" s="2"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="53"/>
+      <c r="P6" s="53"/>
+      <c r="Q6" s="53"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="53"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B7" s="21" t="s">
@@ -8332,7 +8641,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>83</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -8340,7 +8649,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>84</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -8348,7 +8657,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8356,21 +8665,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>86</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="J10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -8861,7 +9170,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.35">
@@ -8877,7 +9186,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
@@ -8893,7 +9202,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
@@ -8901,7 +9210,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.35">
@@ -8909,7 +9218,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8917,21 +9226,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="J10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -8957,7 +9266,7 @@
     <row r="12" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F12" s="8">
         <v>1380</v>
@@ -8966,7 +9275,7 @@
         <v>60</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K12" s="8">
         <v>26.25</v>
@@ -8987,7 +9296,7 @@
         <v>60</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K13" s="9">
         <v>19.443999999999999</v>
@@ -8995,14 +9304,14 @@
       <c r="L13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
+      <c r="N13" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="O13" s="53"/>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="53"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -9016,7 +9325,7 @@
         <v>62</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K14" s="9">
         <v>440.75</v>
@@ -9024,12 +9333,12 @@
       <c r="L14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="53"/>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="53"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="53"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -9037,7 +9346,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="2"/>
       <c r="J15" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K15" s="9">
         <v>29.405550000000002</v>
@@ -9045,12 +9354,12 @@
       <c r="L15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="53"/>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="53"/>
     </row>
     <row r="16" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -9058,20 +9367,20 @@
       <c r="F16" s="9"/>
       <c r="G16" s="2"/>
       <c r="J16" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K16" s="9">
         <v>54</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
+        <v>90</v>
+      </c>
+      <c r="N16" s="53"/>
+      <c r="O16" s="53"/>
+      <c r="P16" s="53"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="53"/>
     </row>
     <row r="17" spans="3:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
@@ -9079,22 +9388,22 @@
       <c r="F17" s="9"/>
       <c r="G17" s="2"/>
       <c r="J17" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K17" s="9">
         <v>45.15</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N17" s="43" t="s">
-        <v>95</v>
-      </c>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
+        <v>90</v>
+      </c>
+      <c r="N17" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="O17" s="53"/>
+      <c r="P17" s="53"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
@@ -9102,20 +9411,20 @@
       <c r="F18" s="9"/>
       <c r="G18" s="2"/>
       <c r="J18" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K18" s="9">
         <v>300</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
+        <v>151</v>
+      </c>
+      <c r="N18" s="53"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="53"/>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -9123,20 +9432,20 @@
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K19" s="9">
         <v>606</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
+        <v>151</v>
+      </c>
+      <c r="N19" s="53"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="53"/>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -9144,20 +9453,20 @@
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K20" s="9">
         <v>19</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
+        <v>177</v>
+      </c>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C21" s="23"/>
@@ -9176,14 +9485,14 @@
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
-      <c r="N22" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="O22" s="44"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="44"/>
-      <c r="R22" s="44"/>
-      <c r="S22" s="44"/>
+      <c r="N22" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C23" s="23"/>
@@ -9202,14 +9511,14 @@
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
-      <c r="N24" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
+      <c r="N24" s="53" t="s">
+        <v>183</v>
+      </c>
+      <c r="O24" s="53"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53"/>
+      <c r="R24" s="53"/>
+      <c r="S24" s="53"/>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
@@ -9219,12 +9528,12 @@
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="53"/>
+      <c r="S25" s="53"/>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -9234,12 +9543,12 @@
       <c r="J26" s="2"/>
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -9249,12 +9558,12 @@
       <c r="J27" s="2"/>
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="43"/>
-      <c r="R27" s="43"/>
-      <c r="S27" s="43"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="53"/>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -9264,14 +9573,14 @@
       <c r="J28" s="2"/>
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
-      <c r="N28" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="O28" s="43"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
+      <c r="N28" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="O28" s="53"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C29" s="23"/>
@@ -9281,12 +9590,12 @@
       <c r="J29" s="2"/>
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="43"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="43"/>
-      <c r="R29" s="43"/>
-      <c r="S29" s="43"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="53"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="53"/>
+      <c r="S29" s="53"/>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -9296,12 +9605,12 @@
       <c r="J30" s="2"/>
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="43"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="43"/>
-      <c r="R30" s="43"/>
-      <c r="S30" s="43"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="53"/>
+      <c r="P30" s="53"/>
+      <c r="Q30" s="53"/>
+      <c r="R30" s="53"/>
+      <c r="S30" s="53"/>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -9311,12 +9620,12 @@
       <c r="J31" s="2"/>
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
+      <c r="P31" s="53"/>
+      <c r="Q31" s="53"/>
+      <c r="R31" s="53"/>
+      <c r="S31" s="53"/>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C32" s="23"/>
@@ -9462,7 +9771,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.35">
@@ -9494,7 +9803,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -9502,7 +9811,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -9510,7 +9819,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9518,21 +9827,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="J10" s="40" t="s">
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="J10" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="42"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -9567,7 +9876,7 @@
         <v>50</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K12" s="8">
         <v>1.5</v>
@@ -9588,7 +9897,7 @@
         <v>33</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K13" s="9">
         <v>1.5</v>
@@ -9609,7 +9918,7 @@
         <v>62</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K14" s="9">
         <v>2.25</v>
@@ -9621,16 +9930,16 @@
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F15" s="9">
         <v>45.15</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K15" s="9">
         <v>3</v>
@@ -9642,16 +9951,16 @@
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F16" s="9">
         <v>54</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K16" s="9">
         <v>6</v>
@@ -9669,7 +9978,7 @@
         <v>104.65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="9"/>

--- a/Game Stuff/Spreadsheet.xlsx
+++ b/Game Stuff/Spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Karn's Conduit\Game Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55E54FA-ACF8-4297-846D-DC0533CFF558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2C7DED-27D1-4DEE-8582-164F35985EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45984" yWindow="-4836" windowWidth="17472" windowHeight="15096" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
+    <workbookView xWindow="1560" yWindow="0" windowWidth="12960" windowHeight="15480" firstSheet="16" activeTab="17" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Summary" sheetId="1" r:id="rId1"/>
@@ -1298,7 +1298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1428,6 +1428,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1823,35 +1826,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3DEAD1A-BE12-4BD3-A45F-18807DFF108B}">
   <dimension ref="B2:J96"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="63" t="s">
+    <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="63" t="s">
+      <c r="H4" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-    </row>
-    <row r="5" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
+    </row>
+    <row r="5" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="35" t="s">
         <v>0</v>
       </c>
@@ -1873,7 +1876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C6" s="47" t="s">
         <v>146</v>
       </c>
@@ -1893,7 +1896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C7" s="6" t="s">
         <v>43</v>
       </c>
@@ -1913,7 +1916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C8" s="6" t="s">
         <v>41</v>
       </c>
@@ -1933,7 +1936,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C9" s="6" t="s">
         <v>5</v>
       </c>
@@ -1953,7 +1956,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C10" s="6" t="s">
         <v>5</v>
       </c>
@@ -1973,7 +1976,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C11" s="6" t="s">
         <v>5</v>
       </c>
@@ -1993,7 +1996,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C12" s="6" t="s">
         <v>5</v>
       </c>
@@ -2013,7 +2016,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C13" s="6" t="s">
         <v>86</v>
       </c>
@@ -2033,7 +2036,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C14" s="6" t="s">
         <v>103</v>
       </c>
@@ -2053,7 +2056,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C15" s="6" t="s">
         <v>87</v>
       </c>
@@ -2073,7 +2076,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C16" s="6" t="s">
         <v>87</v>
       </c>
@@ -2093,7 +2096,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C17" s="6" t="s">
         <v>54</v>
       </c>
@@ -2113,7 +2116,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C18" s="50" t="s">
         <v>137</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="50"/>
       <c r="D19" s="11"/>
       <c r="E19" s="41"/>
@@ -2147,7 +2150,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="48"/>
       <c r="D20" s="11"/>
       <c r="E20" s="41"/>
@@ -2161,7 +2164,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="6"/>
       <c r="D21" s="11"/>
       <c r="E21" s="41"/>
@@ -2175,7 +2178,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="6"/>
       <c r="D22" s="11"/>
       <c r="E22" s="41"/>
@@ -2189,7 +2192,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C23" s="6"/>
       <c r="D23" s="11"/>
       <c r="E23" s="41"/>
@@ -2203,7 +2206,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" s="6"/>
       <c r="D24" s="11"/>
       <c r="E24" s="41"/>
@@ -2217,7 +2220,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C25" s="6"/>
       <c r="D25" s="11"/>
       <c r="E25" s="41"/>
@@ -2231,7 +2234,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C26" s="6"/>
       <c r="D26" s="11"/>
       <c r="E26" s="41"/>
@@ -2245,7 +2248,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C27" s="6"/>
       <c r="D27" s="11"/>
       <c r="E27" s="41"/>
@@ -2259,7 +2262,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C28" s="6"/>
       <c r="D28" s="11"/>
       <c r="E28" s="41"/>
@@ -2273,7 +2276,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C29" s="6"/>
       <c r="D29" s="11"/>
       <c r="E29" s="41"/>
@@ -2287,7 +2290,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C30" s="6"/>
       <c r="D30" s="11"/>
       <c r="E30" s="41"/>
@@ -2301,7 +2304,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C31" s="6"/>
       <c r="D31" s="11"/>
       <c r="E31" s="41"/>
@@ -2315,7 +2318,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C32" s="6"/>
       <c r="D32" s="11"/>
       <c r="E32" s="41"/>
@@ -2329,7 +2332,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C33" s="6"/>
       <c r="D33" s="11"/>
       <c r="E33" s="41"/>
@@ -2343,7 +2346,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C34" s="6"/>
       <c r="D34" s="11"/>
       <c r="E34" s="41"/>
@@ -2357,7 +2360,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C35" s="6"/>
       <c r="D35" s="11"/>
       <c r="E35" s="41"/>
@@ -2371,7 +2374,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C36" s="6"/>
       <c r="D36" s="11"/>
       <c r="E36" s="41"/>
@@ -2385,7 +2388,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C37" s="6"/>
       <c r="D37" s="11"/>
       <c r="E37" s="41"/>
@@ -2399,7 +2402,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="38" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C38" s="7"/>
       <c r="D38" s="45"/>
       <c r="E38" s="43"/>
@@ -2413,7 +2416,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H39" s="2" t="s">
         <v>137</v>
       </c>
@@ -2424,7 +2427,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H40" s="2" t="s">
         <v>138</v>
       </c>
@@ -2435,7 +2438,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H41" s="39" t="s">
         <v>158</v>
       </c>
@@ -2446,7 +2449,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H42" s="39" t="s">
         <v>159</v>
       </c>
@@ -2457,7 +2460,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H43" s="2" t="s">
         <v>164</v>
       </c>
@@ -2468,7 +2471,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H44" s="2" t="s">
         <v>3</v>
       </c>
@@ -2479,7 +2482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H45" s="39" t="s">
         <v>173</v>
       </c>
@@ -2490,7 +2493,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H46" s="39" t="s">
         <v>174</v>
       </c>
@@ -2501,7 +2504,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="47" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H47" s="39" t="s">
         <v>175</v>
       </c>
@@ -2512,7 +2515,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H48" s="39" t="s">
         <v>182</v>
       </c>
@@ -2523,7 +2526,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="49" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H49" s="39" t="s">
         <v>183</v>
       </c>
@@ -2534,7 +2537,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H50" s="39" t="s">
         <v>184</v>
       </c>
@@ -2545,7 +2548,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H51" s="39" t="s">
         <v>185</v>
       </c>
@@ -2556,7 +2559,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H52" s="39" t="s">
         <v>186</v>
       </c>
@@ -2567,7 +2570,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="53" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H53" s="39" t="s">
         <v>187</v>
       </c>
@@ -2578,7 +2581,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H54" s="39" t="s">
         <v>188</v>
       </c>
@@ -2589,7 +2592,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="55" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H55" s="39" t="s">
         <v>189</v>
       </c>
@@ -2600,7 +2603,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="56" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H56" s="39" t="s">
         <v>190</v>
       </c>
@@ -2611,7 +2614,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H57" s="39" t="s">
         <v>191</v>
       </c>
@@ -2622,7 +2625,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="58" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H58" s="39" t="s">
         <v>192</v>
       </c>
@@ -2633,7 +2636,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="59" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H59" s="39" t="s">
         <v>193</v>
       </c>
@@ -2644,7 +2647,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="60" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H60" s="39" t="s">
         <v>194</v>
       </c>
@@ -2655,7 +2658,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H61" s="39" t="s">
         <v>195</v>
       </c>
@@ -2666,7 +2669,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H62" s="2" t="s">
         <v>53</v>
       </c>
@@ -2677,7 +2680,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="63" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H63" s="39" t="s">
         <v>232</v>
       </c>
@@ -2688,7 +2691,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="8:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="8:10" x14ac:dyDescent="0.25">
       <c r="H64" s="39" t="s">
         <v>233</v>
       </c>
@@ -2699,7 +2702,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="65" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H65" s="39" t="s">
         <v>234</v>
       </c>
@@ -2710,7 +2713,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H66" s="39" t="s">
         <v>235</v>
       </c>
@@ -2721,7 +2724,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="67" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H67" s="39" t="s">
         <v>236</v>
       </c>
@@ -2732,7 +2735,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="68" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C68" s="1"/>
       <c r="H68" s="39" t="s">
         <v>237</v>
@@ -2744,9 +2747,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="69" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C69" s="1"/>
-      <c r="H69" s="38" t="s">
+      <c r="H69" s="63" t="s">
         <v>252</v>
       </c>
       <c r="I69" s="8">
@@ -2757,9 +2760,9 @@
         <v>238</v>
       </c>
     </row>
-    <row r="70" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C70" s="1"/>
-      <c r="H70" s="38" t="s">
+      <c r="H70" s="63" t="s">
         <v>253</v>
       </c>
       <c r="I70" s="9">
@@ -2769,8 +2772,8 @@
         <v>238</v>
       </c>
     </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H71" s="38" t="s">
+    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H71" s="63" t="s">
         <v>254</v>
       </c>
       <c r="I71" s="9">
@@ -2780,8 +2783,8 @@
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H72" s="38" t="s">
+    <row r="72" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H72" s="63" t="s">
         <v>255</v>
       </c>
       <c r="I72" s="9">
@@ -2791,8 +2794,8 @@
         <v>238</v>
       </c>
     </row>
-    <row r="73" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H73" s="38" t="s">
+    <row r="73" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H73" s="63" t="s">
         <v>256</v>
       </c>
       <c r="I73" s="9">
@@ -2802,123 +2805,123 @@
         <v>238</v>
       </c>
     </row>
-    <row r="74" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H74" s="2"/>
       <c r="I74" s="57"/>
       <c r="J74" s="41"/>
     </row>
-    <row r="75" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H75" s="2"/>
       <c r="I75" s="57"/>
       <c r="J75" s="41"/>
     </row>
-    <row r="76" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H76" s="2"/>
       <c r="I76" s="57"/>
       <c r="J76" s="41"/>
     </row>
-    <row r="77" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C77" s="1"/>
       <c r="H77" s="2"/>
       <c r="I77" s="57"/>
       <c r="J77" s="41"/>
     </row>
-    <row r="78" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C78" s="1"/>
       <c r="H78" s="2"/>
       <c r="I78" s="57"/>
       <c r="J78" s="41"/>
     </row>
-    <row r="79" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C79" s="1"/>
       <c r="H79" s="2"/>
       <c r="I79" s="57"/>
       <c r="J79" s="41"/>
     </row>
-    <row r="80" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C80" s="1"/>
       <c r="H80" s="2"/>
       <c r="I80" s="57"/>
       <c r="J80" s="41"/>
     </row>
-    <row r="81" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C81" s="1"/>
       <c r="H81" s="2"/>
       <c r="I81" s="57"/>
       <c r="J81" s="41"/>
     </row>
-    <row r="82" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C82" s="1"/>
       <c r="H82" s="2"/>
       <c r="I82" s="57"/>
       <c r="J82" s="41"/>
     </row>
-    <row r="83" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H83" s="2"/>
       <c r="I83" s="57"/>
       <c r="J83" s="41"/>
     </row>
-    <row r="84" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H84" s="2"/>
       <c r="I84" s="57"/>
       <c r="J84" s="41"/>
     </row>
-    <row r="85" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H85" s="2"/>
       <c r="I85" s="57"/>
       <c r="J85" s="41"/>
     </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H86" s="2"/>
       <c r="I86" s="57"/>
       <c r="J86" s="41"/>
     </row>
-    <row r="87" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H87" s="2"/>
       <c r="I87" s="57"/>
       <c r="J87" s="41"/>
     </row>
-    <row r="88" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H88" s="2"/>
       <c r="I88" s="57"/>
       <c r="J88" s="41"/>
     </row>
-    <row r="89" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H89" s="2"/>
       <c r="I89" s="57"/>
       <c r="J89" s="41"/>
     </row>
-    <row r="90" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H90" s="2"/>
       <c r="I90" s="57"/>
       <c r="J90" s="41"/>
     </row>
-    <row r="91" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H91" s="2"/>
       <c r="I91" s="57"/>
       <c r="J91" s="41"/>
     </row>
-    <row r="92" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H92" s="2"/>
       <c r="I92" s="57"/>
       <c r="J92" s="41"/>
     </row>
-    <row r="93" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H93" s="2"/>
       <c r="I93" s="57"/>
       <c r="J93" s="41"/>
     </row>
-    <row r="94" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H94" s="2"/>
       <c r="I94" s="57"/>
       <c r="J94" s="41"/>
     </row>
-    <row r="95" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="3:10" x14ac:dyDescent="0.25">
       <c r="H95" s="2"/>
       <c r="I95" s="57"/>
       <c r="J95" s="41"/>
     </row>
-    <row r="96" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H96" s="3"/>
       <c r="I96" s="59"/>
       <c r="J96" s="43"/>
@@ -2938,20 +2941,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1308C4-E9DD-438E-A79A-D3E0D96AB566}">
   <dimension ref="B1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -2959,7 +2962,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="87" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -2967,7 +2970,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
@@ -2975,7 +2978,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -2983,7 +2986,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -2991,7 +2994,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -2999,7 +3002,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -3007,7 +3010,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -3015,20 +3018,20 @@
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -3049,7 +3052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>61</v>
@@ -3070,7 +3073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>19</v>
@@ -3091,7 +3094,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>43</v>
@@ -3106,7 +3109,7 @@
       <c r="K14" s="9"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>41</v>
@@ -3121,7 +3124,7 @@
       <c r="K15" s="9"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>5</v>
@@ -3136,7 +3139,7 @@
       <c r="K16" s="9"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>103</v>
@@ -3151,7 +3154,7 @@
       <c r="K17" s="9"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -3160,7 +3163,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -3169,7 +3172,7 @@
       <c r="K19" s="9"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -3178,7 +3181,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -3187,7 +3190,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -3196,7 +3199,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -3205,7 +3208,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -3214,7 +3217,7 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -3223,7 +3226,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -3232,7 +3235,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -3241,7 +3244,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -3250,7 +3253,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -3259,7 +3262,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -3268,7 +3271,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -3277,7 +3280,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -3286,7 +3289,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -3295,7 +3298,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -3304,7 +3307,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -3313,7 +3316,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -3322,7 +3325,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -3330,7 +3333,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -3338,7 +3341,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -3346,7 +3349,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -3354,7 +3357,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -3362,7 +3365,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -3370,7 +3373,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -3378,7 +3381,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -3398,21 +3401,21 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CBAD9F1-0099-4C27-8F14-6139C4B3501A}">
   <dimension ref="B1:T44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.90625" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -3420,7 +3423,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -3428,7 +3431,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:20" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:20" ht="75" x14ac:dyDescent="0.25">
       <c r="B4" s="29" t="s">
         <v>11</v>
       </c>
@@ -3436,7 +3439,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -3444,7 +3447,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -3452,7 +3455,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -3460,7 +3463,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -3468,7 +3471,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -3476,21 +3479,21 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="65"/>
-    </row>
-    <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="M10" s="66"/>
+    </row>
+    <row r="11" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -3514,7 +3517,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>105</v>
@@ -3535,16 +3538,16 @@
         <v>8</v>
       </c>
       <c r="M12" s="19"/>
-      <c r="O12" s="66" t="s">
+      <c r="O12" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
-      <c r="T12" s="66"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>19</v>
@@ -3565,14 +3568,14 @@
         <v>25</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-      <c r="T13" s="66"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2"/>
       <c r="F14" s="9"/>
@@ -3587,14 +3590,14 @@
         <v>25</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
-      <c r="T14" s="66"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
@@ -3609,14 +3612,14 @@
         <v>8</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
@@ -3631,16 +3634,16 @@
         <v>111</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="O16" s="66" t="s">
+      <c r="O16" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
@@ -3655,14 +3658,14 @@
         <v>111</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="66"/>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O17" s="67"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -3677,14 +3680,14 @@
         <v>151</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="66"/>
-      <c r="T18" s="66"/>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -3699,14 +3702,14 @@
         <v>151</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66"/>
-      <c r="T19" s="66"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O19" s="67"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -3722,7 +3725,7 @@
       </c>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -3737,16 +3740,16 @@
         <v>213</v>
       </c>
       <c r="M21" s="2"/>
-      <c r="O21" s="67" t="s">
+      <c r="O21" s="68" t="s">
         <v>150</v>
       </c>
-      <c r="P21" s="67"/>
-      <c r="Q21" s="67"/>
-      <c r="R21" s="67"/>
-      <c r="S21" s="67"/>
-      <c r="T21" s="67"/>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="P21" s="68"/>
+      <c r="Q21" s="68"/>
+      <c r="R21" s="68"/>
+      <c r="S21" s="68"/>
+      <c r="T21" s="68"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -3756,7 +3759,7 @@
       <c r="L22" s="4"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -3765,16 +3768,16 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="66" t="s">
+      <c r="O23" s="67" t="s">
         <v>217</v>
       </c>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -3783,14 +3786,14 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O24" s="67"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -3799,14 +3802,14 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O25" s="67"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -3815,14 +3818,14 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O26" s="67"/>
+      <c r="P26" s="67"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -3831,16 +3834,16 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="66" t="s">
+      <c r="O27" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-      <c r="T27" s="66"/>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -3849,14 +3852,14 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -3865,14 +3868,14 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="66"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-      <c r="T29" s="66"/>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O29" s="67"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -3881,14 +3884,14 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="66"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="66"/>
-      <c r="T30" s="66"/>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O30" s="67"/>
+      <c r="P30" s="67"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -3898,7 +3901,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -3908,7 +3911,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -3918,7 +3921,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -3928,7 +3931,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -3938,7 +3941,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -3948,7 +3951,7 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -3957,7 +3960,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -3966,7 +3969,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -3975,7 +3978,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -3984,7 +3987,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -3993,7 +3996,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -4002,7 +4005,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -4011,7 +4014,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -4037,21 +4040,21 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED21A768-E1F1-4F70-B6C9-A662B38F9ACD}">
   <dimension ref="B1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -4059,7 +4062,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -4067,7 +4070,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>11</v>
       </c>
@@ -4075,7 +4078,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -4083,7 +4086,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -4091,7 +4094,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -4099,7 +4102,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -4107,7 +4110,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -4115,20 +4118,20 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -4149,7 +4152,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>132</v>
@@ -4170,7 +4173,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>61</v>
@@ -4191,7 +4194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -4212,7 +4215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>18</v>
@@ -4233,7 +4236,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>19</v>
@@ -4254,7 +4257,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>43</v>
@@ -4275,7 +4278,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -4290,7 +4293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -4305,7 +4308,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -4320,7 +4323,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -4335,7 +4338,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -4350,7 +4353,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -4365,7 +4368,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -4380,7 +4383,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -4389,7 +4392,7 @@
       <c r="K25" s="11"/>
       <c r="L25" s="42"/>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -4398,7 +4401,7 @@
       <c r="K26" s="11"/>
       <c r="L26" s="42"/>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -4407,7 +4410,7 @@
       <c r="K27" s="11"/>
       <c r="L27" s="42"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -4416,7 +4419,7 @@
       <c r="K28" s="11"/>
       <c r="L28" s="42"/>
     </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -4425,7 +4428,7 @@
       <c r="K29" s="11"/>
       <c r="L29" s="42"/>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -4434,7 +4437,7 @@
       <c r="K30" s="11"/>
       <c r="L30" s="41"/>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -4443,7 +4446,7 @@
       <c r="K31" s="11"/>
       <c r="L31" s="41"/>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -4452,7 +4455,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="41"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -4461,7 +4464,7 @@
       <c r="K33" s="11"/>
       <c r="L33" s="41"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -4470,7 +4473,7 @@
       <c r="K34" s="11"/>
       <c r="L34" s="41"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -4479,7 +4482,7 @@
       <c r="K35" s="11"/>
       <c r="L35" s="41"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -4488,7 +4491,7 @@
       <c r="K36" s="11"/>
       <c r="L36" s="41"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -4496,7 +4499,7 @@
       <c r="K37" s="11"/>
       <c r="L37" s="41"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -4504,7 +4507,7 @@
       <c r="K38" s="11"/>
       <c r="L38" s="41"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -4512,7 +4515,7 @@
       <c r="K39" s="11"/>
       <c r="L39" s="41"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -4520,7 +4523,7 @@
       <c r="K40" s="11"/>
       <c r="L40" s="41"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -4528,7 +4531,7 @@
       <c r="K41" s="11"/>
       <c r="L41" s="41"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -4536,7 +4539,7 @@
       <c r="K42" s="11"/>
       <c r="L42" s="41"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -4544,7 +4547,7 @@
       <c r="K43" s="11"/>
       <c r="L43" s="41"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -4564,20 +4567,20 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2930F0-3027-4B2E-8126-4FAD3B96111E}">
   <dimension ref="B1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -4585,7 +4588,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="74.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" ht="74.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -4593,7 +4596,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
@@ -4601,7 +4604,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -4609,7 +4612,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -4617,7 +4620,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -4625,7 +4628,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -4633,7 +4636,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -4641,20 +4644,20 @@
         <v>163</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -4675,7 +4678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>43</v>
@@ -4696,7 +4699,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>87</v>
@@ -4717,7 +4720,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>86</v>
@@ -4738,7 +4741,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>19</v>
@@ -4753,7 +4756,7 @@
       <c r="K15" s="9"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>103</v>
@@ -4768,7 +4771,7 @@
       <c r="K16" s="9"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>5</v>
@@ -4783,7 +4786,7 @@
       <c r="K17" s="9"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2" t="s">
         <v>53</v>
@@ -4798,7 +4801,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2" t="s">
         <v>157</v>
@@ -4813,7 +4816,7 @@
       <c r="K19" s="9"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -4822,7 +4825,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -4831,7 +4834,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -4840,7 +4843,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -4849,7 +4852,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -4858,7 +4861,7 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -4867,7 +4870,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -4876,7 +4879,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -4885,7 +4888,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -4894,7 +4897,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -4903,7 +4906,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -4912,7 +4915,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -4921,7 +4924,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -4930,7 +4933,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -4939,7 +4942,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -4948,7 +4951,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -4957,7 +4960,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -4966,7 +4969,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -4974,7 +4977,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -4982,7 +4985,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -4990,7 +4993,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -4998,7 +5001,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -5006,7 +5009,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -5014,7 +5017,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -5022,7 +5025,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -5042,20 +5045,20 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1051D7C-48A2-4264-A591-A5BE1589053B}">
   <dimension ref="B1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" customWidth="1"/>
-    <col min="11" max="11" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -5063,7 +5066,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -5071,7 +5074,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
@@ -5079,7 +5082,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -5087,7 +5090,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -5095,7 +5098,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -5103,7 +5106,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -5111,7 +5114,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -5119,20 +5122,20 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -5153,7 +5156,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>19</v>
@@ -5174,7 +5177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>171</v>
@@ -5195,7 +5198,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>20</v>
@@ -5216,7 +5219,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>137</v>
@@ -5237,7 +5240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>18</v>
@@ -5258,7 +5261,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>17</v>
@@ -5273,7 +5276,7 @@
       <c r="K17" s="9"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -5282,7 +5285,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -5291,7 +5294,7 @@
       <c r="K19" s="9"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -5300,7 +5303,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -5309,7 +5312,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -5318,7 +5321,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -5327,7 +5330,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -5336,7 +5339,7 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -5345,7 +5348,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -5354,7 +5357,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -5363,7 +5366,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -5372,7 +5375,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -5381,7 +5384,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -5390,7 +5393,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -5399,7 +5402,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -5408,7 +5411,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -5417,7 +5420,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -5426,7 +5429,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -5435,7 +5438,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -5444,7 +5447,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -5452,7 +5455,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -5460,7 +5463,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -5468,7 +5471,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -5476,7 +5479,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -5484,7 +5487,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -5492,7 +5495,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -5500,7 +5503,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -5520,20 +5523,20 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C186B3A-157D-4021-977B-A5A4DB537283}">
   <dimension ref="D3:N29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6328125" customWidth="1"/>
-    <col min="7" max="7" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D4" s="16" t="s">
         <v>9</v>
       </c>
@@ -5541,7 +5544,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="4:14" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="4:14" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="51" t="s">
         <v>10</v>
       </c>
@@ -5549,7 +5552,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D6" s="17" t="s">
         <v>11</v>
       </c>
@@ -5557,13 +5560,13 @@
         <v>238</v>
       </c>
     </row>
-    <row r="7" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D7" s="17" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="41"/>
     </row>
-    <row r="8" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D8" s="17" t="s">
         <v>13</v>
       </c>
@@ -5571,7 +5574,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D9" s="17" t="s">
         <v>14</v>
       </c>
@@ -5579,7 +5582,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D10" s="17" t="s">
         <v>31</v>
       </c>
@@ -5587,7 +5590,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="4:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="18" t="s">
         <v>32</v>
       </c>
@@ -5595,19 +5598,19 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="4:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G12" s="80" t="s">
+    <row r="12" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G12" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="81"/>
-      <c r="I12" s="82"/>
-      <c r="L12" s="80" t="s">
+      <c r="H12" s="82"/>
+      <c r="I12" s="83"/>
+      <c r="L12" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="81"/>
-      <c r="N12" s="82"/>
-    </row>
-    <row r="13" spans="4:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M12" s="82"/>
+      <c r="N12" s="83"/>
+    </row>
+    <row r="13" spans="4:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G13" s="53" t="s">
         <v>0</v>
       </c>
@@ -5627,7 +5630,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G14" s="5" t="s">
         <v>157</v>
       </c>
@@ -5647,7 +5650,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G15" s="6" t="s">
         <v>103</v>
       </c>
@@ -5667,7 +5670,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="4:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="4:14" x14ac:dyDescent="0.25">
       <c r="G16" s="6" t="s">
         <v>87</v>
       </c>
@@ -5687,7 +5690,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G17" s="6" t="s">
         <v>53</v>
       </c>
@@ -5707,7 +5710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G18" s="6" t="s">
         <v>43</v>
       </c>
@@ -5727,7 +5730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G19" s="6" t="s">
         <v>86</v>
       </c>
@@ -5747,7 +5750,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G20" s="6" t="s">
         <v>18</v>
       </c>
@@ -5767,7 +5770,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G21" s="6" t="s">
         <v>17</v>
       </c>
@@ -5787,7 +5790,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G22" s="6" t="s">
         <v>41</v>
       </c>
@@ -5807,7 +5810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G23" s="6" t="s">
         <v>20</v>
       </c>
@@ -5827,7 +5830,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="7:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="7:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G24" s="7" t="s">
         <v>19</v>
       </c>
@@ -5847,7 +5850,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="7:14" x14ac:dyDescent="0.25">
       <c r="L25" s="6">
         <v>5</v>
       </c>
@@ -5858,7 +5861,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="7:14" x14ac:dyDescent="0.25">
       <c r="L26" s="6">
         <v>5</v>
       </c>
@@ -5869,7 +5872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="7:14" x14ac:dyDescent="0.25">
       <c r="L27" s="6">
         <v>11.41666</v>
       </c>
@@ -5880,7 +5883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="7:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="7:14" x14ac:dyDescent="0.25">
       <c r="L28" s="6">
         <v>46</v>
       </c>
@@ -5891,7 +5894,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="29" spans="7:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="7:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L29" s="7">
         <f>391.64167-46</f>
         <v>345.64166999999998</v>
@@ -5915,21 +5918,21 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BAE874B-EB1A-40E9-945A-ABFDF311093C}">
   <dimension ref="B1:O44"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -5937,7 +5940,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -5945,7 +5948,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
@@ -5953,7 +5956,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -5961,7 +5964,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -5969,7 +5972,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -5977,7 +5980,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -5985,7 +5988,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -5993,20 +5996,20 @@
         <v>202</v>
       </c>
     </row>
-    <row r="10" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -6027,7 +6030,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>61</v>
@@ -6048,7 +6051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>18</v>
@@ -6075,7 +6078,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>88</v>
@@ -6096,7 +6099,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>88</v>
@@ -6117,7 +6120,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>17</v>
@@ -6138,7 +6141,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="17" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>19</v>
@@ -6159,7 +6162,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2" t="s">
         <v>132</v>
@@ -6174,7 +6177,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2" t="s">
         <v>132</v>
@@ -6189,7 +6192,7 @@
       <c r="K19" s="9"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -6198,7 +6201,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -6207,7 +6210,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -6216,7 +6219,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -6225,7 +6228,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -6234,7 +6237,7 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -6243,7 +6246,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -6252,7 +6255,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -6261,7 +6264,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -6270,7 +6273,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -6279,7 +6282,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -6288,7 +6291,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -6297,7 +6300,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -6306,7 +6309,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -6315,7 +6318,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -6324,7 +6327,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -6333,7 +6336,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -6342,7 +6345,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -6350,7 +6353,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -6358,7 +6361,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -6366,7 +6369,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -6374,7 +6377,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -6382,7 +6385,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -6390,7 +6393,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -6398,7 +6401,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -6418,20 +6421,20 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E188AE-32E3-44FC-A747-B6B7B3960AE2}">
   <dimension ref="B1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -6439,7 +6442,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" ht="105" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -6447,19 +6450,19 @@
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="25"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="25"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -6467,7 +6470,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -6475,7 +6478,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -6483,7 +6486,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -6491,20 +6494,20 @@
         <v>223</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -6525,7 +6528,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>224</v>
@@ -6546,7 +6549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>61</v>
@@ -6567,7 +6570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>49</v>
@@ -6588,7 +6591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>87</v>
@@ -6609,7 +6612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>225</v>
@@ -6630,7 +6633,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>19</v>
@@ -6651,7 +6654,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2" t="s">
         <v>227</v>
@@ -6666,7 +6669,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2" t="s">
         <v>103</v>
@@ -6681,7 +6684,7 @@
       <c r="K19" s="9"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2" t="s">
         <v>229</v>
@@ -6696,7 +6699,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2" t="s">
         <v>230</v>
@@ -6711,7 +6714,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2" t="s">
         <v>175</v>
@@ -6726,7 +6729,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -6735,7 +6738,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -6744,7 +6747,7 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -6753,7 +6756,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -6762,7 +6765,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -6771,7 +6774,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -6780,7 +6783,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -6789,7 +6792,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -6798,7 +6801,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -6807,7 +6810,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -6816,7 +6819,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -6825,7 +6828,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -6834,7 +6837,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -6843,7 +6846,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -6852,7 +6855,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -6860,7 +6863,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -6868,7 +6871,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -6876,7 +6879,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -6884,7 +6887,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -6892,7 +6895,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -6900,7 +6903,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -6908,7 +6911,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -6928,20 +6931,20 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2B3A23-66AC-4695-AC89-14BEBEA38B1D}">
   <dimension ref="B1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -6949,7 +6952,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" ht="90" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -6957,19 +6960,19 @@
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="25"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="25"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -6977,7 +6980,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -6985,7 +6988,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -6993,7 +6996,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -7001,20 +7004,20 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -7035,7 +7038,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>41</v>
@@ -7057,7 +7060,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>61</v>
@@ -7078,7 +7081,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>49</v>
@@ -7099,7 +7102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>87</v>
@@ -7120,7 +7123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>19</v>
@@ -7141,7 +7144,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>227</v>
@@ -7156,7 +7159,7 @@
       <c r="K17" s="9"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2" t="s">
         <v>5</v>
@@ -7171,7 +7174,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2" t="s">
         <v>229</v>
@@ -7186,7 +7189,7 @@
       <c r="K19" s="9"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2" t="s">
         <v>251</v>
@@ -7201,7 +7204,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -7210,7 +7213,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -7219,7 +7222,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -7228,7 +7231,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -7237,7 +7240,7 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -7246,7 +7249,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -7255,7 +7258,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -7264,7 +7267,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -7273,7 +7276,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -7282,7 +7285,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -7291,7 +7294,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -7300,7 +7303,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -7309,7 +7312,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -7318,7 +7321,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -7327,7 +7330,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -7336,7 +7339,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -7345,7 +7348,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -7353,7 +7356,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -7361,7 +7364,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -7369,7 +7372,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -7377,7 +7380,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -7385,7 +7388,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -7393,7 +7396,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -7401,7 +7404,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -7421,38 +7424,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BDCCE8D-0CE2-4D53-8FB4-EA2891D6F3B5}">
   <dimension ref="C3:M38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="16" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="63" t="s">
+      <c r="F4" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="64"/>
-      <c r="H4" s="65"/>
-      <c r="K4" s="63" t="s">
+      <c r="G4" s="65"/>
+      <c r="H4" s="66"/>
+      <c r="K4" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="64"/>
-      <c r="M4" s="65"/>
-    </row>
-    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="65"/>
+      <c r="M4" s="66"/>
+    </row>
+    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="17" t="s">
         <v>10</v>
       </c>
@@ -7478,7 +7481,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C6" s="17" t="s">
         <v>11</v>
       </c>
@@ -7504,7 +7507,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C7" s="17" t="s">
         <v>12</v>
       </c>
@@ -7530,7 +7533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C8" s="17" t="s">
         <v>13</v>
       </c>
@@ -7556,7 +7559,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="18" t="s">
         <v>14</v>
       </c>
@@ -7582,7 +7585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F10" s="2"/>
       <c r="G10" s="9"/>
       <c r="H10" s="2"/>
@@ -7590,7 +7593,7 @@
       <c r="L10" s="9"/>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F11" s="2"/>
       <c r="G11" s="9"/>
       <c r="H11" s="2"/>
@@ -7598,7 +7601,7 @@
       <c r="L11" s="9"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F12" s="2"/>
       <c r="G12" s="9"/>
       <c r="H12" s="2"/>
@@ -7606,7 +7609,7 @@
       <c r="L12" s="9"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F13" s="2"/>
       <c r="G13" s="9"/>
       <c r="H13" s="2"/>
@@ -7614,7 +7617,7 @@
       <c r="L13" s="9"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F14" s="2"/>
       <c r="G14" s="9"/>
       <c r="H14" s="2"/>
@@ -7622,7 +7625,7 @@
       <c r="L14" s="9"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F15" s="2"/>
       <c r="G15" s="9"/>
       <c r="H15" s="2"/>
@@ -7630,7 +7633,7 @@
       <c r="L15" s="9"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F16" s="2"/>
       <c r="G16" s="9"/>
       <c r="H16" s="2"/>
@@ -7638,7 +7641,7 @@
       <c r="L16" s="9"/>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F17" s="2"/>
       <c r="G17" s="9"/>
       <c r="H17" s="2"/>
@@ -7646,7 +7649,7 @@
       <c r="L17" s="9"/>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F18" s="2"/>
       <c r="G18" s="9"/>
       <c r="H18" s="2"/>
@@ -7654,7 +7657,7 @@
       <c r="L18" s="9"/>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F19" s="2"/>
       <c r="G19" s="9"/>
       <c r="H19" s="2"/>
@@ -7662,7 +7665,7 @@
       <c r="L19" s="9"/>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F20" s="2"/>
       <c r="G20" s="9"/>
       <c r="H20" s="2"/>
@@ -7670,7 +7673,7 @@
       <c r="L20" s="9"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F21" s="2"/>
       <c r="G21" s="9"/>
       <c r="H21" s="2"/>
@@ -7678,7 +7681,7 @@
       <c r="L21" s="9"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F22" s="2"/>
       <c r="G22" s="9"/>
       <c r="H22" s="2"/>
@@ -7686,7 +7689,7 @@
       <c r="L22" s="9"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F23" s="2"/>
       <c r="G23" s="9"/>
       <c r="H23" s="2"/>
@@ -7694,7 +7697,7 @@
       <c r="L23" s="9"/>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F24" s="2"/>
       <c r="G24" s="9"/>
       <c r="H24" s="2"/>
@@ -7702,7 +7705,7 @@
       <c r="L24" s="9"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F25" s="2"/>
       <c r="G25" s="9"/>
       <c r="H25" s="2"/>
@@ -7710,7 +7713,7 @@
       <c r="L25" s="9"/>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F26" s="2"/>
       <c r="G26" s="9"/>
       <c r="H26" s="2"/>
@@ -7718,7 +7721,7 @@
       <c r="L26" s="9"/>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F27" s="2"/>
       <c r="G27" s="9"/>
       <c r="H27" s="2"/>
@@ -7726,7 +7729,7 @@
       <c r="L27" s="9"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F28" s="2"/>
       <c r="G28" s="9"/>
       <c r="H28" s="2"/>
@@ -7734,7 +7737,7 @@
       <c r="L28" s="9"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F29" s="2"/>
       <c r="G29" s="9"/>
       <c r="H29" s="2"/>
@@ -7742,7 +7745,7 @@
       <c r="L29" s="9"/>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F30" s="2"/>
       <c r="G30" s="9"/>
       <c r="H30" s="2"/>
@@ -7750,7 +7753,7 @@
       <c r="L30" s="9"/>
       <c r="M30" s="2"/>
     </row>
-    <row r="31" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F31" s="2"/>
       <c r="G31" s="9"/>
       <c r="H31" s="2"/>
@@ -7758,7 +7761,7 @@
       <c r="L31" s="9"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F32" s="2"/>
       <c r="G32" s="9"/>
       <c r="H32" s="2"/>
@@ -7766,7 +7769,7 @@
       <c r="L32" s="9"/>
       <c r="M32" s="2"/>
     </row>
-    <row r="33" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F33" s="2"/>
       <c r="G33" s="9"/>
       <c r="H33" s="2"/>
@@ -7774,7 +7777,7 @@
       <c r="L33" s="9"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F34" s="2"/>
       <c r="G34" s="9"/>
       <c r="H34" s="2"/>
@@ -7782,7 +7785,7 @@
       <c r="L34" s="9"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F35" s="2"/>
       <c r="G35" s="9"/>
       <c r="H35" s="2"/>
@@ -7790,7 +7793,7 @@
       <c r="L35" s="9"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F36" s="2"/>
       <c r="G36" s="9"/>
       <c r="H36" s="2"/>
@@ -7798,7 +7801,7 @@
       <c r="L36" s="9"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="6:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F37" s="2"/>
       <c r="G37" s="9"/>
       <c r="H37" s="2"/>
@@ -7806,7 +7809,7 @@
       <c r="L37" s="9"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="6:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="6:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F38" s="3"/>
       <c r="G38" s="10"/>
       <c r="H38" s="3"/>
@@ -7826,22 +7829,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A244D34F-6552-48EC-88C9-9BCAF12F75CF}">
   <dimension ref="C3:U1048576"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.7265625" customWidth="1"/>
+    <col min="14" max="14" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C4" s="20" t="s">
         <v>9</v>
       </c>
@@ -7849,7 +7852,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C5" s="21" t="s">
         <v>10</v>
       </c>
@@ -7857,7 +7860,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="3:21" ht="74" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:21" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="29" t="s">
         <v>11</v>
       </c>
@@ -7865,7 +7868,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C7" s="21" t="s">
         <v>12</v>
       </c>
@@ -7873,7 +7876,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C8" s="21" t="s">
         <v>13</v>
       </c>
@@ -7881,7 +7884,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C9" s="21" t="s">
         <v>14</v>
       </c>
@@ -7889,7 +7892,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="3:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:21" x14ac:dyDescent="0.25">
       <c r="C10" s="21" t="s">
         <v>31</v>
       </c>
@@ -7897,7 +7900,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22" t="s">
         <v>32</v>
       </c>
@@ -7905,21 +7908,21 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="63" t="s">
+    <row r="12" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F13" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="64"/>
-      <c r="H13" s="65"/>
-      <c r="K13" s="63" t="s">
+      <c r="G13" s="65"/>
+      <c r="H13" s="66"/>
+      <c r="K13" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64"/>
-      <c r="N13" s="65"/>
-    </row>
-    <row r="14" spans="3:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="66"/>
+    </row>
+    <row r="14" spans="3:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F14" s="14" t="s">
         <v>0</v>
       </c>
@@ -7941,16 +7944,16 @@
       <c r="N14" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="P14" s="66" t="s">
+      <c r="P14" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
-      <c r="T14" s="66"/>
-      <c r="U14" s="66"/>
-    </row>
-    <row r="15" spans="3:21" x14ac:dyDescent="0.35">
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+      <c r="U14" s="67"/>
+    </row>
+    <row r="15" spans="3:21" x14ac:dyDescent="0.25">
       <c r="F15" s="4" t="s">
         <v>34</v>
       </c>
@@ -7970,14 +7973,14 @@
         <v>25</v>
       </c>
       <c r="N15" s="19"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="66"/>
-    </row>
-    <row r="16" spans="3:21" x14ac:dyDescent="0.35">
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+    </row>
+    <row r="16" spans="3:21" x14ac:dyDescent="0.25">
       <c r="F16" s="2" t="s">
         <v>19</v>
       </c>
@@ -7999,14 +8002,14 @@
       <c r="N16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="66"/>
-    </row>
-    <row r="17" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+      <c r="U16" s="67"/>
+    </row>
+    <row r="17" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F17" s="2"/>
       <c r="G17" s="9"/>
       <c r="H17" s="2"/>
@@ -8022,14 +8025,14 @@
       <c r="N17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="66"/>
-      <c r="U17" s="66"/>
-    </row>
-    <row r="18" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+    </row>
+    <row r="18" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F18" s="2"/>
       <c r="G18" s="9"/>
       <c r="H18" s="2"/>
@@ -8046,7 +8049,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F19" s="2"/>
       <c r="G19" s="9"/>
       <c r="H19" s="2"/>
@@ -8063,7 +8066,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F20" s="2"/>
       <c r="G20" s="9"/>
       <c r="H20" s="2"/>
@@ -8077,16 +8080,16 @@
         <v>177</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="P20" s="67" t="s">
+      <c r="P20" s="68" t="s">
         <v>150</v>
       </c>
-      <c r="Q20" s="67"/>
-      <c r="R20" s="67"/>
-      <c r="S20" s="67"/>
-      <c r="T20" s="67"/>
-      <c r="U20" s="67"/>
-    </row>
-    <row r="21" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="Q20" s="68"/>
+      <c r="R20" s="68"/>
+      <c r="S20" s="68"/>
+      <c r="T20" s="68"/>
+      <c r="U20" s="68"/>
+    </row>
+    <row r="21" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F21" s="2"/>
       <c r="G21" s="9"/>
       <c r="H21" s="2"/>
@@ -8101,7 +8104,7 @@
       </c>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F22" s="2"/>
       <c r="G22" s="9"/>
       <c r="H22" s="2"/>
@@ -8109,16 +8112,16 @@
       <c r="L22" s="9"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="P22" s="66" t="s">
+      <c r="P22" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-    </row>
-    <row r="23" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+    </row>
+    <row r="23" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F23" s="2"/>
       <c r="G23" s="9"/>
       <c r="H23" s="2"/>
@@ -8126,14 +8129,14 @@
       <c r="L23" s="9"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="66"/>
-    </row>
-    <row r="24" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+    </row>
+    <row r="24" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F24" s="2"/>
       <c r="G24" s="9"/>
       <c r="H24" s="2"/>
@@ -8141,14 +8144,14 @@
       <c r="L24" s="9"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="66"/>
-    </row>
-    <row r="25" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+    </row>
+    <row r="25" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F25" s="2"/>
       <c r="G25" s="9"/>
       <c r="H25" s="2"/>
@@ -8156,14 +8159,14 @@
       <c r="L25" s="9"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
-      <c r="U25" s="66"/>
-    </row>
-    <row r="26" spans="6:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+    </row>
+    <row r="26" spans="6:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F26" s="2"/>
       <c r="G26" s="9"/>
       <c r="H26" s="2"/>
@@ -8171,16 +8174,16 @@
       <c r="L26" s="9"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
-      <c r="P26" s="66" t="s">
+      <c r="P26" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
-      <c r="U26" s="66"/>
-    </row>
-    <row r="27" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+      <c r="U26" s="67"/>
+    </row>
+    <row r="27" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F27" s="2"/>
       <c r="G27" s="9"/>
       <c r="H27" s="2"/>
@@ -8188,14 +8191,14 @@
       <c r="L27" s="9"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-      <c r="T27" s="66"/>
-      <c r="U27" s="66"/>
-    </row>
-    <row r="28" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+      <c r="U27" s="67"/>
+    </row>
+    <row r="28" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F28" s="2"/>
       <c r="G28" s="9"/>
       <c r="H28" s="2"/>
@@ -8203,14 +8206,14 @@
       <c r="L28" s="9"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="66"/>
-    </row>
-    <row r="29" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+      <c r="U28" s="67"/>
+    </row>
+    <row r="29" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F29" s="2"/>
       <c r="G29" s="9"/>
       <c r="H29" s="2"/>
@@ -8218,14 +8221,14 @@
       <c r="L29" s="9"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-      <c r="T29" s="66"/>
-      <c r="U29" s="66"/>
-    </row>
-    <row r="30" spans="6:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+      <c r="U29" s="67"/>
+    </row>
+    <row r="30" spans="6:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F30" s="2"/>
       <c r="G30" s="9"/>
       <c r="H30" s="2"/>
@@ -8233,16 +8236,16 @@
       <c r="L30" s="9"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="P30" s="66" t="s">
+      <c r="P30" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="66"/>
-      <c r="T30" s="66"/>
-      <c r="U30" s="66"/>
-    </row>
-    <row r="31" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="Q30" s="67"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67"/>
+      <c r="U30" s="67"/>
+    </row>
+    <row r="31" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F31" s="2"/>
       <c r="G31" s="9"/>
       <c r="H31" s="2"/>
@@ -8250,14 +8253,14 @@
       <c r="L31" s="9"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="66"/>
-      <c r="S31" s="66"/>
-      <c r="T31" s="66"/>
-      <c r="U31" s="66"/>
-    </row>
-    <row r="32" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+      <c r="U31" s="67"/>
+    </row>
+    <row r="32" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F32" s="2"/>
       <c r="G32" s="9"/>
       <c r="H32" s="2"/>
@@ -8265,14 +8268,14 @@
       <c r="L32" s="9"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="66"/>
-      <c r="S32" s="66"/>
-      <c r="T32" s="66"/>
-      <c r="U32" s="66"/>
-    </row>
-    <row r="33" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="P32" s="67"/>
+      <c r="Q32" s="67"/>
+      <c r="R32" s="67"/>
+      <c r="S32" s="67"/>
+      <c r="T32" s="67"/>
+      <c r="U32" s="67"/>
+    </row>
+    <row r="33" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F33" s="2"/>
       <c r="G33" s="9"/>
       <c r="H33" s="2"/>
@@ -8280,14 +8283,14 @@
       <c r="L33" s="9"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
-      <c r="P33" s="66"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="66"/>
-      <c r="S33" s="66"/>
-      <c r="T33" s="66"/>
-      <c r="U33" s="66"/>
-    </row>
-    <row r="34" spans="6:21" x14ac:dyDescent="0.35">
+      <c r="P33" s="67"/>
+      <c r="Q33" s="67"/>
+      <c r="R33" s="67"/>
+      <c r="S33" s="67"/>
+      <c r="T33" s="67"/>
+      <c r="U33" s="67"/>
+    </row>
+    <row r="34" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F34" s="2"/>
       <c r="G34" s="9"/>
       <c r="H34" s="2"/>
@@ -8296,7 +8299,7 @@
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F35" s="2"/>
       <c r="G35" s="9"/>
       <c r="H35" s="2"/>
@@ -8305,7 +8308,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F36" s="2"/>
       <c r="G36" s="9"/>
       <c r="H36" s="2"/>
@@ -8314,7 +8317,7 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F37" s="2"/>
       <c r="G37" s="9"/>
       <c r="H37" s="2"/>
@@ -8323,7 +8326,7 @@
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F38" s="2"/>
       <c r="G38" s="9"/>
       <c r="H38" s="2"/>
@@ -8332,7 +8335,7 @@
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
     </row>
-    <row r="39" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="39" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F39" s="2"/>
       <c r="G39" s="9"/>
       <c r="H39" s="2"/>
@@ -8341,7 +8344,7 @@
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
     </row>
-    <row r="40" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="40" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F40" s="2"/>
       <c r="G40" s="9"/>
       <c r="H40" s="2"/>
@@ -8350,7 +8353,7 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
     </row>
-    <row r="41" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="41" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F41" s="2"/>
       <c r="G41" s="9"/>
       <c r="H41" s="2"/>
@@ -8359,7 +8362,7 @@
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
     </row>
-    <row r="42" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="42" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F42" s="2"/>
       <c r="G42" s="9"/>
       <c r="H42" s="2"/>
@@ -8368,7 +8371,7 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="43" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F43" s="2"/>
       <c r="G43" s="9"/>
       <c r="H43" s="2"/>
@@ -8377,7 +8380,7 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
-    <row r="44" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="44" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F44" s="2"/>
       <c r="G44" s="9"/>
       <c r="H44" s="2"/>
@@ -8386,7 +8389,7 @@
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="45" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F45" s="2"/>
       <c r="G45" s="9"/>
       <c r="H45" s="2"/>
@@ -8395,7 +8398,7 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
-    <row r="46" spans="6:21" x14ac:dyDescent="0.35">
+    <row r="46" spans="6:21" x14ac:dyDescent="0.25">
       <c r="F46" s="2"/>
       <c r="G46" s="9"/>
       <c r="H46" s="2"/>
@@ -8404,7 +8407,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="6:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F47" s="3"/>
       <c r="G47" s="10"/>
       <c r="H47" s="3"/>
@@ -8413,7 +8416,7 @@
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
     </row>
-    <row r="1048576" spans="11:11" x14ac:dyDescent="0.35">
+    <row r="1048576" spans="11:11" x14ac:dyDescent="0.25">
       <c r="K1048576" s="4"/>
     </row>
   </sheetData>
@@ -8433,21 +8436,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F1350C4-6C4D-4B59-A3BC-5B1F652DB40B}">
   <dimension ref="B1:O48"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.90625" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" customWidth="1"/>
-    <col min="12" max="12" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.6328125" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -8455,7 +8458,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
         <v>10</v>
       </c>
@@ -8463,7 +8466,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="29" t="s">
         <v>11</v>
       </c>
@@ -8471,7 +8474,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -8479,7 +8482,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -8487,7 +8490,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -8495,7 +8498,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -8503,7 +8506,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -8511,23 +8514,23 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
     </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
-      <c r="J11" s="63" t="s">
+      <c r="F11" s="65"/>
+      <c r="G11" s="66"/>
+      <c r="J11" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="64"/>
-      <c r="L11" s="65"/>
-    </row>
-    <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K11" s="65"/>
+      <c r="L11" s="66"/>
+    </row>
+    <row r="12" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C12" s="23"/>
       <c r="E12" s="14" t="s">
         <v>0</v>
@@ -8548,7 +8551,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="4" t="s">
         <v>52</v>
@@ -8569,7 +8572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
@@ -8590,7 +8593,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
@@ -8605,7 +8608,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
@@ -8620,7 +8623,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
@@ -8635,7 +8638,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -8650,7 +8653,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -8665,7 +8668,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -8674,7 +8677,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -8683,7 +8686,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -8692,7 +8695,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -8701,7 +8704,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -8710,7 +8713,7 @@
       <c r="K24" s="9"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -8719,7 +8722,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -8728,7 +8731,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -8737,7 +8740,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -8746,7 +8749,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -8755,7 +8758,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -8764,7 +8767,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -8773,7 +8776,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -8782,7 +8785,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -8791,7 +8794,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -8800,7 +8803,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -8809,7 +8812,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -8818,7 +8821,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:15" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -8826,7 +8829,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:15" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -8834,7 +8837,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:15" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -8842,7 +8845,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:15" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -8850,7 +8853,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:15" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -8858,7 +8861,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:15" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -8866,7 +8869,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:15" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -8874,7 +8877,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:15" x14ac:dyDescent="0.25">
       <c r="E44" s="2"/>
       <c r="F44" s="9"/>
       <c r="G44" s="2"/>
@@ -8882,7 +8885,7 @@
       <c r="K44" s="9"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E45" s="3"/>
       <c r="F45" s="10"/>
       <c r="G45" s="3"/>
@@ -8890,7 +8893,7 @@
       <c r="K45" s="10"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="48" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:15" x14ac:dyDescent="0.25">
       <c r="O48" t="s">
         <v>218</v>
       </c>
@@ -8907,23 +8910,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD23EB3-FE0B-4D28-A04E-DA4ABD2C8717}">
   <dimension ref="B1:T45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.36328125" customWidth="1"/>
-    <col min="5" max="5" width="10.08984375" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.54296875" customWidth="1"/>
-    <col min="12" max="12" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.6328125" customWidth="1"/>
-    <col min="15" max="15" width="18.08984375" customWidth="1"/>
-    <col min="23" max="24" width="19.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" customWidth="1"/>
+    <col min="12" max="12" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.5703125" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" customWidth="1"/>
+    <col min="23" max="24" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -8931,7 +8934,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
         <v>10</v>
       </c>
@@ -8939,7 +8942,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:20" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:20" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="29" t="s">
         <v>11</v>
       </c>
@@ -8947,7 +8950,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -8955,7 +8958,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -8963,7 +8966,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -8971,7 +8974,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -8979,7 +8982,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -8987,24 +8990,24 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
     </row>
-    <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
-      <c r="J11" s="63" t="s">
+      <c r="F11" s="65"/>
+      <c r="G11" s="66"/>
+      <c r="J11" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="64"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="65"/>
-    </row>
-    <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="66"/>
+    </row>
+    <row r="12" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C12" s="23"/>
       <c r="E12" s="14" t="s">
         <v>0</v>
@@ -9027,16 +9030,16 @@
       <c r="M12" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="O12" s="66" t="s">
+      <c r="O12" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
-      <c r="T12" s="66"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="4" t="s">
         <v>49</v>
@@ -9058,14 +9061,14 @@
         <v>25</v>
       </c>
       <c r="M13" s="19"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-      <c r="T13" s="66"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
@@ -9088,14 +9091,14 @@
       <c r="M14" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="O14" s="66"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
-      <c r="T14" s="66"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
@@ -9112,14 +9115,14 @@
       <c r="M15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
@@ -9136,16 +9139,16 @@
       <c r="M16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="O16" s="66" t="s">
+      <c r="O16" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
@@ -9162,14 +9165,14 @@
       <c r="M17" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="66"/>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O17" s="67"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -9184,14 +9187,14 @@
         <v>151</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="66"/>
-      <c r="T18" s="66"/>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -9206,14 +9209,14 @@
         <v>177</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66"/>
-      <c r="T19" s="66"/>
-    </row>
-    <row r="20" spans="3:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O19" s="67"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+    </row>
+    <row r="20" spans="3:20" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -9223,7 +9226,7 @@
       <c r="L20" s="6"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -9232,16 +9235,16 @@
       <c r="K21" s="9"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="67" t="s">
+      <c r="O21" s="68" t="s">
         <v>150</v>
       </c>
-      <c r="P21" s="67"/>
-      <c r="Q21" s="67"/>
-      <c r="R21" s="67"/>
-      <c r="S21" s="67"/>
-      <c r="T21" s="67"/>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="P21" s="68"/>
+      <c r="Q21" s="68"/>
+      <c r="R21" s="68"/>
+      <c r="S21" s="68"/>
+      <c r="T21" s="68"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -9251,7 +9254,7 @@
       <c r="L22" s="6"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -9260,16 +9263,16 @@
       <c r="K23" s="9"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="66" t="s">
+      <c r="O23" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -9278,14 +9281,14 @@
       <c r="K24" s="9"/>
       <c r="L24" s="6"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O24" s="67"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -9294,14 +9297,14 @@
       <c r="K25" s="9"/>
       <c r="L25" s="6"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O25" s="67"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -9310,14 +9313,14 @@
       <c r="K26" s="9"/>
       <c r="L26" s="6"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O26" s="67"/>
+      <c r="P26" s="67"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -9326,16 +9329,16 @@
       <c r="K27" s="9"/>
       <c r="L27" s="6"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="66" t="s">
+      <c r="O27" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-      <c r="T27" s="66"/>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -9344,14 +9347,14 @@
       <c r="K28" s="9"/>
       <c r="L28" s="6"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -9360,14 +9363,14 @@
       <c r="K29" s="9"/>
       <c r="L29" s="6"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="66"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-      <c r="T29" s="66"/>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O29" s="67"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -9376,14 +9379,14 @@
       <c r="K30" s="9"/>
       <c r="L30" s="6"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="66"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="66"/>
-      <c r="T30" s="66"/>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O30" s="67"/>
+      <c r="P30" s="67"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -9392,16 +9395,16 @@
       <c r="K31" s="9"/>
       <c r="L31" s="6"/>
       <c r="M31" s="2"/>
-      <c r="O31" s="66" t="s">
+      <c r="O31" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="66"/>
-      <c r="S31" s="66"/>
-      <c r="T31" s="66"/>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -9410,14 +9413,14 @@
       <c r="K32" s="9"/>
       <c r="L32" s="6"/>
       <c r="M32" s="2"/>
-      <c r="O32" s="66"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="66"/>
-      <c r="S32" s="66"/>
-      <c r="T32" s="66"/>
-    </row>
-    <row r="33" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O32" s="67"/>
+      <c r="P32" s="67"/>
+      <c r="Q32" s="67"/>
+      <c r="R32" s="67"/>
+      <c r="S32" s="67"/>
+      <c r="T32" s="67"/>
+    </row>
+    <row r="33" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -9426,14 +9429,14 @@
       <c r="K33" s="9"/>
       <c r="L33" s="6"/>
       <c r="M33" s="2"/>
-      <c r="O33" s="66"/>
-      <c r="P33" s="66"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="66"/>
-      <c r="S33" s="66"/>
-      <c r="T33" s="66"/>
-    </row>
-    <row r="34" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O33" s="67"/>
+      <c r="P33" s="67"/>
+      <c r="Q33" s="67"/>
+      <c r="R33" s="67"/>
+      <c r="S33" s="67"/>
+      <c r="T33" s="67"/>
+    </row>
+    <row r="34" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -9442,14 +9445,14 @@
       <c r="K34" s="9"/>
       <c r="L34" s="6"/>
       <c r="M34" s="2"/>
-      <c r="O34" s="66"/>
-      <c r="P34" s="66"/>
-      <c r="Q34" s="66"/>
-      <c r="R34" s="66"/>
-      <c r="S34" s="66"/>
-      <c r="T34" s="66"/>
-    </row>
-    <row r="35" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O34" s="67"/>
+      <c r="P34" s="67"/>
+      <c r="Q34" s="67"/>
+      <c r="R34" s="67"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="67"/>
+    </row>
+    <row r="35" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -9459,7 +9462,7 @@
       <c r="L35" s="6"/>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:20" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -9469,7 +9472,7 @@
       <c r="L36" s="6"/>
       <c r="M36" s="2"/>
     </row>
-    <row r="37" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:20" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -9478,7 +9481,7 @@
       <c r="L37" s="6"/>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:20" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -9487,7 +9490,7 @@
       <c r="L38" s="6"/>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:20" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -9496,7 +9499,7 @@
       <c r="L39" s="6"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:20" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -9505,7 +9508,7 @@
       <c r="L40" s="6"/>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:20" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -9514,7 +9517,7 @@
       <c r="L41" s="6"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:20" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -9523,7 +9526,7 @@
       <c r="L42" s="6"/>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:20" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -9532,7 +9535,7 @@
       <c r="L43" s="6"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="3:20" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:20" x14ac:dyDescent="0.25">
       <c r="E44" s="2"/>
       <c r="F44" s="9"/>
       <c r="G44" s="2"/>
@@ -9541,7 +9544,7 @@
       <c r="L44" s="6"/>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E45" s="3"/>
       <c r="F45" s="10"/>
       <c r="G45" s="3"/>
@@ -9568,20 +9571,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C9AFFE6-32CC-4ED3-90D1-1E871DB3E098}">
   <dimension ref="B1:S45"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.26953125" customWidth="1"/>
-    <col min="12" max="12" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.28515625" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -9589,7 +9592,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
         <v>10</v>
       </c>
@@ -9597,7 +9600,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:19" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="29" t="s">
         <v>11</v>
       </c>
@@ -9605,7 +9608,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -9613,7 +9616,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -9621,7 +9624,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -9629,7 +9632,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -9637,7 +9640,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -9645,23 +9648,23 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
     </row>
-    <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="64"/>
-      <c r="G11" s="65"/>
-      <c r="J11" s="63" t="s">
+      <c r="F11" s="65"/>
+      <c r="G11" s="66"/>
+      <c r="J11" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="64"/>
-      <c r="L11" s="65"/>
-    </row>
-    <row r="12" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K11" s="65"/>
+      <c r="L11" s="66"/>
+    </row>
+    <row r="12" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C12" s="23"/>
       <c r="E12" s="14" t="s">
         <v>0</v>
@@ -9681,16 +9684,16 @@
       <c r="L12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="66" t="s">
+      <c r="N12" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="O12" s="66"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
-    </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="O12" s="67"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="67"/>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="4" t="s">
         <v>41</v>
@@ -9710,14 +9713,14 @@
       <c r="L13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N13" s="66"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="N13" s="67"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -9737,14 +9740,14 @@
       <c r="L14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N14" s="66"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="N14" s="67"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
@@ -9758,14 +9761,14 @@
       <c r="L15" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="N15" s="67"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
@@ -9780,7 +9783,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
@@ -9789,7 +9792,7 @@
       <c r="K17" s="9"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -9798,7 +9801,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -9806,16 +9809,16 @@
       <c r="J19" s="4"/>
       <c r="K19" s="9"/>
       <c r="L19" s="2"/>
-      <c r="N19" s="77" t="s">
+      <c r="N19" s="78" t="s">
         <v>150</v>
       </c>
-      <c r="O19" s="78"/>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="78"/>
-      <c r="S19" s="79"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="O19" s="79"/>
+      <c r="P19" s="79"/>
+      <c r="Q19" s="79"/>
+      <c r="R19" s="79"/>
+      <c r="S19" s="80"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -9823,16 +9826,16 @@
       <c r="J20" s="2"/>
       <c r="K20" s="9"/>
       <c r="L20" s="2"/>
-      <c r="N20" s="68" t="s">
+      <c r="N20" s="69" t="s">
         <v>208</v>
       </c>
-      <c r="O20" s="69"/>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="69"/>
-      <c r="R20" s="69"/>
-      <c r="S20" s="70"/>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="O20" s="70"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="71"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -9840,14 +9843,14 @@
       <c r="J21" s="2"/>
       <c r="K21" s="9"/>
       <c r="L21" s="2"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="73"/>
-    </row>
-    <row r="22" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N21" s="72"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="73"/>
+      <c r="Q21" s="73"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="74"/>
+    </row>
+    <row r="22" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -9855,14 +9858,14 @@
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
       <c r="L22" s="2"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="75"/>
-      <c r="P22" s="75"/>
-      <c r="Q22" s="75"/>
-      <c r="R22" s="75"/>
-      <c r="S22" s="76"/>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N22" s="75"/>
+      <c r="O22" s="76"/>
+      <c r="P22" s="76"/>
+      <c r="Q22" s="76"/>
+      <c r="R22" s="76"/>
+      <c r="S22" s="77"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -9870,16 +9873,16 @@
       <c r="J23" s="2"/>
       <c r="K23" s="9"/>
       <c r="L23" s="2"/>
-      <c r="N23" s="68" t="s">
+      <c r="N23" s="69" t="s">
         <v>242</v>
       </c>
-      <c r="O23" s="69"/>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="69"/>
-      <c r="R23" s="69"/>
-      <c r="S23" s="70"/>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="O23" s="70"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
+      <c r="S23" s="71"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -9887,14 +9890,14 @@
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
       <c r="L24" s="2"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="73"/>
-    </row>
-    <row r="25" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N24" s="72"/>
+      <c r="O24" s="73"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="73"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="74"/>
+    </row>
+    <row r="25" spans="3:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -9902,14 +9905,14 @@
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
       <c r="L25" s="2"/>
-      <c r="N25" s="74"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="76"/>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N25" s="75"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="76"/>
+      <c r="Q25" s="76"/>
+      <c r="R25" s="76"/>
+      <c r="S25" s="77"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -9918,7 +9921,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -9927,7 +9930,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -9936,7 +9939,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -9945,7 +9948,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -9954,7 +9957,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -9963,7 +9966,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -9972,7 +9975,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -9981,7 +9984,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -9990,7 +9993,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -9999,7 +10002,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -10008,7 +10011,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -10016,7 +10019,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -10024,7 +10027,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -10032,7 +10035,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -10040,7 +10043,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -10048,7 +10051,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -10056,7 +10059,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -10064,7 +10067,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E44" s="2"/>
       <c r="F44" s="9"/>
       <c r="G44" s="2"/>
@@ -10072,7 +10075,7 @@
       <c r="K44" s="9"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E45" s="3"/>
       <c r="F45" s="10"/>
       <c r="G45" s="3"/>
@@ -10096,20 +10099,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C5DD3A-A518-4C27-BB69-BA9A009C7B9C}">
   <dimension ref="B1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.90625" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -10117,7 +10120,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -10125,7 +10128,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
@@ -10133,7 +10136,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -10141,7 +10144,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -10149,7 +10152,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -10157,7 +10160,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -10165,7 +10168,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -10173,20 +10176,20 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -10207,7 +10210,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>61</v>
@@ -10228,7 +10231,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>19</v>
@@ -10249,7 +10252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>54</v>
@@ -10270,7 +10273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>43</v>
@@ -10291,7 +10294,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>41</v>
@@ -10312,7 +10315,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>53</v>
@@ -10333,7 +10336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -10348,7 +10351,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -10363,7 +10366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -10378,7 +10381,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -10393,7 +10396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -10408,7 +10411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -10423,7 +10426,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -10438,7 +10441,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -10453,7 +10456,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -10468,7 +10471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -10483,7 +10486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -10498,7 +10501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -10513,7 +10516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -10522,7 +10525,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -10531,7 +10534,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -10540,7 +10543,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -10549,7 +10552,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -10558,7 +10561,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -10567,7 +10570,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -10576,7 +10579,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -10584,7 +10587,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -10592,7 +10595,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -10600,7 +10603,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -10608,7 +10611,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -10616,7 +10619,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -10624,7 +10627,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -10632,7 +10635,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -10655,22 +10658,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122A4D2D-7EB7-44FE-A97D-7046CE3D43BD}">
   <dimension ref="B1:S44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.453125" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -10678,7 +10681,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -10686,7 +10689,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:19" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
@@ -10694,7 +10697,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -10702,7 +10705,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -10710,7 +10713,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -10718,7 +10721,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -10726,7 +10729,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -10734,20 +10737,20 @@
         <v>149</v>
       </c>
     </row>
-    <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -10768,7 +10771,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>88</v>
@@ -10789,7 +10792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>61</v>
@@ -10809,16 +10812,16 @@
       <c r="L13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="66" t="s">
+      <c r="N13" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
@@ -10838,14 +10841,14 @@
       <c r="L14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N14" s="66"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="N14" s="67"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2"/>
       <c r="F15" s="9"/>
@@ -10859,14 +10862,14 @@
       <c r="L15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-    </row>
-    <row r="16" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N15" s="67"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+    </row>
+    <row r="16" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2"/>
       <c r="F16" s="9"/>
@@ -10880,14 +10883,14 @@
       <c r="L16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="N16" s="66"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-    </row>
-    <row r="17" spans="3:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N16" s="67"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+    </row>
+    <row r="17" spans="3:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2"/>
       <c r="F17" s="9"/>
@@ -10901,16 +10904,16 @@
       <c r="L17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="N17" s="66" t="s">
+      <c r="N17" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="66"/>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="O17" s="67"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -10924,14 +10927,14 @@
       <c r="L18" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N18" s="66"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="66"/>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -10945,14 +10948,14 @@
       <c r="L19" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N19" s="67"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -10966,14 +10969,14 @@
       <c r="L20" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="66"/>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N20" s="67"/>
+      <c r="O20" s="67"/>
+      <c r="P20" s="67"/>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="67"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -10988,7 +10991,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -10996,16 +10999,16 @@
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
-      <c r="N22" s="67" t="s">
+      <c r="N22" s="68" t="s">
         <v>150</v>
       </c>
-      <c r="O22" s="67"/>
-      <c r="P22" s="67"/>
-      <c r="Q22" s="67"/>
-      <c r="R22" s="67"/>
-      <c r="S22" s="67"/>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="O22" s="68"/>
+      <c r="P22" s="68"/>
+      <c r="Q22" s="68"/>
+      <c r="R22" s="68"/>
+      <c r="S22" s="68"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -11014,7 +11017,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -11022,16 +11025,16 @@
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
-      <c r="N24" s="66" t="s">
+      <c r="N24" s="67" t="s">
         <v>215</v>
       </c>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="O24" s="67"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -11039,14 +11042,14 @@
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
-      <c r="N25" s="66"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N25" s="67"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -11054,14 +11057,14 @@
       <c r="J26" s="2"/>
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N26" s="67"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="67"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -11069,14 +11072,14 @@
       <c r="J27" s="2"/>
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="66"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N27" s="67"/>
+      <c r="O27" s="67"/>
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -11084,16 +11087,16 @@
       <c r="J28" s="2"/>
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
-      <c r="N28" s="66" t="s">
+      <c r="N28" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -11101,14 +11104,14 @@
       <c r="J29" s="2"/>
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
-      <c r="N29" s="66"/>
-      <c r="O29" s="66"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="66"/>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N29" s="67"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -11116,14 +11119,14 @@
       <c r="J30" s="2"/>
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
-      <c r="N30" s="66"/>
-      <c r="O30" s="66"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="66"/>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N30" s="67"/>
+      <c r="O30" s="67"/>
+      <c r="P30" s="67"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -11131,14 +11134,14 @@
       <c r="J31" s="2"/>
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
-      <c r="N31" s="66"/>
-      <c r="O31" s="66"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="66"/>
-      <c r="S31" s="66"/>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.35">
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -11147,7 +11150,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -11156,7 +11159,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -11165,7 +11168,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -11174,7 +11177,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -11183,7 +11186,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -11191,7 +11194,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -11199,7 +11202,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -11207,7 +11210,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -11215,7 +11218,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -11223,7 +11226,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -11231,7 +11234,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -11239,7 +11242,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>
@@ -11264,20 +11267,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56653220-9795-4D3E-A3FB-8E6AD78BB38D}">
   <dimension ref="B1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
@@ -11285,7 +11288,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
@@ -11293,7 +11296,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
@@ -11301,7 +11304,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
@@ -11309,7 +11312,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
         <v>13</v>
       </c>
@@ -11317,7 +11320,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
         <v>14</v>
       </c>
@@ -11325,7 +11328,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
@@ -11333,7 +11336,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="22" t="s">
         <v>32</v>
       </c>
@@ -11341,20 +11344,20 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="23"/>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65"/>
-      <c r="J10" s="63" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66"/>
+      <c r="J10" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="64"/>
-      <c r="L10" s="65"/>
-    </row>
-    <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="23"/>
       <c r="E11" s="14" t="s">
         <v>0</v>
@@ -11375,7 +11378,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
         <v>53</v>
@@ -11396,7 +11399,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>41</v>
@@ -11417,7 +11420,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>19</v>
@@ -11438,7 +11441,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C15" s="23"/>
       <c r="E15" s="2" t="s">
         <v>87</v>
@@ -11459,7 +11462,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
         <v>86</v>
@@ -11480,7 +11483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
         <v>43</v>
@@ -11495,7 +11498,7 @@
       <c r="K17" s="9"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C18" s="23"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9"/>
@@ -11504,7 +11507,7 @@
       <c r="K18" s="9"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" s="23"/>
       <c r="E19" s="2"/>
       <c r="F19" s="9"/>
@@ -11513,7 +11516,7 @@
       <c r="K19" s="9"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="23"/>
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
@@ -11522,7 +11525,7 @@
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="23"/>
       <c r="E21" s="2"/>
       <c r="F21" s="9"/>
@@ -11531,7 +11534,7 @@
       <c r="K21" s="9"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="23"/>
       <c r="E22" s="2"/>
       <c r="F22" s="9"/>
@@ -11540,7 +11543,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="23"/>
       <c r="E23" s="2"/>
       <c r="F23" s="9"/>
@@ -11549,7 +11552,7 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C24" s="23"/>
       <c r="E24" s="2"/>
       <c r="F24" s="9"/>
@@ -11558,7 +11561,7 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" s="23"/>
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
@@ -11567,7 +11570,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="23"/>
       <c r="E26" s="2"/>
       <c r="F26" s="9"/>
@@ -11576,7 +11579,7 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" s="23"/>
       <c r="E27" s="2"/>
       <c r="F27" s="9"/>
@@ -11585,7 +11588,7 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C28" s="23"/>
       <c r="E28" s="2"/>
       <c r="F28" s="9"/>
@@ -11594,7 +11597,7 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C29" s="23"/>
       <c r="E29" s="2"/>
       <c r="F29" s="9"/>
@@ -11603,7 +11606,7 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="23"/>
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
@@ -11612,7 +11615,7 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="23"/>
       <c r="E31" s="2"/>
       <c r="F31" s="9"/>
@@ -11621,7 +11624,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C32" s="23"/>
       <c r="E32" s="2"/>
       <c r="F32" s="9"/>
@@ -11630,7 +11633,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -11639,7 +11642,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -11648,7 +11651,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -11657,7 +11660,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -11666,7 +11669,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -11674,7 +11677,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -11682,7 +11685,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -11690,7 +11693,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -11698,7 +11701,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -11706,7 +11709,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -11714,7 +11717,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -11722,7 +11725,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E44" s="3"/>
       <c r="F44" s="10"/>
       <c r="G44" s="3"/>

--- a/Game Stuff/Spreadsheet.xlsx
+++ b/Game Stuff/Spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Thassa's Pulse\Game Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CDCE38-96CB-42A8-9597-DCEB445A8937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCFC74F-315E-4114-B8C5-9C10256A9ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
+    <workbookView xWindow="45972" yWindow="-4944" windowWidth="17496" windowHeight="30216" firstSheet="3" activeTab="4" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
   </bookViews>
   <sheets>
     <sheet name="Material Summary" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="282">
   <si>
     <t>Item</t>
   </si>
@@ -566,9 +566,6 @@
     <t>18917.3 Mw</t>
   </si>
   <si>
-    <t>1875.2 MW</t>
-  </si>
-  <si>
     <t>Nitrogen Gas</t>
   </si>
   <si>
@@ -710,9 +707,6 @@
     <t>Rubber Line going to Phyrexian Datavaul, Keldon Armory and Obelisk of Alara  has an extra 145.2 available</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>Oran Rief Mines</t>
   </si>
   <si>
@@ -773,21 +767,12 @@
     <t>Karn's Conduit</t>
   </si>
   <si>
-    <t>Neko's Nexus, Ghirapur Gridworks, Phyrexian Datavault, Keldon Armory , Obelisks of Alara, Karn's Conduit</t>
-  </si>
-  <si>
     <t>Phyrexian Datavault, Keldon Armory, Jund Pyroclast, Urabrask's Refinery, Obelisks of Alara, Karn's Conduit</t>
   </si>
   <si>
-    <t>Thran Foundy, Neko's Nexus, Ghirapur Gridworks, The Abyssal Chains of Shandalar, Keldon Armory, Karn's Conduit</t>
-  </si>
-  <si>
     <t>Obelisks of Alara, Keldon Armory, Riveteers District, Phyrexian Datavault, Thran Foundry , Darksteel Forge</t>
   </si>
   <si>
-    <t>Bottom belt going to Keldon Armory and Karn's Conduit has an extra 277.835 Iron Ingots</t>
-  </si>
-  <si>
     <t>738.9 MW</t>
   </si>
   <si>
@@ -888,6 +873,33 @@
   </si>
   <si>
     <t xml:space="preserve">2.84 Hours </t>
+  </si>
+  <si>
+    <t>Bottom belt going to Keldon Armory, Karn's Conduit And Jund PYroclast has an extra 268.457 Iron Ingots</t>
+  </si>
+  <si>
+    <t>Neko's Nexus, Ghirapur Gridworks, Phyrexian Datavault, Keldon Armory , Obelisks of Alara, Karn's Conduit, Jund Pyroclast</t>
+  </si>
+  <si>
+    <t>Jund Pytoclast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riveteers District, Darksteel Forge, Oran-Rief Mines </t>
+  </si>
+  <si>
+    <t>Thran Foundy, Neko's Nexus, Ghirapur Gridworks, The Abyssal Chains of Shandalar, Keldon Armory, Karn's Conduit, Jund Pyroclast</t>
+  </si>
+  <si>
+    <t>Gas Filter</t>
+  </si>
+  <si>
+    <t>Iodine-Infused Filter</t>
+  </si>
+  <si>
+    <t>3000 MWh</t>
+  </si>
+  <si>
+    <t>1977.3 MW</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1492,9 +1504,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1921,18 +1930,18 @@
     </row>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="73"/>
-      <c r="E4" s="74"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="73"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="72" t="s">
+      <c r="H4" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="73"/>
-      <c r="J4" s="74"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="73"/>
     </row>
     <row r="5" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="35" t="s">
@@ -2001,7 +2010,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="11">
-        <v>1837.835</v>
+        <v>1828.46</v>
       </c>
       <c r="E8" s="41" t="s">
         <v>42</v>
@@ -2084,7 +2093,7 @@
         <v>345.64157</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>67</v>
@@ -2204,7 +2213,7 @@
         <v>1898.3330000000001</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>73</v>
@@ -2512,7 +2521,7 @@
         <v>138</v>
       </c>
       <c r="I40" s="57">
-        <v>61.7</v>
+        <v>60.4375</v>
       </c>
       <c r="J40" s="41" t="s">
         <v>131</v>
@@ -2564,10 +2573,10 @@
     </row>
     <row r="45" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H45" s="39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I45" s="58">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="J45" s="42" t="s">
         <v>165</v>
@@ -2575,7 +2584,7 @@
     </row>
     <row r="46" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H46" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I46" s="58">
         <v>12.5</v>
@@ -2586,7 +2595,7 @@
     </row>
     <row r="47" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H47" s="39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I47" s="58">
         <v>148.44999999999999</v>
@@ -2597,156 +2606,156 @@
     </row>
     <row r="48" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H48" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I48" s="58">
         <v>2</v>
       </c>
       <c r="J48" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H49" s="39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I49" s="58">
         <v>2</v>
       </c>
       <c r="J49" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H50" s="39" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I50" s="58">
         <v>2</v>
       </c>
       <c r="J50" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H51" s="39" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I51" s="58">
         <v>5</v>
       </c>
       <c r="J51" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H52" s="39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I52" s="58">
         <v>5</v>
       </c>
       <c r="J52" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H53" s="39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I53" s="58">
         <v>5</v>
       </c>
       <c r="J53" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="54" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H54" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I54" s="58">
         <v>5</v>
       </c>
       <c r="J54" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H55" s="39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I55" s="57">
         <v>5</v>
       </c>
       <c r="J55" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H56" s="39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I56" s="57">
         <v>5</v>
       </c>
       <c r="J56" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H57" s="39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I57" s="57">
         <v>5</v>
       </c>
       <c r="J57" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H58" s="39" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I58" s="57">
         <v>5</v>
       </c>
       <c r="J58" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H59" s="39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I59" s="57">
         <v>5</v>
       </c>
       <c r="J59" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H60" s="39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I60" s="57">
         <v>5</v>
       </c>
       <c r="J60" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H61" s="39" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I61" s="57">
         <v>11.41666</v>
       </c>
       <c r="J61" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="8:10" x14ac:dyDescent="0.35">
@@ -2754,181 +2763,193 @@
         <v>53</v>
       </c>
       <c r="I62" s="57">
-        <v>7.0670000000000002</v>
+        <v>4.5670000000000002</v>
       </c>
       <c r="J62" s="41" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H63" s="39" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I63" s="58">
         <v>5</v>
       </c>
       <c r="J63" s="41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H64" s="39" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I64" s="58">
         <v>2.5</v>
       </c>
       <c r="J64" s="41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H65" s="39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I65" s="58">
         <v>2</v>
       </c>
       <c r="J65" s="41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H66" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I66" s="58">
         <v>2</v>
       </c>
       <c r="J66" s="41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="3:10" x14ac:dyDescent="0.35">
       <c r="H67" s="39" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I67" s="58">
         <v>2</v>
       </c>
       <c r="J67" s="41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C68" s="1"/>
       <c r="H68" s="39" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I68" s="58">
         <v>1</v>
       </c>
       <c r="J68" s="41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C69" s="1"/>
-      <c r="H69" s="63" t="s">
-        <v>250</v>
+      <c r="H69" s="39" t="s">
+        <v>245</v>
       </c>
       <c r="I69" s="8">
         <f>5/8</f>
         <v>0.625</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C70" s="1"/>
-      <c r="H70" s="63" t="s">
-        <v>251</v>
+      <c r="H70" s="39" t="s">
+        <v>246</v>
       </c>
       <c r="I70" s="9">
         <v>1</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H71" s="63" t="s">
-        <v>252</v>
+      <c r="H71" s="39" t="s">
+        <v>247</v>
       </c>
       <c r="I71" s="9">
         <v>0.5</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="72" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H72" s="63" t="s">
-        <v>253</v>
+      <c r="H72" s="39" t="s">
+        <v>248</v>
       </c>
       <c r="I72" s="9">
         <v>3.5</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H73" s="63" t="s">
-        <v>254</v>
+      <c r="H73" s="39" t="s">
+        <v>249</v>
       </c>
       <c r="I73" s="9">
         <v>0.5</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="74" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H74" s="63" t="s">
-        <v>263</v>
+      <c r="H74" s="39" t="s">
+        <v>258</v>
       </c>
       <c r="I74" s="8">
         <v>20</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H75" s="63" t="s">
-        <v>264</v>
+      <c r="H75" s="39" t="s">
+        <v>259</v>
       </c>
       <c r="I75" s="9">
         <v>0.5</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="H76" s="63" t="s">
-        <v>265</v>
+      <c r="H76" s="39" t="s">
+        <v>260</v>
       </c>
       <c r="I76" s="9">
         <v>0.5</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C77" s="1"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="57"/>
-      <c r="J77" s="41"/>
+      <c r="H77" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="I77" s="9">
+        <v>1.5625</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="78" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C78" s="1"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="57"/>
-      <c r="J78" s="41"/>
+      <c r="H78" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="I78" s="9">
+        <v>1.5625</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="79" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C79" s="1"/>
@@ -3118,16 +3139,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -3534,7 +3555,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
@@ -3579,17 +3600,17 @@
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="73"/>
-      <c r="M10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="73"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -3636,14 +3657,14 @@
         <v>8</v>
       </c>
       <c r="M12" s="19"/>
-      <c r="O12" s="75" t="s">
+      <c r="O12" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="P12" s="75"/>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="75"/>
+      <c r="P12" s="74"/>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="74"/>
+      <c r="T12" s="74"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
@@ -3666,12 +3687,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="74"/>
+      <c r="T13" s="74"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -3688,12 +3709,12 @@
         <v>25</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
-      <c r="T14" s="75"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="74"/>
+      <c r="T14" s="74"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -3710,12 +3731,12 @@
         <v>8</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="75"/>
-      <c r="Q15" s="75"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="74"/>
+      <c r="T15" s="74"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -3732,14 +3753,14 @@
         <v>111</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="O16" s="75" t="s">
+      <c r="O16" s="74" t="s">
         <v>120</v>
       </c>
-      <c r="P16" s="75"/>
-      <c r="Q16" s="75"/>
-      <c r="R16" s="75"/>
-      <c r="S16" s="75"/>
-      <c r="T16" s="75"/>
+      <c r="P16" s="74"/>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="74"/>
+      <c r="S16" s="74"/>
+      <c r="T16" s="74"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
@@ -3756,12 +3777,12 @@
         <v>111</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="O17" s="75"/>
-      <c r="P17" s="75"/>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="75"/>
-      <c r="T17" s="75"/>
+      <c r="O17" s="74"/>
+      <c r="P17" s="74"/>
+      <c r="Q17" s="74"/>
+      <c r="R17" s="74"/>
+      <c r="S17" s="74"/>
+      <c r="T17" s="74"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
@@ -3778,12 +3799,12 @@
         <v>151</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="75"/>
-      <c r="Q18" s="75"/>
-      <c r="R18" s="75"/>
-      <c r="S18" s="75"/>
-      <c r="T18" s="75"/>
+      <c r="O18" s="74"/>
+      <c r="P18" s="74"/>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="74"/>
+      <c r="S18" s="74"/>
+      <c r="T18" s="74"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -3800,12 +3821,12 @@
         <v>151</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="75"/>
-      <c r="Q19" s="75"/>
-      <c r="R19" s="75"/>
-      <c r="S19" s="75"/>
-      <c r="T19" s="75"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="74"/>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="74"/>
+      <c r="T19" s="74"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -3819,7 +3840,7 @@
         <v>2.8</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M20" s="2"/>
     </row>
@@ -3835,17 +3856,17 @@
         <v>109.5</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M21" s="2"/>
-      <c r="O21" s="76" t="s">
+      <c r="O21" s="75" t="s">
         <v>150</v>
       </c>
-      <c r="P21" s="76"/>
-      <c r="Q21" s="76"/>
-      <c r="R21" s="76"/>
-      <c r="S21" s="76"/>
-      <c r="T21" s="76"/>
+      <c r="P21" s="75"/>
+      <c r="Q21" s="75"/>
+      <c r="R21" s="75"/>
+      <c r="S21" s="75"/>
+      <c r="T21" s="75"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="23"/>
@@ -3866,14 +3887,14 @@
       <c r="K23" s="9"/>
       <c r="L23" s="4"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="75" t="s">
-        <v>217</v>
-      </c>
-      <c r="P23" s="75"/>
-      <c r="Q23" s="75"/>
-      <c r="R23" s="75"/>
-      <c r="S23" s="75"/>
-      <c r="T23" s="75"/>
+      <c r="O23" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="P23" s="74"/>
+      <c r="Q23" s="74"/>
+      <c r="R23" s="74"/>
+      <c r="S23" s="74"/>
+      <c r="T23" s="74"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="23"/>
@@ -3884,12 +3905,12 @@
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="75"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="75"/>
-      <c r="S24" s="75"/>
-      <c r="T24" s="75"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="74"/>
+      <c r="Q24" s="74"/>
+      <c r="R24" s="74"/>
+      <c r="S24" s="74"/>
+      <c r="T24" s="74"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
@@ -3900,12 +3921,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="74"/>
+      <c r="Q25" s="74"/>
+      <c r="R25" s="74"/>
+      <c r="S25" s="74"/>
+      <c r="T25" s="74"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -3916,12 +3937,12 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="74"/>
+      <c r="S26" s="74"/>
+      <c r="T26" s="74"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -3932,14 +3953,14 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="75" t="s">
+      <c r="O27" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="75"/>
-      <c r="S27" s="75"/>
-      <c r="T27" s="75"/>
+      <c r="P27" s="74"/>
+      <c r="Q27" s="74"/>
+      <c r="R27" s="74"/>
+      <c r="S27" s="74"/>
+      <c r="T27" s="74"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -3950,12 +3971,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="75"/>
-      <c r="P28" s="75"/>
-      <c r="Q28" s="75"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="75"/>
-      <c r="T28" s="75"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="74"/>
+      <c r="T28" s="74"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C29" s="23"/>
@@ -3966,12 +3987,12 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="75"/>
-      <c r="P29" s="75"/>
-      <c r="Q29" s="75"/>
-      <c r="R29" s="75"/>
-      <c r="S29" s="75"/>
-      <c r="T29" s="75"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="74"/>
+      <c r="Q29" s="74"/>
+      <c r="R29" s="74"/>
+      <c r="S29" s="74"/>
+      <c r="T29" s="74"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -3982,12 +4003,12 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="75"/>
-      <c r="Q30" s="75"/>
-      <c r="R30" s="75"/>
-      <c r="S30" s="75"/>
-      <c r="T30" s="75"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="74"/>
+      <c r="Q30" s="74"/>
+      <c r="R30" s="74"/>
+      <c r="S30" s="74"/>
+      <c r="T30" s="74"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -4146,7 +4167,7 @@
     <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -4168,12 +4189,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="56" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="64" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -4218,16 +4239,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -4349,7 +4370,8 @@
         <v>138</v>
       </c>
       <c r="K16" s="11">
-        <v>62</v>
+        <f>62-1-9/16</f>
+        <v>60.4375</v>
       </c>
       <c r="L16" s="42" t="s">
         <v>8</v>
@@ -4373,7 +4395,7 @@
         <v>7.35</v>
       </c>
       <c r="L17" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
@@ -4448,7 +4470,7 @@
         <v>0.3</v>
       </c>
       <c r="L22" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="3:12" x14ac:dyDescent="0.35">
@@ -4463,7 +4485,7 @@
         <v>176.4</v>
       </c>
       <c r="L23" s="42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
@@ -4478,7 +4500,7 @@
         <v>28.6</v>
       </c>
       <c r="L24" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.35">
@@ -4486,9 +4508,16 @@
       <c r="E25" s="2"/>
       <c r="F25" s="9"/>
       <c r="G25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="42"/>
+      <c r="J25" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K25" s="11">
+        <f>1+9/16</f>
+        <v>1.5625</v>
+      </c>
+      <c r="L25" s="42" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -4699,7 +4728,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -4744,16 +4773,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -4836,7 +4865,7 @@
         <v>158</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.35">
@@ -4857,7 +4886,7 @@
         <v>159</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
@@ -5152,7 +5181,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="5" max="5" width="14.90625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
@@ -5170,12 +5199,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B3" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>131</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
@@ -5183,7 +5212,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -5199,7 +5228,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>170</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -5215,7 +5244,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>166</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5228,16 +5257,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -5266,7 +5295,7 @@
         <v>19</v>
       </c>
       <c r="F12" s="8">
-        <v>980.42</v>
+        <v>986.67</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>62</v>
@@ -5284,19 +5313,19 @@
     <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
       <c r="E13" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F13" s="9">
         <v>300</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="J13" s="38">
+        <v>6.25</v>
+      </c>
+      <c r="K13" s="9" t="s">
         <v>172</v>
-      </c>
-      <c r="J13" s="38">
-        <v>12.5</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>8</v>
@@ -5317,7 +5346,7 @@
         <v>12.5</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>8</v>
@@ -5338,7 +5367,7 @@
         <v>148.44999999999999</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>8</v>
@@ -5359,10 +5388,10 @@
         <v>1.55</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
@@ -5371,38 +5400,72 @@
         <v>17</v>
       </c>
       <c r="F17" s="9">
-        <v>200</v>
+        <v>212.5</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="38"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="4"/>
+      <c r="J17" s="38">
+        <f>1+9/16</f>
+        <v>1.5625</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="2"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="4"/>
+      <c r="E18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="9">
+        <f>9+3/8</f>
+        <v>9.375</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="38">
+        <f>1+9/16</f>
+        <v>1.5625</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="J19" s="11"/>
       <c r="K19" s="9"/>
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F20" s="9">
+        <f>1+9/16</f>
+        <v>1.5625</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="J20" s="11"/>
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
@@ -5645,7 +5708,7 @@
         <v>9</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="4:14" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5653,7 +5716,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="52" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="4:14" x14ac:dyDescent="0.35">
@@ -5661,7 +5724,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="4:14" x14ac:dyDescent="0.35">
@@ -5675,7 +5738,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="4:14" x14ac:dyDescent="0.35">
@@ -5683,7 +5746,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="4:14" x14ac:dyDescent="0.35">
@@ -5703,16 +5766,16 @@
       </c>
     </row>
     <row r="12" spans="4:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G12" s="89" t="s">
+      <c r="G12" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="90"/>
-      <c r="I12" s="91"/>
-      <c r="L12" s="89" t="s">
+      <c r="H12" s="89"/>
+      <c r="I12" s="90"/>
+      <c r="L12" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="90"/>
-      <c r="N12" s="91"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="90"/>
     </row>
     <row r="13" spans="4:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G13" s="53" t="s">
@@ -5748,7 +5811,7 @@
         <v>2</v>
       </c>
       <c r="M14" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N14" s="40" t="s">
         <v>8</v>
@@ -5768,7 +5831,7 @@
         <v>2</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N15" s="41" t="s">
         <v>8</v>
@@ -5788,7 +5851,7 @@
         <v>2</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N16" s="41" t="s">
         <v>8</v>
@@ -5808,7 +5871,7 @@
         <v>5</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N17" s="41" t="s">
         <v>8</v>
@@ -5828,7 +5891,7 @@
         <v>5</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N18" s="41" t="s">
         <v>8</v>
@@ -5848,7 +5911,7 @@
         <v>5</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N19" s="41" t="s">
         <v>8</v>
@@ -5862,13 +5925,13 @@
         <v>30.4666</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L20" s="6">
         <v>5</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N20" s="41" t="s">
         <v>8</v>
@@ -5882,13 +5945,13 @@
         <v>30.4666</v>
       </c>
       <c r="I21" s="41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L21" s="6">
         <v>5</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N21" s="41" t="s">
         <v>8</v>
@@ -5908,7 +5971,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N22" s="41" t="s">
         <v>8</v>
@@ -5928,7 +5991,7 @@
         <v>5</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N23" s="41" t="s">
         <v>8</v>
@@ -5948,7 +6011,7 @@
         <v>5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N24" s="41" t="s">
         <v>8</v>
@@ -5959,7 +6022,7 @@
         <v>5</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N25" s="41" t="s">
         <v>8</v>
@@ -5970,7 +6033,7 @@
         <v>5</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N26" s="41" t="s">
         <v>8</v>
@@ -5981,7 +6044,7 @@
         <v>11.41666</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N27" s="41" t="s">
         <v>8</v>
@@ -5995,7 +6058,7 @@
         <v>5</v>
       </c>
       <c r="N28" s="41" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="7:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6041,7 +6104,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.35">
@@ -6056,8 +6119,8 @@
       <c r="B4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="64" t="s">
-        <v>257</v>
+      <c r="C4" s="63" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.35">
@@ -6065,7 +6128,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.35">
@@ -6073,7 +6136,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
@@ -6081,7 +6144,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
@@ -6089,7 +6152,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6097,21 +6160,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -6173,10 +6236,10 @@
         <v>137</v>
       </c>
       <c r="L13" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="N13" s="49" t="s">
         <v>213</v>
-      </c>
-      <c r="N13" s="49" t="s">
-        <v>214</v>
       </c>
       <c r="O13" s="14" t="s">
         <v>25</v>
@@ -6200,7 +6263,7 @@
         <v>137</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N14" s="5">
         <v>1</v>
@@ -6218,7 +6281,7 @@
         <v>180</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J15" s="38"/>
       <c r="K15" s="9"/>
@@ -6296,7 +6359,7 @@
         <v>180</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="9"/>
@@ -6549,7 +6612,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="101.5" x14ac:dyDescent="0.35">
@@ -6557,7 +6620,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
@@ -6577,7 +6640,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -6585,7 +6648,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -6593,7 +6656,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6601,21 +6664,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -6641,7 +6704,7 @@
     <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C12" s="23"/>
       <c r="E12" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F12" s="8">
         <v>485.50555000000003</v>
@@ -6653,7 +6716,7 @@
         <v>5</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>8</v>
@@ -6674,7 +6737,7 @@
         <v>2.5</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>8</v>
@@ -6695,7 +6758,7 @@
         <v>2</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>8</v>
@@ -6716,7 +6779,7 @@
         <v>2</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>8</v>
@@ -6725,7 +6788,7 @@
     <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
       <c r="E16" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F16" s="9">
         <v>72</v>
@@ -6737,7 +6800,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>8</v>
@@ -6758,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>8</v>
@@ -6767,13 +6830,13 @@
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
       <c r="E18" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F18" s="9">
         <v>392.66660000000002</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J18" s="38"/>
       <c r="K18" s="9"/>
@@ -6797,7 +6860,7 @@
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
       <c r="E20" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F20" s="9">
         <v>72</v>
@@ -6812,13 +6875,13 @@
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C21" s="23"/>
       <c r="E21" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F21" s="9">
         <v>515</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="9"/>
@@ -6827,7 +6890,7 @@
     <row r="22" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C22" s="23"/>
       <c r="E22" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F22" s="9">
         <v>1.55</v>
@@ -7059,7 +7122,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="58" x14ac:dyDescent="0.35">
@@ -7067,7 +7130,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.35">
@@ -7087,7 +7150,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -7095,7 +7158,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -7111,21 +7174,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -7160,7 +7223,7 @@
         <v>33</v>
       </c>
       <c r="J12" s="38" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K12" s="8">
         <f>5/8</f>
@@ -7179,10 +7242,10 @@
         <v>138.01249999999999</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="J13" s="38" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="K13" s="9">
         <v>1</v>
@@ -7200,10 +7263,10 @@
         <v>98.243700000000004</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="J14" s="38" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="K14" s="9">
         <v>0.5</v>
@@ -7224,7 +7287,7 @@
         <v>131</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="K15" s="9">
         <v>3.5</v>
@@ -7245,7 +7308,7 @@
         <v>22</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K16" s="9">
         <v>0.5</v>
@@ -7257,7 +7320,7 @@
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F17" s="9">
         <v>110.01</v>
@@ -7278,7 +7341,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J18" s="38"/>
       <c r="K18" s="9"/>
@@ -7287,7 +7350,7 @@
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
       <c r="E19" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F19" s="9">
         <v>5</v>
@@ -7302,7 +7365,7 @@
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
       <c r="E20" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F20" s="9">
         <v>0.5</v>
@@ -7552,76 +7615,76 @@
       <c r="B2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="66" t="s">
-        <v>255</v>
+      <c r="C2" s="65" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="67" t="s">
-        <v>261</v>
+      <c r="C3" s="66" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="70"/>
+      <c r="C4" s="69"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="68"/>
+      <c r="C5" s="67"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="C6" s="68" t="s">
-        <v>272</v>
+        <v>261</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B7" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="68" t="s">
-        <v>273</v>
+        <v>262</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="C8" s="68" t="s">
-        <v>274</v>
+        <v>263</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="68" t="s">
-        <v>275</v>
+        <v>264</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="C10" s="68" t="s">
-        <v>276</v>
+        <v>265</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="C11" s="69" t="s">
-        <v>277</v>
+        <v>266</v>
+      </c>
+      <c r="C11" s="68" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7629,16 +7692,16 @@
     </row>
     <row r="13" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C13" s="23"/>
-      <c r="E13" s="72" t="s">
+      <c r="E13" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="73"/>
-      <c r="G13" s="74"/>
-      <c r="J13" s="72" t="s">
+      <c r="F13" s="72"/>
+      <c r="G13" s="73"/>
+      <c r="J13" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="73"/>
-      <c r="L13" s="74"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="73"/>
     </row>
     <row r="14" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C14" s="23"/>
@@ -7673,7 +7736,7 @@
         <v>151</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="K15" s="8">
         <v>20</v>
@@ -7694,7 +7757,7 @@
         <v>21</v>
       </c>
       <c r="J16" s="38" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="K16" s="9">
         <v>0.5</v>
@@ -7706,16 +7769,16 @@
     <row r="17" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
       <c r="E17" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F17" s="9">
         <v>25</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="J17" s="38" t="s">
         <v>260</v>
-      </c>
-      <c r="J17" s="38" t="s">
-        <v>265</v>
       </c>
       <c r="K17" s="9">
         <v>0.5</v>
@@ -7733,7 +7796,7 @@
         <v>40.888800000000003</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="J18" s="38"/>
       <c r="K18" s="9"/>
@@ -7748,7 +7811,7 @@
         <v>66.666600000000003</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J19" s="38"/>
       <c r="K19" s="9"/>
@@ -7763,7 +7826,7 @@
         <v>72.8</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J20" s="38"/>
       <c r="K20" s="9"/>
@@ -8045,16 +8108,16 @@
       <c r="D4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="73"/>
-      <c r="H4" s="74"/>
-      <c r="K4" s="72" t="s">
+      <c r="G4" s="72"/>
+      <c r="H4" s="73"/>
+      <c r="K4" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="73"/>
-      <c r="M4" s="74"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="73"/>
     </row>
     <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="17" t="s">
@@ -8433,10 +8496,11 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="24.90625" style="23" customWidth="1"/>
     <col min="6" max="6" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" customWidth="1"/>
     <col min="11" max="11" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27" bestFit="1" customWidth="1"/>
@@ -8466,7 +8530,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="3:21" x14ac:dyDescent="0.35">
@@ -8511,17 +8575,17 @@
     </row>
     <row r="12" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="13" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="72" t="s">
+      <c r="F13" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="73"/>
-      <c r="H13" s="74"/>
-      <c r="K13" s="72" t="s">
+      <c r="G13" s="72"/>
+      <c r="H13" s="73"/>
+      <c r="K13" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="73"/>
-      <c r="M13" s="73"/>
-      <c r="N13" s="74"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="72"/>
+      <c r="N13" s="73"/>
     </row>
     <row r="14" spans="3:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F14" s="14" t="s">
@@ -8545,14 +8609,14 @@
       <c r="N14" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="P14" s="75" t="s">
+      <c r="P14" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
-      <c r="T14" s="75"/>
-      <c r="U14" s="75"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="74"/>
+      <c r="T14" s="74"/>
+      <c r="U14" s="74"/>
     </row>
     <row r="15" spans="3:21" x14ac:dyDescent="0.35">
       <c r="F15" s="4" t="s">
@@ -8568,18 +8632,18 @@
         <v>35</v>
       </c>
       <c r="L15" s="8">
-        <v>1837.835</v>
+        <v>1828.46</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="N15" s="19"/>
-      <c r="P15" s="75"/>
-      <c r="Q15" s="75"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
-      <c r="U15" s="75"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="74"/>
+      <c r="T15" s="74"/>
+      <c r="U15" s="74"/>
     </row>
     <row r="16" spans="3:21" x14ac:dyDescent="0.35">
       <c r="F16" s="2" t="s">
@@ -8603,12 +8667,12 @@
       <c r="N16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P16" s="75"/>
-      <c r="Q16" s="75"/>
-      <c r="R16" s="75"/>
-      <c r="S16" s="75"/>
-      <c r="T16" s="75"/>
-      <c r="U16" s="75"/>
+      <c r="P16" s="74"/>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="74"/>
+      <c r="S16" s="74"/>
+      <c r="T16" s="74"/>
+      <c r="U16" s="74"/>
     </row>
     <row r="17" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
@@ -8626,12 +8690,12 @@
       <c r="N17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="P17" s="75"/>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="75"/>
-      <c r="T17" s="75"/>
-      <c r="U17" s="75"/>
+      <c r="P17" s="74"/>
+      <c r="Q17" s="74"/>
+      <c r="R17" s="74"/>
+      <c r="S17" s="74"/>
+      <c r="T17" s="74"/>
+      <c r="U17" s="74"/>
     </row>
     <row r="18" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
@@ -8678,17 +8742,17 @@
         <v>150</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="P20" s="76" t="s">
+      <c r="P20" s="75" t="s">
         <v>150</v>
       </c>
-      <c r="Q20" s="76"/>
-      <c r="R20" s="76"/>
-      <c r="S20" s="76"/>
-      <c r="T20" s="76"/>
-      <c r="U20" s="76"/>
+      <c r="Q20" s="75"/>
+      <c r="R20" s="75"/>
+      <c r="S20" s="75"/>
+      <c r="T20" s="75"/>
+      <c r="U20" s="75"/>
     </row>
     <row r="21" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F21" s="2"/>
@@ -8701,7 +8765,7 @@
         <v>12.013</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N21" s="2"/>
     </row>
@@ -8709,18 +8773,25 @@
       <c r="F22" s="2"/>
       <c r="G22" s="9"/>
       <c r="H22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="2"/>
+      <c r="K22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L22" s="9">
+        <f>9+3/8</f>
+        <v>9.375</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="N22" s="2"/>
-      <c r="P22" s="75" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q22" s="75"/>
-      <c r="R22" s="75"/>
-      <c r="S22" s="75"/>
-      <c r="T22" s="75"/>
-      <c r="U22" s="75"/>
+      <c r="P22" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q22" s="74"/>
+      <c r="R22" s="74"/>
+      <c r="S22" s="74"/>
+      <c r="T22" s="74"/>
+      <c r="U22" s="74"/>
     </row>
     <row r="23" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F23" s="2"/>
@@ -8730,12 +8801,12 @@
       <c r="L23" s="9"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="P23" s="75"/>
-      <c r="Q23" s="75"/>
-      <c r="R23" s="75"/>
-      <c r="S23" s="75"/>
-      <c r="T23" s="75"/>
-      <c r="U23" s="75"/>
+      <c r="P23" s="74"/>
+      <c r="Q23" s="74"/>
+      <c r="R23" s="74"/>
+      <c r="S23" s="74"/>
+      <c r="T23" s="74"/>
+      <c r="U23" s="74"/>
     </row>
     <row r="24" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F24" s="2"/>
@@ -8745,12 +8816,12 @@
       <c r="L24" s="9"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="75"/>
-      <c r="S24" s="75"/>
-      <c r="T24" s="75"/>
-      <c r="U24" s="75"/>
+      <c r="P24" s="74"/>
+      <c r="Q24" s="74"/>
+      <c r="R24" s="74"/>
+      <c r="S24" s="74"/>
+      <c r="T24" s="74"/>
+      <c r="U24" s="74"/>
     </row>
     <row r="25" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F25" s="2"/>
@@ -8760,12 +8831,12 @@
       <c r="L25" s="9"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
-      <c r="U25" s="75"/>
+      <c r="P25" s="74"/>
+      <c r="Q25" s="74"/>
+      <c r="R25" s="74"/>
+      <c r="S25" s="74"/>
+      <c r="T25" s="74"/>
+      <c r="U25" s="74"/>
     </row>
     <row r="26" spans="6:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F26" s="2"/>
@@ -8775,14 +8846,14 @@
       <c r="L26" s="9"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
-      <c r="P26" s="75" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="75"/>
+      <c r="P26" s="74" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="74"/>
+      <c r="S26" s="74"/>
+      <c r="T26" s="74"/>
+      <c r="U26" s="74"/>
     </row>
     <row r="27" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F27" s="2"/>
@@ -8792,12 +8863,12 @@
       <c r="L27" s="9"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="75"/>
-      <c r="S27" s="75"/>
-      <c r="T27" s="75"/>
-      <c r="U27" s="75"/>
+      <c r="P27" s="74"/>
+      <c r="Q27" s="74"/>
+      <c r="R27" s="74"/>
+      <c r="S27" s="74"/>
+      <c r="T27" s="74"/>
+      <c r="U27" s="74"/>
     </row>
     <row r="28" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F28" s="2"/>
@@ -8807,12 +8878,12 @@
       <c r="L28" s="9"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
-      <c r="P28" s="75"/>
-      <c r="Q28" s="75"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="75"/>
-      <c r="T28" s="75"/>
-      <c r="U28" s="75"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="74"/>
+      <c r="T28" s="74"/>
+      <c r="U28" s="74"/>
     </row>
     <row r="29" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F29" s="2"/>
@@ -8822,12 +8893,12 @@
       <c r="L29" s="9"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
-      <c r="P29" s="75"/>
-      <c r="Q29" s="75"/>
-      <c r="R29" s="75"/>
-      <c r="S29" s="75"/>
-      <c r="T29" s="75"/>
-      <c r="U29" s="75"/>
+      <c r="P29" s="74"/>
+      <c r="Q29" s="74"/>
+      <c r="R29" s="74"/>
+      <c r="S29" s="74"/>
+      <c r="T29" s="74"/>
+      <c r="U29" s="74"/>
     </row>
     <row r="30" spans="6:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F30" s="2"/>
@@ -8837,14 +8908,14 @@
       <c r="L30" s="9"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="P30" s="75" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q30" s="75"/>
-      <c r="R30" s="75"/>
-      <c r="S30" s="75"/>
-      <c r="T30" s="75"/>
-      <c r="U30" s="75"/>
+      <c r="P30" s="74" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q30" s="74"/>
+      <c r="R30" s="74"/>
+      <c r="S30" s="74"/>
+      <c r="T30" s="74"/>
+      <c r="U30" s="74"/>
     </row>
     <row r="31" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
@@ -8854,12 +8925,12 @@
       <c r="L31" s="9"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="75"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="75"/>
-      <c r="T31" s="75"/>
-      <c r="U31" s="75"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="74"/>
+      <c r="R31" s="74"/>
+      <c r="S31" s="74"/>
+      <c r="T31" s="74"/>
+      <c r="U31" s="74"/>
     </row>
     <row r="32" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
@@ -8869,12 +8940,12 @@
       <c r="L32" s="9"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-      <c r="P32" s="75"/>
-      <c r="Q32" s="75"/>
-      <c r="R32" s="75"/>
-      <c r="S32" s="75"/>
-      <c r="T32" s="75"/>
-      <c r="U32" s="75"/>
+      <c r="P32" s="74"/>
+      <c r="Q32" s="74"/>
+      <c r="R32" s="74"/>
+      <c r="S32" s="74"/>
+      <c r="T32" s="74"/>
+      <c r="U32" s="74"/>
     </row>
     <row r="33" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F33" s="2"/>
@@ -8884,12 +8955,12 @@
       <c r="L33" s="9"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
-      <c r="P33" s="75"/>
-      <c r="Q33" s="75"/>
-      <c r="R33" s="75"/>
-      <c r="S33" s="75"/>
-      <c r="T33" s="75"/>
-      <c r="U33" s="75"/>
+      <c r="P33" s="74"/>
+      <c r="Q33" s="74"/>
+      <c r="R33" s="74"/>
+      <c r="S33" s="74"/>
+      <c r="T33" s="74"/>
+      <c r="U33" s="74"/>
     </row>
     <row r="34" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
@@ -8980,6 +9051,10 @@
       <c r="L43" s="9"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
+      <c r="R43">
+        <f>277.832-9-3/8</f>
+        <v>268.45699999999999</v>
+      </c>
     </row>
     <row r="44" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F44" s="2"/>
@@ -9036,7 +9111,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F1350C4-6C4D-4B59-A3BC-5B1F652DB40B}">
-  <dimension ref="B1:O48"/>
+  <dimension ref="B1:L45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
@@ -9067,12 +9142,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -9120,16 +9195,16 @@
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="72" t="s">
+      <c r="E11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="73"/>
-      <c r="G11" s="74"/>
-      <c r="J11" s="72" t="s">
+      <c r="F11" s="72"/>
+      <c r="G11" s="73"/>
+      <c r="J11" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="73"/>
-      <c r="L11" s="74"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="73"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -9167,7 +9242,7 @@
         <v>53</v>
       </c>
       <c r="K13" s="8">
-        <v>7.0670000000000002</v>
+        <v>4.5670000000000002</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>8</v>
@@ -9236,7 +9311,7 @@
         <v>9.6</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
@@ -9251,7 +9326,7 @@
         <v>72</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
@@ -9266,7 +9341,7 @@
         <v>5</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.35">
@@ -9274,9 +9349,15 @@
       <c r="E20" s="2"/>
       <c r="F20" s="9"/>
       <c r="G20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="2"/>
+      <c r="J20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K20" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C21" s="23"/>
@@ -9386,7 +9467,7 @@
       <c r="K32" s="9"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C33" s="23"/>
       <c r="E33" s="2"/>
       <c r="F33" s="9"/>
@@ -9395,7 +9476,7 @@
       <c r="K33" s="9"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C34" s="23"/>
       <c r="E34" s="2"/>
       <c r="F34" s="9"/>
@@ -9404,7 +9485,7 @@
       <c r="K34" s="9"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C35" s="23"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
@@ -9413,7 +9494,7 @@
       <c r="K35" s="9"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C36" s="23"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -9422,7 +9503,7 @@
       <c r="K36" s="9"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
@@ -9430,7 +9511,7 @@
       <c r="K37" s="9"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E38" s="2"/>
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
@@ -9438,7 +9519,7 @@
       <c r="K38" s="9"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E39" s="2"/>
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
@@ -9446,7 +9527,7 @@
       <c r="K39" s="9"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E40" s="2"/>
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
@@ -9454,7 +9535,7 @@
       <c r="K40" s="9"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E41" s="2"/>
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
@@ -9462,7 +9543,7 @@
       <c r="K41" s="9"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E42" s="2"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
@@ -9470,7 +9551,7 @@
       <c r="K42" s="9"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
       <c r="G43" s="2"/>
@@ -9478,7 +9559,7 @@
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E44" s="2"/>
       <c r="F44" s="9"/>
       <c r="G44" s="2"/>
@@ -9486,18 +9567,13 @@
       <c r="K44" s="9"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E45" s="3"/>
       <c r="F45" s="10"/>
       <c r="G45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="10"/>
       <c r="L45" s="3"/>
-    </row>
-    <row r="48" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="O48" t="s">
-        <v>218</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9548,7 +9624,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
@@ -9596,17 +9672,17 @@
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="72" t="s">
+      <c r="E11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="73"/>
-      <c r="G11" s="74"/>
-      <c r="J11" s="72" t="s">
+      <c r="F11" s="72"/>
+      <c r="G11" s="73"/>
+      <c r="J11" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="73"/>
-      <c r="L11" s="73"/>
-      <c r="M11" s="74"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="73"/>
     </row>
     <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -9631,14 +9707,14 @@
       <c r="M12" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="O12" s="75" t="s">
+      <c r="O12" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="P12" s="75"/>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="75"/>
+      <c r="P12" s="74"/>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="74"/>
+      <c r="T12" s="74"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
@@ -9662,12 +9738,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="19"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="74"/>
+      <c r="T13" s="74"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -9692,12 +9768,12 @@
       <c r="M14" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="O14" s="75"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
-      <c r="T14" s="75"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="74"/>
+      <c r="T14" s="74"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -9716,12 +9792,12 @@
       <c r="M15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="O15" s="75"/>
-      <c r="P15" s="75"/>
-      <c r="Q15" s="75"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="74"/>
+      <c r="T15" s="74"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -9740,14 +9816,14 @@
       <c r="M16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="O16" s="75" t="s">
+      <c r="O16" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="P16" s="75"/>
-      <c r="Q16" s="75"/>
-      <c r="R16" s="75"/>
-      <c r="S16" s="75"/>
-      <c r="T16" s="75"/>
+      <c r="P16" s="74"/>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="74"/>
+      <c r="S16" s="74"/>
+      <c r="T16" s="74"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
@@ -9766,12 +9842,12 @@
       <c r="M17" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="O17" s="75"/>
-      <c r="P17" s="75"/>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="75"/>
-      <c r="T17" s="75"/>
+      <c r="O17" s="74"/>
+      <c r="P17" s="74"/>
+      <c r="Q17" s="74"/>
+      <c r="R17" s="74"/>
+      <c r="S17" s="74"/>
+      <c r="T17" s="74"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
@@ -9788,12 +9864,12 @@
         <v>151</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="75"/>
-      <c r="Q18" s="75"/>
-      <c r="R18" s="75"/>
-      <c r="S18" s="75"/>
-      <c r="T18" s="75"/>
+      <c r="O18" s="74"/>
+      <c r="P18" s="74"/>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="74"/>
+      <c r="S18" s="74"/>
+      <c r="T18" s="74"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -9801,21 +9877,21 @@
       <c r="F19" s="9"/>
       <c r="G19" s="2"/>
       <c r="J19" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K19" s="9">
         <v>13.2</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="75"/>
-      <c r="Q19" s="75"/>
-      <c r="R19" s="75"/>
-      <c r="S19" s="75"/>
-      <c r="T19" s="75"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="74"/>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="74"/>
+      <c r="T19" s="74"/>
     </row>
     <row r="20" spans="3:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -9836,14 +9912,14 @@
       <c r="K21" s="9"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="76" t="s">
+      <c r="O21" s="75" t="s">
         <v>150</v>
       </c>
-      <c r="P21" s="76"/>
-      <c r="Q21" s="76"/>
-      <c r="R21" s="76"/>
-      <c r="S21" s="76"/>
-      <c r="T21" s="76"/>
+      <c r="P21" s="75"/>
+      <c r="Q21" s="75"/>
+      <c r="R21" s="75"/>
+      <c r="S21" s="75"/>
+      <c r="T21" s="75"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="23"/>
@@ -9864,14 +9940,14 @@
       <c r="K23" s="9"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="75" t="s">
-        <v>178</v>
-      </c>
-      <c r="P23" s="75"/>
-      <c r="Q23" s="75"/>
-      <c r="R23" s="75"/>
-      <c r="S23" s="75"/>
-      <c r="T23" s="75"/>
+      <c r="O23" s="74" t="s">
+        <v>177</v>
+      </c>
+      <c r="P23" s="74"/>
+      <c r="Q23" s="74"/>
+      <c r="R23" s="74"/>
+      <c r="S23" s="74"/>
+      <c r="T23" s="74"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="23"/>
@@ -9882,12 +9958,12 @@
       <c r="K24" s="9"/>
       <c r="L24" s="6"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="75"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="75"/>
-      <c r="S24" s="75"/>
-      <c r="T24" s="75"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="74"/>
+      <c r="Q24" s="74"/>
+      <c r="R24" s="74"/>
+      <c r="S24" s="74"/>
+      <c r="T24" s="74"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
@@ -9898,12 +9974,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="6"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="74"/>
+      <c r="Q25" s="74"/>
+      <c r="R25" s="74"/>
+      <c r="S25" s="74"/>
+      <c r="T25" s="74"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -9914,12 +9990,12 @@
       <c r="K26" s="9"/>
       <c r="L26" s="6"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="74"/>
+      <c r="S26" s="74"/>
+      <c r="T26" s="74"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -9930,14 +10006,14 @@
       <c r="K27" s="9"/>
       <c r="L27" s="6"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="75" t="s">
+      <c r="O27" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="75"/>
-      <c r="S27" s="75"/>
-      <c r="T27" s="75"/>
+      <c r="P27" s="74"/>
+      <c r="Q27" s="74"/>
+      <c r="R27" s="74"/>
+      <c r="S27" s="74"/>
+      <c r="T27" s="74"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -9948,12 +10024,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="6"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="75"/>
-      <c r="P28" s="75"/>
-      <c r="Q28" s="75"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="75"/>
-      <c r="T28" s="75"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="74"/>
+      <c r="T28" s="74"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C29" s="23"/>
@@ -9964,12 +10040,12 @@
       <c r="K29" s="9"/>
       <c r="L29" s="6"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="75"/>
-      <c r="P29" s="75"/>
-      <c r="Q29" s="75"/>
-      <c r="R29" s="75"/>
-      <c r="S29" s="75"/>
-      <c r="T29" s="75"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="74"/>
+      <c r="Q29" s="74"/>
+      <c r="R29" s="74"/>
+      <c r="S29" s="74"/>
+      <c r="T29" s="74"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -9980,12 +10056,12 @@
       <c r="K30" s="9"/>
       <c r="L30" s="6"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="75"/>
-      <c r="Q30" s="75"/>
-      <c r="R30" s="75"/>
-      <c r="S30" s="75"/>
-      <c r="T30" s="75"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="74"/>
+      <c r="Q30" s="74"/>
+      <c r="R30" s="74"/>
+      <c r="S30" s="74"/>
+      <c r="T30" s="74"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -9996,14 +10072,14 @@
       <c r="K31" s="9"/>
       <c r="L31" s="6"/>
       <c r="M31" s="2"/>
-      <c r="O31" s="75" t="s">
+      <c r="O31" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="75"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="75"/>
-      <c r="T31" s="75"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="74"/>
+      <c r="R31" s="74"/>
+      <c r="S31" s="74"/>
+      <c r="T31" s="74"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C32" s="23"/>
@@ -10014,12 +10090,12 @@
       <c r="K32" s="9"/>
       <c r="L32" s="6"/>
       <c r="M32" s="2"/>
-      <c r="O32" s="75"/>
-      <c r="P32" s="75"/>
-      <c r="Q32" s="75"/>
-      <c r="R32" s="75"/>
-      <c r="S32" s="75"/>
-      <c r="T32" s="75"/>
+      <c r="O32" s="74"/>
+      <c r="P32" s="74"/>
+      <c r="Q32" s="74"/>
+      <c r="R32" s="74"/>
+      <c r="S32" s="74"/>
+      <c r="T32" s="74"/>
     </row>
     <row r="33" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C33" s="23"/>
@@ -10030,12 +10106,12 @@
       <c r="K33" s="9"/>
       <c r="L33" s="6"/>
       <c r="M33" s="2"/>
-      <c r="O33" s="75"/>
-      <c r="P33" s="75"/>
-      <c r="Q33" s="75"/>
-      <c r="R33" s="75"/>
-      <c r="S33" s="75"/>
-      <c r="T33" s="75"/>
+      <c r="O33" s="74"/>
+      <c r="P33" s="74"/>
+      <c r="Q33" s="74"/>
+      <c r="R33" s="74"/>
+      <c r="S33" s="74"/>
+      <c r="T33" s="74"/>
     </row>
     <row r="34" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C34" s="23"/>
@@ -10046,12 +10122,12 @@
       <c r="K34" s="9"/>
       <c r="L34" s="6"/>
       <c r="M34" s="2"/>
-      <c r="O34" s="75"/>
-      <c r="P34" s="75"/>
-      <c r="Q34" s="75"/>
-      <c r="R34" s="75"/>
-      <c r="S34" s="75"/>
-      <c r="T34" s="75"/>
+      <c r="O34" s="74"/>
+      <c r="P34" s="74"/>
+      <c r="Q34" s="74"/>
+      <c r="R34" s="74"/>
+      <c r="S34" s="74"/>
+      <c r="T34" s="74"/>
     </row>
     <row r="35" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C35" s="23"/>
@@ -10206,7 +10282,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
@@ -10254,16 +10330,16 @@
     </row>
     <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="72" t="s">
+      <c r="E11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="73"/>
-      <c r="G11" s="74"/>
-      <c r="J11" s="72" t="s">
+      <c r="F11" s="72"/>
+      <c r="G11" s="73"/>
+      <c r="J11" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="73"/>
-      <c r="L11" s="74"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="73"/>
     </row>
     <row r="12" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -10285,14 +10361,14 @@
       <c r="L12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="75" t="s">
+      <c r="N12" s="74" t="s">
         <v>84</v>
       </c>
-      <c r="O12" s="75"/>
-      <c r="P12" s="75"/>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
+      <c r="O12" s="74"/>
+      <c r="P12" s="74"/>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="74"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
@@ -10314,12 +10390,12 @@
       <c r="L13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N13" s="75"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
+      <c r="N13" s="74"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="74"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -10341,12 +10417,12 @@
       <c r="L14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="N14" s="75"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="74"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -10360,14 +10436,14 @@
         <v>392.666</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="N15" s="75"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="75"/>
-      <c r="Q15" s="75"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
+        <v>206</v>
+      </c>
+      <c r="N15" s="74"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="74"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -10381,7 +10457,7 @@
         <v>110.01</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.35">
@@ -10396,7 +10472,7 @@
         <v>40.887999999999998</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10416,14 +10492,14 @@
       <c r="J19" s="4"/>
       <c r="K19" s="9"/>
       <c r="L19" s="2"/>
-      <c r="N19" s="86" t="s">
+      <c r="N19" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="O19" s="87"/>
-      <c r="P19" s="87"/>
-      <c r="Q19" s="87"/>
-      <c r="R19" s="87"/>
-      <c r="S19" s="88"/>
+      <c r="O19" s="86"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="86"/>
+      <c r="R19" s="86"/>
+      <c r="S19" s="87"/>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -10433,14 +10509,14 @@
       <c r="J20" s="2"/>
       <c r="K20" s="9"/>
       <c r="L20" s="2"/>
-      <c r="N20" s="77" t="s">
-        <v>208</v>
-      </c>
-      <c r="O20" s="78"/>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78"/>
-      <c r="R20" s="78"/>
-      <c r="S20" s="79"/>
+      <c r="N20" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="O20" s="77"/>
+      <c r="P20" s="77"/>
+      <c r="Q20" s="77"/>
+      <c r="R20" s="77"/>
+      <c r="S20" s="78"/>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C21" s="23"/>
@@ -10450,12 +10526,12 @@
       <c r="J21" s="2"/>
       <c r="K21" s="9"/>
       <c r="L21" s="2"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
-      <c r="R21" s="81"/>
-      <c r="S21" s="82"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="81"/>
     </row>
     <row r="22" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C22" s="23"/>
@@ -10465,12 +10541,12 @@
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
       <c r="L22" s="2"/>
-      <c r="N22" s="83"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="84"/>
-      <c r="S22" s="85"/>
+      <c r="N22" s="82"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="83"/>
+      <c r="R22" s="83"/>
+      <c r="S22" s="84"/>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C23" s="23"/>
@@ -10480,14 +10556,14 @@
       <c r="J23" s="2"/>
       <c r="K23" s="9"/>
       <c r="L23" s="2"/>
-      <c r="N23" s="77" t="s">
-        <v>259</v>
-      </c>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
-      <c r="R23" s="78"/>
-      <c r="S23" s="79"/>
+      <c r="N23" s="76" t="s">
+        <v>254</v>
+      </c>
+      <c r="O23" s="77"/>
+      <c r="P23" s="77"/>
+      <c r="Q23" s="77"/>
+      <c r="R23" s="77"/>
+      <c r="S23" s="78"/>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C24" s="23"/>
@@ -10497,12 +10573,12 @@
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
       <c r="L24" s="2"/>
-      <c r="N24" s="80"/>
-      <c r="O24" s="81"/>
-      <c r="P24" s="81"/>
-      <c r="Q24" s="81"/>
-      <c r="R24" s="81"/>
-      <c r="S24" s="82"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="80"/>
+      <c r="P24" s="80"/>
+      <c r="Q24" s="80"/>
+      <c r="R24" s="80"/>
+      <c r="S24" s="81"/>
     </row>
     <row r="25" spans="3:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C25" s="23"/>
@@ -10512,12 +10588,12 @@
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
       <c r="L25" s="2"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="84"/>
-      <c r="P25" s="84"/>
-      <c r="Q25" s="84"/>
-      <c r="R25" s="84"/>
-      <c r="S25" s="85"/>
+      <c r="N25" s="82"/>
+      <c r="O25" s="83"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="83"/>
+      <c r="S25" s="84"/>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -10690,7 +10766,7 @@
       <c r="L45" s="3"/>
     </row>
     <row r="49" spans="7:7" x14ac:dyDescent="0.35">
-      <c r="G49" s="65"/>
+      <c r="G49" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10758,7 +10834,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -10766,7 +10842,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -10782,21 +10858,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -11303,7 +11379,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
@@ -11348,16 +11424,16 @@
     </row>
     <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -11421,14 +11497,14 @@
       <c r="L13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="75" t="s">
+      <c r="N13" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="O13" s="75"/>
-      <c r="P13" s="75"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="75"/>
-      <c r="S13" s="75"/>
+      <c r="O13" s="74"/>
+      <c r="P13" s="74"/>
+      <c r="Q13" s="74"/>
+      <c r="R13" s="74"/>
+      <c r="S13" s="74"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -11450,12 +11526,12 @@
       <c r="L14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N14" s="75"/>
-      <c r="O14" s="75"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="75"/>
-      <c r="S14" s="75"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="74"/>
+      <c r="P14" s="74"/>
+      <c r="Q14" s="74"/>
+      <c r="R14" s="74"/>
+      <c r="S14" s="74"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -11471,12 +11547,12 @@
       <c r="L15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="75"/>
-      <c r="O15" s="75"/>
-      <c r="P15" s="75"/>
-      <c r="Q15" s="75"/>
-      <c r="R15" s="75"/>
-      <c r="S15" s="75"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="74"/>
+      <c r="Q15" s="74"/>
+      <c r="R15" s="74"/>
+      <c r="S15" s="74"/>
     </row>
     <row r="16" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -11492,12 +11568,12 @@
       <c r="L16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="N16" s="75"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="75"/>
-      <c r="Q16" s="75"/>
-      <c r="R16" s="75"/>
-      <c r="S16" s="75"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="74"/>
+      <c r="P16" s="74"/>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="74"/>
+      <c r="S16" s="74"/>
     </row>
     <row r="17" spans="3:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
@@ -11513,14 +11589,14 @@
       <c r="L17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="N17" s="75" t="s">
+      <c r="N17" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="O17" s="75"/>
-      <c r="P17" s="75"/>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="75"/>
+      <c r="O17" s="74"/>
+      <c r="P17" s="74"/>
+      <c r="Q17" s="74"/>
+      <c r="R17" s="74"/>
+      <c r="S17" s="74"/>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
@@ -11536,12 +11612,12 @@
       <c r="L18" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N18" s="75"/>
-      <c r="O18" s="75"/>
-      <c r="P18" s="75"/>
-      <c r="Q18" s="75"/>
-      <c r="R18" s="75"/>
-      <c r="S18" s="75"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="74"/>
+      <c r="P18" s="74"/>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="74"/>
+      <c r="S18" s="74"/>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -11557,12 +11633,12 @@
       <c r="L19" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N19" s="75"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="75"/>
-      <c r="Q19" s="75"/>
-      <c r="R19" s="75"/>
-      <c r="S19" s="75"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="74"/>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="74"/>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -11576,14 +11652,14 @@
         <v>15</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="N20" s="75"/>
-      <c r="O20" s="75"/>
-      <c r="P20" s="75"/>
-      <c r="Q20" s="75"/>
-      <c r="R20" s="75"/>
-      <c r="S20" s="75"/>
+        <v>176</v>
+      </c>
+      <c r="N20" s="74"/>
+      <c r="O20" s="74"/>
+      <c r="P20" s="74"/>
+      <c r="Q20" s="74"/>
+      <c r="R20" s="74"/>
+      <c r="S20" s="74"/>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C21" s="23"/>
@@ -11597,7 +11673,7 @@
         <v>72</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.35">
@@ -11608,14 +11684,14 @@
       <c r="J22" s="2"/>
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
-      <c r="N22" s="76" t="s">
+      <c r="N22" s="75" t="s">
         <v>150</v>
       </c>
-      <c r="O22" s="76"/>
-      <c r="P22" s="76"/>
-      <c r="Q22" s="76"/>
-      <c r="R22" s="76"/>
-      <c r="S22" s="76"/>
+      <c r="O22" s="75"/>
+      <c r="P22" s="75"/>
+      <c r="Q22" s="75"/>
+      <c r="R22" s="75"/>
+      <c r="S22" s="75"/>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C23" s="23"/>
@@ -11634,14 +11710,14 @@
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
       <c r="L24" s="4"/>
-      <c r="N24" s="75" t="s">
-        <v>215</v>
-      </c>
-      <c r="O24" s="75"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="75"/>
-      <c r="S24" s="75"/>
+      <c r="N24" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="O24" s="74"/>
+      <c r="P24" s="74"/>
+      <c r="Q24" s="74"/>
+      <c r="R24" s="74"/>
+      <c r="S24" s="74"/>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
@@ -11651,12 +11727,12 @@
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
-      <c r="N25" s="75"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="74"/>
+      <c r="P25" s="74"/>
+      <c r="Q25" s="74"/>
+      <c r="R25" s="74"/>
+      <c r="S25" s="74"/>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -11666,12 +11742,12 @@
       <c r="J26" s="2"/>
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
-      <c r="N26" s="75"/>
-      <c r="O26" s="75"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="74"/>
+      <c r="S26" s="74"/>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -11681,12 +11757,12 @@
       <c r="J27" s="2"/>
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
-      <c r="N27" s="75"/>
-      <c r="O27" s="75"/>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="75"/>
-      <c r="R27" s="75"/>
-      <c r="S27" s="75"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="74"/>
+      <c r="Q27" s="74"/>
+      <c r="R27" s="74"/>
+      <c r="S27" s="74"/>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -11696,14 +11772,14 @@
       <c r="J28" s="2"/>
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
-      <c r="N28" s="75" t="s">
+      <c r="N28" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="O28" s="75"/>
-      <c r="P28" s="75"/>
-      <c r="Q28" s="75"/>
-      <c r="R28" s="75"/>
-      <c r="S28" s="75"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="74"/>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C29" s="23"/>
@@ -11713,12 +11789,12 @@
       <c r="J29" s="2"/>
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
-      <c r="N29" s="75"/>
-      <c r="O29" s="75"/>
-      <c r="P29" s="75"/>
-      <c r="Q29" s="75"/>
-      <c r="R29" s="75"/>
-      <c r="S29" s="75"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="74"/>
+      <c r="Q29" s="74"/>
+      <c r="R29" s="74"/>
+      <c r="S29" s="74"/>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -11728,12 +11804,12 @@
       <c r="J30" s="2"/>
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
-      <c r="N30" s="75"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="75"/>
-      <c r="Q30" s="75"/>
-      <c r="R30" s="75"/>
-      <c r="S30" s="75"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="74"/>
+      <c r="Q30" s="74"/>
+      <c r="R30" s="74"/>
+      <c r="S30" s="74"/>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -11743,12 +11819,12 @@
       <c r="J31" s="2"/>
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="75"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="75"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="75"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="74"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="74"/>
+      <c r="R31" s="74"/>
+      <c r="S31" s="74"/>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C32" s="23"/>
@@ -11955,16 +12031,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74"/>
-      <c r="J10" s="72" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="J10" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>

--- a/Game Stuff/Spreadsheet.xlsx
+++ b/Game Stuff/Spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\The Interplanar Beacon 5\Game Stuff\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\The Interplanar Beacon 7\Game Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AC2F20-808B-45BF-B922-1CB12C2912CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4770DB44-CB90-45E0-85CA-E14B656CE9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E9D95B66-7EA4-4203-9BE9-B35EAC251241}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="554">
   <si>
     <t>Item</t>
   </si>
@@ -1284,9 +1284,6 @@
     <t>Bottom belt going to Keldon Armory, Simic Subline, Karn's Conduit, The Mirrodin Trigon And Jund PYroclast has an extra 195.6402 Iron Ingots</t>
   </si>
   <si>
-    <t>Karn's Conduit, Thassa's Pulse, Simic Subline</t>
-  </si>
-  <si>
     <t>Oran-Rief Mines, Ketria Crystals, Kaladesh Refinery, Riveteers District, Thran Foundry, Darksteel Forge, Phyrexian Datavault</t>
   </si>
   <si>
@@ -1659,10 +1656,73 @@
     <t>Phyrexian Datavault, Keldon Armory, Jund Pyroclast, Urabrask's Refinery, Obelisks of Alara, Karn's Conduit, Tollarian Meltdown. Aetherflux Reactor, The Interplanar Beacon</t>
   </si>
   <si>
-    <t>The Fourfold Furnace, Tollarian Meltdown, Kaladesh Refinery, Aetherflux Reactor, Riveteers District, Keldon Armory</t>
-  </si>
-  <si>
     <t>Karn's Conduit, Tollarian Meltdown, The Interplanar Beacon</t>
+  </si>
+  <si>
+    <t>Final Stage</t>
+  </si>
+  <si>
+    <t>The Fourfold Furnace, Tollarian Meltdown, Kaladesh Refinery, Aetherflux Reactor, Riveteers District, Keldon Armory, Phyrexian Datavault</t>
+  </si>
+  <si>
+    <t>Karn's Conduit, Thassa's Pulse, Simic Subline, The Interplanar Beacon, Aetherflux Reactor</t>
+  </si>
+  <si>
+    <t>5.4 going directly to Dimensional Depot</t>
+  </si>
+  <si>
+    <t>Excited Photonic Matter</t>
+  </si>
+  <si>
+    <t>Neural Quantum Processors</t>
+  </si>
+  <si>
+    <t>AI Expansion Server</t>
+  </si>
+  <si>
+    <t>Space Elevator</t>
+  </si>
+  <si>
+    <t>2 Different Places</t>
+  </si>
+  <si>
+    <t>Neural Quantum Processor</t>
+  </si>
+  <si>
+    <t>Producing 20 without time Crystals</t>
+  </si>
+  <si>
+    <t>Producing 35 with time Crystals</t>
+  </si>
+  <si>
+    <t>Producing 31.533 with time Crystals</t>
+  </si>
+  <si>
+    <t>Producing 13.733 without time Crystals</t>
+  </si>
+  <si>
+    <t>5858 MW</t>
+  </si>
+  <si>
+    <t>7900 MWh</t>
+  </si>
+  <si>
+    <t>Cut-off Unstable</t>
+  </si>
+  <si>
+    <t>Cut-off Stable</t>
+  </si>
+  <si>
+    <t>1.34 Hours</t>
+  </si>
+  <si>
+    <t>18779.75 MW</t>
+  </si>
+  <si>
+    <t>Ballistic Warp Drives</t>
+  </si>
+  <si>
+    <t>19700 MWh</t>
   </si>
 </sst>
 </file>
@@ -2439,7 +2499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2638,25 +2698,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2762,6 +2810,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3116,18 +3185,18 @@
     </row>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="117"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="113"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="115" t="s">
+      <c r="H4" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
     </row>
     <row r="5" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="35" t="s">
@@ -3157,7 +3226,7 @@
       </c>
       <c r="D6" s="43">
         <f>'Riveteers District'!K13</f>
-        <v>132.80000000000001</v>
+        <v>26.3333333333333</v>
       </c>
       <c r="E6" s="39" t="s">
         <v>130</v>
@@ -3422,13 +3491,13 @@
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C19" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D19" s="11">
         <v>2.25</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>74</v>
@@ -3449,7 +3518,7 @@
         <v>256.18666666666667</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>75</v>
@@ -3470,7 +3539,7 @@
         <v>537.22400000000005</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>76</v>
@@ -3491,7 +3560,7 @@
         <v>435.88592592592596</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>77</v>
@@ -3509,10 +3578,10 @@
       </c>
       <c r="D23" s="9">
         <f>'Aetherflux Reactor'!$K$24</f>
-        <v>192.92777777777781</v>
+        <v>32.927777777777806</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>78</v>
@@ -3530,10 +3599,10 @@
       </c>
       <c r="D24" s="11">
         <f>'Aetherflux Reactor'!$K$31</f>
-        <v>1431.1666666666667</v>
+        <v>1344.7666666666667</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>79</v>
@@ -3553,7 +3622,7 @@
         <v>194</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>80</v>
@@ -3574,7 +3643,7 @@
         <v>19.812156862745098</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>86</v>
@@ -3587,9 +3656,16 @@
       </c>
     </row>
     <row r="27" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C27" s="6"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="40"/>
+      <c r="C27" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D27" s="9">
+        <f>'The Fourfold Furnace'!K18</f>
+        <v>778.18055555555554</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>505</v>
+      </c>
       <c r="H27" s="6" t="s">
         <v>87</v>
       </c>
@@ -3784,7 +3860,7 @@
       </c>
       <c r="I41" s="11">
         <f>'Phyrexian Datavault'!J12</f>
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="J41" s="40" t="s">
         <v>146</v>
@@ -3852,7 +3928,7 @@
       </c>
       <c r="I47" s="11">
         <f>'Jund Pyroclast'!J15</f>
-        <v>140.07999999999998</v>
+        <v>138.5</v>
       </c>
       <c r="J47" s="40" t="s">
         <v>158</v>
@@ -4412,7 +4488,7 @@
       <c r="C95" s="1"/>
       <c r="D95"/>
       <c r="H95" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I95" s="11">
         <v>4</v>
@@ -4426,13 +4502,13 @@
       <c r="C96" s="1"/>
       <c r="D96"/>
       <c r="H96" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I96" s="11">
         <v>0.1</v>
       </c>
       <c r="J96" s="40" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="97" spans="2:20" x14ac:dyDescent="0.35">
@@ -4447,7 +4523,7 @@
         <v>6.333333333333333</v>
       </c>
       <c r="J97" s="40" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.35">
@@ -4455,13 +4531,13 @@
       <c r="C98" s="1"/>
       <c r="D98"/>
       <c r="H98" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I98" s="11">
         <v>1</v>
       </c>
       <c r="J98" s="40" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="R98" s="1"/>
     </row>
@@ -4470,14 +4546,14 @@
       <c r="C99" s="1"/>
       <c r="D99"/>
       <c r="H99" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I99" s="38">
         <f>364/1215</f>
         <v>0.29958847736625516</v>
       </c>
       <c r="J99" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="R99" s="1"/>
     </row>
@@ -4492,7 +4568,7 @@
         <v>5</v>
       </c>
       <c r="J100" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="101" spans="2:20" x14ac:dyDescent="0.35">
@@ -4504,7 +4580,7 @@
         <v>8.3333333333333339</v>
       </c>
       <c r="J101" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.35">
@@ -4515,7 +4591,7 @@
         <v>45</v>
       </c>
       <c r="J102" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="T102" s="1"/>
     </row>
@@ -4527,7 +4603,7 @@
         <v>45</v>
       </c>
       <c r="J103" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="T103" s="1"/>
     </row>
@@ -4539,20 +4615,20 @@
         <v>5</v>
       </c>
       <c r="J104" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O104" s="1"/>
       <c r="T104" s="1"/>
     </row>
     <row r="105" spans="2:20" x14ac:dyDescent="0.35">
       <c r="H105" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I105" s="11">
         <v>5</v>
       </c>
       <c r="J105" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O105" s="1"/>
       <c r="T105" s="1"/>
@@ -4565,7 +4641,7 @@
         <v>5</v>
       </c>
       <c r="J106" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O106" s="1"/>
       <c r="T106" s="1"/>
@@ -4578,20 +4654,20 @@
         <v>3.75</v>
       </c>
       <c r="J107" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P107" s="1"/>
       <c r="T107" s="1"/>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.35">
       <c r="H108" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I108" s="11">
         <v>2.5</v>
       </c>
       <c r="J108" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P108" s="1"/>
     </row>
@@ -4603,32 +4679,33 @@
         <v>30</v>
       </c>
       <c r="J109" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P109" s="1"/>
     </row>
     <row r="110" spans="2:20" x14ac:dyDescent="0.35">
       <c r="H110" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I110" s="11">
-        <v>15</v>
+        <f>'Aetherflux Reactor'!K33</f>
+        <v>1</v>
       </c>
       <c r="J110" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P110" s="1"/>
     </row>
     <row r="111" spans="2:20" x14ac:dyDescent="0.35">
       <c r="H111" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I111" s="11">
         <f>14+2/3</f>
         <v>14.666666666666666</v>
       </c>
       <c r="J111" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P111" s="1"/>
     </row>
@@ -4640,7 +4717,7 @@
         <v>5</v>
       </c>
       <c r="J112" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P112" s="1"/>
     </row>
@@ -4652,19 +4729,19 @@
         <v>5</v>
       </c>
       <c r="J113" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P113" s="1"/>
     </row>
     <row r="114" spans="4:16" x14ac:dyDescent="0.35">
       <c r="H114" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="I114" s="11">
         <v>5</v>
       </c>
       <c r="J114" s="41" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="115" spans="4:16" x14ac:dyDescent="0.35">
@@ -4672,11 +4749,11 @@
         <v>358</v>
       </c>
       <c r="I115" s="11">
-        <f>'The Interplanar Beacon'!L12</f>
+        <f>'The Interplanar Beacon'!L14</f>
         <v>13.466666666666667</v>
       </c>
       <c r="J115" s="40" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="116" spans="4:16" x14ac:dyDescent="0.35">
@@ -4687,24 +4764,42 @@
         <v>5.4</v>
       </c>
       <c r="J116" s="97" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="117" spans="4:16" x14ac:dyDescent="0.35">
-      <c r="H117" s="6"/>
-      <c r="I117" s="11"/>
-      <c r="J117" s="40"/>
+      <c r="H117" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="I117" s="9">
+        <v>2.4</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>514</v>
+      </c>
       <c r="O117" s="1"/>
     </row>
     <row r="118" spans="4:16" x14ac:dyDescent="0.35">
-      <c r="H118" s="6"/>
-      <c r="I118" s="11"/>
-      <c r="J118" s="40"/>
+      <c r="H118" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="I118" s="9">
+        <v>1</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="119" spans="4:16" x14ac:dyDescent="0.35">
-      <c r="H119" s="6"/>
-      <c r="I119" s="11"/>
-      <c r="J119" s="40"/>
+      <c r="H119" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="I119" s="9">
+        <v>7</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="120" spans="4:16" x14ac:dyDescent="0.35">
       <c r="H120" s="6"/>
@@ -4875,16 +4970,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -5291,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.35">
@@ -5336,17 +5431,17 @@
     </row>
     <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="116"/>
-      <c r="M10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="113"/>
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -5393,12 +5488,12 @@
         <v>8</v>
       </c>
       <c r="M12" s="19"/>
-      <c r="O12" s="118"/>
-      <c r="P12" s="118"/>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="118"/>
-      <c r="S12" s="118"/>
-      <c r="T12" s="118"/>
+      <c r="O12" s="114"/>
+      <c r="P12" s="114"/>
+      <c r="Q12" s="114"/>
+      <c r="R12" s="114"/>
+      <c r="S12" s="114"/>
+      <c r="T12" s="114"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
@@ -5419,15 +5514,15 @@
         <v>28.745490196078421</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M13" s="2"/>
-      <c r="O13" s="118"/>
-      <c r="P13" s="118"/>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
-      <c r="T13" s="118"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -5445,12 +5540,12 @@
         <v>25</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="118"/>
-      <c r="P14" s="118"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
-      <c r="S14" s="118"/>
-      <c r="T14" s="118"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -5467,12 +5562,12 @@
         <v>8</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="O15" s="118"/>
-      <c r="P15" s="118"/>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
-      <c r="S15" s="118"/>
-      <c r="T15" s="118"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -5489,14 +5584,14 @@
         <v>111</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="O16" s="118" t="s">
+      <c r="O16" s="114" t="s">
         <v>120</v>
       </c>
-      <c r="P16" s="118"/>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="118"/>
-      <c r="S16" s="118"/>
-      <c r="T16" s="118"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="114"/>
+      <c r="T16" s="114"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
@@ -5513,12 +5608,12 @@
         <v>111</v>
       </c>
       <c r="M17" s="2"/>
-      <c r="O17" s="118"/>
-      <c r="P17" s="118"/>
-      <c r="Q17" s="118"/>
-      <c r="R17" s="118"/>
-      <c r="S17" s="118"/>
-      <c r="T17" s="118"/>
+      <c r="O17" s="114"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
@@ -5535,12 +5630,12 @@
         <v>146</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
+      <c r="S18" s="114"/>
+      <c r="T18" s="114"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -5557,12 +5652,12 @@
         <v>146</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="118"/>
-      <c r="Q19" s="118"/>
-      <c r="R19" s="118"/>
-      <c r="S19" s="118"/>
-      <c r="T19" s="118"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="114"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -5595,14 +5690,14 @@
         <v>199</v>
       </c>
       <c r="M21" s="2"/>
-      <c r="O21" s="119" t="s">
+      <c r="O21" s="115" t="s">
         <v>145</v>
       </c>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="119"/>
-      <c r="R21" s="119"/>
-      <c r="S21" s="119"/>
-      <c r="T21" s="119"/>
+      <c r="P21" s="115"/>
+      <c r="Q21" s="115"/>
+      <c r="R21" s="115"/>
+      <c r="S21" s="115"/>
+      <c r="T21" s="115"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="23"/>
@@ -5636,12 +5731,12 @@
         <v>397</v>
       </c>
       <c r="M23" s="2"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="118"/>
-      <c r="Q23" s="118"/>
-      <c r="R23" s="118"/>
-      <c r="S23" s="118"/>
-      <c r="T23" s="118"/>
+      <c r="O23" s="114"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="114"/>
+      <c r="R23" s="114"/>
+      <c r="S23" s="114"/>
+      <c r="T23" s="114"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="23"/>
@@ -5656,15 +5751,15 @@
         <v>37.166666666666664</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M24" s="2"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="118"/>
-      <c r="Q24" s="118"/>
-      <c r="R24" s="118"/>
-      <c r="S24" s="118"/>
-      <c r="T24" s="118"/>
+      <c r="O24" s="114"/>
+      <c r="P24" s="114"/>
+      <c r="Q24" s="114"/>
+      <c r="R24" s="114"/>
+      <c r="S24" s="114"/>
+      <c r="T24" s="114"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
@@ -5675,12 +5770,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="118"/>
-      <c r="Q25" s="118"/>
-      <c r="R25" s="118"/>
-      <c r="S25" s="118"/>
-      <c r="T25" s="118"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="114"/>
+      <c r="T25" s="114"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -5691,12 +5786,12 @@
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="118"/>
-      <c r="Q26" s="118"/>
-      <c r="R26" s="118"/>
-      <c r="S26" s="118"/>
-      <c r="T26" s="118"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="114"/>
+      <c r="T26" s="114"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -5707,14 +5802,14 @@
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="118" t="s">
-        <v>455</v>
-      </c>
-      <c r="P27" s="118"/>
-      <c r="Q27" s="118"/>
-      <c r="R27" s="118"/>
-      <c r="S27" s="118"/>
-      <c r="T27" s="118"/>
+      <c r="O27" s="114" t="s">
+        <v>454</v>
+      </c>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="114"/>
+      <c r="T27" s="114"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -5725,12 +5820,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="118"/>
-      <c r="Q28" s="118"/>
-      <c r="R28" s="118"/>
-      <c r="S28" s="118"/>
-      <c r="T28" s="118"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="114"/>
+      <c r="Q28" s="114"/>
+      <c r="R28" s="114"/>
+      <c r="S28" s="114"/>
+      <c r="T28" s="114"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C29" s="23"/>
@@ -5741,12 +5836,12 @@
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="118"/>
-      <c r="Q29" s="118"/>
-      <c r="R29" s="118"/>
-      <c r="S29" s="118"/>
-      <c r="T29" s="118"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="114"/>
+      <c r="R29" s="114"/>
+      <c r="S29" s="114"/>
+      <c r="T29" s="114"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -5757,12 +5852,12 @@
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="118"/>
-      <c r="Q30" s="118"/>
-      <c r="R30" s="118"/>
-      <c r="S30" s="118"/>
-      <c r="T30" s="118"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="114"/>
+      <c r="Q30" s="114"/>
+      <c r="R30" s="114"/>
+      <c r="S30" s="114"/>
+      <c r="T30" s="114"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -5912,11 +6007,11 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED21A768-E1F1-4F70-B6C9-A662B38F9ACD}">
-  <dimension ref="B1:L44"/>
+  <dimension ref="B1:L66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" customWidth="1"/>
+    <col min="3" max="3" width="30.08984375" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
@@ -5943,12 +6038,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="103.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="101.5" x14ac:dyDescent="0.35">
       <c r="B4" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -5964,7 +6059,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.35">
@@ -5972,7 +6067,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -5980,7 +6075,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5988,21 +6083,21 @@
         <v>32</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -6061,8 +6156,8 @@
         <v>134</v>
       </c>
       <c r="K13" s="11">
-        <f>246+2/3-K28</f>
-        <v>132.80000000000001</v>
+        <f>246+2/3-K28-K30</f>
+        <v>26.3333333333333</v>
       </c>
       <c r="L13" s="41" t="s">
         <v>25</v>
@@ -6315,11 +6410,11 @@
         <v>141</v>
       </c>
       <c r="K28" s="11">
-        <f>114-2/15</f>
-        <v>113.86666666666666</v>
+        <f>114+2/15</f>
+        <v>114.13333333333334</v>
       </c>
       <c r="L28" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" spans="3:12" x14ac:dyDescent="0.35">
@@ -6334,7 +6429,7 @@
         <v>40</v>
       </c>
       <c r="L29" s="41" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" spans="3:12" x14ac:dyDescent="0.35">
@@ -6342,9 +6437,16 @@
       <c r="E30" s="2"/>
       <c r="F30" s="9"/>
       <c r="G30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="40"/>
+      <c r="J30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K30" s="11">
+        <f>106+1/5</f>
+        <v>106.2</v>
+      </c>
+      <c r="L30" s="40" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -6463,6 +6565,18 @@
       <c r="J44" s="3"/>
       <c r="K44" s="44"/>
       <c r="L44" s="42"/>
+    </row>
+    <row r="64" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L64">
+        <f>296-49-1/3-K28-90</f>
+        <v>42.533333333333303</v>
+      </c>
+    </row>
+    <row r="66" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L66">
+        <f>L64/638*241</f>
+        <v>16.066666666666656</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6485,7 +6599,7 @@
     <col min="7" max="7" width="16.36328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.6328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -6502,15 +6616,15 @@
         <v>10</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="21" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B4" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>407</v>
+        <v>534</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -6555,16 +6669,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -6599,8 +6713,8 @@
         <v>133</v>
       </c>
       <c r="J12" s="38">
-        <f>10-J14-J16</f>
-        <v>8.5</v>
+        <f>10-J14-J16-J18</f>
+        <v>0.5</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>151</v>
@@ -6712,7 +6826,7 @@
         <v>152</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="3:12" x14ac:dyDescent="0.35">
@@ -6726,9 +6840,15 @@
       <c r="G18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J18" s="38"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="4"/>
+      <c r="J18" s="38">
+        <v>8</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="19" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -7053,16 +7173,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -7161,7 +7281,7 @@
       </c>
       <c r="J15" s="38">
         <f>150-J16-J19</f>
-        <v>140.07999999999998</v>
+        <v>138.5</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>167</v>
@@ -7182,7 +7302,7 @@
         <v>21</v>
       </c>
       <c r="J16" s="38">
-        <v>1.55</v>
+        <v>3.13</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>167</v>
@@ -7527,7 +7647,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="50" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.35">
@@ -7569,16 +7689,16 @@
       </c>
     </row>
     <row r="12" spans="4:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G12" s="132" t="s">
+      <c r="G12" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="133"/>
-      <c r="I12" s="134"/>
-      <c r="K12" s="115" t="s">
+      <c r="H12" s="129"/>
+      <c r="I12" s="130"/>
+      <c r="K12" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="116"/>
-      <c r="M12" s="117"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="113"/>
     </row>
     <row r="13" spans="4:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G13" s="51" t="s">
@@ -7918,7 +8038,7 @@
         <v>38.5</v>
       </c>
       <c r="M33" s="40" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="34" spans="11:13" x14ac:dyDescent="0.35">
@@ -7993,7 +8113,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.35">
@@ -8042,16 +8162,16 @@
     </row>
     <row r="10" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -8226,7 +8346,7 @@
         <v>136</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N17" s="7">
         <v>4</v>
@@ -8254,7 +8374,7 @@
         <v>136</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.35">
@@ -8576,16 +8696,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -8800,7 +8920,8 @@
         <v>167</v>
       </c>
       <c r="F22" s="9">
-        <v>1.55</v>
+        <f>1.55+1.58</f>
+        <v>3.13</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>158</v>
@@ -9086,16 +9207,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -9599,16 +9720,16 @@
     </row>
     <row r="13" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C13" s="23"/>
-      <c r="E13" s="115" t="s">
+      <c r="E13" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="116"/>
-      <c r="G13" s="117"/>
-      <c r="J13" s="115" t="s">
+      <c r="F13" s="112"/>
+      <c r="G13" s="113"/>
+      <c r="J13" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="116"/>
-      <c r="L13" s="117"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="113"/>
     </row>
     <row r="14" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C14" s="23"/>
@@ -10015,16 +10136,16 @@
       <c r="D4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="115" t="s">
+      <c r="F4" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="116"/>
-      <c r="H4" s="117"/>
-      <c r="K4" s="115" t="s">
+      <c r="G4" s="112"/>
+      <c r="H4" s="113"/>
+      <c r="K4" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="116"/>
-      <c r="M4" s="117"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="113"/>
     </row>
     <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="17" t="s">
@@ -10451,7 +10572,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="62" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.35">
@@ -10459,7 +10580,7 @@
         <v>355</v>
       </c>
       <c r="C5" s="60" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.35">
@@ -10491,7 +10612,7 @@
         <v>395</v>
       </c>
       <c r="C9" s="60" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.35">
@@ -10499,7 +10620,7 @@
         <v>356</v>
       </c>
       <c r="C10" s="60" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.35">
@@ -10515,7 +10636,7 @@
         <v>396</v>
       </c>
       <c r="C12" s="60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.35">
@@ -10547,31 +10668,31 @@
     </row>
     <row r="18" spans="3:32" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C18" s="23"/>
-      <c r="E18" s="115" t="s">
+      <c r="E18" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="116"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="117"/>
-      <c r="K18" s="115" t="s">
+      <c r="F18" s="112"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="113"/>
+      <c r="K18" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="L18" s="116"/>
-      <c r="M18" s="117"/>
-      <c r="O18" s="115" t="s">
+      <c r="L18" s="112"/>
+      <c r="M18" s="113"/>
+      <c r="O18" s="111" t="s">
         <v>262</v>
       </c>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="116"/>
-      <c r="R18" s="116"/>
-      <c r="S18" s="116"/>
-      <c r="T18" s="117"/>
-      <c r="V18" s="115" t="s">
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
+      <c r="S18" s="112"/>
+      <c r="T18" s="113"/>
+      <c r="V18" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="W18" s="116"/>
-      <c r="X18" s="116"/>
-      <c r="Y18" s="117"/>
+      <c r="W18" s="112"/>
+      <c r="X18" s="112"/>
+      <c r="Y18" s="113"/>
       <c r="AA18" s="71" t="s">
         <v>283</v>
       </c>
@@ -10614,26 +10735,26 @@
       <c r="M19" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="O19" s="140" t="s">
+      <c r="O19" s="136" t="s">
         <v>263</v>
       </c>
-      <c r="P19" s="141"/>
-      <c r="Q19" s="138" t="s">
+      <c r="P19" s="137"/>
+      <c r="Q19" s="134" t="s">
         <v>264</v>
       </c>
-      <c r="R19" s="139"/>
-      <c r="S19" s="138" t="s">
+      <c r="R19" s="135"/>
+      <c r="S19" s="134" t="s">
         <v>270</v>
       </c>
-      <c r="T19" s="139"/>
-      <c r="V19" s="140" t="s">
+      <c r="T19" s="135"/>
+      <c r="V19" s="136" t="s">
         <v>254</v>
       </c>
-      <c r="W19" s="141"/>
-      <c r="X19" s="140" t="s">
+      <c r="W19" s="137"/>
+      <c r="X19" s="136" t="s">
         <v>272</v>
       </c>
-      <c r="Y19" s="142"/>
+      <c r="Y19" s="138"/>
       <c r="AA19" s="75" t="s">
         <v>302</v>
       </c>
@@ -10745,7 +10866,7 @@
         <v>101.06666666666666</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="O21" s="38">
         <f>127+23/40</f>
@@ -11005,7 +11126,7 @@
         <v>4.8533333333333335</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="O25" s="11">
         <f>72+124/225</f>
@@ -11250,12 +11371,12 @@
       <c r="V29" s="47" t="s">
         <v>277</v>
       </c>
-      <c r="W29" s="135">
+      <c r="W29" s="131">
         <f>W28+Y28</f>
         <v>372.36370370370366</v>
       </c>
-      <c r="X29" s="136"/>
-      <c r="Y29" s="137"/>
+      <c r="X29" s="132"/>
+      <c r="Y29" s="133"/>
       <c r="AA29" s="78" t="s">
         <v>289</v>
       </c>
@@ -11479,7 +11600,7 @@
         <v>52.8</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AA34" s="78" t="s">
         <v>302</v>
@@ -12891,7 +13012,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -12969,17 +13090,17 @@
     </row>
     <row r="15" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C15" s="23"/>
-      <c r="E15" s="143" t="s">
+      <c r="E15" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="145"/>
-      <c r="J15" s="115" t="s">
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="141"/>
+      <c r="J15" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K15" s="116"/>
-      <c r="L15" s="117"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="113"/>
     </row>
     <row r="16" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C16" s="23"/>
@@ -13157,7 +13278,7 @@
         <v>760</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.35">
@@ -13448,7 +13569,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.35">
@@ -13468,7 +13589,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.35">
@@ -13476,7 +13597,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.35">
@@ -13484,7 +13605,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -13492,22 +13613,22 @@
         <v>32</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="115" t="s">
+      <c r="E11" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="145"/>
-      <c r="J11" s="115" t="s">
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="141"/>
+      <c r="J11" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="116"/>
-      <c r="L11" s="117"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="113"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -13546,7 +13667,7 @@
       </c>
       <c r="H13" s="88"/>
       <c r="J13" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K13" s="8">
         <v>4</v>
@@ -13684,7 +13805,7 @@
         <v>128.33333333333334</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H21" s="79"/>
       <c r="J21" s="2"/>
@@ -13701,7 +13822,7 @@
         <v>146.41333333333333</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H22" s="79"/>
       <c r="J22" s="2"/>
@@ -13718,7 +13839,7 @@
         <v>172.6</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H23" s="79"/>
       <c r="J23" s="2"/>
@@ -13977,7 +14098,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="87" x14ac:dyDescent="0.35">
@@ -13985,7 +14106,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="29" customHeight="1" x14ac:dyDescent="0.35">
@@ -13993,7 +14114,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.35">
@@ -14001,7 +14122,7 @@
         <v>236</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.35">
@@ -14009,7 +14130,7 @@
         <v>237</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.35">
@@ -14017,15 +14138,15 @@
         <v>355</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B8" s="21" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.35">
@@ -14033,7 +14154,7 @@
         <v>239</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.35">
@@ -14041,7 +14162,7 @@
         <v>240</v>
       </c>
       <c r="C10" s="98" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.35">
@@ -14049,37 +14170,37 @@
         <v>356</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="22" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C13" s="23"/>
-      <c r="E13" s="115" t="s">
+      <c r="E13" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="116"/>
-      <c r="G13" s="116"/>
-      <c r="H13" s="145"/>
-      <c r="J13" s="115" t="s">
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="141"/>
+      <c r="J13" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="116"/>
-      <c r="L13" s="117"/>
-      <c r="N13" s="138" t="s">
-        <v>482</v>
-      </c>
-      <c r="O13" s="146"/>
-      <c r="P13" s="146"/>
-      <c r="Q13" s="146"/>
-      <c r="R13" s="146"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="113"/>
+      <c r="N13" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="O13" s="142"/>
+      <c r="P13" s="142"/>
+      <c r="Q13" s="142"/>
+      <c r="R13" s="142"/>
       <c r="S13" s="103"/>
     </row>
     <row r="14" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14112,16 +14233,16 @@
         <v>1</v>
       </c>
       <c r="P14" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q14" s="14" t="s">
         <v>480</v>
-      </c>
-      <c r="Q14" s="14" t="s">
-        <v>481</v>
       </c>
       <c r="R14" s="14" t="s">
         <v>284</v>
       </c>
       <c r="S14" s="14" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
@@ -14138,7 +14259,7 @@
       </c>
       <c r="H15" s="19"/>
       <c r="J15" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K15" s="8">
         <f>364/1215</f>
@@ -14157,7 +14278,7 @@
         <v>346</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="R15" s="4">
         <f>(384.6+96.1)/2</f>
@@ -14178,7 +14299,7 @@
         <v>242.66666666666666</v>
       </c>
       <c r="G16" s="95" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>346</v>
@@ -14194,7 +14315,7 @@
         <v>25</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O16" s="2">
         <v>10</v>
@@ -14203,7 +14324,7 @@
         <v>346</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="R16" s="2">
         <f>1922.8/2</f>
@@ -14226,7 +14347,7 @@
         <v>62</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>87</v>
@@ -14248,7 +14369,7 @@
         <v>346</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="R17" s="2">
         <f>(1442.1+480.7)/2</f>
@@ -14272,7 +14393,7 @@
         <v>62</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>88</v>
@@ -14293,7 +14414,7 @@
         <v>346</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="R18" s="2">
         <f>(61.5+15.4)/2</f>
@@ -14307,7 +14428,7 @@
     <row r="19" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
       <c r="E19" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F19" s="11">
         <v>760</v>
@@ -14316,7 +14437,7 @@
         <v>375</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>61</v>
@@ -14335,10 +14456,10 @@
         <v>3</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R19" s="2">
         <f>(288.1+72)/2</f>
@@ -14362,7 +14483,7 @@
         <v>382</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>34</v>
@@ -14380,7 +14501,7 @@
         <v>14</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>235</v>
@@ -14404,10 +14525,10 @@
         <v>140.44444444444446</v>
       </c>
       <c r="G21" s="95" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>41</v>
@@ -14425,7 +14546,7 @@
         <v>2</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>319</v>
@@ -14451,7 +14572,7 @@
         <v>60</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>54</v>
@@ -14470,7 +14591,7 @@
         <v>5</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>325</v>
@@ -14515,10 +14636,10 @@
         <v>2</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="R23" s="2">
         <f>(255.9+64)/2</f>
@@ -14548,8 +14669,8 @@
         <v>136</v>
       </c>
       <c r="K24" s="9">
-        <f>996+25/36-K37-K39</f>
-        <v>192.92777777777781</v>
+        <f>996+25/36-K37-K39-K43</f>
+        <v>32.927777777777806</v>
       </c>
       <c r="L24" s="4" t="s">
         <v>25</v>
@@ -14561,10 +14682,10 @@
         <v>1</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="R24" s="3">
         <f>(1403.8+467.9)/2</f>
@@ -14591,7 +14712,7 @@
         <v>227</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K25" s="9">
         <v>5</v>
@@ -14602,14 +14723,14 @@
       <c r="N25" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="O25" s="147">
+      <c r="O25" s="143">
         <f>SUM(S15:S24)</f>
         <v>31929.550000000003</v>
       </c>
-      <c r="P25" s="148"/>
-      <c r="Q25" s="148"/>
-      <c r="R25" s="148"/>
-      <c r="S25" s="149"/>
+      <c r="P25" s="144"/>
+      <c r="Q25" s="144"/>
+      <c r="R25" s="144"/>
+      <c r="S25" s="145"/>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -14624,7 +14745,7 @@
         <v>62</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>131</v>
@@ -14648,7 +14769,7 @@
         <v>60</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>18</v>
@@ -14672,7 +14793,7 @@
         <v>60</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>18</v>
@@ -14681,7 +14802,7 @@
         <v>590</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.35">
@@ -14697,10 +14818,10 @@
         <v>60</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K29" s="9">
         <v>2.5</v>
@@ -14722,7 +14843,7 @@
         <v>62</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>49</v>
@@ -14746,14 +14867,14 @@
         <v>191</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>163</v>
       </c>
       <c r="K31" s="9">
         <f>1650-158-5/6-K40</f>
-        <v>1431.1666666666667</v>
+        <v>1344.7666666666667</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>25</v>
@@ -14771,7 +14892,7 @@
         <v>60</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>61</v>
@@ -14795,13 +14916,14 @@
         <v>60</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K33" s="9">
-        <v>15</v>
+        <f>15-K44</f>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>8</v>
@@ -14819,10 +14941,10 @@
         <v>60</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K34" s="9">
         <f>14+2/3</f>
@@ -14844,7 +14966,7 @@
         <v>106</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>17</v>
@@ -14869,7 +14991,7 @@
         <v>60</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>43</v>
@@ -14894,7 +15016,7 @@
         <v>60</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>136</v>
@@ -14903,7 +15025,7 @@
         <v>447.5</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.35">
@@ -14919,7 +15041,7 @@
         <v>62</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>163</v>
@@ -14928,7 +15050,7 @@
         <v>442.5</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.35">
@@ -14944,7 +15066,7 @@
         <v>60</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>136</v>
@@ -14954,7 +15076,7 @@
         <v>356.26666666666665</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.35">
@@ -14966,19 +15088,19 @@
         <v>1650</v>
       </c>
       <c r="G40" s="95" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>163</v>
       </c>
       <c r="K40" s="9">
-        <v>60</v>
+        <v>146.4</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.35">
@@ -14994,7 +15116,7 @@
         <v>62</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>86</v>
@@ -15003,7 +15125,7 @@
         <v>142</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.35">
@@ -15017,7 +15139,7 @@
         <v>146</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>54</v>
@@ -15027,12 +15149,12 @@
         <v>309.16666666666669</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E43" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F43" s="11">
         <f>114+2/15</f>
@@ -15042,11 +15164,17 @@
         <v>130</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="J43" s="2"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K43" s="9">
+        <v>160</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="44" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E44" s="6" t="s">
@@ -15060,11 +15188,17 @@
         <v>60</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="J44" s="2"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="K44" s="9">
+        <v>14</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="45" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E45" s="6" t="s">
@@ -15077,7 +15211,7 @@
         <v>60</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="9"/>
@@ -15095,7 +15229,7 @@
         <v>60</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="9"/>
@@ -15113,7 +15247,7 @@
         <v>62</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="9"/>
@@ -15121,16 +15255,16 @@
     </row>
     <row r="48" spans="3:12" x14ac:dyDescent="0.35">
       <c r="E48" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F48" s="11">
         <v>70</v>
       </c>
       <c r="G48" s="95" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="9"/>
@@ -15147,7 +15281,7 @@
         <v>23</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="10"/>
@@ -15162,10 +15296,10 @@
         <v>71.333333333333329</v>
       </c>
       <c r="G50" s="95" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="51" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15175,17 +15309,17 @@
       <c r="H51" s="66"/>
     </row>
     <row r="52" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E52" s="132" t="s">
-        <v>473</v>
-      </c>
-      <c r="F52" s="133"/>
-      <c r="G52" s="133"/>
-      <c r="H52" s="134"/>
-      <c r="J52" s="132" t="s">
-        <v>473</v>
-      </c>
-      <c r="K52" s="133"/>
-      <c r="L52" s="134"/>
+      <c r="E52" s="128" t="s">
+        <v>472</v>
+      </c>
+      <c r="F52" s="129"/>
+      <c r="G52" s="129"/>
+      <c r="H52" s="130"/>
+      <c r="J52" s="128" t="s">
+        <v>472</v>
+      </c>
+      <c r="K52" s="129"/>
+      <c r="L52" s="130"/>
       <c r="M52" s="13"/>
     </row>
     <row r="53" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15224,7 +15358,7 @@
       </c>
       <c r="H54" s="4"/>
       <c r="J54" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K54" s="38">
         <f>364/1215</f>
@@ -15244,7 +15378,7 @@
       </c>
       <c r="H55" s="2"/>
       <c r="J55" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K55" s="11">
         <v>2.5</v>
@@ -15273,17 +15407,17 @@
     </row>
     <row r="57" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E57" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F57" s="2">
         <v>70</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H57" s="2"/>
       <c r="J57" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K57" s="11">
         <v>5</v>
@@ -15292,7 +15426,7 @@
     </row>
     <row r="58" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E58" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F58" s="11">
         <f>114+2/15</f>
@@ -15358,11 +15492,11 @@
         <v>454.44444444444446</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H61" s="2"/>
       <c r="J61" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K61" s="11">
         <f>14+2/3</f>
@@ -15382,7 +15516,7 @@
       </c>
       <c r="H62" s="2"/>
       <c r="J62" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K62" s="11">
         <v>15</v>
@@ -15410,7 +15544,7 @@
     </row>
     <row r="64" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E64" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F64" s="2">
         <v>760</v>
@@ -15474,7 +15608,7 @@
         <v>1650</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H67" s="2"/>
       <c r="J67" s="6" t="s">
@@ -15488,7 +15622,7 @@
     </row>
     <row r="68" spans="5:12" x14ac:dyDescent="0.35">
       <c r="E68" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F68" s="2">
         <v>1800</v>
@@ -15515,7 +15649,7 @@
         <v>4038.2732641975308</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H69" s="2"/>
       <c r="J69" s="6" t="s">
@@ -15636,7 +15770,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="29" x14ac:dyDescent="0.35">
@@ -15644,7 +15778,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="38.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -15652,7 +15786,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.35">
@@ -15660,7 +15794,7 @@
         <v>236</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.35">
@@ -15668,15 +15802,15 @@
         <v>237</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B7" s="21" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.35">
@@ -15684,7 +15818,7 @@
         <v>239</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.35">
@@ -15692,37 +15826,37 @@
         <v>240</v>
       </c>
       <c r="C9" s="98" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="115" t="s">
+      <c r="E11" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="145"/>
-      <c r="J11" s="115" t="s">
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="141"/>
+      <c r="J11" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="116"/>
-      <c r="L11" s="117"/>
-      <c r="N11" s="132" t="s">
-        <v>423</v>
-      </c>
-      <c r="O11" s="133"/>
-      <c r="P11" s="133"/>
-      <c r="Q11" s="133"/>
-      <c r="R11" s="134"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="113"/>
+      <c r="N11" s="128" t="s">
+        <v>422</v>
+      </c>
+      <c r="O11" s="129"/>
+      <c r="P11" s="129"/>
+      <c r="Q11" s="129"/>
+      <c r="R11" s="130"/>
     </row>
     <row r="12" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -15751,7 +15885,7 @@
         <v>283</v>
       </c>
       <c r="O12" s="90" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P12" s="90" t="s">
         <v>284</v>
@@ -15776,14 +15910,14 @@
       </c>
       <c r="H13" s="88"/>
       <c r="J13" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K13" s="8">
         <f>597-K19</f>
         <v>142.55555555555554</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N13" s="5" t="s">
         <v>322</v>
@@ -15799,7 +15933,7 @@
         <v>4500</v>
       </c>
       <c r="R13" s="41" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.35">
@@ -15815,7 +15949,7 @@
       </c>
       <c r="H14" s="79"/>
       <c r="J14" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K14" s="9">
         <v>2.25</v>
@@ -15837,7 +15971,7 @@
         <v>341</v>
       </c>
       <c r="R14" s="40" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.35">
@@ -15850,7 +15984,7 @@
         <v>1950</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H15" s="79"/>
       <c r="J15" s="4" t="s">
@@ -15860,7 +15994,7 @@
         <v>13.2</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>323</v>
@@ -15893,7 +16027,7 @@
       </c>
       <c r="H16" s="79"/>
       <c r="J16" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K16" s="9">
         <v>0.1</v>
@@ -15916,7 +16050,7 @@
         <v>3884.8</v>
       </c>
       <c r="R16" s="40" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="3:18" x14ac:dyDescent="0.35">
@@ -15942,7 +16076,7 @@
         <v>8</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O17" s="2">
         <v>8</v>
@@ -15956,7 +16090,7 @@
         <v>5784.8</v>
       </c>
       <c r="R17" s="40" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" spans="3:18" x14ac:dyDescent="0.35">
@@ -15972,7 +16106,7 @@
       </c>
       <c r="H18" s="79"/>
       <c r="J18" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K18" s="9">
         <v>1</v>
@@ -15995,7 +16129,7 @@
         <v>776.8</v>
       </c>
       <c r="R18" s="40" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" spans="3:18" x14ac:dyDescent="0.35">
@@ -16010,14 +16144,14 @@
       <c r="G19" s="6"/>
       <c r="H19" s="79"/>
       <c r="J19" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K19" s="9">
         <f>4090/9</f>
         <v>454.44444444444446</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>323</v>
@@ -16034,7 +16168,7 @@
         <v>282</v>
       </c>
       <c r="R19" s="40" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" spans="3:18" x14ac:dyDescent="0.35">
@@ -16044,16 +16178,16 @@
       <c r="G20" s="6"/>
       <c r="H20" s="79"/>
       <c r="J20" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K20" s="9">
         <v>70</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O20" s="2">
         <v>8</v>
@@ -16067,7 +16201,7 @@
         <v>5541.6</v>
       </c>
       <c r="R20" s="40" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" spans="3:18" x14ac:dyDescent="0.35">
@@ -16094,7 +16228,7 @@
         <v>2063</v>
       </c>
       <c r="R21" s="40" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="3:18" x14ac:dyDescent="0.35">
@@ -16107,7 +16241,7 @@
       <c r="K22" s="9"/>
       <c r="L22" s="4"/>
       <c r="N22" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O22" s="2">
         <v>6</v>
@@ -16121,7 +16255,7 @@
         <v>3557.1000000000004</v>
       </c>
       <c r="R22" s="40" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="23" spans="3:18" x14ac:dyDescent="0.35">
@@ -16148,7 +16282,7 @@
         <v>257.90000000000003</v>
       </c>
       <c r="R23" s="40" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="24" spans="3:18" x14ac:dyDescent="0.35">
@@ -16175,7 +16309,7 @@
         <v>1324.1999999999998</v>
       </c>
       <c r="R24" s="40" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="25" spans="3:18" x14ac:dyDescent="0.35">
@@ -16188,7 +16322,7 @@
       <c r="K25" s="9"/>
       <c r="L25" s="4"/>
       <c r="N25" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="O25" s="2">
         <v>2</v>
@@ -16238,13 +16372,13 @@
       <c r="N27" s="92" t="s">
         <v>268</v>
       </c>
-      <c r="O27" s="136">
+      <c r="O27" s="132">
         <f>SUM(Q13:Q26)</f>
         <v>36259.599999999999</v>
       </c>
-      <c r="P27" s="136"/>
-      <c r="Q27" s="136"/>
-      <c r="R27" s="137"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="132"/>
+      <c r="R27" s="133"/>
     </row>
     <row r="28" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -16456,7 +16590,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="136" customHeight="1" x14ac:dyDescent="0.35">
@@ -16464,7 +16598,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.35">
@@ -16472,7 +16606,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.35">
@@ -16480,7 +16614,7 @@
         <v>236</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.35">
@@ -16488,7 +16622,7 @@
         <v>237</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.35">
@@ -16496,15 +16630,15 @@
         <v>355</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B8" s="21" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.35">
@@ -16512,7 +16646,7 @@
         <v>239</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.35">
@@ -16520,7 +16654,7 @@
         <v>240</v>
       </c>
       <c r="C10" s="98" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.35">
@@ -16528,36 +16662,36 @@
         <v>356</v>
       </c>
       <c r="C11" s="98" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="12" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="22" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E13" s="115" t="s">
+      <c r="E13" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="116"/>
-      <c r="G13" s="116"/>
-      <c r="H13" s="145"/>
-      <c r="J13" s="115" t="s">
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="141"/>
+      <c r="J13" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="116"/>
-      <c r="L13" s="117"/>
-      <c r="N13" s="132" t="s">
-        <v>423</v>
-      </c>
-      <c r="O13" s="133"/>
-      <c r="P13" s="133"/>
-      <c r="Q13" s="133"/>
-      <c r="R13" s="134"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="113"/>
+      <c r="N13" s="128" t="s">
+        <v>422</v>
+      </c>
+      <c r="O13" s="129"/>
+      <c r="P13" s="129"/>
+      <c r="Q13" s="129"/>
+      <c r="R13" s="130"/>
     </row>
     <row r="14" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E14" s="32" t="s">
@@ -16585,7 +16719,7 @@
         <v>283</v>
       </c>
       <c r="O14" s="90" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P14" s="90" t="s">
         <v>284</v>
@@ -16605,7 +16739,7 @@
         <v>600</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H15" s="88"/>
       <c r="J15" s="4" t="s">
@@ -16633,7 +16767,7 @@
         <v>1776.3000000000002</v>
       </c>
       <c r="R15" s="41" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.35">
@@ -16656,10 +16790,10 @@
         <v>180.1878431372549</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O16" s="2">
         <v>12</v>
@@ -16673,7 +16807,7 @@
         <v>2385.6000000000004</v>
       </c>
       <c r="R16" s="40" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17" spans="5:18" x14ac:dyDescent="0.35">
@@ -16688,7 +16822,7 @@
       </c>
       <c r="H17" s="79"/>
       <c r="J17" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K17" s="9">
         <v>5</v>
@@ -16697,7 +16831,7 @@
         <v>8</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O17" s="2">
         <v>4</v>
@@ -16711,7 +16845,7 @@
         <v>898</v>
       </c>
       <c r="R17" s="40" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" spans="5:18" x14ac:dyDescent="0.35">
@@ -16722,12 +16856,19 @@
         <v>13.2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H18" s="79"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="4"/>
+      <c r="J18" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="K18" s="9">
+        <f>858+13/72-K19</f>
+        <v>778.18055555555554</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="N18" s="6" t="s">
         <v>322</v>
       </c>
@@ -16743,7 +16884,7 @@
         <v>2305.6499999999996</v>
       </c>
       <c r="R18" s="40" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="19" spans="5:18" x14ac:dyDescent="0.35">
@@ -16755,14 +16896,20 @@
         <v>142.55555555555554</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H19" s="79"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="K19" s="9">
+        <v>80</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>514</v>
+      </c>
       <c r="N19" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O19" s="2">
         <v>2</v>
@@ -16776,7 +16923,7 @@
         <v>433</v>
       </c>
       <c r="R19" s="40" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" spans="5:18" x14ac:dyDescent="0.35">
@@ -16787,14 +16934,14 @@
         <v>447.5</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H20" s="79"/>
       <c r="J20" s="4"/>
       <c r="K20" s="9"/>
       <c r="L20" s="4"/>
       <c r="N20" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O20" s="2">
         <v>1</v>
@@ -16808,7 +16955,7 @@
         <v>4.75</v>
       </c>
       <c r="R20" s="40" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="21" spans="5:18" x14ac:dyDescent="0.35">
@@ -16819,7 +16966,7 @@
         <v>590</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H21" s="79"/>
       <c r="J21" s="4"/>
@@ -16839,7 +16986,7 @@
         <v>442.5</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H22" s="79"/>
       <c r="J22" s="2"/>
@@ -16952,13 +17099,13 @@
       <c r="N29" s="105" t="s">
         <v>268</v>
       </c>
-      <c r="O29" s="136">
+      <c r="O29" s="132">
         <f>SUM(Q15:Q20)</f>
         <v>7803.3</v>
       </c>
-      <c r="P29" s="136"/>
-      <c r="Q29" s="148"/>
-      <c r="R29" s="137"/>
+      <c r="P29" s="132"/>
+      <c r="Q29" s="144"/>
+      <c r="R29" s="133"/>
     </row>
     <row r="30" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E30" s="2"/>
@@ -17135,7 +17282,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D69D620-923C-4937-810A-6C8CDA7CC8CD}">
-  <dimension ref="C2:U70"/>
+  <dimension ref="C2:U72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="25.90625" bestFit="1" customWidth="1"/>
@@ -17149,8 +17296,8 @@
     <col min="13" max="13" width="17.90625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.08984375" customWidth="1"/>
+    <col min="17" max="17" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.90625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="40.08984375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16.7265625" bestFit="1" customWidth="1"/>
@@ -17162,7 +17309,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="3:21" ht="96" customHeight="1" x14ac:dyDescent="0.35">
@@ -17170,7 +17317,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="3:21" x14ac:dyDescent="0.35">
@@ -17178,302 +17325,312 @@
         <v>11</v>
       </c>
       <c r="D5" s="25"/>
-      <c r="H5">
-        <f>G14+G29</f>
-        <v>218.24</v>
-      </c>
     </row>
     <row r="6" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C6" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="D6" s="25"/>
+      <c r="D6" s="25" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="7" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C7" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="D7" s="25"/>
+      <c r="D7" s="25" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="8" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C8" s="21" t="s">
+        <v>549</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="9" spans="3:21" x14ac:dyDescent="0.35">
+      <c r="C9" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="D8" s="25"/>
-    </row>
-    <row r="9" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C9" s="22" t="s">
+      <c r="D9" s="25" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="10" spans="3:21" x14ac:dyDescent="0.35">
+      <c r="C10" s="99" t="s">
         <v>240</v>
       </c>
-      <c r="D9" s="26"/>
-    </row>
-    <row r="10" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D10" s="23"/>
-      <c r="F10" s="115" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="116"/>
-      <c r="H10" s="116"/>
-      <c r="I10" s="145"/>
-      <c r="K10" s="115" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="116"/>
-      <c r="M10" s="117"/>
-      <c r="O10" s="115" t="s">
-        <v>482</v>
-      </c>
-      <c r="P10" s="116"/>
-      <c r="Q10" s="116"/>
-      <c r="R10" s="116"/>
-      <c r="S10" s="116"/>
-      <c r="T10" s="116"/>
-      <c r="U10" s="117"/>
+      <c r="D10" s="98" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="11" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D11" s="23"/>
-      <c r="F11" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" s="34" t="s">
-        <v>516</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="O11" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="P11" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="34" t="s">
-        <v>480</v>
-      </c>
-      <c r="R11" s="34" t="s">
-        <v>514</v>
-      </c>
-      <c r="S11" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="T11" s="34" t="s">
-        <v>284</v>
-      </c>
-      <c r="U11" s="34" t="s">
-        <v>484</v>
-      </c>
+      <c r="C11" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="D11" s="26"/>
     </row>
     <row r="12" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D12" s="23"/>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="111" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="141"/>
+      <c r="K12" s="111" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="112"/>
+      <c r="M12" s="113"/>
+      <c r="O12" s="111" t="s">
+        <v>481</v>
+      </c>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="112"/>
+      <c r="R12" s="112"/>
+      <c r="S12" s="112"/>
+      <c r="T12" s="112"/>
+      <c r="U12" s="113"/>
+    </row>
+    <row r="13" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D13" s="23"/>
+      <c r="F13" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="101" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="P13" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="R13" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="S13" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="U13" s="34" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="14" spans="3:21" x14ac:dyDescent="0.35">
+      <c r="D14" s="23"/>
+      <c r="F14" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G14" s="43">
         <v>1200</v>
       </c>
-      <c r="H12" s="102" t="s">
+      <c r="H14" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="19" t="s">
-        <v>517</v>
-      </c>
-      <c r="K12" s="4" t="s">
+      <c r="I14" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L14" s="8">
         <f>13+7/15</f>
         <v>13.466666666666667</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="106" t="s">
+      <c r="O14" s="106" t="s">
         <v>322</v>
       </c>
-      <c r="P12" s="43">
+      <c r="P14" s="43">
         <v>6</v>
       </c>
-      <c r="Q12" s="107" t="s">
-        <v>517</v>
-      </c>
-      <c r="R12" s="43" t="s">
+      <c r="Q14" s="107" t="s">
+        <v>516</v>
+      </c>
+      <c r="R14" s="43" t="s">
         <v>319</v>
       </c>
-      <c r="S12" s="107" t="s">
+      <c r="S14" s="107" t="s">
         <v>325</v>
       </c>
-      <c r="T12" s="43">
+      <c r="T14" s="106">
         <f>(250+750)/2</f>
         <v>500</v>
       </c>
-      <c r="U12" s="108">
-        <f>P12*T12</f>
+      <c r="U14" s="43">
+        <f t="shared" ref="U14:U25" si="0">P14*T14</f>
         <v>3000</v>
       </c>
-    </row>
-    <row r="13" spans="3:21" x14ac:dyDescent="0.35">
-      <c r="D13" s="23"/>
-      <c r="F13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="11">
-        <f>270+127+34/65+0.2</f>
-        <v>397.72307692307692</v>
-      </c>
-      <c r="H13" s="95" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L13" s="9">
-        <f>310-304.6</f>
-        <v>5.3999999999999773</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="O13" s="109" t="s">
-        <v>497</v>
-      </c>
-      <c r="P13" s="11">
-        <v>20</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="R13" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="T13" s="11">
-        <f>(100+400)/2</f>
-        <v>250</v>
-      </c>
-      <c r="U13" s="108">
-        <f>P13*T13</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="14" spans="3:21" x14ac:dyDescent="0.35">
-      <c r="D14" s="23"/>
-      <c r="F14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="11">
-        <v>127.2</v>
-      </c>
-      <c r="H14" s="95" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="4"/>
-      <c r="O14" s="109"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="110"/>
     </row>
     <row r="15" spans="3:21" x14ac:dyDescent="0.35">
       <c r="D15" s="23"/>
       <c r="F15" s="6" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G15" s="11">
-        <f>473+27/65</f>
-        <v>473.4153846153846</v>
+        <f>270+127+34/65+0.2</f>
+        <v>397.72307692307692</v>
       </c>
       <c r="H15" s="95" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="4"/>
-      <c r="O15" s="109"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="110"/>
+        <v>518</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="9">
+        <f>310-304.6</f>
+        <v>5.3999999999999773</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="108" t="s">
+        <v>496</v>
+      </c>
+      <c r="P15" s="11">
+        <v>20</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="R15" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="T15" s="108">
+        <f>(100+400)/2</f>
+        <v>250</v>
+      </c>
+      <c r="U15" s="11">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
     </row>
     <row r="16" spans="3:21" x14ac:dyDescent="0.35">
       <c r="D16" s="23"/>
       <c r="F16" s="6" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G16" s="11">
-        <f>128+109/117</f>
-        <v>128.93162393162393</v>
+        <v>127.2</v>
       </c>
       <c r="H16" s="95" t="s">
         <v>60</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="4"/>
-      <c r="O16" s="109"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="110"/>
+        <v>518</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="L16" s="9">
+        <v>2.4</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="108" t="s">
+        <v>496</v>
+      </c>
+      <c r="P16" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R16" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="T16" s="108">
+        <f>(23.4+93.6)/2</f>
+        <v>58.5</v>
+      </c>
+      <c r="U16" s="11">
+        <f t="shared" si="0"/>
+        <v>175.5</v>
+      </c>
     </row>
     <row r="17" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D17" s="23"/>
       <c r="F17" s="6" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G17" s="11">
-        <f>73+79/117</f>
-        <v>73.675213675213669</v>
+        <f>473+27/65</f>
+        <v>473.4153846153846</v>
       </c>
       <c r="H17" s="95" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="4"/>
-      <c r="O17" s="109"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="110"/>
+        <v>518</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="L17" s="9">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="108" t="s">
+        <v>496</v>
+      </c>
+      <c r="P17" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R17" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="T17" s="108">
+        <f>(39.1+156.5)/2</f>
+        <v>97.8</v>
+      </c>
+      <c r="U17" s="11">
+        <f t="shared" si="0"/>
+        <v>293.39999999999998</v>
+      </c>
     </row>
     <row r="18" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D18" s="23"/>
@@ -17481,77 +17638,131 @@
         <v>34</v>
       </c>
       <c r="G18" s="11">
-        <f>231+1897/5265</f>
-        <v>231.36030389363722</v>
+        <f>128+109/117</f>
+        <v>128.93162393162393</v>
       </c>
       <c r="H18" s="95" t="s">
         <v>60</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="4"/>
-      <c r="O18" s="109"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="110"/>
+        <v>519</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="L18" s="9">
+        <v>7</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="108" t="s">
+        <v>496</v>
+      </c>
+      <c r="P18" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R18" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="T18" s="108">
+        <f>(58.5+234)/2</f>
+        <v>146.25</v>
+      </c>
+      <c r="U18" s="11">
+        <f t="shared" si="0"/>
+        <v>438.75</v>
+      </c>
     </row>
     <row r="19" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D19" s="23"/>
       <c r="F19" s="6" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="G19" s="11">
-        <f>'The Fourfold Furnace'!$K$16</f>
-        <v>180.1878431372549</v>
+        <f>73+79/117</f>
+        <v>73.675213675213669</v>
       </c>
       <c r="H19" s="95" t="s">
-        <v>506</v>
+        <v>62</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="K19" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="K19" s="4"/>
       <c r="L19" s="9"/>
       <c r="M19" s="4"/>
-      <c r="O19" s="109"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="110"/>
+      <c r="O19" s="108" t="s">
+        <v>425</v>
+      </c>
+      <c r="P19" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R19" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="T19" s="108">
+        <f>1676.4/2</f>
+        <v>838.2</v>
+      </c>
+      <c r="U19" s="11">
+        <f t="shared" si="0"/>
+        <v>1676.4</v>
+      </c>
     </row>
     <row r="20" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D20" s="23"/>
       <c r="F20" s="6" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="G20" s="11">
-        <f>101+1/15</f>
-        <v>101.06666666666666</v>
+        <f>231+1897/5265</f>
+        <v>231.36030389363722</v>
       </c>
       <c r="H20" s="95" t="s">
-        <v>251</v>
+        <v>60</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="K20" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="K20" s="4"/>
       <c r="L20" s="9"/>
       <c r="M20" s="4"/>
-      <c r="O20" s="109"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="110"/>
+      <c r="O20" s="108" t="s">
+        <v>425</v>
+      </c>
+      <c r="P20" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R20" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="T20" s="108">
+        <f>1456.4/2</f>
+        <v>728.2</v>
+      </c>
+      <c r="U20" s="11">
+        <f t="shared" si="0"/>
+        <v>2184.6000000000004</v>
+      </c>
     </row>
     <row r="21" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D21" s="23"/>
@@ -17559,774 +17770,1057 @@
         <v>103</v>
       </c>
       <c r="G21" s="11">
-        <f>'Kaladesh Refinery'!$K$13</f>
-        <v>28.745490196078421</v>
+        <f>'The Fourfold Furnace'!$K$16</f>
+        <v>180.1878431372549</v>
       </c>
       <c r="H21" s="95" t="s">
-        <v>106</v>
+        <v>505</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="9"/>
       <c r="M21" s="4"/>
-      <c r="O21" s="109"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="110"/>
+      <c r="O21" s="108" t="s">
+        <v>425</v>
+      </c>
+      <c r="P21" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R21" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="T21" s="108">
+        <f>1711.6/2</f>
+        <v>855.8</v>
+      </c>
+      <c r="U21" s="11">
+        <f t="shared" si="0"/>
+        <v>2567.3999999999996</v>
+      </c>
     </row>
     <row r="22" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D22" s="23"/>
       <c r="F22" s="6" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="G22" s="11">
-        <f>86+2/5</f>
-        <v>86.4</v>
+        <f>101+1/15</f>
+        <v>101.06666666666666</v>
       </c>
       <c r="H22" s="95" t="s">
-        <v>60</v>
+        <v>251</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="9"/>
       <c r="M22" s="4"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="11"/>
-      <c r="U22" s="110"/>
+      <c r="O22" s="108" t="s">
+        <v>322</v>
+      </c>
+      <c r="P22" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R22" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="T22" s="108">
+        <f>(500+1500)/2</f>
+        <v>1000</v>
+      </c>
+      <c r="U22" s="11">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
     </row>
     <row r="23" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D23" s="23"/>
       <c r="F23" s="6" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="G23" s="11">
-        <f>204+1084/5265</f>
-        <v>204.20588793922127</v>
+        <f>'Kaladesh Refinery'!$K$13</f>
+        <v>28.745490196078421</v>
       </c>
       <c r="H23" s="95" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="9"/>
       <c r="M23" s="4"/>
-      <c r="O23" s="109"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="110"/>
+      <c r="O23" s="108" t="s">
+        <v>322</v>
+      </c>
+      <c r="P23" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R23" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="T23" s="108">
+        <f>(245.2+735.6)/2</f>
+        <v>490.4</v>
+      </c>
+      <c r="U23" s="11">
+        <f t="shared" si="0"/>
+        <v>980.8</v>
+      </c>
     </row>
     <row r="24" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D24" s="23"/>
       <c r="F24" s="6" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="G24" s="11">
+        <f>86+2/5</f>
+        <v>86.4</v>
+      </c>
+      <c r="H24" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="H24" s="95" t="s">
-        <v>443</v>
-      </c>
       <c r="I24" s="2" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="9"/>
       <c r="M24" s="4"/>
-      <c r="O24" s="109"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="110"/>
+      <c r="O24" s="108" t="s">
+        <v>322</v>
+      </c>
+      <c r="P24" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R24" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="T24" s="108">
+        <f>(213.6+640.9)/2</f>
+        <v>427.25</v>
+      </c>
+      <c r="U24" s="11">
+        <f t="shared" si="0"/>
+        <v>854.5</v>
+      </c>
     </row>
     <row r="25" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D25" s="23"/>
       <c r="F25" s="6" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="G25" s="11">
-        <f>71+19/75</f>
-        <v>71.25333333333333</v>
+        <f>204+1084/5265</f>
+        <v>204.20588793922127</v>
       </c>
       <c r="H25" s="95" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="9"/>
       <c r="M25" s="4"/>
-      <c r="O25" s="109"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="110"/>
+      <c r="O25" s="108" t="s">
+        <v>322</v>
+      </c>
+      <c r="P25" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="R25" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="T25" s="108">
+        <f>(304.2+912.6)/2</f>
+        <v>608.4</v>
+      </c>
+      <c r="U25" s="11">
+        <f t="shared" si="0"/>
+        <v>608.4</v>
+      </c>
     </row>
     <row r="26" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D26" s="23"/>
       <c r="F26" s="6" t="s">
-        <v>19</v>
+        <v>525</v>
       </c>
       <c r="G26" s="11">
-        <f>47+113/225</f>
-        <v>47.502222222222223</v>
+        <v>146.4</v>
       </c>
       <c r="H26" s="95" t="s">
-        <v>62</v>
+        <v>442</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="9"/>
       <c r="M26" s="4"/>
-      <c r="O26" s="109"/>
+      <c r="O26" s="108"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="11"/>
       <c r="S26" s="9"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="110"/>
+      <c r="T26" s="108"/>
+      <c r="U26" s="11"/>
     </row>
     <row r="27" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D27" s="23"/>
       <c r="F27" s="6" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="G27" s="11">
-        <f>356+4/15</f>
-        <v>356.26666666666665</v>
+        <f>71+19/75</f>
+        <v>71.25333333333333</v>
       </c>
       <c r="H27" s="95" t="s">
-        <v>443</v>
+        <v>60</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="9"/>
       <c r="M27" s="4"/>
-      <c r="O27" s="109"/>
+      <c r="O27" s="108"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="11"/>
       <c r="S27" s="9"/>
-      <c r="T27" s="11"/>
-      <c r="U27" s="110"/>
+      <c r="T27" s="108"/>
+      <c r="U27" s="11"/>
     </row>
     <row r="28" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D28" s="23"/>
       <c r="F28" s="6" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="G28" s="11">
-        <f>113+3/15</f>
-        <v>113.2</v>
+        <f>47+113/225</f>
+        <v>47.502222222222223</v>
       </c>
       <c r="H28" s="95" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="9"/>
       <c r="M28" s="4"/>
-      <c r="O28" s="109"/>
+      <c r="O28" s="108"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="11"/>
       <c r="S28" s="9"/>
-      <c r="T28" s="11"/>
-      <c r="U28" s="110"/>
+      <c r="T28" s="108"/>
+      <c r="U28" s="11"/>
     </row>
     <row r="29" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D29" s="23"/>
       <c r="F29" s="6" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="G29" s="11">
-        <f>91+1/25</f>
-        <v>91.04</v>
+        <f>356+4/15</f>
+        <v>356.26666666666665</v>
       </c>
       <c r="H29" s="95" t="s">
-        <v>60</v>
+        <v>442</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="K29" s="2"/>
       <c r="L29" s="9"/>
       <c r="M29" s="4"/>
-      <c r="O29" s="109"/>
+      <c r="O29" s="108"/>
       <c r="P29" s="11"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="11"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="11"/>
-      <c r="U29" s="110"/>
+      <c r="T29" s="108"/>
+      <c r="U29" s="11"/>
     </row>
     <row r="30" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D30" s="23"/>
       <c r="F30" s="6" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G30" s="11">
-        <f>179+47/75</f>
-        <v>179.62666666666667</v>
+        <f>113+3/15</f>
+        <v>113.2</v>
       </c>
       <c r="H30" s="95" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="9"/>
-      <c r="M30" s="2"/>
-      <c r="O30" s="109"/>
+      <c r="M30" s="4"/>
+      <c r="O30" s="108"/>
       <c r="P30" s="11"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="11"/>
       <c r="S30" s="9"/>
-      <c r="T30" s="11"/>
-      <c r="U30" s="110"/>
+      <c r="T30" s="108"/>
+      <c r="U30" s="11"/>
     </row>
     <row r="31" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D31" s="23"/>
       <c r="F31" s="6" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="G31" s="11">
-        <f>52+4/5</f>
-        <v>52.8</v>
+        <f>99+1/25</f>
+        <v>99.04</v>
       </c>
       <c r="H31" s="95" t="s">
-        <v>251</v>
+        <v>60</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="9"/>
-      <c r="M31" s="2"/>
-      <c r="O31" s="109"/>
+      <c r="M31" s="4"/>
+      <c r="O31" s="108"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="11"/>
       <c r="S31" s="9"/>
-      <c r="T31" s="11"/>
-      <c r="U31" s="110"/>
+      <c r="T31" s="108"/>
+      <c r="U31" s="11"/>
     </row>
     <row r="32" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D32" s="23"/>
       <c r="F32" s="6" t="s">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="G32" s="11">
-        <v>40</v>
+        <f>179+47/75</f>
+        <v>179.62666666666667</v>
       </c>
       <c r="H32" s="95" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="9"/>
       <c r="M32" s="2"/>
-      <c r="O32" s="109"/>
+      <c r="O32" s="108"/>
       <c r="P32" s="11"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="11"/>
       <c r="S32" s="9"/>
-      <c r="T32" s="11"/>
-      <c r="U32" s="110"/>
+      <c r="T32" s="108"/>
+      <c r="U32" s="11"/>
     </row>
     <row r="33" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D33" s="23"/>
       <c r="F33" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G33" s="11">
-        <v>142</v>
+        <f>52+4/5</f>
+        <v>52.8</v>
       </c>
       <c r="H33" s="95" t="s">
-        <v>443</v>
+        <v>251</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="9"/>
       <c r="M33" s="2"/>
-      <c r="O33" s="109"/>
+      <c r="O33" s="108"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="11"/>
       <c r="S33" s="9"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="110"/>
+      <c r="T33" s="108"/>
+      <c r="U33" s="11"/>
     </row>
     <row r="34" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D34" s="23"/>
       <c r="F34" s="6" t="s">
-        <v>521</v>
+        <v>150</v>
       </c>
       <c r="G34" s="11">
-        <f>322+17/162</f>
-        <v>322.10493827160496</v>
+        <v>40</v>
       </c>
       <c r="H34" s="95" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="9"/>
       <c r="M34" s="2"/>
-      <c r="O34" s="109"/>
+      <c r="O34" s="108"/>
       <c r="P34" s="11"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="11"/>
       <c r="S34" s="9"/>
-      <c r="T34" s="11"/>
-      <c r="U34" s="110"/>
+      <c r="T34" s="108"/>
+      <c r="U34" s="11"/>
     </row>
     <row r="35" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D35" s="23"/>
       <c r="F35" s="6" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="G35" s="11">
-        <f>306+1/4</f>
-        <v>306.25</v>
+        <v>142</v>
       </c>
       <c r="H35" s="95" t="s">
-        <v>60</v>
+        <v>442</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="9"/>
       <c r="M35" s="2"/>
-      <c r="O35" s="109"/>
+      <c r="O35" s="108"/>
       <c r="P35" s="11"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="11"/>
       <c r="S35" s="9"/>
-      <c r="T35" s="11"/>
-      <c r="U35" s="110"/>
-    </row>
-    <row r="36" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="T35" s="108"/>
+      <c r="U35" s="11"/>
+    </row>
+    <row r="36" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D36" s="23"/>
       <c r="F36" s="6" t="s">
-        <v>19</v>
+        <v>520</v>
       </c>
       <c r="G36" s="11">
-        <f>255+5/24</f>
-        <v>255.20833333333334</v>
+        <f>322+17/162</f>
+        <v>322.10493827160496</v>
       </c>
       <c r="H36" s="95" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="9"/>
       <c r="M36" s="2"/>
-      <c r="O36" s="112"/>
-      <c r="P36" s="68"/>
-      <c r="Q36" s="113"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="113"/>
-      <c r="T36" s="68"/>
-      <c r="U36" s="114"/>
-    </row>
-    <row r="37" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O36" s="108"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="108"/>
+      <c r="U36" s="11"/>
+    </row>
+    <row r="37" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D37" s="23"/>
       <c r="F37" s="6" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G37" s="11">
-        <f>309+1/6</f>
-        <v>309.16666666666669</v>
+        <f>306+1/4</f>
+        <v>306.25</v>
       </c>
       <c r="H37" s="95" t="s">
-        <v>443</v>
+        <v>60</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="9"/>
       <c r="M37" s="2"/>
-      <c r="O37" s="47" t="s">
-        <v>473</v>
-      </c>
-      <c r="P37" s="129">
-        <f>SUM(U12:U36)</f>
-        <v>8000</v>
-      </c>
-      <c r="Q37" s="130"/>
-      <c r="R37" s="130"/>
-      <c r="S37" s="130"/>
-      <c r="T37" s="130"/>
-      <c r="U37" s="131"/>
-    </row>
-    <row r="38" spans="4:21" x14ac:dyDescent="0.35">
+      <c r="O37" s="108"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="108"/>
+      <c r="U37" s="11"/>
+    </row>
+    <row r="38" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D38" s="23"/>
       <c r="F38" s="6" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="G38" s="11">
-        <f>99</f>
-        <v>99</v>
+        <f>255+5/24</f>
+        <v>255.20833333333334</v>
       </c>
       <c r="H38" s="95" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="9"/>
       <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="4:21" x14ac:dyDescent="0.35">
+      <c r="O38" s="109"/>
+      <c r="P38" s="68"/>
+      <c r="Q38" s="110"/>
+      <c r="R38" s="44"/>
+      <c r="S38" s="110"/>
+      <c r="T38" s="109"/>
+      <c r="U38" s="44"/>
+    </row>
+    <row r="39" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D39" s="23"/>
       <c r="F39" s="6" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="G39" s="11">
-        <v>38.5</v>
+        <f>309+1/6</f>
+        <v>309.16666666666669</v>
       </c>
       <c r="H39" s="95" t="s">
-        <v>169</v>
+        <v>442</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="9"/>
       <c r="M39" s="2"/>
+      <c r="O39" s="47" t="s">
+        <v>472</v>
+      </c>
+      <c r="P39" s="125">
+        <f>SUM(U14:U38)</f>
+        <v>18779.75</v>
+      </c>
+      <c r="Q39" s="126"/>
+      <c r="R39" s="126"/>
+      <c r="S39" s="126"/>
+      <c r="T39" s="126"/>
+      <c r="U39" s="146"/>
     </row>
     <row r="40" spans="4:21" x14ac:dyDescent="0.35">
-      <c r="F40" s="6"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="95"/>
-      <c r="I40" s="2"/>
+      <c r="D40" s="23"/>
+      <c r="F40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="11">
+        <f>99</f>
+        <v>99</v>
+      </c>
+      <c r="H40" s="95" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>522</v>
+      </c>
       <c r="K40" s="2"/>
       <c r="L40" s="9"/>
       <c r="M40" s="2"/>
     </row>
     <row r="41" spans="4:21" x14ac:dyDescent="0.35">
-      <c r="F41" s="6"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="95"/>
-      <c r="I41" s="2"/>
+      <c r="F41" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="H41" s="95" t="s">
+        <v>169</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>522</v>
+      </c>
       <c r="K41" s="2"/>
       <c r="L41" s="9"/>
       <c r="M41" s="2"/>
     </row>
     <row r="42" spans="4:21" x14ac:dyDescent="0.35">
-      <c r="F42" s="6"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="95"/>
-      <c r="I42" s="2"/>
+      <c r="F42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G42" s="11">
+        <v>160</v>
+      </c>
+      <c r="H42" s="95" t="s">
+        <v>442</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>449</v>
+      </c>
       <c r="K42" s="2"/>
       <c r="L42" s="9"/>
       <c r="M42" s="2"/>
     </row>
     <row r="43" spans="4:21" x14ac:dyDescent="0.35">
-      <c r="F43" s="6"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="95"/>
-      <c r="I43" s="2"/>
+      <c r="F43" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G43" s="11">
+        <v>80</v>
+      </c>
+      <c r="H43" s="95" t="s">
+        <v>505</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>449</v>
+      </c>
       <c r="K43" s="2"/>
       <c r="L43" s="9"/>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="4:21" x14ac:dyDescent="0.35">
-      <c r="F44" s="6"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="95"/>
-      <c r="I44" s="2"/>
+      <c r="F44" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G44" s="11">
+        <v>8</v>
+      </c>
+      <c r="H44" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>532</v>
+      </c>
       <c r="K44" s="2"/>
       <c r="L44" s="9"/>
       <c r="M44" s="2"/>
     </row>
     <row r="45" spans="4:21" x14ac:dyDescent="0.35">
-      <c r="F45" s="6"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="95"/>
-      <c r="I45" s="2"/>
+      <c r="F45" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="G45" s="11">
+        <v>14</v>
+      </c>
+      <c r="H45" s="95" t="s">
+        <v>442</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>532</v>
+      </c>
       <c r="K45" s="2"/>
       <c r="L45" s="9"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F46" s="6"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="95"/>
-      <c r="I46" s="2"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="3"/>
+    <row r="46" spans="4:21" x14ac:dyDescent="0.35">
+      <c r="F46" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G46" s="11">
+        <f>106+1/5</f>
+        <v>106.2</v>
+      </c>
+      <c r="H46" s="95" t="s">
+        <v>130</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="K46" s="2"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="2"/>
     </row>
     <row r="47" spans="4:21" x14ac:dyDescent="0.35">
       <c r="F47" s="6"/>
-      <c r="G47" s="2"/>
+      <c r="G47" s="11"/>
       <c r="H47" s="95"/>
       <c r="I47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="2"/>
     </row>
     <row r="48" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F48" s="93"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="96"/>
-      <c r="I48" s="66"/>
-    </row>
-    <row r="49" spans="6:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F49" s="132" t="s">
-        <v>473</v>
-      </c>
-      <c r="G49" s="133"/>
-      <c r="H49" s="133"/>
-      <c r="I49" s="134"/>
-      <c r="K49" s="132" t="s">
-        <v>473</v>
-      </c>
-      <c r="L49" s="133"/>
-      <c r="M49" s="134"/>
-      <c r="N49" s="13"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="95"/>
+      <c r="I48" s="2"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="6:14" x14ac:dyDescent="0.35">
+      <c r="F49" s="6"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="95"/>
+      <c r="I49" s="2"/>
     </row>
     <row r="50" spans="6:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="93"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="96"/>
+      <c r="I50" s="66"/>
+    </row>
+    <row r="51" spans="6:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F51" s="128" t="s">
+        <v>472</v>
+      </c>
+      <c r="G51" s="129"/>
+      <c r="H51" s="129"/>
+      <c r="I51" s="130"/>
+      <c r="K51" s="128" t="s">
+        <v>472</v>
+      </c>
+      <c r="L51" s="129"/>
+      <c r="M51" s="130"/>
+      <c r="N51" s="13"/>
+    </row>
+    <row r="52" spans="6:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F52" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G52" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="H50" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="I50" s="52" t="s">
+      <c r="H52" s="111" t="s">
         <v>403</v>
       </c>
-      <c r="K50" s="47" t="s">
+      <c r="I52" s="113"/>
+      <c r="K52" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="L50" s="14" t="s">
+      <c r="L52" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="M50" s="53" t="s">
+      <c r="M52" s="53" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="51" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="38"/>
-      <c r="M51" s="41"/>
-    </row>
-    <row r="52" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="40"/>
-    </row>
     <row r="53" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="40"/>
+      <c r="F53" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G53" s="4">
+        <f>G42+G29</f>
+        <v>516.26666666666665</v>
+      </c>
+      <c r="H53" s="147"/>
+      <c r="I53" s="148"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="41"/>
     </row>
     <row r="54" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
+      <c r="F54" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G54" s="2">
+        <f>G26</f>
+        <v>146.4</v>
+      </c>
+      <c r="H54" s="149"/>
+      <c r="I54" s="150"/>
       <c r="K54" s="6"/>
       <c r="L54" s="11"/>
       <c r="M54" s="40"/>
     </row>
     <row r="55" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F55" s="2"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
+      <c r="F55" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G55">
+        <f>G36+G20+G17+G18</f>
+        <v>1155.8122507122507</v>
+      </c>
+      <c r="H55" s="149"/>
+      <c r="I55" s="150"/>
       <c r="K55" s="6"/>
       <c r="L55" s="11"/>
       <c r="M55" s="40"/>
     </row>
     <row r="56" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F56" s="2"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
+      <c r="F56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="2">
+        <f>G38+G32+G28+G25+G19+G15</f>
+        <v>1157.9414007597341</v>
+      </c>
+      <c r="H56" s="149"/>
+      <c r="I56" s="150"/>
       <c r="K56" s="6"/>
       <c r="L56" s="11"/>
       <c r="M56" s="40"/>
     </row>
     <row r="57" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
+      <c r="F57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" s="11">
+        <f>G37+G24</f>
+        <v>392.65</v>
+      </c>
+      <c r="H57" s="149"/>
+      <c r="I57" s="150"/>
       <c r="K57" s="6"/>
       <c r="L57" s="11"/>
       <c r="M57" s="40"/>
     </row>
     <row r="58" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
+      <c r="F58" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G58" s="11">
+        <f>G31+G27</f>
+        <v>170.29333333333335</v>
+      </c>
+      <c r="H58" s="149"/>
+      <c r="I58" s="150"/>
       <c r="K58" s="6"/>
       <c r="L58" s="11"/>
       <c r="M58" s="40"/>
     </row>
     <row r="59" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
+      <c r="F59" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59" s="2">
+        <f>G16+G40+G30</f>
+        <v>339.4</v>
+      </c>
+      <c r="H59" s="149"/>
+      <c r="I59" s="150"/>
       <c r="K59" s="6"/>
       <c r="L59" s="11"/>
       <c r="M59" s="40"/>
     </row>
     <row r="60" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
+      <c r="F60" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G60" s="2">
+        <f>G23+G22+G21</f>
+        <v>310</v>
+      </c>
+      <c r="H60" s="149" t="s">
+        <v>535</v>
+      </c>
+      <c r="I60" s="150"/>
       <c r="K60" s="6"/>
       <c r="L60" s="11"/>
       <c r="M60" s="40"/>
     </row>
     <row r="61" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
+      <c r="F61" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G61" s="2">
+        <f>G33</f>
+        <v>52.8</v>
+      </c>
+      <c r="H61" s="149"/>
+      <c r="I61" s="150"/>
       <c r="K61" s="6"/>
       <c r="L61" s="11"/>
       <c r="M61" s="40"/>
     </row>
     <row r="62" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
+      <c r="F62" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G62" s="2">
+        <f>G39</f>
+        <v>309.16666666666669</v>
+      </c>
+      <c r="H62" s="149"/>
+      <c r="I62" s="150"/>
       <c r="K62" s="6"/>
       <c r="L62" s="11"/>
       <c r="M62" s="40"/>
     </row>
     <row r="63" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
+      <c r="F63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="2">
+        <f>G41</f>
+        <v>38.5</v>
+      </c>
+      <c r="H63" s="149"/>
+      <c r="I63" s="150"/>
       <c r="K63" s="6"/>
       <c r="L63" s="11"/>
       <c r="M63" s="40"/>
     </row>
     <row r="64" spans="6:14" x14ac:dyDescent="0.35">
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
+      <c r="F64" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="G64" s="2">
+        <f>G45</f>
+        <v>14</v>
+      </c>
+      <c r="H64" s="149"/>
+      <c r="I64" s="150"/>
       <c r="K64" s="6"/>
       <c r="L64" s="11"/>
       <c r="M64" s="40"/>
     </row>
     <row r="65" spans="6:13" x14ac:dyDescent="0.35">
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
+      <c r="F65" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G65" s="2">
+        <f>G35</f>
+        <v>142</v>
+      </c>
+      <c r="H65" s="149"/>
+      <c r="I65" s="150"/>
       <c r="K65" s="6"/>
       <c r="L65" s="11"/>
       <c r="M65" s="40"/>
     </row>
     <row r="66" spans="6:13" x14ac:dyDescent="0.35">
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
+      <c r="F66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="2">
+        <f>G14</f>
+        <v>1200</v>
+      </c>
+      <c r="H66" s="149"/>
+      <c r="I66" s="150"/>
       <c r="K66" s="6"/>
       <c r="L66" s="11"/>
       <c r="M66" s="40"/>
     </row>
     <row r="67" spans="6:13" x14ac:dyDescent="0.35">
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
+      <c r="F67" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G67" s="2">
+        <f>G44</f>
+        <v>8</v>
+      </c>
+      <c r="H67" s="149"/>
+      <c r="I67" s="150"/>
       <c r="K67" s="6"/>
       <c r="L67" s="11"/>
       <c r="M67" s="40"/>
     </row>
     <row r="68" spans="6:13" x14ac:dyDescent="0.35">
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="L68" s="9"/>
-      <c r="M68" s="2"/>
-    </row>
-    <row r="69" spans="6:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="3"/>
+      <c r="F68" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G68" s="2">
+        <f>G43</f>
+        <v>80</v>
+      </c>
+      <c r="H68" s="149"/>
+      <c r="I68" s="150"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="40"/>
+    </row>
+    <row r="69" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="F69" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G69" s="2">
+        <f>G46</f>
+        <v>106.2</v>
+      </c>
+      <c r="H69" s="149"/>
+      <c r="I69" s="150"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="40"/>
     </row>
     <row r="70" spans="6:13" x14ac:dyDescent="0.35">
-      <c r="L70" s="1"/>
+      <c r="F70" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G70" s="2">
+        <f>G34</f>
+        <v>40</v>
+      </c>
+      <c r="H70" s="149"/>
+      <c r="I70" s="150"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="2"/>
+    </row>
+    <row r="71" spans="6:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="151"/>
+      <c r="I71" s="152"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="6:13" x14ac:dyDescent="0.35">
+      <c r="L72" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="O10:U10"/>
-    <mergeCell ref="P37:U37"/>
+  <mergeCells count="26">
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="O12:U12"/>
+    <mergeCell ref="P39:U39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18417,17 +18911,17 @@
     </row>
     <row r="12" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="13" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F13" s="115" t="s">
+      <c r="F13" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="116"/>
-      <c r="H13" s="117"/>
-      <c r="K13" s="115" t="s">
+      <c r="G13" s="112"/>
+      <c r="H13" s="113"/>
+      <c r="K13" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="116"/>
-      <c r="M13" s="116"/>
-      <c r="N13" s="117"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="113"/>
     </row>
     <row r="14" spans="3:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F14" s="14" t="s">
@@ -18451,14 +18945,14 @@
       <c r="N14" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="P14" s="118" t="s">
+      <c r="P14" s="114" t="s">
         <v>115</v>
       </c>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
-      <c r="S14" s="118"/>
-      <c r="T14" s="118"/>
-      <c r="U14" s="118"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
+      <c r="U14" s="114"/>
     </row>
     <row r="15" spans="3:21" x14ac:dyDescent="0.35">
       <c r="F15" s="4" t="s">
@@ -18481,12 +18975,12 @@
         <v>25</v>
       </c>
       <c r="N15" s="19"/>
-      <c r="P15" s="118"/>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
-      <c r="S15" s="118"/>
-      <c r="T15" s="118"/>
-      <c r="U15" s="118"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
+      <c r="U15" s="114"/>
     </row>
     <row r="16" spans="3:21" x14ac:dyDescent="0.35">
       <c r="F16" s="2" t="s">
@@ -18510,12 +19004,12 @@
       <c r="N16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="P16" s="118"/>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="118"/>
-      <c r="S16" s="118"/>
-      <c r="T16" s="118"/>
-      <c r="U16" s="118"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="114"/>
+      <c r="T16" s="114"/>
+      <c r="U16" s="114"/>
     </row>
     <row r="17" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F17" s="2"/>
@@ -18533,12 +19027,12 @@
       <c r="N17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="P17" s="118"/>
-      <c r="Q17" s="118"/>
-      <c r="R17" s="118"/>
-      <c r="S17" s="118"/>
-      <c r="T17" s="118"/>
-      <c r="U17" s="118"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="114"/>
     </row>
     <row r="18" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F18" s="2"/>
@@ -18588,14 +19082,14 @@
         <v>169</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="P20" s="119" t="s">
+      <c r="P20" s="115" t="s">
         <v>145</v>
       </c>
-      <c r="Q20" s="119"/>
-      <c r="R20" s="119"/>
-      <c r="S20" s="119"/>
-      <c r="T20" s="119"/>
-      <c r="U20" s="119"/>
+      <c r="Q20" s="115"/>
+      <c r="R20" s="115"/>
+      <c r="S20" s="115"/>
+      <c r="T20" s="115"/>
+      <c r="U20" s="115"/>
     </row>
     <row r="21" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F21" s="2"/>
@@ -18627,14 +19121,14 @@
         <v>158</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="P22" s="118" t="s">
+      <c r="P22" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="Q22" s="118"/>
-      <c r="R22" s="118"/>
-      <c r="S22" s="118"/>
-      <c r="T22" s="118"/>
-      <c r="U22" s="118"/>
+      <c r="Q22" s="114"/>
+      <c r="R22" s="114"/>
+      <c r="S22" s="114"/>
+      <c r="T22" s="114"/>
+      <c r="U22" s="114"/>
     </row>
     <row r="23" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F23" s="2"/>
@@ -18651,12 +19145,12 @@
         <v>251</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="P23" s="118"/>
-      <c r="Q23" s="118"/>
-      <c r="R23" s="118"/>
-      <c r="S23" s="118"/>
-      <c r="T23" s="118"/>
-      <c r="U23" s="118"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="114"/>
+      <c r="R23" s="114"/>
+      <c r="S23" s="114"/>
+      <c r="T23" s="114"/>
+      <c r="U23" s="114"/>
     </row>
     <row r="24" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F24" s="2"/>
@@ -18673,12 +19167,12 @@
         <v>375</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="P24" s="118"/>
-      <c r="Q24" s="118"/>
-      <c r="R24" s="118"/>
-      <c r="S24" s="118"/>
-      <c r="T24" s="118"/>
-      <c r="U24" s="118"/>
+      <c r="P24" s="114"/>
+      <c r="Q24" s="114"/>
+      <c r="R24" s="114"/>
+      <c r="S24" s="114"/>
+      <c r="T24" s="114"/>
+      <c r="U24" s="114"/>
     </row>
     <row r="25" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F25" s="2"/>
@@ -18697,12 +19191,12 @@
       <c r="N25" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="P25" s="118"/>
-      <c r="Q25" s="118"/>
-      <c r="R25" s="118"/>
-      <c r="S25" s="118"/>
-      <c r="T25" s="118"/>
-      <c r="U25" s="118"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="114"/>
+      <c r="T25" s="114"/>
+      <c r="U25" s="114"/>
     </row>
     <row r="26" spans="6:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F26" s="2"/>
@@ -18715,17 +19209,17 @@
         <v>997.25</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="P26" s="118" t="s">
+      <c r="P26" s="114" t="s">
         <v>261</v>
       </c>
-      <c r="Q26" s="118"/>
-      <c r="R26" s="118"/>
-      <c r="S26" s="118"/>
-      <c r="T26" s="118"/>
-      <c r="U26" s="118"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="114"/>
+      <c r="T26" s="114"/>
+      <c r="U26" s="114"/>
     </row>
     <row r="27" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F27" s="2"/>
@@ -18735,12 +19229,12 @@
       <c r="L27" s="9"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
-      <c r="P27" s="118"/>
-      <c r="Q27" s="118"/>
-      <c r="R27" s="118"/>
-      <c r="S27" s="118"/>
-      <c r="T27" s="118"/>
-      <c r="U27" s="118"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="114"/>
+      <c r="T27" s="114"/>
+      <c r="U27" s="114"/>
     </row>
     <row r="28" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F28" s="2"/>
@@ -18750,12 +19244,12 @@
       <c r="L28" s="9"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
-      <c r="P28" s="118"/>
-      <c r="Q28" s="118"/>
-      <c r="R28" s="118"/>
-      <c r="S28" s="118"/>
-      <c r="T28" s="118"/>
-      <c r="U28" s="118"/>
+      <c r="P28" s="114"/>
+      <c r="Q28" s="114"/>
+      <c r="R28" s="114"/>
+      <c r="S28" s="114"/>
+      <c r="T28" s="114"/>
+      <c r="U28" s="114"/>
     </row>
     <row r="29" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F29" s="2"/>
@@ -18765,12 +19259,12 @@
       <c r="L29" s="9"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
-      <c r="P29" s="118"/>
-      <c r="Q29" s="118"/>
-      <c r="R29" s="118"/>
-      <c r="S29" s="118"/>
-      <c r="T29" s="118"/>
-      <c r="U29" s="118"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="114"/>
+      <c r="R29" s="114"/>
+      <c r="S29" s="114"/>
+      <c r="T29" s="114"/>
+      <c r="U29" s="114"/>
     </row>
     <row r="30" spans="6:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F30" s="2"/>
@@ -18780,14 +19274,14 @@
       <c r="L30" s="9"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="P30" s="118" t="s">
+      <c r="P30" s="114" t="s">
         <v>406</v>
       </c>
-      <c r="Q30" s="118"/>
-      <c r="R30" s="118"/>
-      <c r="S30" s="118"/>
-      <c r="T30" s="118"/>
-      <c r="U30" s="118"/>
+      <c r="Q30" s="114"/>
+      <c r="R30" s="114"/>
+      <c r="S30" s="114"/>
+      <c r="T30" s="114"/>
+      <c r="U30" s="114"/>
     </row>
     <row r="31" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F31" s="2"/>
@@ -18797,12 +19291,12 @@
       <c r="L31" s="9"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
-      <c r="P31" s="118"/>
-      <c r="Q31" s="118"/>
-      <c r="R31" s="118"/>
-      <c r="S31" s="118"/>
-      <c r="T31" s="118"/>
-      <c r="U31" s="118"/>
+      <c r="P31" s="114"/>
+      <c r="Q31" s="114"/>
+      <c r="R31" s="114"/>
+      <c r="S31" s="114"/>
+      <c r="T31" s="114"/>
+      <c r="U31" s="114"/>
     </row>
     <row r="32" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F32" s="2"/>
@@ -18812,12 +19306,12 @@
       <c r="L32" s="9"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-      <c r="P32" s="118"/>
-      <c r="Q32" s="118"/>
-      <c r="R32" s="118"/>
-      <c r="S32" s="118"/>
-      <c r="T32" s="118"/>
-      <c r="U32" s="118"/>
+      <c r="P32" s="114"/>
+      <c r="Q32" s="114"/>
+      <c r="R32" s="114"/>
+      <c r="S32" s="114"/>
+      <c r="T32" s="114"/>
+      <c r="U32" s="114"/>
     </row>
     <row r="33" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F33" s="2"/>
@@ -18827,12 +19321,12 @@
       <c r="L33" s="9"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
-      <c r="P33" s="118"/>
-      <c r="Q33" s="118"/>
-      <c r="R33" s="118"/>
-      <c r="S33" s="118"/>
-      <c r="T33" s="118"/>
-      <c r="U33" s="118"/>
+      <c r="P33" s="114"/>
+      <c r="Q33" s="114"/>
+      <c r="R33" s="114"/>
+      <c r="S33" s="114"/>
+      <c r="T33" s="114"/>
+      <c r="U33" s="114"/>
     </row>
     <row r="34" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F34" s="2"/>
@@ -18842,14 +19336,14 @@
       <c r="L34" s="9"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
-      <c r="P34" s="118" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q34" s="118"/>
-      <c r="R34" s="118"/>
-      <c r="S34" s="118"/>
-      <c r="T34" s="118"/>
-      <c r="U34" s="118"/>
+      <c r="P34" s="114" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q34" s="114"/>
+      <c r="R34" s="114"/>
+      <c r="S34" s="114"/>
+      <c r="T34" s="114"/>
+      <c r="U34" s="114"/>
     </row>
     <row r="35" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F35" s="2"/>
@@ -18859,12 +19353,12 @@
       <c r="L35" s="9"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
-      <c r="P35" s="118"/>
-      <c r="Q35" s="118"/>
-      <c r="R35" s="118"/>
-      <c r="S35" s="118"/>
-      <c r="T35" s="118"/>
-      <c r="U35" s="118"/>
+      <c r="P35" s="114"/>
+      <c r="Q35" s="114"/>
+      <c r="R35" s="114"/>
+      <c r="S35" s="114"/>
+      <c r="T35" s="114"/>
+      <c r="U35" s="114"/>
     </row>
     <row r="36" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F36" s="2"/>
@@ -18874,12 +19368,12 @@
       <c r="L36" s="9"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-      <c r="P36" s="118"/>
-      <c r="Q36" s="118"/>
-      <c r="R36" s="118"/>
-      <c r="S36" s="118"/>
-      <c r="T36" s="118"/>
-      <c r="U36" s="118"/>
+      <c r="P36" s="114"/>
+      <c r="Q36" s="114"/>
+      <c r="R36" s="114"/>
+      <c r="S36" s="114"/>
+      <c r="T36" s="114"/>
+      <c r="U36" s="114"/>
     </row>
     <row r="37" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F37" s="2"/>
@@ -18889,12 +19383,12 @@
       <c r="L37" s="9"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-      <c r="P37" s="118"/>
-      <c r="Q37" s="118"/>
-      <c r="R37" s="118"/>
-      <c r="S37" s="118"/>
-      <c r="T37" s="118"/>
-      <c r="U37" s="118"/>
+      <c r="P37" s="114"/>
+      <c r="Q37" s="114"/>
+      <c r="R37" s="114"/>
+      <c r="S37" s="114"/>
+      <c r="T37" s="114"/>
+      <c r="U37" s="114"/>
     </row>
     <row r="38" spans="6:21" x14ac:dyDescent="0.35">
       <c r="F38" s="2"/>
@@ -19090,16 +19584,16 @@
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="115" t="s">
+      <c r="E11" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="117"/>
-      <c r="J11" s="115" t="s">
+      <c r="F11" s="112"/>
+      <c r="G11" s="113"/>
+      <c r="J11" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="116"/>
-      <c r="L11" s="117"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="113"/>
     </row>
     <row r="12" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -19576,17 +20070,17 @@
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="115" t="s">
+      <c r="E11" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="117"/>
-      <c r="J11" s="115" t="s">
+      <c r="F11" s="112"/>
+      <c r="G11" s="113"/>
+      <c r="J11" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="116"/>
-      <c r="L11" s="116"/>
-      <c r="M11" s="117"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="113"/>
     </row>
     <row r="12" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -19611,14 +20105,14 @@
       <c r="M12" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="O12" s="118" t="s">
+      <c r="O12" s="114" t="s">
         <v>93</v>
       </c>
-      <c r="P12" s="118"/>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="118"/>
-      <c r="S12" s="118"/>
-      <c r="T12" s="118"/>
+      <c r="P12" s="114"/>
+      <c r="Q12" s="114"/>
+      <c r="R12" s="114"/>
+      <c r="S12" s="114"/>
+      <c r="T12" s="114"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
@@ -19642,12 +20136,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="19"/>
-      <c r="O13" s="118"/>
-      <c r="P13" s="118"/>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
-      <c r="T13" s="118"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -19672,12 +20166,12 @@
       <c r="M14" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="O14" s="118"/>
-      <c r="P14" s="118"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
-      <c r="S14" s="118"/>
-      <c r="T14" s="118"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -19696,12 +20190,12 @@
       <c r="M15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="O15" s="118"/>
-      <c r="P15" s="118"/>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
-      <c r="S15" s="118"/>
-      <c r="T15" s="118"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -19720,14 +20214,14 @@
       <c r="M16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="O16" s="118" t="s">
+      <c r="O16" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="P16" s="118"/>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="118"/>
-      <c r="S16" s="118"/>
-      <c r="T16" s="118"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="114"/>
+      <c r="T16" s="114"/>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
@@ -19746,12 +20240,12 @@
       <c r="M17" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O17" s="118"/>
-      <c r="P17" s="118"/>
-      <c r="Q17" s="118"/>
-      <c r="R17" s="118"/>
-      <c r="S17" s="118"/>
-      <c r="T17" s="118"/>
+      <c r="O17" s="114"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
@@ -19768,12 +20262,12 @@
         <v>146</v>
       </c>
       <c r="M18" s="2"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
+      <c r="S18" s="114"/>
+      <c r="T18" s="114"/>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -19790,12 +20284,12 @@
         <v>169</v>
       </c>
       <c r="M19" s="2"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="118"/>
-      <c r="Q19" s="118"/>
-      <c r="R19" s="118"/>
-      <c r="S19" s="118"/>
-      <c r="T19" s="118"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
+      <c r="T19" s="114"/>
     </row>
     <row r="20" spans="3:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -19823,14 +20317,14 @@
       <c r="K21" s="9"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="119" t="s">
+      <c r="O21" s="115" t="s">
         <v>145</v>
       </c>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="119"/>
-      <c r="R21" s="119"/>
-      <c r="S21" s="119"/>
-      <c r="T21" s="119"/>
+      <c r="P21" s="115"/>
+      <c r="Q21" s="115"/>
+      <c r="R21" s="115"/>
+      <c r="S21" s="115"/>
+      <c r="T21" s="115"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C22" s="23"/>
@@ -19851,14 +20345,14 @@
       <c r="K23" s="9"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="118" t="s">
+      <c r="O23" s="114" t="s">
         <v>170</v>
       </c>
-      <c r="P23" s="118"/>
-      <c r="Q23" s="118"/>
-      <c r="R23" s="118"/>
-      <c r="S23" s="118"/>
-      <c r="T23" s="118"/>
+      <c r="P23" s="114"/>
+      <c r="Q23" s="114"/>
+      <c r="R23" s="114"/>
+      <c r="S23" s="114"/>
+      <c r="T23" s="114"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="23"/>
@@ -19869,12 +20363,12 @@
       <c r="K24" s="9"/>
       <c r="L24" s="6"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="118"/>
-      <c r="Q24" s="118"/>
-      <c r="R24" s="118"/>
-      <c r="S24" s="118"/>
-      <c r="T24" s="118"/>
+      <c r="O24" s="114"/>
+      <c r="P24" s="114"/>
+      <c r="Q24" s="114"/>
+      <c r="R24" s="114"/>
+      <c r="S24" s="114"/>
+      <c r="T24" s="114"/>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
@@ -19885,12 +20379,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="6"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="118"/>
-      <c r="Q25" s="118"/>
-      <c r="R25" s="118"/>
-      <c r="S25" s="118"/>
-      <c r="T25" s="118"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="114"/>
+      <c r="T25" s="114"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -19901,12 +20395,12 @@
       <c r="K26" s="9"/>
       <c r="L26" s="6"/>
       <c r="M26" s="2"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="118"/>
-      <c r="Q26" s="118"/>
-      <c r="R26" s="118"/>
-      <c r="S26" s="118"/>
-      <c r="T26" s="118"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="114"/>
+      <c r="T26" s="114"/>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -19917,14 +20411,14 @@
       <c r="K27" s="9"/>
       <c r="L27" s="6"/>
       <c r="M27" s="2"/>
-      <c r="O27" s="118" t="s">
+      <c r="O27" s="114" t="s">
         <v>148</v>
       </c>
-      <c r="P27" s="118"/>
-      <c r="Q27" s="118"/>
-      <c r="R27" s="118"/>
-      <c r="S27" s="118"/>
-      <c r="T27" s="118"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="114"/>
+      <c r="T27" s="114"/>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -19935,12 +20429,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="6"/>
       <c r="M28" s="2"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="118"/>
-      <c r="Q28" s="118"/>
-      <c r="R28" s="118"/>
-      <c r="S28" s="118"/>
-      <c r="T28" s="118"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="114"/>
+      <c r="Q28" s="114"/>
+      <c r="R28" s="114"/>
+      <c r="S28" s="114"/>
+      <c r="T28" s="114"/>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C29" s="23"/>
@@ -19951,12 +20445,12 @@
       <c r="K29" s="9"/>
       <c r="L29" s="6"/>
       <c r="M29" s="2"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="118"/>
-      <c r="Q29" s="118"/>
-      <c r="R29" s="118"/>
-      <c r="S29" s="118"/>
-      <c r="T29" s="118"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="114"/>
+      <c r="R29" s="114"/>
+      <c r="S29" s="114"/>
+      <c r="T29" s="114"/>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -19967,12 +20461,12 @@
       <c r="K30" s="9"/>
       <c r="L30" s="6"/>
       <c r="M30" s="2"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="118"/>
-      <c r="Q30" s="118"/>
-      <c r="R30" s="118"/>
-      <c r="S30" s="118"/>
-      <c r="T30" s="118"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="114"/>
+      <c r="Q30" s="114"/>
+      <c r="R30" s="114"/>
+      <c r="S30" s="114"/>
+      <c r="T30" s="114"/>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -19983,14 +20477,14 @@
       <c r="K31" s="9"/>
       <c r="L31" s="6"/>
       <c r="M31" s="2"/>
-      <c r="O31" s="118" t="s">
+      <c r="O31" s="114" t="s">
         <v>149</v>
       </c>
-      <c r="P31" s="118"/>
-      <c r="Q31" s="118"/>
-      <c r="R31" s="118"/>
-      <c r="S31" s="118"/>
-      <c r="T31" s="118"/>
+      <c r="P31" s="114"/>
+      <c r="Q31" s="114"/>
+      <c r="R31" s="114"/>
+      <c r="S31" s="114"/>
+      <c r="T31" s="114"/>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C32" s="23"/>
@@ -20001,12 +20495,12 @@
       <c r="K32" s="9"/>
       <c r="L32" s="6"/>
       <c r="M32" s="2"/>
-      <c r="O32" s="118"/>
-      <c r="P32" s="118"/>
-      <c r="Q32" s="118"/>
-      <c r="R32" s="118"/>
-      <c r="S32" s="118"/>
-      <c r="T32" s="118"/>
+      <c r="O32" s="114"/>
+      <c r="P32" s="114"/>
+      <c r="Q32" s="114"/>
+      <c r="R32" s="114"/>
+      <c r="S32" s="114"/>
+      <c r="T32" s="114"/>
     </row>
     <row r="33" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C33" s="23"/>
@@ -20017,12 +20511,12 @@
       <c r="K33" s="9"/>
       <c r="L33" s="6"/>
       <c r="M33" s="2"/>
-      <c r="O33" s="118"/>
-      <c r="P33" s="118"/>
-      <c r="Q33" s="118"/>
-      <c r="R33" s="118"/>
-      <c r="S33" s="118"/>
-      <c r="T33" s="118"/>
+      <c r="O33" s="114"/>
+      <c r="P33" s="114"/>
+      <c r="Q33" s="114"/>
+      <c r="R33" s="114"/>
+      <c r="S33" s="114"/>
+      <c r="T33" s="114"/>
     </row>
     <row r="34" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C34" s="23"/>
@@ -20033,12 +20527,12 @@
       <c r="K34" s="9"/>
       <c r="L34" s="6"/>
       <c r="M34" s="2"/>
-      <c r="O34" s="118"/>
-      <c r="P34" s="118"/>
-      <c r="Q34" s="118"/>
-      <c r="R34" s="118"/>
-      <c r="S34" s="118"/>
-      <c r="T34" s="118"/>
+      <c r="O34" s="114"/>
+      <c r="P34" s="114"/>
+      <c r="Q34" s="114"/>
+      <c r="R34" s="114"/>
+      <c r="S34" s="114"/>
+      <c r="T34" s="114"/>
     </row>
     <row r="35" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C35" s="23"/>
@@ -20049,14 +20543,14 @@
       <c r="K35" s="9"/>
       <c r="L35" s="6"/>
       <c r="M35" s="2"/>
-      <c r="O35" s="118" t="s">
+      <c r="O35" s="114" t="s">
         <v>259</v>
       </c>
-      <c r="P35" s="118"/>
-      <c r="Q35" s="118"/>
-      <c r="R35" s="118"/>
-      <c r="S35" s="118"/>
-      <c r="T35" s="118"/>
+      <c r="P35" s="114"/>
+      <c r="Q35" s="114"/>
+      <c r="R35" s="114"/>
+      <c r="S35" s="114"/>
+      <c r="T35" s="114"/>
     </row>
     <row r="36" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C36" s="23"/>
@@ -20067,12 +20561,12 @@
       <c r="K36" s="9"/>
       <c r="L36" s="6"/>
       <c r="M36" s="2"/>
-      <c r="O36" s="118"/>
-      <c r="P36" s="118"/>
-      <c r="Q36" s="118"/>
-      <c r="R36" s="118"/>
-      <c r="S36" s="118"/>
-      <c r="T36" s="118"/>
+      <c r="O36" s="114"/>
+      <c r="P36" s="114"/>
+      <c r="Q36" s="114"/>
+      <c r="R36" s="114"/>
+      <c r="S36" s="114"/>
+      <c r="T36" s="114"/>
     </row>
     <row r="37" spans="3:20" x14ac:dyDescent="0.35">
       <c r="E37" s="2"/>
@@ -20082,12 +20576,12 @@
       <c r="K37" s="9"/>
       <c r="L37" s="6"/>
       <c r="M37" s="2"/>
-      <c r="O37" s="118"/>
-      <c r="P37" s="118"/>
-      <c r="Q37" s="118"/>
-      <c r="R37" s="118"/>
-      <c r="S37" s="118"/>
-      <c r="T37" s="118"/>
+      <c r="O37" s="114"/>
+      <c r="P37" s="114"/>
+      <c r="Q37" s="114"/>
+      <c r="R37" s="114"/>
+      <c r="S37" s="114"/>
+      <c r="T37" s="114"/>
     </row>
     <row r="38" spans="3:20" x14ac:dyDescent="0.35">
       <c r="E38" s="2"/>
@@ -20097,12 +20591,12 @@
       <c r="K38" s="9"/>
       <c r="L38" s="6"/>
       <c r="M38" s="2"/>
-      <c r="O38" s="118"/>
-      <c r="P38" s="118"/>
-      <c r="Q38" s="118"/>
-      <c r="R38" s="118"/>
-      <c r="S38" s="118"/>
-      <c r="T38" s="118"/>
+      <c r="O38" s="114"/>
+      <c r="P38" s="114"/>
+      <c r="Q38" s="114"/>
+      <c r="R38" s="114"/>
+      <c r="S38" s="114"/>
+      <c r="T38" s="114"/>
     </row>
     <row r="39" spans="3:20" x14ac:dyDescent="0.35">
       <c r="E39" s="2"/>
@@ -20270,17 +20764,17 @@
     </row>
     <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
-      <c r="E11" s="115" t="s">
+      <c r="E11" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="116"/>
-      <c r="G11" s="117"/>
-      <c r="J11" s="115" t="s">
+      <c r="F11" s="112"/>
+      <c r="G11" s="113"/>
+      <c r="J11" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="116"/>
-      <c r="L11" s="116"/>
-      <c r="M11" s="117"/>
+      <c r="K11" s="112"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="113"/>
     </row>
     <row r="12" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="23"/>
@@ -20305,14 +20799,14 @@
       <c r="M12" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="O12" s="118" t="s">
+      <c r="O12" s="114" t="s">
         <v>84</v>
       </c>
-      <c r="P12" s="118"/>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="118"/>
-      <c r="S12" s="118"/>
-      <c r="T12" s="118"/>
+      <c r="P12" s="114"/>
+      <c r="Q12" s="114"/>
+      <c r="R12" s="114"/>
+      <c r="S12" s="114"/>
+      <c r="T12" s="114"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C13" s="23"/>
@@ -20336,12 +20830,12 @@
         <v>25</v>
       </c>
       <c r="M13" s="19"/>
-      <c r="O13" s="118"/>
-      <c r="P13" s="118"/>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
-      <c r="T13" s="118"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -20364,12 +20858,12 @@
         <v>81</v>
       </c>
       <c r="M14" s="2"/>
-      <c r="O14" s="118"/>
-      <c r="P14" s="118"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
-      <c r="S14" s="118"/>
-      <c r="T14" s="118"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -20388,12 +20882,12 @@
       <c r="M15" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="O15" s="118"/>
-      <c r="P15" s="118"/>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
-      <c r="S15" s="118"/>
-      <c r="T15" s="118"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -20468,14 +20962,14 @@
       <c r="M19" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="O19" s="129" t="s">
+      <c r="O19" s="125" t="s">
         <v>145</v>
       </c>
-      <c r="P19" s="130"/>
-      <c r="Q19" s="130"/>
-      <c r="R19" s="130"/>
-      <c r="S19" s="130"/>
-      <c r="T19" s="131"/>
+      <c r="P19" s="126"/>
+      <c r="Q19" s="126"/>
+      <c r="R19" s="126"/>
+      <c r="S19" s="126"/>
+      <c r="T19" s="127"/>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -20495,14 +20989,14 @@
       <c r="M20" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="O20" s="120" t="s">
+      <c r="O20" s="116" t="s">
         <v>402</v>
       </c>
-      <c r="P20" s="121"/>
-      <c r="Q20" s="121"/>
-      <c r="R20" s="121"/>
-      <c r="S20" s="121"/>
-      <c r="T20" s="122"/>
+      <c r="P20" s="117"/>
+      <c r="Q20" s="117"/>
+      <c r="R20" s="117"/>
+      <c r="S20" s="117"/>
+      <c r="T20" s="118"/>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C21" s="23"/>
@@ -20513,12 +21007,12 @@
       <c r="K21" s="9"/>
       <c r="L21" s="6"/>
       <c r="M21" s="2"/>
-      <c r="O21" s="123"/>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="124"/>
-      <c r="R21" s="124"/>
-      <c r="S21" s="124"/>
-      <c r="T21" s="125"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="120"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="120"/>
+      <c r="S21" s="120"/>
+      <c r="T21" s="121"/>
     </row>
     <row r="22" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C22" s="23"/>
@@ -20529,12 +21023,12 @@
       <c r="K22" s="9"/>
       <c r="L22" s="6"/>
       <c r="M22" s="2"/>
-      <c r="O22" s="126"/>
-      <c r="P22" s="127"/>
-      <c r="Q22" s="127"/>
-      <c r="R22" s="127"/>
-      <c r="S22" s="127"/>
-      <c r="T22" s="128"/>
+      <c r="O22" s="122"/>
+      <c r="P22" s="123"/>
+      <c r="Q22" s="123"/>
+      <c r="R22" s="123"/>
+      <c r="S22" s="123"/>
+      <c r="T22" s="124"/>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C23" s="23"/>
@@ -20545,14 +21039,14 @@
       <c r="K23" s="9"/>
       <c r="L23" s="6"/>
       <c r="M23" s="2"/>
-      <c r="O23" s="120" t="s">
+      <c r="O23" s="116" t="s">
         <v>279</v>
       </c>
-      <c r="P23" s="121"/>
-      <c r="Q23" s="121"/>
-      <c r="R23" s="121"/>
-      <c r="S23" s="121"/>
-      <c r="T23" s="122"/>
+      <c r="P23" s="117"/>
+      <c r="Q23" s="117"/>
+      <c r="R23" s="117"/>
+      <c r="S23" s="117"/>
+      <c r="T23" s="118"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C24" s="23"/>
@@ -20563,12 +21057,12 @@
       <c r="K24" s="9"/>
       <c r="L24" s="6"/>
       <c r="M24" s="2"/>
-      <c r="O24" s="123"/>
-      <c r="P24" s="124"/>
-      <c r="Q24" s="124"/>
-      <c r="R24" s="124"/>
-      <c r="S24" s="124"/>
-      <c r="T24" s="125"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="120"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="120"/>
+      <c r="S24" s="120"/>
+      <c r="T24" s="121"/>
     </row>
     <row r="25" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C25" s="23"/>
@@ -20579,12 +21073,12 @@
       <c r="K25" s="9"/>
       <c r="L25" s="6"/>
       <c r="M25" s="2"/>
-      <c r="O25" s="126"/>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="127"/>
-      <c r="R25" s="127"/>
-      <c r="S25" s="127"/>
-      <c r="T25" s="128"/>
+      <c r="O25" s="122"/>
+      <c r="P25" s="123"/>
+      <c r="Q25" s="123"/>
+      <c r="R25" s="123"/>
+      <c r="S25" s="123"/>
+      <c r="T25" s="124"/>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -20874,16 +21368,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -21435,16 +21929,16 @@
     </row>
     <row r="10" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
@@ -21508,14 +22002,14 @@
       <c r="L13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="118" t="s">
+      <c r="N13" s="114" t="s">
         <v>91</v>
       </c>
-      <c r="O13" s="118"/>
-      <c r="P13" s="118"/>
-      <c r="Q13" s="118"/>
-      <c r="R13" s="118"/>
-      <c r="S13" s="118"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C14" s="23"/>
@@ -21538,12 +22032,12 @@
       <c r="L14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N14" s="118"/>
-      <c r="O14" s="118"/>
-      <c r="P14" s="118"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="118"/>
-      <c r="S14" s="118"/>
+      <c r="N14" s="114"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.35">
       <c r="C15" s="23"/>
@@ -21559,12 +22053,12 @@
       <c r="L15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="118"/>
-      <c r="O15" s="118"/>
-      <c r="P15" s="118"/>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
-      <c r="S15" s="118"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
     </row>
     <row r="16" spans="2:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C16" s="23"/>
@@ -21580,12 +22074,12 @@
       <c r="L16" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="N16" s="118"/>
-      <c r="O16" s="118"/>
-      <c r="P16" s="118"/>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="118"/>
-      <c r="S16" s="118"/>
+      <c r="N16" s="114"/>
+      <c r="O16" s="114"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="114"/>
     </row>
     <row r="17" spans="3:19" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C17" s="23"/>
@@ -21601,14 +22095,14 @@
       <c r="L17" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="N17" s="118" t="s">
+      <c r="N17" s="114" t="s">
         <v>92</v>
       </c>
-      <c r="O17" s="118"/>
-      <c r="P17" s="118"/>
-      <c r="Q17" s="118"/>
-      <c r="R17" s="118"/>
-      <c r="S17" s="118"/>
+      <c r="O17" s="114"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C18" s="23"/>
@@ -21624,12 +22118,12 @@
       <c r="L18" s="86" t="s">
         <v>146</v>
       </c>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
+      <c r="N18" s="114"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
+      <c r="S18" s="114"/>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C19" s="23"/>
@@ -21645,12 +22139,12 @@
       <c r="L19" s="86" t="s">
         <v>146</v>
       </c>
-      <c r="N19" s="118"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="118"/>
-      <c r="Q19" s="118"/>
-      <c r="R19" s="118"/>
-      <c r="S19" s="118"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="114"/>
+      <c r="P19" s="114"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="114"/>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C20" s="23"/>
@@ -21666,12 +22160,12 @@
       <c r="L20" s="86" t="s">
         <v>169</v>
       </c>
-      <c r="N20" s="118"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="118"/>
-      <c r="Q20" s="118"/>
-      <c r="R20" s="118"/>
-      <c r="S20" s="118"/>
+      <c r="N20" s="114"/>
+      <c r="O20" s="114"/>
+      <c r="P20" s="114"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="114"/>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C21" s="23"/>
@@ -21702,14 +22196,14 @@
       <c r="L22" s="86" t="s">
         <v>252</v>
       </c>
-      <c r="N22" s="119" t="s">
+      <c r="N22" s="115" t="s">
         <v>145</v>
       </c>
-      <c r="O22" s="119"/>
-      <c r="P22" s="119"/>
-      <c r="Q22" s="119"/>
-      <c r="R22" s="119"/>
-      <c r="S22" s="119"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="115"/>
+      <c r="Q22" s="115"/>
+      <c r="R22" s="115"/>
+      <c r="S22" s="115"/>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C23" s="23"/>
@@ -21734,14 +22228,14 @@
       <c r="J24" s="2"/>
       <c r="K24" s="9"/>
       <c r="L24" s="86"/>
-      <c r="N24" s="118" t="s">
+      <c r="N24" s="114" t="s">
         <v>398</v>
       </c>
-      <c r="O24" s="118"/>
-      <c r="P24" s="118"/>
-      <c r="Q24" s="118"/>
-      <c r="R24" s="118"/>
-      <c r="S24" s="118"/>
+      <c r="O24" s="114"/>
+      <c r="P24" s="114"/>
+      <c r="Q24" s="114"/>
+      <c r="R24" s="114"/>
+      <c r="S24" s="114"/>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C25" s="23"/>
@@ -21751,12 +22245,12 @@
       <c r="J25" s="2"/>
       <c r="K25" s="9"/>
       <c r="L25" s="86"/>
-      <c r="N25" s="118"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="118"/>
-      <c r="Q25" s="118"/>
-      <c r="R25" s="118"/>
-      <c r="S25" s="118"/>
+      <c r="N25" s="114"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="114"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="114"/>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C26" s="23"/>
@@ -21766,12 +22260,12 @@
       <c r="J26" s="2"/>
       <c r="K26" s="9"/>
       <c r="L26" s="4"/>
-      <c r="N26" s="118"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="118"/>
-      <c r="Q26" s="118"/>
-      <c r="R26" s="118"/>
-      <c r="S26" s="118"/>
+      <c r="N26" s="114"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="114"/>
+      <c r="S26" s="114"/>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C27" s="23"/>
@@ -21781,12 +22275,12 @@
       <c r="J27" s="2"/>
       <c r="K27" s="9"/>
       <c r="L27" s="4"/>
-      <c r="N27" s="118"/>
-      <c r="O27" s="118"/>
-      <c r="P27" s="118"/>
-      <c r="Q27" s="118"/>
-      <c r="R27" s="118"/>
-      <c r="S27" s="118"/>
+      <c r="N27" s="114"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="114"/>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C28" s="23"/>
@@ -21796,14 +22290,14 @@
       <c r="J28" s="2"/>
       <c r="K28" s="9"/>
       <c r="L28" s="4"/>
-      <c r="N28" s="118" t="s">
+      <c r="N28" s="114" t="s">
         <v>147</v>
       </c>
-      <c r="O28" s="118"/>
-      <c r="P28" s="118"/>
-      <c r="Q28" s="118"/>
-      <c r="R28" s="118"/>
-      <c r="S28" s="118"/>
+      <c r="O28" s="114"/>
+      <c r="P28" s="114"/>
+      <c r="Q28" s="114"/>
+      <c r="R28" s="114"/>
+      <c r="S28" s="114"/>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C29" s="23"/>
@@ -21813,12 +22307,12 @@
       <c r="J29" s="2"/>
       <c r="K29" s="9"/>
       <c r="L29" s="4"/>
-      <c r="N29" s="118"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="118"/>
-      <c r="Q29" s="118"/>
-      <c r="R29" s="118"/>
-      <c r="S29" s="118"/>
+      <c r="N29" s="114"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="114"/>
+      <c r="R29" s="114"/>
+      <c r="S29" s="114"/>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C30" s="23"/>
@@ -21828,12 +22322,12 @@
       <c r="J30" s="2"/>
       <c r="K30" s="9"/>
       <c r="L30" s="2"/>
-      <c r="N30" s="118"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="118"/>
-      <c r="Q30" s="118"/>
-      <c r="R30" s="118"/>
-      <c r="S30" s="118"/>
+      <c r="N30" s="114"/>
+      <c r="O30" s="114"/>
+      <c r="P30" s="114"/>
+      <c r="Q30" s="114"/>
+      <c r="R30" s="114"/>
+      <c r="S30" s="114"/>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C31" s="23"/>
@@ -21843,12 +22337,12 @@
       <c r="J31" s="2"/>
       <c r="K31" s="9"/>
       <c r="L31" s="2"/>
-      <c r="N31" s="118"/>
-      <c r="O31" s="118"/>
-      <c r="P31" s="118"/>
-      <c r="Q31" s="118"/>
-      <c r="R31" s="118"/>
-      <c r="S31" s="118"/>
+      <c r="N31" s="114"/>
+      <c r="O31" s="114"/>
+      <c r="P31" s="114"/>
+      <c r="Q31" s="114"/>
+      <c r="R31" s="114"/>
+      <c r="S31" s="114"/>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.35">
       <c r="C32" s="23"/>
@@ -22055,16 +22549,16 @@
     </row>
     <row r="10" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C10" s="23"/>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="116"/>
-      <c r="G10" s="117"/>
-      <c r="J10" s="115" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="J10" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="116"/>
-      <c r="L10" s="117"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="113"/>
     </row>
     <row r="11" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C11" s="23"/>
